--- a/content-export/04_사업영역_문구.xlsx
+++ b/content-export/04_사업영역_문구.xlsx
@@ -14,10 +14,10 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화합물 전력 반도체" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$I$137</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'에너지 솔루션'!$A$1:$I$228</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'인공지능 플랫폼'!$A$1:$I$65</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'화합물 전력 반도체'!$A$1:$I$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$J$137</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'에너지 솔루션'!$A$1:$J$228</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'인공지능 플랫폼'!$A$1:$J$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'화합물 전력 반도체'!$A$1:$J$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -56,7 +56,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill/>
     </fill>
@@ -76,6 +76,11 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FFF6D6"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F1FB"/>
       </patternFill>
     </fill>
   </fills>
@@ -105,7 +110,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -122,6 +127,9 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -492,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B23"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -543,7 +551,7 @@
     <row r="8" ht="30" customHeight="1">
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>노란 칸(변경 문구)에만 쓰시면 됩니다. 그대로 둘 줄은 비워 두세요 — 빈 칸은 '그대로'로 읽습니다.</t>
+          <t>색 있는 두 칸에만 쓰시면 됩니다. 노란 칸에 한글, 파란 칸에 영문입니다. 그대로 둘 줄은 비워 두세요 — 빈 칸은 '그대로'로 읽습니다.</t>
         </is>
       </c>
     </row>
@@ -574,67 +582,105 @@
     <row r="13" ht="22" customHeight="1">
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>묶음 칸</t>
+          <t>영문 문구 칸</t>
         </is>
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>같은 문구가 여러 곳에 있으면 같은 묶음 번호를 달아 두었습니다. 그중 한 줄만 채우면 나머지도 같이 바꿔 넣습니다. 굳이 여러 번 쓰지 않으셔도 됩니다.</t>
+          <t>영문 사이트에 쓸 글입니다. 지금 회색 사이트에는 영문 장이 아직 없어서, 채워 주신 영문은 바로 화면에 붙지 않습니다. 별도 파일로 모아 두고 영문 장을 만들 때 그대로 씁니다.</t>
         </is>
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>소분류 이름을 바꾸시면 좌측 인덱스 · 띠지 · 메가 메뉴 · 푸터에 있는 같은 이름도 제가 함께 고칩니다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1">
-      <c r="B16" s="2" t="inlineStr"/>
+          <t>이미 영문뿐인 줄(영문 제목, Grid Stabilization 같은 항목)은 미리 채워 두었습니다. 손볼 게 없으면 그대로 두시면 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>한글만 고치고 영문은 나중에 하셔도 됩니다. 두 칸은 서로 기다리지 않습니다.</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="B17" s="3" t="inlineStr">
-        <is>
-          <t>구분 칸</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="B18" s="2" t="inlineStr">
-        <is>
-          <t>문구 — 읽는 글입니다. 대체글 — 눈이 아닌 화면 낭독기가 읽는 사진 설명입니다. 번호 — 01, 02 같은 자리 번호입니다. 자리표시 — 아직 글이 안 들어온 자리입니다.</t>
+      <c r="B17" s="2" t="inlineStr"/>
+    </row>
+    <row r="18" ht="22" customHeight="1">
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>묶음 칸</t>
         </is>
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
       <c r="B19" s="2" t="inlineStr">
         <is>
+          <t>같은 문구가 여러 곳에 있으면 같은 묶음 번호를 달아 두었습니다. 그중 한 줄만 채우면 나머지도 같이 바꿔 넣습니다. 한글과 영문 모두 그렇습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>굳이 여러 번 쓰지 않으셔도 됩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="30" customHeight="1">
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>소분류 이름을 바꾸시면 좌측 인덱스 · 띠지 · 메가 메뉴 · 푸터에 있는 같은 이름도 제가 함께 고칩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="B22" s="2" t="inlineStr"/>
+    </row>
+    <row r="23" ht="22" customHeight="1">
+      <c r="B23" s="3" t="inlineStr">
+        <is>
+          <t>구분 칸</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>문구 — 읽는 글입니다. 대체글 — 눈이 아닌 화면 낭독기가 읽는 사진 설명입니다. 번호 — 01, 02 같은 자리 번호로, 채울 칸을 회색으로 막아 두었습니다. 자리표시 — 아직 글이 안 들어온 자리입니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="30" customHeight="1">
+      <c r="B25" s="2" t="inlineStr">
+        <is>
           <t>대체글은 화면에 보이지 않지만 검색과 접근성에 쓰입니다. 손대지 않으셔도 제가 문구에 맞춰 다듬습니다.</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="B20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="B21" s="3" t="inlineStr">
+    <row r="26" ht="22" customHeight="1">
+      <c r="B26" s="2" t="inlineStr"/>
+    </row>
+    <row r="27" ht="22" customHeight="1">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>마지막 칸(자리표)</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="30" customHeight="1">
-      <c r="B22" s="2" t="inlineStr">
+    <row r="28" ht="30" customHeight="1">
+      <c r="B28" s="2" t="inlineStr">
         <is>
           <t>제가 그 문구를 페이지에서 찾는 데 쓰는 주소입니다. 지우거나 고치면 그 줄을 넣을 수 없습니다.</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="30" customHeight="1">
-      <c r="B23" s="2" t="inlineStr">
+    <row r="29" ht="30" customHeight="1">
+      <c r="B29" s="2" t="inlineStr">
         <is>
           <t>돌려주실 때는 이 파일을 그대로 저장해서 주시면 됩니다. 시트 이름과 열 순서만 지켜 주세요.</t>
         </is>
@@ -651,18 +697,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I137"/>
+  <dimension ref="A1:J137"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
-    <col width="62" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="54" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -703,10 +750,15 @@
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
+          <t>영문 문구</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>자리표(건드리지 마세요)</t>
         </is>
@@ -738,8 +790,9 @@
         </is>
       </c>
       <c r="G2" s="7" t="n"/>
-      <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[1]/div/div/h1/span[1]|text</t>
         </is>
@@ -771,8 +824,13 @@
         </is>
       </c>
       <c r="G3" s="7" t="n"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>Smart Factory</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[1]/div/div/h1/span[2]|text</t>
         </is>
@@ -804,8 +862,9 @@
         </is>
       </c>
       <c r="G4" s="7" t="n"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[1]/p/span[1]|text</t>
         </is>
@@ -837,8 +896,9 @@
         </is>
       </c>
       <c r="G5" s="7" t="n"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[1]/p/span[2]|text</t>
         </is>
@@ -870,8 +930,9 @@
         </is>
       </c>
       <c r="G6" s="7" t="n"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[1]/div/img|alt</t>
         </is>
@@ -905,12 +966,13 @@
         </is>
       </c>
       <c r="G7" s="7" t="n"/>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>묶음 1 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[2]/ul/li[1]/p|text</t>
         </is>
@@ -944,12 +1006,13 @@
         </is>
       </c>
       <c r="G8" s="7" t="n"/>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>묶음 2 — 같은 문구 4 곳</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[2]/ul/li[2]/p|text</t>
         </is>
@@ -983,12 +1046,13 @@
         </is>
       </c>
       <c r="G9" s="7" t="n"/>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>묶음 3 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[2]/ul/li[3]/p|text</t>
         </is>
@@ -1022,12 +1086,13 @@
         </is>
       </c>
       <c r="G10" s="7" t="n"/>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>묶음 4 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[2]/ul/li[4]/p|text</t>
         </is>
@@ -1060,13 +1125,14 @@
           <t>01</t>
         </is>
       </c>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>묶음 5 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[1]/p/span[1]|text</t>
         </is>
@@ -1100,12 +1166,13 @@
         </is>
       </c>
       <c r="G12" s="7" t="n"/>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>묶음 1 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[1]/p/span[2]|text</t>
         </is>
@@ -1139,12 +1206,13 @@
         </is>
       </c>
       <c r="G13" s="7" t="n"/>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>묶음 6 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[1]/a[1]|text</t>
         </is>
@@ -1178,12 +1246,13 @@
         </is>
       </c>
       <c r="G14" s="7" t="n"/>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>묶음 7 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[1]/a[2]|text</t>
         </is>
@@ -1216,13 +1285,14 @@
           <t>02</t>
         </is>
       </c>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>묶음 8 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[2]/p/span[1]|text</t>
         </is>
@@ -1256,12 +1326,13 @@
         </is>
       </c>
       <c r="G16" s="7" t="n"/>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>묶음 2 — 같은 문구 4 곳</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[2]/p/span[2]|text</t>
         </is>
@@ -1295,12 +1366,13 @@
         </is>
       </c>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>묶음 2 — 같은 문구 4 곳</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[2]/a[1]|text</t>
         </is>
@@ -1330,16 +1402,17 @@
       </c>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>MES</t>
+          <t>모니터링 시스템</t>
         </is>
       </c>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>묶음 9 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[2]/a[2]|text</t>
         </is>
@@ -1372,13 +1445,14 @@
           <t>03</t>
         </is>
       </c>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>묶음 10 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[3]/p/span[1]|text</t>
         </is>
@@ -1412,12 +1486,13 @@
         </is>
       </c>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>묶음 3 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[3]/p/span[2]|text</t>
         </is>
@@ -1451,12 +1526,13 @@
         </is>
       </c>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>묶음 11 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[3]/a[1]|text</t>
         </is>
@@ -1488,8 +1564,9 @@
         </is>
       </c>
       <c r="G22" s="7" t="n"/>
-      <c r="H22" s="5" t="inlineStr"/>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="5" t="inlineStr"/>
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[3]/a[2]|text</t>
         </is>
@@ -1522,13 +1599,14 @@
           <t>04</t>
         </is>
       </c>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>묶음 12 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[4]/p/span[1]|text</t>
         </is>
@@ -1562,12 +1640,13 @@
         </is>
       </c>
       <c r="G24" s="7" t="n"/>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>묶음 4 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[4]/p/span[2]|text</t>
         </is>
@@ -1601,12 +1680,13 @@
         </is>
       </c>
       <c r="G25" s="7" t="n"/>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>묶음 13 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[4]/a[1]|text</t>
         </is>
@@ -1640,12 +1720,13 @@
         </is>
       </c>
       <c r="G26" s="7" t="n"/>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>묶음 14 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[4]/a[2]|text</t>
         </is>
@@ -1679,12 +1760,13 @@
         </is>
       </c>
       <c r="G27" s="7" t="n"/>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" s="8" t="n"/>
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>묶음 15 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[4]/a[3]|text</t>
         </is>
@@ -1718,12 +1800,13 @@
         </is>
       </c>
       <c r="G28" s="7" t="n"/>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>묶음 16 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[4]/a[4]|text</t>
         </is>
@@ -1757,12 +1840,13 @@
         </is>
       </c>
       <c r="G29" s="7" t="n"/>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>묶음 17 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[4]/a[5]|text</t>
         </is>
@@ -1795,13 +1879,14 @@
           <t>01234567890123456789-0123456789</t>
         </is>
       </c>
-      <c r="G30" s="7" t="n"/>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="G30" s="6" t="n"/>
+      <c r="H30" s="6" t="n"/>
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>묶음 18 — 같은 문구 4 곳</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[1]/span|text</t>
         </is>
@@ -1835,12 +1920,13 @@
         </is>
       </c>
       <c r="G31" s="7" t="n"/>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H31" s="8" t="n"/>
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>묶음 19 — 같은 문구 18 곳</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[1]/span|text</t>
         </is>
@@ -1872,8 +1958,9 @@
         </is>
       </c>
       <c r="G32" s="7" t="n"/>
-      <c r="H32" s="5" t="inlineStr"/>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[3]/img|alt</t>
         </is>
@@ -1907,12 +1994,13 @@
         </is>
       </c>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>묶음 19 — 같은 문구 18 곳</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[4]/span|text</t>
         </is>
@@ -1944,8 +2032,9 @@
         </is>
       </c>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[5]/img|alt</t>
         </is>
@@ -1979,12 +2068,13 @@
         </is>
       </c>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="5" t="inlineStr">
+      <c r="H35" s="8" t="n"/>
+      <c r="I35" s="5" t="inlineStr">
         <is>
           <t>묶음 19 — 같은 문구 18 곳</t>
         </is>
       </c>
-      <c r="I35" s="8" t="inlineStr">
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[6]/span|text</t>
         </is>
@@ -2016,8 +2106,9 @@
         </is>
       </c>
       <c r="G36" s="7" t="n"/>
-      <c r="H36" s="5" t="inlineStr"/>
-      <c r="I36" s="8" t="inlineStr">
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="5" t="inlineStr"/>
+      <c r="J36" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[7]/div[1]/div/img|alt</t>
         </is>
@@ -2049,8 +2140,9 @@
         </is>
       </c>
       <c r="G37" s="7" t="n"/>
-      <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[7]/div[1]/p/b|text</t>
         </is>
@@ -2082,8 +2174,9 @@
         </is>
       </c>
       <c r="G38" s="7" t="n"/>
-      <c r="H38" s="5" t="inlineStr"/>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="5" t="inlineStr"/>
+      <c r="J38" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[7]/div[1]/p/span|text</t>
         </is>
@@ -2115,8 +2208,9 @@
         </is>
       </c>
       <c r="G39" s="7" t="n"/>
-      <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="H39" s="8" t="n"/>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[7]/div[2]/div/img|alt</t>
         </is>
@@ -2148,8 +2242,9 @@
         </is>
       </c>
       <c r="G40" s="7" t="n"/>
-      <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[7]/div[2]/p/b|text</t>
         </is>
@@ -2181,8 +2276,9 @@
         </is>
       </c>
       <c r="G41" s="7" t="n"/>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="8" t="inlineStr">
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[7]/div[2]/p/span|text</t>
         </is>
@@ -2214,8 +2310,9 @@
         </is>
       </c>
       <c r="G42" s="7" t="n"/>
-      <c r="H42" s="5" t="inlineStr"/>
-      <c r="I42" s="8" t="inlineStr">
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="5" t="inlineStr"/>
+      <c r="J42" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[7]/div[3]/div/img|alt</t>
         </is>
@@ -2247,8 +2344,9 @@
         </is>
       </c>
       <c r="G43" s="7" t="n"/>
-      <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[7]/div[3]/p/b|text</t>
         </is>
@@ -2280,8 +2378,9 @@
         </is>
       </c>
       <c r="G44" s="7" t="n"/>
-      <c r="H44" s="5" t="inlineStr"/>
-      <c r="I44" s="8" t="inlineStr">
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[7]/div[3]/p/span|text</t>
         </is>
@@ -2313,8 +2412,9 @@
         </is>
       </c>
       <c r="G45" s="7" t="n"/>
-      <c r="H45" s="5" t="inlineStr"/>
-      <c r="I45" s="8" t="inlineStr">
+      <c r="H45" s="8" t="n"/>
+      <c r="I45" s="5" t="inlineStr"/>
+      <c r="J45" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[8]/img|alt</t>
         </is>
@@ -2346,8 +2446,9 @@
         </is>
       </c>
       <c r="G46" s="7" t="n"/>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="8" t="inlineStr">
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[9]/img|alt</t>
         </is>
@@ -2379,8 +2480,9 @@
         </is>
       </c>
       <c r="G47" s="7" t="n"/>
-      <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="8" t="inlineStr">
+      <c r="H47" s="8" t="n"/>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[10]/img|alt</t>
         </is>
@@ -2414,12 +2516,13 @@
         </is>
       </c>
       <c r="G48" s="7" t="n"/>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H48" s="8" t="n"/>
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>묶음 19 — 같은 문구 18 곳</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
+      <c r="J48" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[11]/span|text</t>
         </is>
@@ -2453,12 +2556,13 @@
         </is>
       </c>
       <c r="G49" s="7" t="n"/>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="H49" s="8" t="n"/>
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>묶음 6 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I49" s="8" t="inlineStr">
+      <c r="J49" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/h2|text</t>
         </is>
@@ -2490,8 +2594,9 @@
         </is>
       </c>
       <c r="G50" s="7" t="n"/>
-      <c r="H50" s="5" t="inlineStr"/>
-      <c r="I50" s="8" t="inlineStr">
+      <c r="H50" s="8" t="n"/>
+      <c r="I50" s="5" t="inlineStr"/>
+      <c r="J50" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[1]|text</t>
         </is>
@@ -2523,8 +2628,9 @@
         </is>
       </c>
       <c r="G51" s="7" t="n"/>
-      <c r="H51" s="5" t="inlineStr"/>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="H51" s="8" t="n"/>
+      <c r="I51" s="5" t="inlineStr"/>
+      <c r="J51" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[2]|text</t>
         </is>
@@ -2556,8 +2662,9 @@
         </is>
       </c>
       <c r="G52" s="7" t="n"/>
-      <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="8" t="inlineStr">
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[3]|text</t>
         </is>
@@ -2590,13 +2697,14 @@
           <t>01</t>
         </is>
       </c>
-      <c r="G53" s="7" t="n"/>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="G53" s="6" t="n"/>
+      <c r="H53" s="6" t="n"/>
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>묶음 5 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I53" s="8" t="inlineStr">
+      <c r="J53" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[1]/b|text</t>
         </is>
@@ -2628,8 +2736,9 @@
         </is>
       </c>
       <c r="G54" s="7" t="n"/>
-      <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="8" t="inlineStr">
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[1]/span|text</t>
         </is>
@@ -2662,13 +2771,14 @@
           <t>02</t>
         </is>
       </c>
-      <c r="G55" s="7" t="n"/>
-      <c r="H55" s="5" t="inlineStr">
+      <c r="G55" s="6" t="n"/>
+      <c r="H55" s="6" t="n"/>
+      <c r="I55" s="5" t="inlineStr">
         <is>
           <t>묶음 8 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I55" s="8" t="inlineStr">
+      <c r="J55" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[2]/b|text</t>
         </is>
@@ -2700,8 +2810,9 @@
         </is>
       </c>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="5" t="inlineStr"/>
-      <c r="I56" s="8" t="inlineStr">
+      <c r="H56" s="8" t="n"/>
+      <c r="I56" s="5" t="inlineStr"/>
+      <c r="J56" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[2]/span|text</t>
         </is>
@@ -2734,13 +2845,14 @@
           <t>03</t>
         </is>
       </c>
-      <c r="G57" s="7" t="n"/>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="G57" s="6" t="n"/>
+      <c r="H57" s="6" t="n"/>
+      <c r="I57" s="5" t="inlineStr">
         <is>
           <t>묶음 10 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I57" s="8" t="inlineStr">
+      <c r="J57" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[3]/b|text</t>
         </is>
@@ -2772,8 +2884,9 @@
         </is>
       </c>
       <c r="G58" s="7" t="n"/>
-      <c r="H58" s="5" t="inlineStr"/>
-      <c r="I58" s="8" t="inlineStr">
+      <c r="H58" s="8" t="n"/>
+      <c r="I58" s="5" t="inlineStr"/>
+      <c r="J58" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[3]/span|text</t>
         </is>
@@ -2806,13 +2919,14 @@
           <t>04</t>
         </is>
       </c>
-      <c r="G59" s="7" t="n"/>
-      <c r="H59" s="5" t="inlineStr">
+      <c r="G59" s="6" t="n"/>
+      <c r="H59" s="6" t="n"/>
+      <c r="I59" s="5" t="inlineStr">
         <is>
           <t>묶음 12 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I59" s="8" t="inlineStr">
+      <c r="J59" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[4]/b|text</t>
         </is>
@@ -2844,8 +2958,9 @@
         </is>
       </c>
       <c r="G60" s="7" t="n"/>
-      <c r="H60" s="5" t="inlineStr"/>
-      <c r="I60" s="8" t="inlineStr">
+      <c r="H60" s="8" t="n"/>
+      <c r="I60" s="5" t="inlineStr"/>
+      <c r="J60" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[4]/span|text</t>
         </is>
@@ -2878,13 +2993,14 @@
           <t>05</t>
         </is>
       </c>
-      <c r="G61" s="7" t="n"/>
-      <c r="H61" s="5" t="inlineStr">
+      <c r="G61" s="6" t="n"/>
+      <c r="H61" s="6" t="n"/>
+      <c r="I61" s="5" t="inlineStr">
         <is>
           <t>묶음 20 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I61" s="8" t="inlineStr">
+      <c r="J61" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[5]/b|text</t>
         </is>
@@ -2916,8 +3032,9 @@
         </is>
       </c>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="5" t="inlineStr"/>
-      <c r="I62" s="8" t="inlineStr">
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="5" t="inlineStr"/>
+      <c r="J62" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[5]/span|text</t>
         </is>
@@ -2948,9 +3065,10 @@
           <t>06</t>
         </is>
       </c>
-      <c r="G63" s="7" t="n"/>
-      <c r="H63" s="5" t="inlineStr"/>
-      <c r="I63" s="8" t="inlineStr">
+      <c r="G63" s="6" t="n"/>
+      <c r="H63" s="6" t="n"/>
+      <c r="I63" s="5" t="inlineStr"/>
+      <c r="J63" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[6]/b|text</t>
         </is>
@@ -2982,8 +3100,9 @@
         </is>
       </c>
       <c r="G64" s="7" t="n"/>
-      <c r="H64" s="5" t="inlineStr"/>
-      <c r="I64" s="8" t="inlineStr">
+      <c r="H64" s="8" t="n"/>
+      <c r="I64" s="5" t="inlineStr"/>
+      <c r="J64" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[6]/span|text</t>
         </is>
@@ -3017,12 +3136,13 @@
         </is>
       </c>
       <c r="G65" s="7" t="n"/>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="H65" s="8" t="n"/>
+      <c r="I65" s="5" t="inlineStr">
         <is>
           <t>묶음 7 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I65" s="8" t="inlineStr">
+      <c r="J65" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/h2|text</t>
         </is>
@@ -3054,8 +3174,9 @@
         </is>
       </c>
       <c r="G66" s="7" t="n"/>
-      <c r="H66" s="5" t="inlineStr"/>
-      <c r="I66" s="8" t="inlineStr">
+      <c r="H66" s="8" t="n"/>
+      <c r="I66" s="5" t="inlineStr"/>
+      <c r="J66" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[1]|text</t>
         </is>
@@ -3087,8 +3208,9 @@
         </is>
       </c>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="5" t="inlineStr"/>
-      <c r="I67" s="8" t="inlineStr">
+      <c r="H67" s="8" t="n"/>
+      <c r="I67" s="5" t="inlineStr"/>
+      <c r="J67" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[2]|text</t>
         </is>
@@ -3120,8 +3242,9 @@
         </is>
       </c>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="5" t="inlineStr"/>
-      <c r="I68" s="8" t="inlineStr">
+      <c r="H68" s="8" t="n"/>
+      <c r="I68" s="5" t="inlineStr"/>
+      <c r="J68" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[3]|text</t>
         </is>
@@ -3155,12 +3278,13 @@
         </is>
       </c>
       <c r="G69" s="7" t="n"/>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="H69" s="8" t="n"/>
+      <c r="I69" s="5" t="inlineStr">
         <is>
           <t>묶음 2 — 같은 문구 4 곳</t>
         </is>
       </c>
-      <c r="I69" s="8" t="inlineStr">
+      <c r="J69" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/h2|text</t>
         </is>
@@ -3194,12 +3318,13 @@
         </is>
       </c>
       <c r="G70" s="7" t="n"/>
-      <c r="H70" s="5" t="inlineStr">
+      <c r="H70" s="8" t="n"/>
+      <c r="I70" s="5" t="inlineStr">
         <is>
           <t>묶음 21 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I70" s="8" t="inlineStr">
+      <c r="J70" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[1]|text</t>
         </is>
@@ -3233,12 +3358,13 @@
         </is>
       </c>
       <c r="G71" s="7" t="n"/>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="H71" s="8" t="n"/>
+      <c r="I71" s="5" t="inlineStr">
         <is>
           <t>묶음 22 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I71" s="8" t="inlineStr">
+      <c r="J71" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[2]|text</t>
         </is>
@@ -3272,12 +3398,13 @@
         </is>
       </c>
       <c r="G72" s="7" t="n"/>
-      <c r="H72" s="5" t="inlineStr">
+      <c r="H72" s="8" t="n"/>
+      <c r="I72" s="5" t="inlineStr">
         <is>
           <t>묶음 23 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I72" s="8" t="inlineStr">
+      <c r="J72" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[3]|text</t>
         </is>
@@ -3311,12 +3438,13 @@
         </is>
       </c>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="H73" s="8" t="n"/>
+      <c r="I73" s="5" t="inlineStr">
         <is>
           <t>묶음 24 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I73" s="8" t="inlineStr">
+      <c r="J73" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[4]|text</t>
         </is>
@@ -3328,7 +3456,7 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>02-2 MES</t>
+          <t>02-2 모니터링 시스템</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
@@ -3346,16 +3474,17 @@
       </c>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>MES</t>
+          <t>모니터링 시스템</t>
         </is>
       </c>
       <c r="G74" s="7" t="n"/>
-      <c r="H74" s="5" t="inlineStr">
+      <c r="H74" s="8" t="n"/>
+      <c r="I74" s="5" t="inlineStr">
         <is>
           <t>묶음 9 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I74" s="8" t="inlineStr">
+      <c r="J74" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div[1]/h2|text</t>
         </is>
@@ -3367,7 +3496,7 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>02-2 MES</t>
+          <t>02-2 모니터링 시스템</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
@@ -3387,8 +3516,13 @@
         </is>
       </c>
       <c r="G75" s="7" t="n"/>
-      <c r="H75" s="5" t="inlineStr"/>
-      <c r="I75" s="8" t="inlineStr">
+      <c r="H75" s="8" t="inlineStr">
+        <is>
+          <t>Module Inspection Equipment</t>
+        </is>
+      </c>
+      <c r="I75" s="5" t="inlineStr"/>
+      <c r="J75" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div[1]/p|text</t>
         </is>
@@ -3400,7 +3534,7 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>02-2 MES</t>
+          <t>02-2 모니터링 시스템</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
@@ -3422,12 +3556,13 @@
         </is>
       </c>
       <c r="G76" s="7" t="n"/>
-      <c r="H76" s="5" t="inlineStr">
+      <c r="H76" s="8" t="n"/>
+      <c r="I76" s="5" t="inlineStr">
         <is>
           <t>묶음 21 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I76" s="8" t="inlineStr">
+      <c r="J76" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div[2]/p[1]|text</t>
         </is>
@@ -3439,7 +3574,7 @@
       </c>
       <c r="B77" s="5" t="inlineStr">
         <is>
-          <t>02-2 MES</t>
+          <t>02-2 모니터링 시스템</t>
         </is>
       </c>
       <c r="C77" s="5" t="inlineStr">
@@ -3461,12 +3596,13 @@
         </is>
       </c>
       <c r="G77" s="7" t="n"/>
-      <c r="H77" s="5" t="inlineStr">
+      <c r="H77" s="8" t="n"/>
+      <c r="I77" s="5" t="inlineStr">
         <is>
           <t>묶음 22 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I77" s="8" t="inlineStr">
+      <c r="J77" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div[2]/p[2]|text</t>
         </is>
@@ -3478,7 +3614,7 @@
       </c>
       <c r="B78" s="5" t="inlineStr">
         <is>
-          <t>02-2 MES</t>
+          <t>02-2 모니터링 시스템</t>
         </is>
       </c>
       <c r="C78" s="5" t="inlineStr">
@@ -3500,12 +3636,13 @@
         </is>
       </c>
       <c r="G78" s="7" t="n"/>
-      <c r="H78" s="5" t="inlineStr">
+      <c r="H78" s="8" t="n"/>
+      <c r="I78" s="5" t="inlineStr">
         <is>
           <t>묶음 23 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I78" s="8" t="inlineStr">
+      <c r="J78" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div[2]/p[3]|text</t>
         </is>
@@ -3517,7 +3654,7 @@
       </c>
       <c r="B79" s="5" t="inlineStr">
         <is>
-          <t>02-2 MES</t>
+          <t>02-2 모니터링 시스템</t>
         </is>
       </c>
       <c r="C79" s="5" t="inlineStr">
@@ -3539,12 +3676,13 @@
         </is>
       </c>
       <c r="G79" s="7" t="n"/>
-      <c r="H79" s="5" t="inlineStr">
+      <c r="H79" s="8" t="n"/>
+      <c r="I79" s="5" t="inlineStr">
         <is>
           <t>묶음 24 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I79" s="8" t="inlineStr">
+      <c r="J79" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div[2]/p[4]|text</t>
         </is>
@@ -3578,12 +3716,13 @@
         </is>
       </c>
       <c r="G80" s="7" t="n"/>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="H80" s="8" t="n"/>
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>묶음 11 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I80" s="8" t="inlineStr">
+      <c r="J80" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/h2|text</t>
         </is>
@@ -3615,8 +3754,13 @@
         </is>
       </c>
       <c r="G81" s="7" t="n"/>
-      <c r="H81" s="5" t="inlineStr"/>
-      <c r="I81" s="8" t="inlineStr">
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>Programmable Logic Controller</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr"/>
+      <c r="J81" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/p|text</t>
         </is>
@@ -3648,8 +3792,9 @@
         </is>
       </c>
       <c r="G82" s="7" t="n"/>
-      <c r="H82" s="5" t="inlineStr"/>
-      <c r="I82" s="8" t="inlineStr">
+      <c r="H82" s="8" t="n"/>
+      <c r="I82" s="5" t="inlineStr"/>
+      <c r="J82" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[1]/p[1]|text</t>
         </is>
@@ -3681,8 +3826,9 @@
         </is>
       </c>
       <c r="G83" s="7" t="n"/>
-      <c r="H83" s="5" t="inlineStr"/>
-      <c r="I83" s="8" t="inlineStr">
+      <c r="H83" s="8" t="n"/>
+      <c r="I83" s="5" t="inlineStr"/>
+      <c r="J83" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[1]/p[2]|text</t>
         </is>
@@ -3714,8 +3860,9 @@
         </is>
       </c>
       <c r="G84" s="7" t="n"/>
-      <c r="H84" s="5" t="inlineStr"/>
-      <c r="I84" s="8" t="inlineStr">
+      <c r="H84" s="8" t="n"/>
+      <c r="I84" s="5" t="inlineStr"/>
+      <c r="J84" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[2]/p[1]|text</t>
         </is>
@@ -3747,8 +3894,9 @@
         </is>
       </c>
       <c r="G85" s="7" t="n"/>
-      <c r="H85" s="5" t="inlineStr"/>
-      <c r="I85" s="8" t="inlineStr">
+      <c r="H85" s="8" t="n"/>
+      <c r="I85" s="5" t="inlineStr"/>
+      <c r="J85" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[2]/p[2]|text</t>
         </is>
@@ -3780,8 +3928,9 @@
         </is>
       </c>
       <c r="G86" s="7" t="n"/>
-      <c r="H86" s="5" t="inlineStr"/>
-      <c r="I86" s="8" t="inlineStr">
+      <c r="H86" s="8" t="n"/>
+      <c r="I86" s="5" t="inlineStr"/>
+      <c r="J86" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[3]/p[1]|text</t>
         </is>
@@ -3813,8 +3962,9 @@
         </is>
       </c>
       <c r="G87" s="7" t="n"/>
-      <c r="H87" s="5" t="inlineStr"/>
-      <c r="I87" s="8" t="inlineStr">
+      <c r="H87" s="8" t="n"/>
+      <c r="I87" s="5" t="inlineStr"/>
+      <c r="J87" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[3]/p[2]|text</t>
         </is>
@@ -3846,8 +3996,9 @@
         </is>
       </c>
       <c r="G88" s="7" t="n"/>
-      <c r="H88" s="5" t="inlineStr"/>
-      <c r="I88" s="8" t="inlineStr">
+      <c r="H88" s="8" t="n"/>
+      <c r="I88" s="5" t="inlineStr"/>
+      <c r="J88" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[4]/p[1]|text</t>
         </is>
@@ -3879,8 +4030,9 @@
         </is>
       </c>
       <c r="G89" s="7" t="n"/>
-      <c r="H89" s="5" t="inlineStr"/>
-      <c r="I89" s="8" t="inlineStr">
+      <c r="H89" s="8" t="n"/>
+      <c r="I89" s="5" t="inlineStr"/>
+      <c r="J89" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[4]/p[2]|text</t>
         </is>
@@ -3912,8 +4064,9 @@
         </is>
       </c>
       <c r="G90" s="7" t="n"/>
-      <c r="H90" s="5" t="inlineStr"/>
-      <c r="I90" s="8" t="inlineStr">
+      <c r="H90" s="8" t="n"/>
+      <c r="I90" s="5" t="inlineStr"/>
+      <c r="J90" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/h2|text</t>
         </is>
@@ -3945,8 +4098,9 @@
         </is>
       </c>
       <c r="G91" s="7" t="n"/>
-      <c r="H91" s="5" t="inlineStr"/>
-      <c r="I91" s="8" t="inlineStr">
+      <c r="H91" s="8" t="n"/>
+      <c r="I91" s="5" t="inlineStr"/>
+      <c r="J91" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul/li[1]/p[1]|text</t>
         </is>
@@ -3978,8 +4132,9 @@
         </is>
       </c>
       <c r="G92" s="7" t="n"/>
-      <c r="H92" s="5" t="inlineStr"/>
-      <c r="I92" s="8" t="inlineStr">
+      <c r="H92" s="8" t="n"/>
+      <c r="I92" s="5" t="inlineStr"/>
+      <c r="J92" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul/li[1]/p[2]|text</t>
         </is>
@@ -4011,8 +4166,9 @@
         </is>
       </c>
       <c r="G93" s="7" t="n"/>
-      <c r="H93" s="5" t="inlineStr"/>
-      <c r="I93" s="8" t="inlineStr">
+      <c r="H93" s="8" t="n"/>
+      <c r="I93" s="5" t="inlineStr"/>
+      <c r="J93" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul/li[2]/p[1]|text</t>
         </is>
@@ -4044,8 +4200,9 @@
         </is>
       </c>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="5" t="inlineStr"/>
-      <c r="I94" s="8" t="inlineStr">
+      <c r="H94" s="8" t="n"/>
+      <c r="I94" s="5" t="inlineStr"/>
+      <c r="J94" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul/li[2]/p[2]|text</t>
         </is>
@@ -4077,8 +4234,9 @@
         </is>
       </c>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="5" t="inlineStr"/>
-      <c r="I95" s="8" t="inlineStr">
+      <c r="H95" s="8" t="n"/>
+      <c r="I95" s="5" t="inlineStr"/>
+      <c r="J95" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul/li[3]/p[1]|text</t>
         </is>
@@ -4110,8 +4268,9 @@
         </is>
       </c>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="5" t="inlineStr"/>
-      <c r="I96" s="8" t="inlineStr">
+      <c r="H96" s="8" t="n"/>
+      <c r="I96" s="5" t="inlineStr"/>
+      <c r="J96" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul/li[3]/p[2]|text</t>
         </is>
@@ -4143,8 +4302,9 @@
         </is>
       </c>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="5" t="inlineStr"/>
-      <c r="I97" s="8" t="inlineStr">
+      <c r="H97" s="8" t="n"/>
+      <c r="I97" s="5" t="inlineStr"/>
+      <c r="J97" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul/li[4]/p[1]|text</t>
         </is>
@@ -4176,8 +4336,9 @@
         </is>
       </c>
       <c r="G98" s="7" t="n"/>
-      <c r="H98" s="5" t="inlineStr"/>
-      <c r="I98" s="8" t="inlineStr">
+      <c r="H98" s="8" t="n"/>
+      <c r="I98" s="5" t="inlineStr"/>
+      <c r="J98" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul/li[4]/p[2]|text</t>
         </is>
@@ -4211,12 +4372,13 @@
         </is>
       </c>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="5" t="inlineStr">
+      <c r="H99" s="8" t="n"/>
+      <c r="I99" s="5" t="inlineStr">
         <is>
           <t>묶음 13 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I99" s="8" t="inlineStr">
+      <c r="J99" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div[1]/h2|text</t>
         </is>
@@ -4248,8 +4410,9 @@
         </is>
       </c>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="5" t="inlineStr"/>
-      <c r="I100" s="8" t="inlineStr">
+      <c r="H100" s="8" t="n"/>
+      <c r="I100" s="5" t="inlineStr"/>
+      <c r="J100" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div[1]/div/p[1]|text</t>
         </is>
@@ -4281,8 +4444,9 @@
         </is>
       </c>
       <c r="G101" s="7" t="n"/>
-      <c r="H101" s="5" t="inlineStr"/>
-      <c r="I101" s="8" t="inlineStr">
+      <c r="H101" s="8" t="n"/>
+      <c r="I101" s="5" t="inlineStr"/>
+      <c r="J101" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div[1]/div/p[2]|text</t>
         </is>
@@ -4315,8 +4479,14 @@
         </is>
       </c>
       <c r="G102" s="7" t="n"/>
-      <c r="H102" s="5" t="inlineStr"/>
-      <c r="I102" s="8" t="inlineStr">
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t>SW/FW-
+CNT Powder</t>
+        </is>
+      </c>
+      <c r="I102" s="5" t="inlineStr"/>
+      <c r="J102" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div[2]/button[1]/span[2]|text</t>
         </is>
@@ -4349,8 +4519,14 @@
         </is>
       </c>
       <c r="G103" s="7" t="n"/>
-      <c r="H103" s="5" t="inlineStr"/>
-      <c r="I103" s="8" t="inlineStr">
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>SW/FW-
+CNT Slurry</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr"/>
+      <c r="J103" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div[2]/button[2]/span[2]|text</t>
         </is>
@@ -4383,8 +4559,14 @@
         </is>
       </c>
       <c r="G104" s="7" t="n"/>
-      <c r="H104" s="5" t="inlineStr"/>
-      <c r="I104" s="8" t="inlineStr">
+      <c r="H104" s="8" t="inlineStr">
+        <is>
+          <t>Carbon
+Black</t>
+        </is>
+      </c>
+      <c r="I104" s="5" t="inlineStr"/>
+      <c r="J104" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div[2]/button[3]/span[2]|text</t>
         </is>
@@ -4418,12 +4600,13 @@
         </is>
       </c>
       <c r="G105" s="7" t="n"/>
-      <c r="H105" s="5" t="inlineStr">
+      <c r="H105" s="8" t="n"/>
+      <c r="I105" s="5" t="inlineStr">
         <is>
           <t>묶음 14 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I105" s="8" t="inlineStr">
+      <c r="J105" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/h2|text</t>
         </is>
@@ -4455,8 +4638,9 @@
         </is>
       </c>
       <c r="G106" s="7" t="n"/>
-      <c r="H106" s="5" t="inlineStr"/>
-      <c r="I106" s="8" t="inlineStr">
+      <c r="H106" s="8" t="n"/>
+      <c r="I106" s="5" t="inlineStr"/>
+      <c r="J106" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[1]|text</t>
         </is>
@@ -4488,8 +4672,9 @@
         </is>
       </c>
       <c r="G107" s="7" t="n"/>
-      <c r="H107" s="5" t="inlineStr"/>
-      <c r="I107" s="8" t="inlineStr">
+      <c r="H107" s="8" t="n"/>
+      <c r="I107" s="5" t="inlineStr"/>
+      <c r="J107" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[2]|text</t>
         </is>
@@ -4523,12 +4708,13 @@
         </is>
       </c>
       <c r="G108" s="7" t="n"/>
-      <c r="H108" s="5" t="inlineStr">
+      <c r="H108" s="8" t="n"/>
+      <c r="I108" s="5" t="inlineStr">
         <is>
           <t>묶음 15 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I108" s="8" t="inlineStr">
+      <c r="J108" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/h2|text</t>
         </is>
@@ -4560,8 +4746,9 @@
         </is>
       </c>
       <c r="G109" s="7" t="n"/>
-      <c r="H109" s="5" t="inlineStr"/>
-      <c r="I109" s="8" t="inlineStr">
+      <c r="H109" s="8" t="n"/>
+      <c r="I109" s="5" t="inlineStr"/>
+      <c r="J109" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[1]|text</t>
         </is>
@@ -4593,8 +4780,9 @@
         </is>
       </c>
       <c r="G110" s="7" t="n"/>
-      <c r="H110" s="5" t="inlineStr"/>
-      <c r="I110" s="8" t="inlineStr">
+      <c r="H110" s="8" t="n"/>
+      <c r="I110" s="5" t="inlineStr"/>
+      <c r="J110" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[2]|text</t>
         </is>
@@ -4626,8 +4814,9 @@
         </is>
       </c>
       <c r="G111" s="7" t="n"/>
-      <c r="H111" s="5" t="inlineStr"/>
-      <c r="I111" s="8" t="inlineStr">
+      <c r="H111" s="8" t="n"/>
+      <c r="I111" s="5" t="inlineStr"/>
+      <c r="J111" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ul/li[1]/p[1]|text</t>
         </is>
@@ -4659,8 +4848,9 @@
         </is>
       </c>
       <c r="G112" s="7" t="n"/>
-      <c r="H112" s="5" t="inlineStr"/>
-      <c r="I112" s="8" t="inlineStr">
+      <c r="H112" s="8" t="n"/>
+      <c r="I112" s="5" t="inlineStr"/>
+      <c r="J112" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ul/li[1]/p[2]|text</t>
         </is>
@@ -4692,8 +4882,9 @@
         </is>
       </c>
       <c r="G113" s="7" t="n"/>
-      <c r="H113" s="5" t="inlineStr"/>
-      <c r="I113" s="8" t="inlineStr">
+      <c r="H113" s="8" t="n"/>
+      <c r="I113" s="5" t="inlineStr"/>
+      <c r="J113" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ul/li[2]/p[1]|text</t>
         </is>
@@ -4725,8 +4916,9 @@
         </is>
       </c>
       <c r="G114" s="7" t="n"/>
-      <c r="H114" s="5" t="inlineStr"/>
-      <c r="I114" s="8" t="inlineStr">
+      <c r="H114" s="8" t="n"/>
+      <c r="I114" s="5" t="inlineStr"/>
+      <c r="J114" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ul/li[2]/p[2]|text</t>
         </is>
@@ -4758,8 +4950,9 @@
         </is>
       </c>
       <c r="G115" s="7" t="n"/>
-      <c r="H115" s="5" t="inlineStr"/>
-      <c r="I115" s="8" t="inlineStr">
+      <c r="H115" s="8" t="n"/>
+      <c r="I115" s="5" t="inlineStr"/>
+      <c r="J115" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ul/li[3]/p[1]|text</t>
         </is>
@@ -4791,8 +4984,9 @@
         </is>
       </c>
       <c r="G116" s="7" t="n"/>
-      <c r="H116" s="5" t="inlineStr"/>
-      <c r="I116" s="8" t="inlineStr">
+      <c r="H116" s="8" t="n"/>
+      <c r="I116" s="5" t="inlineStr"/>
+      <c r="J116" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ul/li[3]/p[2]|text</t>
         </is>
@@ -4824,8 +5018,9 @@
         </is>
       </c>
       <c r="G117" s="7" t="n"/>
-      <c r="H117" s="5" t="inlineStr"/>
-      <c r="I117" s="8" t="inlineStr">
+      <c r="H117" s="8" t="n"/>
+      <c r="I117" s="5" t="inlineStr"/>
+      <c r="J117" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ul/li[4]/p[1]|text</t>
         </is>
@@ -4857,8 +5052,9 @@
         </is>
       </c>
       <c r="G118" s="7" t="n"/>
-      <c r="H118" s="5" t="inlineStr"/>
-      <c r="I118" s="8" t="inlineStr">
+      <c r="H118" s="8" t="n"/>
+      <c r="I118" s="5" t="inlineStr"/>
+      <c r="J118" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ul/li[4]/p[2]|text</t>
         </is>
@@ -4890,8 +5086,9 @@
         </is>
       </c>
       <c r="G119" s="7" t="n"/>
-      <c r="H119" s="5" t="inlineStr"/>
-      <c r="I119" s="8" t="inlineStr">
+      <c r="H119" s="8" t="n"/>
+      <c r="I119" s="5" t="inlineStr"/>
+      <c r="J119" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ul/li[5]/p[1]|text</t>
         </is>
@@ -4923,8 +5120,9 @@
         </is>
       </c>
       <c r="G120" s="7" t="n"/>
-      <c r="H120" s="5" t="inlineStr"/>
-      <c r="I120" s="8" t="inlineStr">
+      <c r="H120" s="8" t="n"/>
+      <c r="I120" s="5" t="inlineStr"/>
+      <c r="J120" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ul/li[5]/p[2]|text</t>
         </is>
@@ -4958,12 +5156,13 @@
         </is>
       </c>
       <c r="G121" s="7" t="n"/>
-      <c r="H121" s="5" t="inlineStr">
+      <c r="H121" s="8" t="n"/>
+      <c r="I121" s="5" t="inlineStr">
         <is>
           <t>묶음 16 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I121" s="8" t="inlineStr">
+      <c r="J121" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/div/h2|text</t>
         </is>
@@ -4995,8 +5194,9 @@
         </is>
       </c>
       <c r="G122" s="7" t="n"/>
-      <c r="H122" s="5" t="inlineStr"/>
-      <c r="I122" s="8" t="inlineStr">
+      <c r="H122" s="8" t="n"/>
+      <c r="I122" s="5" t="inlineStr"/>
+      <c r="J122" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/div/div/p[1]|text</t>
         </is>
@@ -5028,8 +5228,9 @@
         </is>
       </c>
       <c r="G123" s="7" t="n"/>
-      <c r="H123" s="5" t="inlineStr"/>
-      <c r="I123" s="8" t="inlineStr">
+      <c r="H123" s="8" t="n"/>
+      <c r="I123" s="5" t="inlineStr"/>
+      <c r="J123" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/div/div/p[2]|text</t>
         </is>
@@ -5062,13 +5263,14 @@
           <t>01</t>
         </is>
       </c>
-      <c r="G124" s="7" t="n"/>
-      <c r="H124" s="5" t="inlineStr">
+      <c r="G124" s="6" t="n"/>
+      <c r="H124" s="6" t="n"/>
+      <c r="I124" s="5" t="inlineStr">
         <is>
           <t>묶음 5 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I124" s="8" t="inlineStr">
+      <c r="J124" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/ol/li[1]/b|text</t>
         </is>
@@ -5100,8 +5302,9 @@
         </is>
       </c>
       <c r="G125" s="7" t="n"/>
-      <c r="H125" s="5" t="inlineStr"/>
-      <c r="I125" s="8" t="inlineStr">
+      <c r="H125" s="8" t="n"/>
+      <c r="I125" s="5" t="inlineStr"/>
+      <c r="J125" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/ol/li[1]/span|text</t>
         </is>
@@ -5134,13 +5337,14 @@
           <t>02</t>
         </is>
       </c>
-      <c r="G126" s="7" t="n"/>
-      <c r="H126" s="5" t="inlineStr">
+      <c r="G126" s="6" t="n"/>
+      <c r="H126" s="6" t="n"/>
+      <c r="I126" s="5" t="inlineStr">
         <is>
           <t>묶음 8 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I126" s="8" t="inlineStr">
+      <c r="J126" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/ol/li[2]/b|text</t>
         </is>
@@ -5172,8 +5376,9 @@
         </is>
       </c>
       <c r="G127" s="7" t="n"/>
-      <c r="H127" s="5" t="inlineStr"/>
-      <c r="I127" s="8" t="inlineStr">
+      <c r="H127" s="8" t="n"/>
+      <c r="I127" s="5" t="inlineStr"/>
+      <c r="J127" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/ol/li[2]/span|text</t>
         </is>
@@ -5206,13 +5411,14 @@
           <t>03</t>
         </is>
       </c>
-      <c r="G128" s="7" t="n"/>
-      <c r="H128" s="5" t="inlineStr">
+      <c r="G128" s="6" t="n"/>
+      <c r="H128" s="6" t="n"/>
+      <c r="I128" s="5" t="inlineStr">
         <is>
           <t>묶음 10 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I128" s="8" t="inlineStr">
+      <c r="J128" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/ol/li[3]/b|text</t>
         </is>
@@ -5244,8 +5450,9 @@
         </is>
       </c>
       <c r="G129" s="7" t="n"/>
-      <c r="H129" s="5" t="inlineStr"/>
-      <c r="I129" s="8" t="inlineStr">
+      <c r="H129" s="8" t="n"/>
+      <c r="I129" s="5" t="inlineStr"/>
+      <c r="J129" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/ol/li[3]/span|text</t>
         </is>
@@ -5278,13 +5485,14 @@
           <t>04</t>
         </is>
       </c>
-      <c r="G130" s="7" t="n"/>
-      <c r="H130" s="5" t="inlineStr">
+      <c r="G130" s="6" t="n"/>
+      <c r="H130" s="6" t="n"/>
+      <c r="I130" s="5" t="inlineStr">
         <is>
           <t>묶음 12 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I130" s="8" t="inlineStr">
+      <c r="J130" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/ol/li[4]/b|text</t>
         </is>
@@ -5316,8 +5524,9 @@
         </is>
       </c>
       <c r="G131" s="7" t="n"/>
-      <c r="H131" s="5" t="inlineStr"/>
-      <c r="I131" s="8" t="inlineStr">
+      <c r="H131" s="8" t="n"/>
+      <c r="I131" s="5" t="inlineStr"/>
+      <c r="J131" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/ol/li[4]/span|text</t>
         </is>
@@ -5350,13 +5559,14 @@
           <t>05</t>
         </is>
       </c>
-      <c r="G132" s="7" t="n"/>
-      <c r="H132" s="5" t="inlineStr">
+      <c r="G132" s="6" t="n"/>
+      <c r="H132" s="6" t="n"/>
+      <c r="I132" s="5" t="inlineStr">
         <is>
           <t>묶음 20 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I132" s="8" t="inlineStr">
+      <c r="J132" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/ol/li[5]/b|text</t>
         </is>
@@ -5388,8 +5598,9 @@
         </is>
       </c>
       <c r="G133" s="7" t="n"/>
-      <c r="H133" s="5" t="inlineStr"/>
-      <c r="I133" s="8" t="inlineStr">
+      <c r="H133" s="8" t="n"/>
+      <c r="I133" s="5" t="inlineStr"/>
+      <c r="J133" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/ol/li[5]/span|text</t>
         </is>
@@ -5423,12 +5634,13 @@
         </is>
       </c>
       <c r="G134" s="7" t="n"/>
-      <c r="H134" s="5" t="inlineStr">
+      <c r="H134" s="8" t="n"/>
+      <c r="I134" s="5" t="inlineStr">
         <is>
           <t>묶음 17 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I134" s="8" t="inlineStr">
+      <c r="J134" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[11]/div/div[2]/div/h2|text</t>
         </is>
@@ -5460,8 +5672,9 @@
         </is>
       </c>
       <c r="G135" s="7" t="n"/>
-      <c r="H135" s="5" t="inlineStr"/>
-      <c r="I135" s="8" t="inlineStr">
+      <c r="H135" s="8" t="n"/>
+      <c r="I135" s="5" t="inlineStr"/>
+      <c r="J135" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[11]/div/div[2]/div/div/p[1]|text</t>
         </is>
@@ -5493,8 +5706,9 @@
         </is>
       </c>
       <c r="G136" s="7" t="n"/>
-      <c r="H136" s="5" t="inlineStr"/>
-      <c r="I136" s="8" t="inlineStr">
+      <c r="H136" s="8" t="n"/>
+      <c r="I136" s="5" t="inlineStr"/>
+      <c r="J136" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[11]/div/div[2]/div/div/p[2]|text</t>
         </is>
@@ -5526,15 +5740,16 @@
         </is>
       </c>
       <c r="G137" s="7" t="n"/>
-      <c r="H137" s="5" t="inlineStr"/>
-      <c r="I137" s="8" t="inlineStr">
+      <c r="H137" s="8" t="n"/>
+      <c r="I137" s="5" t="inlineStr"/>
+      <c r="J137" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[11]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I137"/>
+  <autoFilter ref="A1:J137"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5545,18 +5760,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I228"/>
+  <dimension ref="A1:J228"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
-    <col width="62" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="54" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -5597,10 +5813,15 @@
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
+          <t>영문 문구</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>자리표(건드리지 마세요)</t>
         </is>
@@ -5632,8 +5853,9 @@
         </is>
       </c>
       <c r="G2" s="7" t="n"/>
-      <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[1]/div/div/h1/span[1]|text</t>
         </is>
@@ -5665,8 +5887,13 @@
         </is>
       </c>
       <c r="G3" s="7" t="n"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>Energy Solution</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[1]/div/div/h1/span[2]|text</t>
         </is>
@@ -5698,8 +5925,9 @@
         </is>
       </c>
       <c r="G4" s="7" t="n"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[1]/p/span[1]|text</t>
         </is>
@@ -5731,8 +5959,9 @@
         </is>
       </c>
       <c r="G5" s="7" t="n"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[1]/p/span[2]|text</t>
         </is>
@@ -5764,8 +5993,9 @@
         </is>
       </c>
       <c r="G6" s="7" t="n"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[1]/div/img|alt</t>
         </is>
@@ -5799,12 +6029,13 @@
         </is>
       </c>
       <c r="G7" s="7" t="n"/>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>묶음 25 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[2]/ul/li[1]/p|text</t>
         </is>
@@ -5838,12 +6069,13 @@
         </is>
       </c>
       <c r="G8" s="7" t="n"/>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>묶음 26 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[2]/ul/li[2]/p|text</t>
         </is>
@@ -5877,12 +6109,13 @@
         </is>
       </c>
       <c r="G9" s="7" t="n"/>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>묶음 27 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[2]/ul/li[3]/p|text</t>
         </is>
@@ -5915,13 +6148,14 @@
           <t>01</t>
         </is>
       </c>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>묶음 5 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[1]/p/span[1]|text</t>
         </is>
@@ -5955,12 +6189,13 @@
         </is>
       </c>
       <c r="G11" s="7" t="n"/>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>묶음 25 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[1]/p/span[2]|text</t>
         </is>
@@ -5994,12 +6229,13 @@
         </is>
       </c>
       <c r="G12" s="7" t="n"/>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>묶음 28 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[1]/a[1]|text</t>
         </is>
@@ -6033,12 +6269,13 @@
         </is>
       </c>
       <c r="G13" s="7" t="n"/>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>묶음 29 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[1]/a[2]|text</t>
         </is>
@@ -6072,12 +6309,13 @@
         </is>
       </c>
       <c r="G14" s="7" t="n"/>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>묶음 30 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[1]/a[3]|text</t>
         </is>
@@ -6110,13 +6348,14 @@
           <t>02</t>
         </is>
       </c>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>묶음 8 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[2]/p/span[1]|text</t>
         </is>
@@ -6150,12 +6389,13 @@
         </is>
       </c>
       <c r="G16" s="7" t="n"/>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>묶음 26 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[2]/p/span[2]|text</t>
         </is>
@@ -6189,12 +6429,13 @@
         </is>
       </c>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>묶음 31 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[2]/a[1]|text</t>
         </is>
@@ -6228,12 +6469,13 @@
         </is>
       </c>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>묶음 32 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[2]/a[2]|text</t>
         </is>
@@ -6267,12 +6509,13 @@
         </is>
       </c>
       <c r="G19" s="7" t="n"/>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="H19" s="8" t="n"/>
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>묶음 33 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[2]/a[3]|text</t>
         </is>
@@ -6305,13 +6548,14 @@
           <t>03</t>
         </is>
       </c>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>묶음 10 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[3]/p/span[1]|text</t>
         </is>
@@ -6345,12 +6589,13 @@
         </is>
       </c>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>묶음 27 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[3]/p/span[2]|text</t>
         </is>
@@ -6384,12 +6629,13 @@
         </is>
       </c>
       <c r="G22" s="7" t="n"/>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>묶음 34 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[3]/a[1]|text</t>
         </is>
@@ -6423,12 +6669,13 @@
         </is>
       </c>
       <c r="G23" s="7" t="n"/>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>묶음 35 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[3]/a[2]|text</t>
         </is>
@@ -6462,12 +6709,13 @@
         </is>
       </c>
       <c r="G24" s="7" t="n"/>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>묶음 36 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[3]/a[3]|text</t>
         </is>
@@ -6501,12 +6749,13 @@
         </is>
       </c>
       <c r="G25" s="7" t="n"/>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>묶음 37 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[3]/a[4]|text</t>
         </is>
@@ -6539,13 +6788,14 @@
           <t>01234567890123456789-0123456789</t>
         </is>
       </c>
-      <c r="G26" s="7" t="n"/>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="G26" s="6" t="n"/>
+      <c r="H26" s="6" t="n"/>
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>묶음 18 — 같은 문구 4 곳</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[1]/div/div[1]/span|text</t>
         </is>
@@ -6579,12 +6829,13 @@
         </is>
       </c>
       <c r="G27" s="7" t="n"/>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" s="8" t="n"/>
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>묶음 19 — 같은 문구 18 곳</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[1]/div/div[2]/figure[1]/span|text</t>
         </is>
@@ -6618,12 +6869,13 @@
         </is>
       </c>
       <c r="G28" s="7" t="n"/>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>묶음 19 — 같은 문구 18 곳</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[1]/div/div[2]/figure[2]/span|text</t>
         </is>
@@ -6657,12 +6909,13 @@
         </is>
       </c>
       <c r="G29" s="7" t="n"/>
-      <c r="H29" s="5" t="inlineStr">
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="5" t="inlineStr">
         <is>
           <t>묶음 19 — 같은 문구 18 곳</t>
         </is>
       </c>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[1]/div/div[2]/figure[3]/span|text</t>
         </is>
@@ -6696,12 +6949,13 @@
         </is>
       </c>
       <c r="G30" s="7" t="n"/>
-      <c r="H30" s="5" t="inlineStr">
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="5" t="inlineStr">
         <is>
           <t>묶음 19 — 같은 문구 18 곳</t>
         </is>
       </c>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[1]/div/div[2]/figure[4]/span|text</t>
         </is>
@@ -6735,12 +6989,13 @@
         </is>
       </c>
       <c r="G31" s="7" t="n"/>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H31" s="8" t="n"/>
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>묶음 19 — 같은 문구 18 곳</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[1]/div/div[2]/figure[5]/span|text</t>
         </is>
@@ -6774,12 +7029,13 @@
         </is>
       </c>
       <c r="G32" s="7" t="n"/>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>묶음 19 — 같은 문구 18 곳</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[1]/div/div[2]/figure[6]/span|text</t>
         </is>
@@ -6813,12 +7069,13 @@
         </is>
       </c>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="5" t="inlineStr">
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="5" t="inlineStr">
         <is>
           <t>묶음 28 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[1]/div/div/div/p[1]|text</t>
         </is>
@@ -6850,8 +7107,13 @@
         </is>
       </c>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="H34" s="8" t="inlineStr">
+        <is>
+          <t>Power Grid Stability</t>
+        </is>
+      </c>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[1]/div/div/div/h2|text</t>
         </is>
@@ -6883,8 +7145,9 @@
         </is>
       </c>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="8" t="inlineStr">
+      <c r="H35" s="8" t="n"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[1]/div/div/div/p[2]|text</t>
         </is>
@@ -6917,13 +7180,14 @@
           <t>01</t>
         </is>
       </c>
-      <c r="G36" s="7" t="n"/>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="G36" s="6" t="n"/>
+      <c r="H36" s="6" t="n"/>
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>묶음 5 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr">
+      <c r="J36" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[1]/div/div/ol/li[1]/b|text</t>
         </is>
@@ -6955,8 +7219,13 @@
         </is>
       </c>
       <c r="G37" s="7" t="n"/>
-      <c r="H37" s="5" t="inlineStr"/>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="H37" s="8" t="inlineStr">
+        <is>
+          <t>Grid Stabilization</t>
+        </is>
+      </c>
+      <c r="I37" s="5" t="inlineStr"/>
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[1]/div/div/ol/li[1]/span|text</t>
         </is>
@@ -6989,13 +7258,14 @@
           <t>02</t>
         </is>
       </c>
-      <c r="G38" s="7" t="n"/>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="6" t="n"/>
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>묶음 8 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="J38" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[1]/div/div/ol/li[2]/b|text</t>
         </is>
@@ -7027,8 +7297,13 @@
         </is>
       </c>
       <c r="G39" s="7" t="n"/>
-      <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="H39" s="8" t="inlineStr">
+        <is>
+          <t>Frequency Regulation</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[1]/div/div/ol/li[2]/span|text</t>
         </is>
@@ -7061,13 +7336,14 @@
           <t>03</t>
         </is>
       </c>
-      <c r="G40" s="7" t="n"/>
-      <c r="H40" s="5" t="inlineStr">
+      <c r="G40" s="6" t="n"/>
+      <c r="H40" s="6" t="n"/>
+      <c r="I40" s="5" t="inlineStr">
         <is>
           <t>묶음 10 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="J40" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[1]/div/div/ol/li[3]/b|text</t>
         </is>
@@ -7099,8 +7375,13 @@
         </is>
       </c>
       <c r="G41" s="7" t="n"/>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="8" t="inlineStr">
+      <c r="H41" s="8" t="inlineStr">
+        <is>
+          <t>Peak Shaving</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[1]/div/div/ol/li[3]/span|text</t>
         </is>
@@ -7133,13 +7414,14 @@
           <t>04</t>
         </is>
       </c>
-      <c r="G42" s="7" t="n"/>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="G42" s="6" t="n"/>
+      <c r="H42" s="6" t="n"/>
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>묶음 12 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
+      <c r="J42" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[1]/div/div/ol/li[4]/b|text</t>
         </is>
@@ -7171,8 +7453,13 @@
         </is>
       </c>
       <c r="G43" s="7" t="n"/>
-      <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="H43" s="8" t="inlineStr">
+        <is>
+          <t>Load Shifting</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[1]/div/div/ol/li[4]/span|text</t>
         </is>
@@ -7206,12 +7493,13 @@
         </is>
       </c>
       <c r="G44" s="7" t="n"/>
-      <c r="H44" s="5" t="inlineStr">
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="5" t="inlineStr">
         <is>
           <t>묶음 29 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I44" s="8" t="inlineStr">
+      <c r="J44" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[2]/div/div/div/p[1]|text</t>
         </is>
@@ -7245,12 +7533,13 @@
         </is>
       </c>
       <c r="G45" s="7" t="n"/>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H45" s="8" t="n"/>
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>묶음 38 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
+      <c r="J45" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[2]/div/div/div/h2|text</t>
         </is>
@@ -7282,8 +7571,9 @@
         </is>
       </c>
       <c r="G46" s="7" t="n"/>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="8" t="inlineStr">
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[2]/div/div/div/p[2]|text</t>
         </is>
@@ -7316,13 +7606,14 @@
           <t>01</t>
         </is>
       </c>
-      <c r="G47" s="7" t="n"/>
-      <c r="H47" s="5" t="inlineStr">
+      <c r="G47" s="6" t="n"/>
+      <c r="H47" s="6" t="n"/>
+      <c r="I47" s="5" t="inlineStr">
         <is>
           <t>묶음 5 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I47" s="8" t="inlineStr">
+      <c r="J47" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[2]/div/div/ol/li[1]/b|text</t>
         </is>
@@ -7354,8 +7645,13 @@
         </is>
       </c>
       <c r="G48" s="7" t="n"/>
-      <c r="H48" s="5" t="inlineStr"/>
-      <c r="I48" s="8" t="inlineStr">
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Solar Energy</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr"/>
+      <c r="J48" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[2]/div/div/ol/li[1]/span|text</t>
         </is>
@@ -7388,13 +7684,14 @@
           <t>02</t>
         </is>
       </c>
-      <c r="G49" s="7" t="n"/>
-      <c r="H49" s="5" t="inlineStr">
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="6" t="n"/>
+      <c r="I49" s="5" t="inlineStr">
         <is>
           <t>묶음 8 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I49" s="8" t="inlineStr">
+      <c r="J49" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[2]/div/div/ol/li[2]/b|text</t>
         </is>
@@ -7426,8 +7723,13 @@
         </is>
       </c>
       <c r="G50" s="7" t="n"/>
-      <c r="H50" s="5" t="inlineStr"/>
-      <c r="I50" s="8" t="inlineStr">
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>Wind Energy</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr"/>
+      <c r="J50" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[2]/div/div/ol/li[2]/span|text</t>
         </is>
@@ -7460,13 +7762,14 @@
           <t>03</t>
         </is>
       </c>
-      <c r="G51" s="7" t="n"/>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="6" t="n"/>
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>묶음 10 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="J51" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[2]/div/div/ol/li[3]/b|text</t>
         </is>
@@ -7500,12 +7803,13 @@
         </is>
       </c>
       <c r="G52" s="7" t="n"/>
-      <c r="H52" s="5" t="inlineStr">
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="5" t="inlineStr">
         <is>
           <t>묶음 38 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I52" s="8" t="inlineStr">
+      <c r="J52" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[2]/div/div/ol/li[3]/span|text</t>
         </is>
@@ -7539,12 +7843,13 @@
         </is>
       </c>
       <c r="G53" s="7" t="n"/>
-      <c r="H53" s="5" t="inlineStr">
+      <c r="H53" s="8" t="n"/>
+      <c r="I53" s="5" t="inlineStr">
         <is>
           <t>묶음 30 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I53" s="8" t="inlineStr">
+      <c r="J53" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[3]/div/div/div/p[1]|text</t>
         </is>
@@ -7577,8 +7882,14 @@
         </is>
       </c>
       <c r="G54" s="7" t="n"/>
-      <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="8" t="inlineStr">
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>Commercial &amp;
+Industrial Energy Storage</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[3]/div/div/div/h2|text</t>
         </is>
@@ -7610,8 +7921,9 @@
         </is>
       </c>
       <c r="G55" s="7" t="n"/>
-      <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="8" t="inlineStr">
+      <c r="H55" s="8" t="n"/>
+      <c r="I55" s="5" t="inlineStr"/>
+      <c r="J55" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[3]/div/div/div/p[2]|text</t>
         </is>
@@ -7644,13 +7956,14 @@
           <t>01</t>
         </is>
       </c>
-      <c r="G56" s="7" t="n"/>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="G56" s="6" t="n"/>
+      <c r="H56" s="6" t="n"/>
+      <c r="I56" s="5" t="inlineStr">
         <is>
           <t>묶음 5 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I56" s="8" t="inlineStr">
+      <c r="J56" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[3]/div/div/ol/li[1]/b|text</t>
         </is>
@@ -7682,8 +7995,13 @@
         </is>
       </c>
       <c r="G57" s="7" t="n"/>
-      <c r="H57" s="5" t="inlineStr"/>
-      <c r="I57" s="8" t="inlineStr">
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>Factory</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr"/>
+      <c r="J57" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[3]/div/div/ol/li[1]/span|text</t>
         </is>
@@ -7716,13 +8034,14 @@
           <t>02</t>
         </is>
       </c>
-      <c r="G58" s="7" t="n"/>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="G58" s="6" t="n"/>
+      <c r="H58" s="6" t="n"/>
+      <c r="I58" s="5" t="inlineStr">
         <is>
           <t>묶음 8 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I58" s="8" t="inlineStr">
+      <c r="J58" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[3]/div/div/ol/li[2]/b|text</t>
         </is>
@@ -7754,8 +8073,13 @@
         </is>
       </c>
       <c r="G59" s="7" t="n"/>
-      <c r="H59" s="5" t="inlineStr"/>
-      <c r="I59" s="8" t="inlineStr">
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>Commercial Building</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr"/>
+      <c r="J59" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[3]/div/div/ol/li[2]/span|text</t>
         </is>
@@ -7788,13 +8112,14 @@
           <t>03</t>
         </is>
       </c>
-      <c r="G60" s="7" t="n"/>
-      <c r="H60" s="5" t="inlineStr">
+      <c r="G60" s="6" t="n"/>
+      <c r="H60" s="6" t="n"/>
+      <c r="I60" s="5" t="inlineStr">
         <is>
           <t>묶음 10 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I60" s="8" t="inlineStr">
+      <c r="J60" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[3]/div/div/ol/li[3]/b|text</t>
         </is>
@@ -7826,8 +8151,13 @@
         </is>
       </c>
       <c r="G61" s="7" t="n"/>
-      <c r="H61" s="5" t="inlineStr"/>
-      <c r="I61" s="8" t="inlineStr">
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>Industrial Facility</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[3]/div/div/ol/li[3]/span|text</t>
         </is>
@@ -7860,13 +8190,14 @@
           <t>04</t>
         </is>
       </c>
-      <c r="G62" s="7" t="n"/>
-      <c r="H62" s="5" t="inlineStr">
+      <c r="G62" s="6" t="n"/>
+      <c r="H62" s="6" t="n"/>
+      <c r="I62" s="5" t="inlineStr">
         <is>
           <t>묶음 12 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I62" s="8" t="inlineStr">
+      <c r="J62" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[3]/div/div/ol/li[4]/b|text</t>
         </is>
@@ -7898,8 +8229,13 @@
         </is>
       </c>
       <c r="G63" s="7" t="n"/>
-      <c r="H63" s="5" t="inlineStr"/>
-      <c r="I63" s="8" t="inlineStr">
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>Microgrid</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr"/>
+      <c r="J63" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[3]/div/div/ol/li[4]/span|text</t>
         </is>
@@ -7933,12 +8269,13 @@
         </is>
       </c>
       <c r="G64" s="7" t="n"/>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="H64" s="8" t="n"/>
+      <c r="I64" s="5" t="inlineStr">
         <is>
           <t>묶음 31 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I64" s="8" t="inlineStr">
+      <c r="J64" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[4]/div/div/div/p[1]|text</t>
         </is>
@@ -7973,12 +8310,13 @@
         </is>
       </c>
       <c r="G65" s="7" t="n"/>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="H65" s="8" t="n"/>
+      <c r="I65" s="5" t="inlineStr">
         <is>
           <t>묶음 39 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I65" s="8" t="inlineStr">
+      <c r="J65" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[4]/div/div/div/h2|text</t>
         </is>
@@ -8010,8 +8348,9 @@
         </is>
       </c>
       <c r="G66" s="7" t="n"/>
-      <c r="H66" s="5" t="inlineStr"/>
-      <c r="I66" s="8" t="inlineStr">
+      <c r="H66" s="8" t="n"/>
+      <c r="I66" s="5" t="inlineStr"/>
+      <c r="J66" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[4]/div/div/div/p[2]|text</t>
         </is>
@@ -8044,13 +8383,14 @@
           <t>01</t>
         </is>
       </c>
-      <c r="G67" s="7" t="n"/>
-      <c r="H67" s="5" t="inlineStr">
+      <c r="G67" s="6" t="n"/>
+      <c r="H67" s="6" t="n"/>
+      <c r="I67" s="5" t="inlineStr">
         <is>
           <t>묶음 5 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I67" s="8" t="inlineStr">
+      <c r="J67" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[4]/div/div/ol/li[1]/b|text</t>
         </is>
@@ -8082,8 +8422,13 @@
         </is>
       </c>
       <c r="G68" s="7" t="n"/>
-      <c r="H68" s="5" t="inlineStr"/>
-      <c r="I68" s="8" t="inlineStr">
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>Data Center</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr"/>
+      <c r="J68" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[4]/div/div/ol/li[1]/span|text</t>
         </is>
@@ -8116,13 +8461,14 @@
           <t>02</t>
         </is>
       </c>
-      <c r="G69" s="7" t="n"/>
-      <c r="H69" s="5" t="inlineStr">
+      <c r="G69" s="6" t="n"/>
+      <c r="H69" s="6" t="n"/>
+      <c r="I69" s="5" t="inlineStr">
         <is>
           <t>묶음 8 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I69" s="8" t="inlineStr">
+      <c r="J69" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[4]/div/div/ol/li[2]/b|text</t>
         </is>
@@ -8154,8 +8500,13 @@
         </is>
       </c>
       <c r="G70" s="7" t="n"/>
-      <c r="H70" s="5" t="inlineStr"/>
-      <c r="I70" s="8" t="inlineStr">
+      <c r="H70" s="8" t="inlineStr">
+        <is>
+          <t>AI Data Center</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr"/>
+      <c r="J70" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[4]/div/div/ol/li[2]/span|text</t>
         </is>
@@ -8188,13 +8539,14 @@
           <t>03</t>
         </is>
       </c>
-      <c r="G71" s="7" t="n"/>
-      <c r="H71" s="5" t="inlineStr">
+      <c r="G71" s="6" t="n"/>
+      <c r="H71" s="6" t="n"/>
+      <c r="I71" s="5" t="inlineStr">
         <is>
           <t>묶음 10 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I71" s="8" t="inlineStr">
+      <c r="J71" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[4]/div/div/ol/li[3]/b|text</t>
         </is>
@@ -8226,8 +8578,13 @@
         </is>
       </c>
       <c r="G72" s="7" t="n"/>
-      <c r="H72" s="5" t="inlineStr"/>
-      <c r="I72" s="8" t="inlineStr">
+      <c r="H72" s="8" t="inlineStr">
+        <is>
+          <t>Cloud &amp; Hyperscale Data Center</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr"/>
+      <c r="J72" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[4]/div/div/ol/li[3]/span|text</t>
         </is>
@@ -8260,13 +8617,14 @@
           <t>04</t>
         </is>
       </c>
-      <c r="G73" s="7" t="n"/>
-      <c r="H73" s="5" t="inlineStr">
+      <c r="G73" s="6" t="n"/>
+      <c r="H73" s="6" t="n"/>
+      <c r="I73" s="5" t="inlineStr">
         <is>
           <t>묶음 12 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I73" s="8" t="inlineStr">
+      <c r="J73" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[4]/div/div/ol/li[4]/b|text</t>
         </is>
@@ -8298,8 +8656,13 @@
         </is>
       </c>
       <c r="G74" s="7" t="n"/>
-      <c r="H74" s="5" t="inlineStr"/>
-      <c r="I74" s="8" t="inlineStr">
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Colocation Data Center</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr"/>
+      <c r="J74" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[4]/div/div/ol/li[4]/span|text</t>
         </is>
@@ -8333,12 +8696,13 @@
         </is>
       </c>
       <c r="G75" s="7" t="n"/>
-      <c r="H75" s="5" t="inlineStr">
+      <c r="H75" s="8" t="n"/>
+      <c r="I75" s="5" t="inlineStr">
         <is>
           <t>묶음 32 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I75" s="8" t="inlineStr">
+      <c r="J75" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[5]/div/div/div/p[1]|text</t>
         </is>
@@ -8373,12 +8737,13 @@
         </is>
       </c>
       <c r="G76" s="7" t="n"/>
-      <c r="H76" s="5" t="inlineStr">
+      <c r="H76" s="8" t="n"/>
+      <c r="I76" s="5" t="inlineStr">
         <is>
           <t>묶음 39 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I76" s="8" t="inlineStr">
+      <c r="J76" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[5]/div/div/div/h2|text</t>
         </is>
@@ -8410,8 +8775,9 @@
         </is>
       </c>
       <c r="G77" s="7" t="n"/>
-      <c r="H77" s="5" t="inlineStr"/>
-      <c r="I77" s="8" t="inlineStr">
+      <c r="H77" s="8" t="n"/>
+      <c r="I77" s="5" t="inlineStr"/>
+      <c r="J77" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[5]/div/div/div/p[2]|text</t>
         </is>
@@ -8444,13 +8810,14 @@
           <t>01</t>
         </is>
       </c>
-      <c r="G78" s="7" t="n"/>
-      <c r="H78" s="5" t="inlineStr">
+      <c r="G78" s="6" t="n"/>
+      <c r="H78" s="6" t="n"/>
+      <c r="I78" s="5" t="inlineStr">
         <is>
           <t>묶음 5 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I78" s="8" t="inlineStr">
+      <c r="J78" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[5]/div/div/ol/li[1]/b|text</t>
         </is>
@@ -8482,8 +8849,13 @@
         </is>
       </c>
       <c r="G79" s="7" t="n"/>
-      <c r="H79" s="5" t="inlineStr"/>
-      <c r="I79" s="8" t="inlineStr">
+      <c r="H79" s="8" t="inlineStr">
+        <is>
+          <t>Manufacturing Facility</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr"/>
+      <c r="J79" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[5]/div/div/ol/li[1]/span|text</t>
         </is>
@@ -8516,13 +8888,14 @@
           <t>02</t>
         </is>
       </c>
-      <c r="G80" s="7" t="n"/>
-      <c r="H80" s="5" t="inlineStr">
+      <c r="G80" s="6" t="n"/>
+      <c r="H80" s="6" t="n"/>
+      <c r="I80" s="5" t="inlineStr">
         <is>
           <t>묶음 8 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I80" s="8" t="inlineStr">
+      <c r="J80" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[5]/div/div/ol/li[2]/b|text</t>
         </is>
@@ -8554,8 +8927,13 @@
         </is>
       </c>
       <c r="G81" s="7" t="n"/>
-      <c r="H81" s="5" t="inlineStr"/>
-      <c r="I81" s="8" t="inlineStr">
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>Semiconductor &amp; Display Facility</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr"/>
+      <c r="J81" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[5]/div/div/ol/li[2]/span|text</t>
         </is>
@@ -8588,13 +8966,14 @@
           <t>03</t>
         </is>
       </c>
-      <c r="G82" s="7" t="n"/>
-      <c r="H82" s="5" t="inlineStr">
+      <c r="G82" s="6" t="n"/>
+      <c r="H82" s="6" t="n"/>
+      <c r="I82" s="5" t="inlineStr">
         <is>
           <t>묶음 10 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I82" s="8" t="inlineStr">
+      <c r="J82" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[5]/div/div/ol/li[3]/b|text</t>
         </is>
@@ -8626,8 +9005,13 @@
         </is>
       </c>
       <c r="G83" s="7" t="n"/>
-      <c r="H83" s="5" t="inlineStr"/>
-      <c r="I83" s="8" t="inlineStr">
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>Process Industry</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr"/>
+      <c r="J83" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[5]/div/div/ol/li[3]/span|text</t>
         </is>
@@ -8660,13 +9044,14 @@
           <t>04</t>
         </is>
       </c>
-      <c r="G84" s="7" t="n"/>
-      <c r="H84" s="5" t="inlineStr">
+      <c r="G84" s="6" t="n"/>
+      <c r="H84" s="6" t="n"/>
+      <c r="I84" s="5" t="inlineStr">
         <is>
           <t>묶음 12 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I84" s="8" t="inlineStr">
+      <c r="J84" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[5]/div/div/ol/li[4]/b|text</t>
         </is>
@@ -8698,8 +9083,13 @@
         </is>
       </c>
       <c r="G85" s="7" t="n"/>
-      <c r="H85" s="5" t="inlineStr"/>
-      <c r="I85" s="8" t="inlineStr">
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>Industrial Automation</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr"/>
+      <c r="J85" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[5]/div/div/ol/li[4]/span|text</t>
         </is>
@@ -8733,12 +9123,13 @@
         </is>
       </c>
       <c r="G86" s="7" t="n"/>
-      <c r="H86" s="5" t="inlineStr">
+      <c r="H86" s="8" t="n"/>
+      <c r="I86" s="5" t="inlineStr">
         <is>
           <t>묶음 33 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I86" s="8" t="inlineStr">
+      <c r="J86" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[6]/div/div/div/p[1]|text</t>
         </is>
@@ -8771,8 +9162,14 @@
         </is>
       </c>
       <c r="G87" s="7" t="n"/>
-      <c r="H87" s="5" t="inlineStr"/>
-      <c r="I87" s="8" t="inlineStr">
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>Continuous Power
+for Critical Infrastructure</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr"/>
+      <c r="J87" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[6]/div/div/div/h2|text</t>
         </is>
@@ -8804,8 +9201,9 @@
         </is>
       </c>
       <c r="G88" s="7" t="n"/>
-      <c r="H88" s="5" t="inlineStr"/>
-      <c r="I88" s="8" t="inlineStr">
+      <c r="H88" s="8" t="n"/>
+      <c r="I88" s="5" t="inlineStr"/>
+      <c r="J88" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[6]/div/div/div/p[2]|text</t>
         </is>
@@ -8838,13 +9236,14 @@
           <t>01</t>
         </is>
       </c>
-      <c r="G89" s="7" t="n"/>
-      <c r="H89" s="5" t="inlineStr">
+      <c r="G89" s="6" t="n"/>
+      <c r="H89" s="6" t="n"/>
+      <c r="I89" s="5" t="inlineStr">
         <is>
           <t>묶음 5 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I89" s="8" t="inlineStr">
+      <c r="J89" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[6]/div/div/ol/li[1]/b|text</t>
         </is>
@@ -8876,8 +9275,13 @@
         </is>
       </c>
       <c r="G90" s="7" t="n"/>
-      <c r="H90" s="5" t="inlineStr"/>
-      <c r="I90" s="8" t="inlineStr">
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>Hospital &amp; Healthcare</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr"/>
+      <c r="J90" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[6]/div/div/ol/li[1]/span|text</t>
         </is>
@@ -8910,13 +9314,14 @@
           <t>02</t>
         </is>
       </c>
-      <c r="G91" s="7" t="n"/>
-      <c r="H91" s="5" t="inlineStr">
+      <c r="G91" s="6" t="n"/>
+      <c r="H91" s="6" t="n"/>
+      <c r="I91" s="5" t="inlineStr">
         <is>
           <t>묶음 8 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I91" s="8" t="inlineStr">
+      <c r="J91" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[6]/div/div/ol/li[2]/b|text</t>
         </is>
@@ -8948,8 +9353,13 @@
         </is>
       </c>
       <c r="G92" s="7" t="n"/>
-      <c r="H92" s="5" t="inlineStr"/>
-      <c r="I92" s="8" t="inlineStr">
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>Telecommunication</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr"/>
+      <c r="J92" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[6]/div/div/ol/li[2]/span|text</t>
         </is>
@@ -8982,13 +9392,14 @@
           <t>03</t>
         </is>
       </c>
-      <c r="G93" s="7" t="n"/>
-      <c r="H93" s="5" t="inlineStr">
+      <c r="G93" s="6" t="n"/>
+      <c r="H93" s="6" t="n"/>
+      <c r="I93" s="5" t="inlineStr">
         <is>
           <t>묶음 10 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I93" s="8" t="inlineStr">
+      <c r="J93" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[6]/div/div/ol/li[3]/b|text</t>
         </is>
@@ -9020,8 +9431,13 @@
         </is>
       </c>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="5" t="inlineStr"/>
-      <c r="I94" s="8" t="inlineStr">
+      <c r="H94" s="8" t="inlineStr">
+        <is>
+          <t>Transportation Infrastructure</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr"/>
+      <c r="J94" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[6]/div/div/ol/li[3]/span|text</t>
         </is>
@@ -9054,13 +9470,14 @@
           <t>04</t>
         </is>
       </c>
-      <c r="G95" s="7" t="n"/>
-      <c r="H95" s="5" t="inlineStr">
+      <c r="G95" s="6" t="n"/>
+      <c r="H95" s="6" t="n"/>
+      <c r="I95" s="5" t="inlineStr">
         <is>
           <t>묶음 12 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I95" s="8" t="inlineStr">
+      <c r="J95" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[6]/div/div/ol/li[4]/b|text</t>
         </is>
@@ -9092,8 +9509,13 @@
         </is>
       </c>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="5" t="inlineStr"/>
-      <c r="I96" s="8" t="inlineStr">
+      <c r="H96" s="8" t="inlineStr">
+        <is>
+          <t>Emergency &amp; Critical Facilities</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr"/>
+      <c r="J96" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[1]/div[2]/section[6]/div/div/ol/li[4]/span|text</t>
         </is>
@@ -9124,9 +9546,10 @@
           <t>03-1</t>
         </is>
       </c>
-      <c r="G97" s="7" t="n"/>
-      <c r="H97" s="5" t="inlineStr"/>
-      <c r="I97" s="8" t="inlineStr">
+      <c r="G97" s="6" t="n"/>
+      <c r="H97" s="6" t="n"/>
+      <c r="I97" s="5" t="inlineStr"/>
+      <c r="J97" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[1]/p/span|text</t>
         </is>
@@ -9160,12 +9583,13 @@
         </is>
       </c>
       <c r="G98" s="7" t="n"/>
-      <c r="H98" s="5" t="inlineStr">
+      <c r="H98" s="8" t="n"/>
+      <c r="I98" s="5" t="inlineStr">
         <is>
           <t>묶음 34 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I98" s="8" t="inlineStr">
+      <c r="J98" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[1]/div/div[1]/h2|text</t>
         </is>
@@ -9197,8 +9621,9 @@
         </is>
       </c>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="5" t="inlineStr"/>
-      <c r="I99" s="8" t="inlineStr">
+      <c r="H99" s="8" t="n"/>
+      <c r="I99" s="5" t="inlineStr"/>
+      <c r="J99" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[1]/div/div[1]/p|text</t>
         </is>
@@ -9232,12 +9657,13 @@
         </is>
       </c>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="5" t="inlineStr">
+      <c r="H100" s="8" t="n"/>
+      <c r="I100" s="5" t="inlineStr">
         <is>
           <t>묶음 40 — 같은 문구 4 곳</t>
         </is>
       </c>
-      <c r="I100" s="8" t="inlineStr">
+      <c r="J100" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[1]/div/div[2]/p|text</t>
         </is>
@@ -9271,12 +9697,13 @@
         </is>
       </c>
       <c r="G101" s="7" t="n"/>
-      <c r="H101" s="5" t="inlineStr">
+      <c r="H101" s="8" t="n"/>
+      <c r="I101" s="5" t="inlineStr">
         <is>
           <t>묶음 41 — 같은 문구 8 곳</t>
         </is>
       </c>
-      <c r="I101" s="8" t="inlineStr">
+      <c r="J101" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[1]/div/div[2]/ul/li[1]|text</t>
         </is>
@@ -9310,12 +9737,13 @@
         </is>
       </c>
       <c r="G102" s="7" t="n"/>
-      <c r="H102" s="5" t="inlineStr">
+      <c r="H102" s="8" t="n"/>
+      <c r="I102" s="5" t="inlineStr">
         <is>
           <t>묶음 41 — 같은 문구 8 곳</t>
         </is>
       </c>
-      <c r="I102" s="8" t="inlineStr">
+      <c r="J102" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[1]/div/div[2]/ul/li[2]|text</t>
         </is>
@@ -9347,8 +9775,9 @@
         </is>
       </c>
       <c r="G103" s="7" t="n"/>
-      <c r="H103" s="5" t="inlineStr"/>
-      <c r="I103" s="8" t="inlineStr">
+      <c r="H103" s="8" t="n"/>
+      <c r="I103" s="5" t="inlineStr"/>
+      <c r="J103" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[1]/div[1]/img|alt</t>
         </is>
@@ -9380,8 +9809,9 @@
         </is>
       </c>
       <c r="G104" s="7" t="n"/>
-      <c r="H104" s="5" t="inlineStr"/>
-      <c r="I104" s="8" t="inlineStr">
+      <c r="H104" s="8" t="n"/>
+      <c r="I104" s="5" t="inlineStr"/>
+      <c r="J104" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[1]/div[2]/p/b|text</t>
         </is>
@@ -9413,8 +9843,9 @@
         </is>
       </c>
       <c r="G105" s="7" t="n"/>
-      <c r="H105" s="5" t="inlineStr"/>
-      <c r="I105" s="8" t="inlineStr">
+      <c r="H105" s="8" t="n"/>
+      <c r="I105" s="5" t="inlineStr"/>
+      <c r="J105" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[1]/div[2]/div/ul/li[1]/span/span[1]|text</t>
         </is>
@@ -9446,8 +9877,9 @@
         </is>
       </c>
       <c r="G106" s="7" t="n"/>
-      <c r="H106" s="5" t="inlineStr"/>
-      <c r="I106" s="8" t="inlineStr">
+      <c r="H106" s="8" t="n"/>
+      <c r="I106" s="5" t="inlineStr"/>
+      <c r="J106" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[1]/div[2]/div/ul/li[1]/span/span[2]|text</t>
         </is>
@@ -9479,8 +9911,9 @@
         </is>
       </c>
       <c r="G107" s="7" t="n"/>
-      <c r="H107" s="5" t="inlineStr"/>
-      <c r="I107" s="8" t="inlineStr">
+      <c r="H107" s="8" t="n"/>
+      <c r="I107" s="5" t="inlineStr"/>
+      <c r="J107" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[1]/div[2]/div/ul/li[2]/span/span[1]|text</t>
         </is>
@@ -9512,8 +9945,9 @@
         </is>
       </c>
       <c r="G108" s="7" t="n"/>
-      <c r="H108" s="5" t="inlineStr"/>
-      <c r="I108" s="8" t="inlineStr">
+      <c r="H108" s="8" t="n"/>
+      <c r="I108" s="5" t="inlineStr"/>
+      <c r="J108" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[1]/div[2]/div/ul/li[2]/span/span[2]|text</t>
         </is>
@@ -9545,8 +9979,9 @@
         </is>
       </c>
       <c r="G109" s="7" t="n"/>
-      <c r="H109" s="5" t="inlineStr"/>
-      <c r="I109" s="8" t="inlineStr">
+      <c r="H109" s="8" t="n"/>
+      <c r="I109" s="5" t="inlineStr"/>
+      <c r="J109" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[1]/div[2]/div/ul/li[3]/span/span[1]|text</t>
         </is>
@@ -9578,8 +10013,9 @@
         </is>
       </c>
       <c r="G110" s="7" t="n"/>
-      <c r="H110" s="5" t="inlineStr"/>
-      <c r="I110" s="8" t="inlineStr">
+      <c r="H110" s="8" t="n"/>
+      <c r="I110" s="5" t="inlineStr"/>
+      <c r="J110" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[1]/div[2]/div/ul/li[3]/span/span[2]|text</t>
         </is>
@@ -9613,12 +10049,13 @@
         </is>
       </c>
       <c r="G111" s="7" t="n"/>
-      <c r="H111" s="5" t="inlineStr">
+      <c r="H111" s="8" t="n"/>
+      <c r="I111" s="5" t="inlineStr">
         <is>
           <t>묶음 42 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I111" s="8" t="inlineStr">
+      <c r="J111" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[1]/div[2]/div/ul/li[4]/span/span[1]|text</t>
         </is>
@@ -9650,8 +10087,9 @@
         </is>
       </c>
       <c r="G112" s="7" t="n"/>
-      <c r="H112" s="5" t="inlineStr"/>
-      <c r="I112" s="8" t="inlineStr">
+      <c r="H112" s="8" t="n"/>
+      <c r="I112" s="5" t="inlineStr"/>
+      <c r="J112" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[1]/div[2]/div/ul/li[4]/span/span[2]|text</t>
         </is>
@@ -9685,12 +10123,13 @@
         </is>
       </c>
       <c r="G113" s="7" t="n"/>
-      <c r="H113" s="5" t="inlineStr">
+      <c r="H113" s="8" t="n"/>
+      <c r="I113" s="5" t="inlineStr">
         <is>
           <t>묶음 43 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I113" s="8" t="inlineStr">
+      <c r="J113" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[1]/div[2]/div/p/b|text</t>
         </is>
@@ -9724,12 +10163,13 @@
         </is>
       </c>
       <c r="G114" s="7" t="n"/>
-      <c r="H114" s="5" t="inlineStr">
+      <c r="H114" s="8" t="n"/>
+      <c r="I114" s="5" t="inlineStr">
         <is>
           <t>묶음 44 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I114" s="8" t="inlineStr">
+      <c r="J114" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[1]/div[2]/div/p/span|text</t>
         </is>
@@ -9761,8 +10201,9 @@
         </is>
       </c>
       <c r="G115" s="7" t="n"/>
-      <c r="H115" s="5" t="inlineStr"/>
-      <c r="I115" s="8" t="inlineStr">
+      <c r="H115" s="8" t="n"/>
+      <c r="I115" s="5" t="inlineStr"/>
+      <c r="J115" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[2]/div[1]/img|alt</t>
         </is>
@@ -9794,8 +10235,9 @@
         </is>
       </c>
       <c r="G116" s="7" t="n"/>
-      <c r="H116" s="5" t="inlineStr"/>
-      <c r="I116" s="8" t="inlineStr">
+      <c r="H116" s="8" t="n"/>
+      <c r="I116" s="5" t="inlineStr"/>
+      <c r="J116" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[2]/div[2]/p/b|text</t>
         </is>
@@ -9829,12 +10271,13 @@
         </is>
       </c>
       <c r="G117" s="7" t="n"/>
-      <c r="H117" s="5" t="inlineStr">
+      <c r="H117" s="8" t="n"/>
+      <c r="I117" s="5" t="inlineStr">
         <is>
           <t>묶음 45 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I117" s="8" t="inlineStr">
+      <c r="J117" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[2]/div[2]/div/ul/li[1]/span/span[1]|text</t>
         </is>
@@ -9866,8 +10309,9 @@
         </is>
       </c>
       <c r="G118" s="7" t="n"/>
-      <c r="H118" s="5" t="inlineStr"/>
-      <c r="I118" s="8" t="inlineStr">
+      <c r="H118" s="8" t="n"/>
+      <c r="I118" s="5" t="inlineStr"/>
+      <c r="J118" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[2]/div[2]/div/ul/li[1]/span/span[2]|text</t>
         </is>
@@ -9901,12 +10345,13 @@
         </is>
       </c>
       <c r="G119" s="7" t="n"/>
-      <c r="H119" s="5" t="inlineStr">
+      <c r="H119" s="8" t="n"/>
+      <c r="I119" s="5" t="inlineStr">
         <is>
           <t>묶음 46 — 같은 문구 3 곳</t>
         </is>
       </c>
-      <c r="I119" s="8" t="inlineStr">
+      <c r="J119" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[2]/div[2]/div/ul/li[2]/span/span[1]|text</t>
         </is>
@@ -9938,8 +10383,9 @@
         </is>
       </c>
       <c r="G120" s="7" t="n"/>
-      <c r="H120" s="5" t="inlineStr"/>
-      <c r="I120" s="8" t="inlineStr">
+      <c r="H120" s="8" t="n"/>
+      <c r="I120" s="5" t="inlineStr"/>
+      <c r="J120" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[2]/div[2]/div/ul/li[2]/span/span[2]|text</t>
         </is>
@@ -9973,12 +10419,13 @@
         </is>
       </c>
       <c r="G121" s="7" t="n"/>
-      <c r="H121" s="5" t="inlineStr">
+      <c r="H121" s="8" t="n"/>
+      <c r="I121" s="5" t="inlineStr">
         <is>
           <t>묶음 47 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I121" s="8" t="inlineStr">
+      <c r="J121" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[2]/div[2]/div/ul/li[3]/span/span[1]|text</t>
         </is>
@@ -10012,12 +10459,13 @@
         </is>
       </c>
       <c r="G122" s="7" t="n"/>
-      <c r="H122" s="5" t="inlineStr">
+      <c r="H122" s="8" t="n"/>
+      <c r="I122" s="5" t="inlineStr">
         <is>
           <t>묶음 48 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I122" s="8" t="inlineStr">
+      <c r="J122" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[2]/div[2]/div/ul/li[3]/span/span[2]|text</t>
         </is>
@@ -10051,12 +10499,13 @@
         </is>
       </c>
       <c r="G123" s="7" t="n"/>
-      <c r="H123" s="5" t="inlineStr">
+      <c r="H123" s="8" t="n"/>
+      <c r="I123" s="5" t="inlineStr">
         <is>
           <t>묶음 49 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I123" s="8" t="inlineStr">
+      <c r="J123" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[2]/div[2]/div/ul/li[4]/span/span[1]|text</t>
         </is>
@@ -10090,12 +10539,13 @@
         </is>
       </c>
       <c r="G124" s="7" t="n"/>
-      <c r="H124" s="5" t="inlineStr">
+      <c r="H124" s="8" t="n"/>
+      <c r="I124" s="5" t="inlineStr">
         <is>
           <t>묶음 50 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I124" s="8" t="inlineStr">
+      <c r="J124" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[2]/div[2]/div/ul/li[4]/span/span[2]|text</t>
         </is>
@@ -10129,12 +10579,13 @@
         </is>
       </c>
       <c r="G125" s="7" t="n"/>
-      <c r="H125" s="5" t="inlineStr">
+      <c r="H125" s="8" t="n"/>
+      <c r="I125" s="5" t="inlineStr">
         <is>
           <t>묶음 43 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I125" s="8" t="inlineStr">
+      <c r="J125" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[2]/div[2]/div/p/b|text</t>
         </is>
@@ -10168,12 +10619,13 @@
         </is>
       </c>
       <c r="G126" s="7" t="n"/>
-      <c r="H126" s="5" t="inlineStr">
+      <c r="H126" s="8" t="n"/>
+      <c r="I126" s="5" t="inlineStr">
         <is>
           <t>묶음 44 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I126" s="8" t="inlineStr">
+      <c r="J126" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[1]/div[2]/div[2]/div[2]/div/p/span|text</t>
         </is>
@@ -10204,9 +10656,10 @@
           <t>03-2</t>
         </is>
       </c>
-      <c r="G127" s="7" t="n"/>
-      <c r="H127" s="5" t="inlineStr"/>
-      <c r="I127" s="8" t="inlineStr">
+      <c r="G127" s="6" t="n"/>
+      <c r="H127" s="6" t="n"/>
+      <c r="I127" s="5" t="inlineStr"/>
+      <c r="J127" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[1]/p/span|text</t>
         </is>
@@ -10240,12 +10693,13 @@
         </is>
       </c>
       <c r="G128" s="7" t="n"/>
-      <c r="H128" s="5" t="inlineStr">
+      <c r="H128" s="8" t="n"/>
+      <c r="I128" s="5" t="inlineStr">
         <is>
           <t>묶음 35 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I128" s="8" t="inlineStr">
+      <c r="J128" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[1]/div/div[1]/h2|text</t>
         </is>
@@ -10277,8 +10731,9 @@
         </is>
       </c>
       <c r="G129" s="7" t="n"/>
-      <c r="H129" s="5" t="inlineStr"/>
-      <c r="I129" s="8" t="inlineStr">
+      <c r="H129" s="8" t="n"/>
+      <c r="I129" s="5" t="inlineStr"/>
+      <c r="J129" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[1]/div/div[1]/p|text</t>
         </is>
@@ -10312,12 +10767,13 @@
         </is>
       </c>
       <c r="G130" s="7" t="n"/>
-      <c r="H130" s="5" t="inlineStr">
+      <c r="H130" s="8" t="n"/>
+      <c r="I130" s="5" t="inlineStr">
         <is>
           <t>묶음 40 — 같은 문구 4 곳</t>
         </is>
       </c>
-      <c r="I130" s="8" t="inlineStr">
+      <c r="J130" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[1]/div/div[2]/p|text</t>
         </is>
@@ -10351,12 +10807,13 @@
         </is>
       </c>
       <c r="G131" s="7" t="n"/>
-      <c r="H131" s="5" t="inlineStr">
+      <c r="H131" s="8" t="n"/>
+      <c r="I131" s="5" t="inlineStr">
         <is>
           <t>묶음 41 — 같은 문구 8 곳</t>
         </is>
       </c>
-      <c r="I131" s="8" t="inlineStr">
+      <c r="J131" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[1]/div/div[2]/ul/li[1]|text</t>
         </is>
@@ -10390,12 +10847,13 @@
         </is>
       </c>
       <c r="G132" s="7" t="n"/>
-      <c r="H132" s="5" t="inlineStr">
+      <c r="H132" s="8" t="n"/>
+      <c r="I132" s="5" t="inlineStr">
         <is>
           <t>묶음 41 — 같은 문구 8 곳</t>
         </is>
       </c>
-      <c r="I132" s="8" t="inlineStr">
+      <c r="J132" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[1]/div/div[2]/ul/li[2]|text</t>
         </is>
@@ -10427,8 +10885,9 @@
         </is>
       </c>
       <c r="G133" s="7" t="n"/>
-      <c r="H133" s="5" t="inlineStr"/>
-      <c r="I133" s="8" t="inlineStr">
+      <c r="H133" s="8" t="n"/>
+      <c r="I133" s="5" t="inlineStr"/>
+      <c r="J133" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[1]/div[1]/img|alt</t>
         </is>
@@ -10460,8 +10919,13 @@
         </is>
       </c>
       <c r="G134" s="7" t="n"/>
-      <c r="H134" s="5" t="inlineStr"/>
-      <c r="I134" s="8" t="inlineStr">
+      <c r="H134" s="8" t="inlineStr">
+        <is>
+          <t>High Energy Type Rack</t>
+        </is>
+      </c>
+      <c r="I134" s="5" t="inlineStr"/>
+      <c r="J134" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[1]/div[2]/p/b|text</t>
         </is>
@@ -10493,8 +10957,9 @@
         </is>
       </c>
       <c r="G135" s="7" t="n"/>
-      <c r="H135" s="5" t="inlineStr"/>
-      <c r="I135" s="8" t="inlineStr">
+      <c r="H135" s="8" t="n"/>
+      <c r="I135" s="5" t="inlineStr"/>
+      <c r="J135" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[1]/div[2]/div/ul/li[1]/span/span[1]|text</t>
         </is>
@@ -10526,8 +10991,9 @@
         </is>
       </c>
       <c r="G136" s="7" t="n"/>
-      <c r="H136" s="5" t="inlineStr"/>
-      <c r="I136" s="8" t="inlineStr">
+      <c r="H136" s="8" t="n"/>
+      <c r="I136" s="5" t="inlineStr"/>
+      <c r="J136" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[1]/div[2]/div/ul/li[1]/span/span[2]|text</t>
         </is>
@@ -10559,8 +11025,9 @@
         </is>
       </c>
       <c r="G137" s="7" t="n"/>
-      <c r="H137" s="5" t="inlineStr"/>
-      <c r="I137" s="8" t="inlineStr">
+      <c r="H137" s="8" t="n"/>
+      <c r="I137" s="5" t="inlineStr"/>
+      <c r="J137" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[1]/div[2]/div/ul/li[2]/span/span[1]|text</t>
         </is>
@@ -10592,8 +11059,9 @@
         </is>
       </c>
       <c r="G138" s="7" t="n"/>
-      <c r="H138" s="5" t="inlineStr"/>
-      <c r="I138" s="8" t="inlineStr">
+      <c r="H138" s="8" t="n"/>
+      <c r="I138" s="5" t="inlineStr"/>
+      <c r="J138" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[1]/div[2]/div/ul/li[2]/span/span[2]|text</t>
         </is>
@@ -10625,8 +11093,9 @@
         </is>
       </c>
       <c r="G139" s="7" t="n"/>
-      <c r="H139" s="5" t="inlineStr"/>
-      <c r="I139" s="8" t="inlineStr">
+      <c r="H139" s="8" t="n"/>
+      <c r="I139" s="5" t="inlineStr"/>
+      <c r="J139" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[1]/div[2]/div/ul/li[3]/span/span[1]|text</t>
         </is>
@@ -10658,8 +11127,9 @@
         </is>
       </c>
       <c r="G140" s="7" t="n"/>
-      <c r="H140" s="5" t="inlineStr"/>
-      <c r="I140" s="8" t="inlineStr">
+      <c r="H140" s="8" t="n"/>
+      <c r="I140" s="5" t="inlineStr"/>
+      <c r="J140" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[1]/div[2]/div/ul/li[3]/span/span[2]|text</t>
         </is>
@@ -10691,8 +11161,9 @@
         </is>
       </c>
       <c r="G141" s="7" t="n"/>
-      <c r="H141" s="5" t="inlineStr"/>
-      <c r="I141" s="8" t="inlineStr">
+      <c r="H141" s="8" t="n"/>
+      <c r="I141" s="5" t="inlineStr"/>
+      <c r="J141" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[1]/div[2]/div/ul/li[4]/span/span[1]|text</t>
         </is>
@@ -10724,8 +11195,9 @@
         </is>
       </c>
       <c r="G142" s="7" t="n"/>
-      <c r="H142" s="5" t="inlineStr"/>
-      <c r="I142" s="8" t="inlineStr">
+      <c r="H142" s="8" t="n"/>
+      <c r="I142" s="5" t="inlineStr"/>
+      <c r="J142" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[1]/div[2]/div/ul/li[4]/span/span[2]|text</t>
         </is>
@@ -10759,12 +11231,13 @@
         </is>
       </c>
       <c r="G143" s="7" t="n"/>
-      <c r="H143" s="5" t="inlineStr">
+      <c r="H143" s="8" t="n"/>
+      <c r="I143" s="5" t="inlineStr">
         <is>
           <t>묶음 43 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I143" s="8" t="inlineStr">
+      <c r="J143" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[1]/div[2]/div/p/b|text</t>
         </is>
@@ -10798,12 +11271,13 @@
         </is>
       </c>
       <c r="G144" s="7" t="n"/>
-      <c r="H144" s="5" t="inlineStr">
+      <c r="H144" s="8" t="n"/>
+      <c r="I144" s="5" t="inlineStr">
         <is>
           <t>묶음 44 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I144" s="8" t="inlineStr">
+      <c r="J144" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[1]/div[2]/div/p/span|text</t>
         </is>
@@ -10835,8 +11309,9 @@
         </is>
       </c>
       <c r="G145" s="7" t="n"/>
-      <c r="H145" s="5" t="inlineStr"/>
-      <c r="I145" s="8" t="inlineStr">
+      <c r="H145" s="8" t="n"/>
+      <c r="I145" s="5" t="inlineStr"/>
+      <c r="J145" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[2]/div[1]/img|alt</t>
         </is>
@@ -10868,8 +11343,13 @@
         </is>
       </c>
       <c r="G146" s="7" t="n"/>
-      <c r="H146" s="5" t="inlineStr"/>
-      <c r="I146" s="8" t="inlineStr">
+      <c r="H146" s="8" t="inlineStr">
+        <is>
+          <t>High Power Type Rack</t>
+        </is>
+      </c>
+      <c r="I146" s="5" t="inlineStr"/>
+      <c r="J146" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[2]/div[2]/p/b|text</t>
         </is>
@@ -10901,8 +11381,9 @@
         </is>
       </c>
       <c r="G147" s="7" t="n"/>
-      <c r="H147" s="5" t="inlineStr"/>
-      <c r="I147" s="8" t="inlineStr">
+      <c r="H147" s="8" t="n"/>
+      <c r="I147" s="5" t="inlineStr"/>
+      <c r="J147" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[2]/div[2]/div/ul/li[1]/span/span[1]|text</t>
         </is>
@@ -10934,8 +11415,9 @@
         </is>
       </c>
       <c r="G148" s="7" t="n"/>
-      <c r="H148" s="5" t="inlineStr"/>
-      <c r="I148" s="8" t="inlineStr">
+      <c r="H148" s="8" t="n"/>
+      <c r="I148" s="5" t="inlineStr"/>
+      <c r="J148" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[2]/div[2]/div/ul/li[1]/span/span[2]|text</t>
         </is>
@@ -10967,8 +11449,9 @@
         </is>
       </c>
       <c r="G149" s="7" t="n"/>
-      <c r="H149" s="5" t="inlineStr"/>
-      <c r="I149" s="8" t="inlineStr">
+      <c r="H149" s="8" t="n"/>
+      <c r="I149" s="5" t="inlineStr"/>
+      <c r="J149" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[2]/div[2]/div/ul/li[2]/span/span[1]|text</t>
         </is>
@@ -11000,8 +11483,9 @@
         </is>
       </c>
       <c r="G150" s="7" t="n"/>
-      <c r="H150" s="5" t="inlineStr"/>
-      <c r="I150" s="8" t="inlineStr">
+      <c r="H150" s="8" t="n"/>
+      <c r="I150" s="5" t="inlineStr"/>
+      <c r="J150" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[2]/div[2]/div/ul/li[2]/span/span[2]|text</t>
         </is>
@@ -11035,12 +11519,13 @@
         </is>
       </c>
       <c r="G151" s="7" t="n"/>
-      <c r="H151" s="5" t="inlineStr">
+      <c r="H151" s="8" t="n"/>
+      <c r="I151" s="5" t="inlineStr">
         <is>
           <t>묶음 46 — 같은 문구 3 곳</t>
         </is>
       </c>
-      <c r="I151" s="8" t="inlineStr">
+      <c r="J151" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[2]/div[2]/div/ul/li[3]/span/span[1]|text</t>
         </is>
@@ -11072,8 +11557,9 @@
         </is>
       </c>
       <c r="G152" s="7" t="n"/>
-      <c r="H152" s="5" t="inlineStr"/>
-      <c r="I152" s="8" t="inlineStr">
+      <c r="H152" s="8" t="n"/>
+      <c r="I152" s="5" t="inlineStr"/>
+      <c r="J152" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[2]/div[2]/div/ul/li[3]/span/span[2]|text</t>
         </is>
@@ -11105,8 +11591,9 @@
         </is>
       </c>
       <c r="G153" s="7" t="n"/>
-      <c r="H153" s="5" t="inlineStr"/>
-      <c r="I153" s="8" t="inlineStr">
+      <c r="H153" s="8" t="n"/>
+      <c r="I153" s="5" t="inlineStr"/>
+      <c r="J153" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[2]/div[2]/div/ul/li[4]/span/span[1]|text</t>
         </is>
@@ -11138,8 +11625,9 @@
         </is>
       </c>
       <c r="G154" s="7" t="n"/>
-      <c r="H154" s="5" t="inlineStr"/>
-      <c r="I154" s="8" t="inlineStr">
+      <c r="H154" s="8" t="n"/>
+      <c r="I154" s="5" t="inlineStr"/>
+      <c r="J154" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[2]/div[2]/div/ul/li[4]/span/span[2]|text</t>
         </is>
@@ -11173,12 +11661,13 @@
         </is>
       </c>
       <c r="G155" s="7" t="n"/>
-      <c r="H155" s="5" t="inlineStr">
+      <c r="H155" s="8" t="n"/>
+      <c r="I155" s="5" t="inlineStr">
         <is>
           <t>묶음 43 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I155" s="8" t="inlineStr">
+      <c r="J155" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[2]/div[2]/div/p/b|text</t>
         </is>
@@ -11212,12 +11701,13 @@
         </is>
       </c>
       <c r="G156" s="7" t="n"/>
-      <c r="H156" s="5" t="inlineStr">
+      <c r="H156" s="8" t="n"/>
+      <c r="I156" s="5" t="inlineStr">
         <is>
           <t>묶음 44 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I156" s="8" t="inlineStr">
+      <c r="J156" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[2]/div[2]/div[2]/div[2]/div/p/span|text</t>
         </is>
@@ -11248,9 +11738,10 @@
           <t>03-3</t>
         </is>
       </c>
-      <c r="G157" s="7" t="n"/>
-      <c r="H157" s="5" t="inlineStr"/>
-      <c r="I157" s="8" t="inlineStr">
+      <c r="G157" s="6" t="n"/>
+      <c r="H157" s="6" t="n"/>
+      <c r="I157" s="5" t="inlineStr"/>
+      <c r="J157" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[1]/p/span|text</t>
         </is>
@@ -11284,12 +11775,13 @@
         </is>
       </c>
       <c r="G158" s="7" t="n"/>
-      <c r="H158" s="5" t="inlineStr">
+      <c r="H158" s="8" t="n"/>
+      <c r="I158" s="5" t="inlineStr">
         <is>
           <t>묶음 36 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I158" s="8" t="inlineStr">
+      <c r="J158" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[1]/div/div[1]/h2|text</t>
         </is>
@@ -11321,8 +11813,9 @@
         </is>
       </c>
       <c r="G159" s="7" t="n"/>
-      <c r="H159" s="5" t="inlineStr"/>
-      <c r="I159" s="8" t="inlineStr">
+      <c r="H159" s="8" t="n"/>
+      <c r="I159" s="5" t="inlineStr"/>
+      <c r="J159" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[1]/div/div[1]/p|text</t>
         </is>
@@ -11356,12 +11849,13 @@
         </is>
       </c>
       <c r="G160" s="7" t="n"/>
-      <c r="H160" s="5" t="inlineStr">
+      <c r="H160" s="8" t="n"/>
+      <c r="I160" s="5" t="inlineStr">
         <is>
           <t>묶음 40 — 같은 문구 4 곳</t>
         </is>
       </c>
-      <c r="I160" s="8" t="inlineStr">
+      <c r="J160" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[1]/div/div[2]/p|text</t>
         </is>
@@ -11395,12 +11889,13 @@
         </is>
       </c>
       <c r="G161" s="7" t="n"/>
-      <c r="H161" s="5" t="inlineStr">
+      <c r="H161" s="8" t="n"/>
+      <c r="I161" s="5" t="inlineStr">
         <is>
           <t>묶음 41 — 같은 문구 8 곳</t>
         </is>
       </c>
-      <c r="I161" s="8" t="inlineStr">
+      <c r="J161" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[1]/div/div[2]/ul/li[1]|text</t>
         </is>
@@ -11434,12 +11929,13 @@
         </is>
       </c>
       <c r="G162" s="7" t="n"/>
-      <c r="H162" s="5" t="inlineStr">
+      <c r="H162" s="8" t="n"/>
+      <c r="I162" s="5" t="inlineStr">
         <is>
           <t>묶음 41 — 같은 문구 8 곳</t>
         </is>
       </c>
-      <c r="I162" s="8" t="inlineStr">
+      <c r="J162" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[1]/div/div[2]/ul/li[2]|text</t>
         </is>
@@ -11471,8 +11967,9 @@
         </is>
       </c>
       <c r="G163" s="7" t="n"/>
-      <c r="H163" s="5" t="inlineStr"/>
-      <c r="I163" s="8" t="inlineStr">
+      <c r="H163" s="8" t="n"/>
+      <c r="I163" s="5" t="inlineStr"/>
+      <c r="J163" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[1]/img|alt</t>
         </is>
@@ -11504,8 +12001,13 @@
         </is>
       </c>
       <c r="G164" s="7" t="n"/>
-      <c r="H164" s="5" t="inlineStr"/>
-      <c r="I164" s="8" t="inlineStr">
+      <c r="H164" s="8" t="inlineStr">
+        <is>
+          <t>Container Air Cooling Type</t>
+        </is>
+      </c>
+      <c r="I164" s="5" t="inlineStr"/>
+      <c r="J164" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/p/b|text</t>
         </is>
@@ -11537,8 +12039,9 @@
         </is>
       </c>
       <c r="G165" s="7" t="n"/>
-      <c r="H165" s="5" t="inlineStr"/>
-      <c r="I165" s="8" t="inlineStr">
+      <c r="H165" s="8" t="n"/>
+      <c r="I165" s="5" t="inlineStr"/>
+      <c r="J165" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[1]/span/span[1]|text</t>
         </is>
@@ -11570,8 +12073,9 @@
         </is>
       </c>
       <c r="G166" s="7" t="n"/>
-      <c r="H166" s="5" t="inlineStr"/>
-      <c r="I166" s="8" t="inlineStr">
+      <c r="H166" s="8" t="n"/>
+      <c r="I166" s="5" t="inlineStr"/>
+      <c r="J166" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[1]/span/span[2]|text</t>
         </is>
@@ -11603,8 +12107,9 @@
         </is>
       </c>
       <c r="G167" s="7" t="n"/>
-      <c r="H167" s="5" t="inlineStr"/>
-      <c r="I167" s="8" t="inlineStr">
+      <c r="H167" s="8" t="n"/>
+      <c r="I167" s="5" t="inlineStr"/>
+      <c r="J167" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[2]/span/span[1]|text</t>
         </is>
@@ -11636,8 +12141,9 @@
         </is>
       </c>
       <c r="G168" s="7" t="n"/>
-      <c r="H168" s="5" t="inlineStr"/>
-      <c r="I168" s="8" t="inlineStr">
+      <c r="H168" s="8" t="n"/>
+      <c r="I168" s="5" t="inlineStr"/>
+      <c r="J168" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[2]/span/span[2]|text</t>
         </is>
@@ -11669,8 +12175,9 @@
         </is>
       </c>
       <c r="G169" s="7" t="n"/>
-      <c r="H169" s="5" t="inlineStr"/>
-      <c r="I169" s="8" t="inlineStr">
+      <c r="H169" s="8" t="n"/>
+      <c r="I169" s="5" t="inlineStr"/>
+      <c r="J169" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[3]/span/span[1]|text</t>
         </is>
@@ -11702,8 +12209,9 @@
         </is>
       </c>
       <c r="G170" s="7" t="n"/>
-      <c r="H170" s="5" t="inlineStr"/>
-      <c r="I170" s="8" t="inlineStr">
+      <c r="H170" s="8" t="n"/>
+      <c r="I170" s="5" t="inlineStr"/>
+      <c r="J170" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[3]/span/span[2]|text</t>
         </is>
@@ -11737,12 +12245,13 @@
         </is>
       </c>
       <c r="G171" s="7" t="n"/>
-      <c r="H171" s="5" t="inlineStr">
+      <c r="H171" s="8" t="n"/>
+      <c r="I171" s="5" t="inlineStr">
         <is>
           <t>묶음 42 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I171" s="8" t="inlineStr">
+      <c r="J171" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[4]/span/span[1]|text</t>
         </is>
@@ -11774,8 +12283,9 @@
         </is>
       </c>
       <c r="G172" s="7" t="n"/>
-      <c r="H172" s="5" t="inlineStr"/>
-      <c r="I172" s="8" t="inlineStr">
+      <c r="H172" s="8" t="n"/>
+      <c r="I172" s="5" t="inlineStr"/>
+      <c r="J172" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[4]/span/span[2]|text</t>
         </is>
@@ -11809,12 +12319,13 @@
         </is>
       </c>
       <c r="G173" s="7" t="n"/>
-      <c r="H173" s="5" t="inlineStr">
+      <c r="H173" s="8" t="n"/>
+      <c r="I173" s="5" t="inlineStr">
         <is>
           <t>묶음 43 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I173" s="8" t="inlineStr">
+      <c r="J173" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/p/b|text</t>
         </is>
@@ -11848,12 +12359,13 @@
         </is>
       </c>
       <c r="G174" s="7" t="n"/>
-      <c r="H174" s="5" t="inlineStr">
+      <c r="H174" s="8" t="n"/>
+      <c r="I174" s="5" t="inlineStr">
         <is>
           <t>묶음 44 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I174" s="8" t="inlineStr">
+      <c r="J174" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/p/span|text</t>
         </is>
@@ -11885,8 +12397,9 @@
         </is>
       </c>
       <c r="G175" s="7" t="n"/>
-      <c r="H175" s="5" t="inlineStr"/>
-      <c r="I175" s="8" t="inlineStr">
+      <c r="H175" s="8" t="n"/>
+      <c r="I175" s="5" t="inlineStr"/>
+      <c r="J175" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[1]/img|alt</t>
         </is>
@@ -11918,8 +12431,13 @@
         </is>
       </c>
       <c r="G176" s="7" t="n"/>
-      <c r="H176" s="5" t="inlineStr"/>
-      <c r="I176" s="8" t="inlineStr">
+      <c r="H176" s="8" t="inlineStr">
+        <is>
+          <t>Container Liquid Cooling Type</t>
+        </is>
+      </c>
+      <c r="I176" s="5" t="inlineStr"/>
+      <c r="J176" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/p/b|text</t>
         </is>
@@ -11953,12 +12471,13 @@
         </is>
       </c>
       <c r="G177" s="7" t="n"/>
-      <c r="H177" s="5" t="inlineStr">
+      <c r="H177" s="8" t="n"/>
+      <c r="I177" s="5" t="inlineStr">
         <is>
           <t>묶음 45 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I177" s="8" t="inlineStr">
+      <c r="J177" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[1]/span/span[1]|text</t>
         </is>
@@ -11990,8 +12509,9 @@
         </is>
       </c>
       <c r="G178" s="7" t="n"/>
-      <c r="H178" s="5" t="inlineStr"/>
-      <c r="I178" s="8" t="inlineStr">
+      <c r="H178" s="8" t="n"/>
+      <c r="I178" s="5" t="inlineStr"/>
+      <c r="J178" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[1]/span/span[2]|text</t>
         </is>
@@ -12025,12 +12545,13 @@
         </is>
       </c>
       <c r="G179" s="7" t="n"/>
-      <c r="H179" s="5" t="inlineStr">
+      <c r="H179" s="8" t="n"/>
+      <c r="I179" s="5" t="inlineStr">
         <is>
           <t>묶음 46 — 같은 문구 3 곳</t>
         </is>
       </c>
-      <c r="I179" s="8" t="inlineStr">
+      <c r="J179" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[2]/span/span[1]|text</t>
         </is>
@@ -12062,8 +12583,9 @@
         </is>
       </c>
       <c r="G180" s="7" t="n"/>
-      <c r="H180" s="5" t="inlineStr"/>
-      <c r="I180" s="8" t="inlineStr">
+      <c r="H180" s="8" t="n"/>
+      <c r="I180" s="5" t="inlineStr"/>
+      <c r="J180" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[2]/span/span[2]|text</t>
         </is>
@@ -12097,12 +12619,13 @@
         </is>
       </c>
       <c r="G181" s="7" t="n"/>
-      <c r="H181" s="5" t="inlineStr">
+      <c r="H181" s="8" t="n"/>
+      <c r="I181" s="5" t="inlineStr">
         <is>
           <t>묶음 47 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I181" s="8" t="inlineStr">
+      <c r="J181" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[3]/span/span[1]|text</t>
         </is>
@@ -12136,12 +12659,13 @@
         </is>
       </c>
       <c r="G182" s="7" t="n"/>
-      <c r="H182" s="5" t="inlineStr">
+      <c r="H182" s="8" t="n"/>
+      <c r="I182" s="5" t="inlineStr">
         <is>
           <t>묶음 48 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I182" s="8" t="inlineStr">
+      <c r="J182" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[3]/span/span[2]|text</t>
         </is>
@@ -12175,12 +12699,13 @@
         </is>
       </c>
       <c r="G183" s="7" t="n"/>
-      <c r="H183" s="5" t="inlineStr">
+      <c r="H183" s="8" t="n"/>
+      <c r="I183" s="5" t="inlineStr">
         <is>
           <t>묶음 49 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I183" s="8" t="inlineStr">
+      <c r="J183" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[4]/span/span[1]|text</t>
         </is>
@@ -12214,12 +12739,13 @@
         </is>
       </c>
       <c r="G184" s="7" t="n"/>
-      <c r="H184" s="5" t="inlineStr">
+      <c r="H184" s="8" t="n"/>
+      <c r="I184" s="5" t="inlineStr">
         <is>
           <t>묶음 50 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I184" s="8" t="inlineStr">
+      <c r="J184" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[4]/span/span[2]|text</t>
         </is>
@@ -12253,12 +12779,13 @@
         </is>
       </c>
       <c r="G185" s="7" t="n"/>
-      <c r="H185" s="5" t="inlineStr">
+      <c r="H185" s="8" t="n"/>
+      <c r="I185" s="5" t="inlineStr">
         <is>
           <t>묶음 43 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I185" s="8" t="inlineStr">
+      <c r="J185" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/p/b|text</t>
         </is>
@@ -12292,12 +12819,13 @@
         </is>
       </c>
       <c r="G186" s="7" t="n"/>
-      <c r="H186" s="5" t="inlineStr">
+      <c r="H186" s="8" t="n"/>
+      <c r="I186" s="5" t="inlineStr">
         <is>
           <t>묶음 44 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I186" s="8" t="inlineStr">
+      <c r="J186" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/p/span|text</t>
         </is>
@@ -12328,9 +12856,10 @@
           <t>03-4</t>
         </is>
       </c>
-      <c r="G187" s="7" t="n"/>
-      <c r="H187" s="5" t="inlineStr"/>
-      <c r="I187" s="8" t="inlineStr">
+      <c r="G187" s="6" t="n"/>
+      <c r="H187" s="6" t="n"/>
+      <c r="I187" s="5" t="inlineStr"/>
+      <c r="J187" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[1]/p/span|text</t>
         </is>
@@ -12364,12 +12893,13 @@
         </is>
       </c>
       <c r="G188" s="7" t="n"/>
-      <c r="H188" s="5" t="inlineStr">
+      <c r="H188" s="8" t="n"/>
+      <c r="I188" s="5" t="inlineStr">
         <is>
           <t>묶음 37 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I188" s="8" t="inlineStr">
+      <c r="J188" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[1]/div/div[1]/h2|text</t>
         </is>
@@ -12401,8 +12931,9 @@
         </is>
       </c>
       <c r="G189" s="7" t="n"/>
-      <c r="H189" s="5" t="inlineStr"/>
-      <c r="I189" s="8" t="inlineStr">
+      <c r="H189" s="8" t="n"/>
+      <c r="I189" s="5" t="inlineStr"/>
+      <c r="J189" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[1]/div/div[1]/p|text</t>
         </is>
@@ -12436,12 +12967,13 @@
         </is>
       </c>
       <c r="G190" s="7" t="n"/>
-      <c r="H190" s="5" t="inlineStr">
+      <c r="H190" s="8" t="n"/>
+      <c r="I190" s="5" t="inlineStr">
         <is>
           <t>묶음 40 — 같은 문구 4 곳</t>
         </is>
       </c>
-      <c r="I190" s="8" t="inlineStr">
+      <c r="J190" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[1]/div/div[2]/p|text</t>
         </is>
@@ -12475,12 +13007,13 @@
         </is>
       </c>
       <c r="G191" s="7" t="n"/>
-      <c r="H191" s="5" t="inlineStr">
+      <c r="H191" s="8" t="n"/>
+      <c r="I191" s="5" t="inlineStr">
         <is>
           <t>묶음 41 — 같은 문구 8 곳</t>
         </is>
       </c>
-      <c r="I191" s="8" t="inlineStr">
+      <c r="J191" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[1]/div/div[2]/ul/li[1]|text</t>
         </is>
@@ -12514,12 +13047,13 @@
         </is>
       </c>
       <c r="G192" s="7" t="n"/>
-      <c r="H192" s="5" t="inlineStr">
+      <c r="H192" s="8" t="n"/>
+      <c r="I192" s="5" t="inlineStr">
         <is>
           <t>묶음 41 — 같은 문구 8 곳</t>
         </is>
       </c>
-      <c r="I192" s="8" t="inlineStr">
+      <c r="J192" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[1]/div/div[2]/ul/li[2]|text</t>
         </is>
@@ -12551,8 +13085,9 @@
         </is>
       </c>
       <c r="G193" s="7" t="n"/>
-      <c r="H193" s="5" t="inlineStr"/>
-      <c r="I193" s="8" t="inlineStr">
+      <c r="H193" s="8" t="n"/>
+      <c r="I193" s="5" t="inlineStr"/>
+      <c r="J193" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[1]/img|alt</t>
         </is>
@@ -12584,8 +13119,13 @@
         </is>
       </c>
       <c r="G194" s="7" t="n"/>
-      <c r="H194" s="5" t="inlineStr"/>
-      <c r="I194" s="8" t="inlineStr">
+      <c r="H194" s="8" t="inlineStr">
+        <is>
+          <t>Module BMS(CMU)</t>
+        </is>
+      </c>
+      <c r="I194" s="5" t="inlineStr"/>
+      <c r="J194" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/p/b|text</t>
         </is>
@@ -12617,8 +13157,9 @@
         </is>
       </c>
       <c r="G195" s="7" t="n"/>
-      <c r="H195" s="5" t="inlineStr"/>
-      <c r="I195" s="8" t="inlineStr">
+      <c r="H195" s="8" t="n"/>
+      <c r="I195" s="5" t="inlineStr"/>
+      <c r="J195" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[1]/span/span[1]|text</t>
         </is>
@@ -12650,8 +13191,9 @@
         </is>
       </c>
       <c r="G196" s="7" t="n"/>
-      <c r="H196" s="5" t="inlineStr"/>
-      <c r="I196" s="8" t="inlineStr">
+      <c r="H196" s="8" t="n"/>
+      <c r="I196" s="5" t="inlineStr"/>
+      <c r="J196" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[1]/span/span[2]|text</t>
         </is>
@@ -12683,8 +13225,9 @@
         </is>
       </c>
       <c r="G197" s="7" t="n"/>
-      <c r="H197" s="5" t="inlineStr"/>
-      <c r="I197" s="8" t="inlineStr">
+      <c r="H197" s="8" t="n"/>
+      <c r="I197" s="5" t="inlineStr"/>
+      <c r="J197" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[2]/span/span[1]|text</t>
         </is>
@@ -12716,8 +13259,9 @@
         </is>
       </c>
       <c r="G198" s="7" t="n"/>
-      <c r="H198" s="5" t="inlineStr"/>
-      <c r="I198" s="8" t="inlineStr">
+      <c r="H198" s="8" t="n"/>
+      <c r="I198" s="5" t="inlineStr"/>
+      <c r="J198" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[2]/span/span[2]|text</t>
         </is>
@@ -12749,8 +13293,9 @@
         </is>
       </c>
       <c r="G199" s="7" t="n"/>
-      <c r="H199" s="5" t="inlineStr"/>
-      <c r="I199" s="8" t="inlineStr">
+      <c r="H199" s="8" t="n"/>
+      <c r="I199" s="5" t="inlineStr"/>
+      <c r="J199" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[3]/span/span[1]|text</t>
         </is>
@@ -12782,8 +13327,9 @@
         </is>
       </c>
       <c r="G200" s="7" t="n"/>
-      <c r="H200" s="5" t="inlineStr"/>
-      <c r="I200" s="8" t="inlineStr">
+      <c r="H200" s="8" t="n"/>
+      <c r="I200" s="5" t="inlineStr"/>
+      <c r="J200" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[3]/span/span[2]|text</t>
         </is>
@@ -12815,8 +13361,9 @@
         </is>
       </c>
       <c r="G201" s="7" t="n"/>
-      <c r="H201" s="5" t="inlineStr"/>
-      <c r="I201" s="8" t="inlineStr">
+      <c r="H201" s="8" t="n"/>
+      <c r="I201" s="5" t="inlineStr"/>
+      <c r="J201" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[4]/span/span[1]|text</t>
         </is>
@@ -12848,8 +13395,9 @@
         </is>
       </c>
       <c r="G202" s="7" t="n"/>
-      <c r="H202" s="5" t="inlineStr"/>
-      <c r="I202" s="8" t="inlineStr">
+      <c r="H202" s="8" t="n"/>
+      <c r="I202" s="5" t="inlineStr"/>
+      <c r="J202" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[4]/span/span[2]|text</t>
         </is>
@@ -12883,12 +13431,13 @@
         </is>
       </c>
       <c r="G203" s="7" t="n"/>
-      <c r="H203" s="5" t="inlineStr">
+      <c r="H203" s="8" t="n"/>
+      <c r="I203" s="5" t="inlineStr">
         <is>
           <t>묶음 43 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I203" s="8" t="inlineStr">
+      <c r="J203" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/p/b|text</t>
         </is>
@@ -12922,12 +13471,13 @@
         </is>
       </c>
       <c r="G204" s="7" t="n"/>
-      <c r="H204" s="5" t="inlineStr">
+      <c r="H204" s="8" t="n"/>
+      <c r="I204" s="5" t="inlineStr">
         <is>
           <t>묶음 44 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I204" s="8" t="inlineStr">
+      <c r="J204" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/p/span|text</t>
         </is>
@@ -12959,8 +13509,9 @@
         </is>
       </c>
       <c r="G205" s="7" t="n"/>
-      <c r="H205" s="5" t="inlineStr"/>
-      <c r="I205" s="8" t="inlineStr">
+      <c r="H205" s="8" t="n"/>
+      <c r="I205" s="5" t="inlineStr"/>
+      <c r="J205" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[1]/img|alt</t>
         </is>
@@ -12992,8 +13543,13 @@
         </is>
       </c>
       <c r="G206" s="7" t="n"/>
-      <c r="H206" s="5" t="inlineStr"/>
-      <c r="I206" s="8" t="inlineStr">
+      <c r="H206" s="8" t="inlineStr">
+        <is>
+          <t>Rack BMS(BPU)</t>
+        </is>
+      </c>
+      <c r="I206" s="5" t="inlineStr"/>
+      <c r="J206" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/p/b|text</t>
         </is>
@@ -13025,8 +13581,9 @@
         </is>
       </c>
       <c r="G207" s="7" t="n"/>
-      <c r="H207" s="5" t="inlineStr"/>
-      <c r="I207" s="8" t="inlineStr">
+      <c r="H207" s="8" t="n"/>
+      <c r="I207" s="5" t="inlineStr"/>
+      <c r="J207" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[1]/span/span[1]|text</t>
         </is>
@@ -13058,8 +13615,9 @@
         </is>
       </c>
       <c r="G208" s="7" t="n"/>
-      <c r="H208" s="5" t="inlineStr"/>
-      <c r="I208" s="8" t="inlineStr">
+      <c r="H208" s="8" t="n"/>
+      <c r="I208" s="5" t="inlineStr"/>
+      <c r="J208" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[1]/span/span[2]|text</t>
         </is>
@@ -13091,8 +13649,9 @@
         </is>
       </c>
       <c r="G209" s="7" t="n"/>
-      <c r="H209" s="5" t="inlineStr"/>
-      <c r="I209" s="8" t="inlineStr">
+      <c r="H209" s="8" t="n"/>
+      <c r="I209" s="5" t="inlineStr"/>
+      <c r="J209" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[2]/span/span[1]|text</t>
         </is>
@@ -13124,8 +13683,9 @@
         </is>
       </c>
       <c r="G210" s="7" t="n"/>
-      <c r="H210" s="5" t="inlineStr"/>
-      <c r="I210" s="8" t="inlineStr">
+      <c r="H210" s="8" t="n"/>
+      <c r="I210" s="5" t="inlineStr"/>
+      <c r="J210" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[2]/span/span[2]|text</t>
         </is>
@@ -13157,8 +13717,9 @@
         </is>
       </c>
       <c r="G211" s="7" t="n"/>
-      <c r="H211" s="5" t="inlineStr"/>
-      <c r="I211" s="8" t="inlineStr">
+      <c r="H211" s="8" t="n"/>
+      <c r="I211" s="5" t="inlineStr"/>
+      <c r="J211" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[3]/span/span[1]|text</t>
         </is>
@@ -13190,8 +13751,9 @@
         </is>
       </c>
       <c r="G212" s="7" t="n"/>
-      <c r="H212" s="5" t="inlineStr"/>
-      <c r="I212" s="8" t="inlineStr">
+      <c r="H212" s="8" t="n"/>
+      <c r="I212" s="5" t="inlineStr"/>
+      <c r="J212" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[3]/span/span[2]|text</t>
         </is>
@@ -13223,8 +13785,9 @@
         </is>
       </c>
       <c r="G213" s="7" t="n"/>
-      <c r="H213" s="5" t="inlineStr"/>
-      <c r="I213" s="8" t="inlineStr">
+      <c r="H213" s="8" t="n"/>
+      <c r="I213" s="5" t="inlineStr"/>
+      <c r="J213" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[4]/span/span[1]|text</t>
         </is>
@@ -13256,8 +13819,9 @@
         </is>
       </c>
       <c r="G214" s="7" t="n"/>
-      <c r="H214" s="5" t="inlineStr"/>
-      <c r="I214" s="8" t="inlineStr">
+      <c r="H214" s="8" t="n"/>
+      <c r="I214" s="5" t="inlineStr"/>
+      <c r="J214" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[4]/span/span[2]|text</t>
         </is>
@@ -13291,12 +13855,13 @@
         </is>
       </c>
       <c r="G215" s="7" t="n"/>
-      <c r="H215" s="5" t="inlineStr">
+      <c r="H215" s="8" t="n"/>
+      <c r="I215" s="5" t="inlineStr">
         <is>
           <t>묶음 43 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I215" s="8" t="inlineStr">
+      <c r="J215" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/p/b|text</t>
         </is>
@@ -13330,12 +13895,13 @@
         </is>
       </c>
       <c r="G216" s="7" t="n"/>
-      <c r="H216" s="5" t="inlineStr">
+      <c r="H216" s="8" t="n"/>
+      <c r="I216" s="5" t="inlineStr">
         <is>
           <t>묶음 44 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I216" s="8" t="inlineStr">
+      <c r="J216" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/p/span|text</t>
         </is>
@@ -13367,8 +13933,9 @@
         </is>
       </c>
       <c r="G217" s="7" t="n"/>
-      <c r="H217" s="5" t="inlineStr"/>
-      <c r="I217" s="8" t="inlineStr">
+      <c r="H217" s="8" t="n"/>
+      <c r="I217" s="5" t="inlineStr"/>
+      <c r="J217" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[1]/img|alt</t>
         </is>
@@ -13400,8 +13967,13 @@
         </is>
       </c>
       <c r="G218" s="7" t="n"/>
-      <c r="H218" s="5" t="inlineStr"/>
-      <c r="I218" s="8" t="inlineStr">
+      <c r="H218" s="8" t="inlineStr">
+        <is>
+          <t>System BMS(BCP)</t>
+        </is>
+      </c>
+      <c r="I218" s="5" t="inlineStr"/>
+      <c r="J218" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/p/b|text</t>
         </is>
@@ -13433,8 +14005,9 @@
         </is>
       </c>
       <c r="G219" s="7" t="n"/>
-      <c r="H219" s="5" t="inlineStr"/>
-      <c r="I219" s="8" t="inlineStr">
+      <c r="H219" s="8" t="n"/>
+      <c r="I219" s="5" t="inlineStr"/>
+      <c r="J219" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[1]/span/span[1]|text</t>
         </is>
@@ -13466,8 +14039,9 @@
         </is>
       </c>
       <c r="G220" s="7" t="n"/>
-      <c r="H220" s="5" t="inlineStr"/>
-      <c r="I220" s="8" t="inlineStr">
+      <c r="H220" s="8" t="n"/>
+      <c r="I220" s="5" t="inlineStr"/>
+      <c r="J220" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[1]/span/span[2]|text</t>
         </is>
@@ -13499,8 +14073,9 @@
         </is>
       </c>
       <c r="G221" s="7" t="n"/>
-      <c r="H221" s="5" t="inlineStr"/>
-      <c r="I221" s="8" t="inlineStr">
+      <c r="H221" s="8" t="n"/>
+      <c r="I221" s="5" t="inlineStr"/>
+      <c r="J221" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[2]/span/span[1]|text</t>
         </is>
@@ -13532,8 +14107,9 @@
         </is>
       </c>
       <c r="G222" s="7" t="n"/>
-      <c r="H222" s="5" t="inlineStr"/>
-      <c r="I222" s="8" t="inlineStr">
+      <c r="H222" s="8" t="n"/>
+      <c r="I222" s="5" t="inlineStr"/>
+      <c r="J222" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[2]/span/span[2]|text</t>
         </is>
@@ -13565,8 +14141,9 @@
         </is>
       </c>
       <c r="G223" s="7" t="n"/>
-      <c r="H223" s="5" t="inlineStr"/>
-      <c r="I223" s="8" t="inlineStr">
+      <c r="H223" s="8" t="n"/>
+      <c r="I223" s="5" t="inlineStr"/>
+      <c r="J223" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[3]/span/span[1]|text</t>
         </is>
@@ -13598,8 +14175,9 @@
         </is>
       </c>
       <c r="G224" s="7" t="n"/>
-      <c r="H224" s="5" t="inlineStr"/>
-      <c r="I224" s="8" t="inlineStr">
+      <c r="H224" s="8" t="n"/>
+      <c r="I224" s="5" t="inlineStr"/>
+      <c r="J224" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[3]/span/span[2]|text</t>
         </is>
@@ -13631,8 +14209,9 @@
         </is>
       </c>
       <c r="G225" s="7" t="n"/>
-      <c r="H225" s="5" t="inlineStr"/>
-      <c r="I225" s="8" t="inlineStr">
+      <c r="H225" s="8" t="n"/>
+      <c r="I225" s="5" t="inlineStr"/>
+      <c r="J225" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[4]/span/span[1]|text</t>
         </is>
@@ -13664,8 +14243,9 @@
         </is>
       </c>
       <c r="G226" s="7" t="n"/>
-      <c r="H226" s="5" t="inlineStr"/>
-      <c r="I226" s="8" t="inlineStr">
+      <c r="H226" s="8" t="n"/>
+      <c r="I226" s="5" t="inlineStr"/>
+      <c r="J226" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[4]/span/span[2]|text</t>
         </is>
@@ -13699,12 +14279,13 @@
         </is>
       </c>
       <c r="G227" s="7" t="n"/>
-      <c r="H227" s="5" t="inlineStr">
+      <c r="H227" s="8" t="n"/>
+      <c r="I227" s="5" t="inlineStr">
         <is>
           <t>묶음 43 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I227" s="8" t="inlineStr">
+      <c r="J227" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/p/b|text</t>
         </is>
@@ -13738,19 +14319,20 @@
         </is>
       </c>
       <c r="G228" s="7" t="n"/>
-      <c r="H228" s="5" t="inlineStr">
+      <c r="H228" s="8" t="n"/>
+      <c r="I228" s="5" t="inlineStr">
         <is>
           <t>묶음 44 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I228" s="8" t="inlineStr">
+      <c r="J228" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/p/span|text</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I228"/>
+  <autoFilter ref="A1:J228"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -13761,18 +14343,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I65"/>
+  <dimension ref="A1:J65"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
-    <col width="62" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="54" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -13813,10 +14396,15 @@
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
+          <t>영문 문구</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>자리표(건드리지 마세요)</t>
         </is>
@@ -13848,8 +14436,9 @@
         </is>
       </c>
       <c r="G2" s="7" t="n"/>
-      <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[1]/div/div/h1/span[1]|text</t>
         </is>
@@ -13881,8 +14470,13 @@
         </is>
       </c>
       <c r="G3" s="7" t="n"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>Intelligent AI Platform</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[1]/div/div/h1/span[2]|text</t>
         </is>
@@ -13914,8 +14508,9 @@
         </is>
       </c>
       <c r="G4" s="7" t="n"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[1]/p/span[1]|text</t>
         </is>
@@ -13947,8 +14542,9 @@
         </is>
       </c>
       <c r="G5" s="7" t="n"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[1]/p/span[2]|text</t>
         </is>
@@ -13980,8 +14576,9 @@
         </is>
       </c>
       <c r="G6" s="7" t="n"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[1]/div/img|alt</t>
         </is>
@@ -14015,12 +14612,13 @@
         </is>
       </c>
       <c r="G7" s="7" t="n"/>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>묶음 51 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[2]/ul/li[1]/p|text</t>
         </is>
@@ -14054,12 +14652,13 @@
         </is>
       </c>
       <c r="G8" s="7" t="n"/>
-      <c r="H8" s="5" t="inlineStr">
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
         <is>
           <t>묶음 52 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[2]/ul/li[2]/p|text</t>
         </is>
@@ -14093,12 +14692,13 @@
         </is>
       </c>
       <c r="G9" s="7" t="n"/>
-      <c r="H9" s="5" t="inlineStr">
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="5" t="inlineStr">
         <is>
           <t>묶음 53 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[2]/ul/li[3]/p|text</t>
         </is>
@@ -14132,12 +14732,13 @@
         </is>
       </c>
       <c r="G10" s="7" t="n"/>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="H10" s="8" t="n"/>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>묶음 54 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[2]/ul/li[4]/p|text</t>
         </is>
@@ -14170,13 +14771,14 @@
           <t>01</t>
         </is>
       </c>
-      <c r="G11" s="7" t="n"/>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="G11" s="6" t="n"/>
+      <c r="H11" s="6" t="n"/>
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>묶음 5 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[1]/p/span[1]|text</t>
         </is>
@@ -14210,12 +14812,13 @@
         </is>
       </c>
       <c r="G12" s="7" t="n"/>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>묶음 51 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[1]/p/span[2]|text</t>
         </is>
@@ -14249,12 +14852,13 @@
         </is>
       </c>
       <c r="G13" s="7" t="n"/>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>묶음 55 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[1]/a[1]|text</t>
         </is>
@@ -14288,12 +14892,13 @@
         </is>
       </c>
       <c r="G14" s="7" t="n"/>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>묶음 56 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[1]/a[2]|text</t>
         </is>
@@ -14326,13 +14931,14 @@
           <t>02</t>
         </is>
       </c>
-      <c r="G15" s="7" t="n"/>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="G15" s="6" t="n"/>
+      <c r="H15" s="6" t="n"/>
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>묶음 8 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[2]/p/span[1]|text</t>
         </is>
@@ -14366,12 +14972,13 @@
         </is>
       </c>
       <c r="G16" s="7" t="n"/>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>묶음 52 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[2]/p/span[2]|text</t>
         </is>
@@ -14405,12 +15012,13 @@
         </is>
       </c>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>묶음 57 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[2]/a[1]|text</t>
         </is>
@@ -14444,12 +15052,13 @@
         </is>
       </c>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>묶음 58 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[2]/a[2]|text</t>
         </is>
@@ -14482,13 +15091,14 @@
           <t>03</t>
         </is>
       </c>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>묶음 10 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[3]/p/span[1]|text</t>
         </is>
@@ -14522,12 +15132,13 @@
         </is>
       </c>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>묶음 53 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[3]/p/span[2]|text</t>
         </is>
@@ -14561,12 +15172,13 @@
         </is>
       </c>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>묶음 59 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[3]/a[1]|text</t>
         </is>
@@ -14600,12 +15212,13 @@
         </is>
       </c>
       <c r="G22" s="7" t="n"/>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>묶음 60 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[3]/a[2]|text</t>
         </is>
@@ -14638,13 +15251,14 @@
           <t>04</t>
         </is>
       </c>
-      <c r="G23" s="7" t="n"/>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="G23" s="6" t="n"/>
+      <c r="H23" s="6" t="n"/>
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>묶음 12 — 같은 문구 9 곳</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[4]/p/span[1]|text</t>
         </is>
@@ -14678,12 +15292,13 @@
         </is>
       </c>
       <c r="G24" s="7" t="n"/>
-      <c r="H24" s="5" t="inlineStr">
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="5" t="inlineStr">
         <is>
           <t>묶음 54 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[4]/p/span[2]|text</t>
         </is>
@@ -14717,12 +15332,13 @@
         </is>
       </c>
       <c r="G25" s="7" t="n"/>
-      <c r="H25" s="5" t="inlineStr">
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="5" t="inlineStr">
         <is>
           <t>묶음 61 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[4]/a[1]|text</t>
         </is>
@@ -14756,12 +15372,13 @@
         </is>
       </c>
       <c r="G26" s="7" t="n"/>
-      <c r="H26" s="5" t="inlineStr">
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="5" t="inlineStr">
         <is>
           <t>묶음 62 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[4]/a[2]|text</t>
         </is>
@@ -14795,12 +15412,13 @@
         </is>
       </c>
       <c r="G27" s="7" t="n"/>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" s="8" t="n"/>
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>묶음 63 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[4]/a[3]|text</t>
         </is>
@@ -14833,13 +15451,14 @@
           <t>01234567890123456789-0123456789</t>
         </is>
       </c>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="5" t="inlineStr">
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="5" t="inlineStr">
         <is>
           <t>묶음 18 — 같은 문구 4 곳</t>
         </is>
       </c>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[1]/span|text</t>
         </is>
@@ -14871,8 +15490,9 @@
         </is>
       </c>
       <c r="G29" s="7" t="n"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[1]/img|alt</t>
         </is>
@@ -14904,8 +15524,9 @@
         </is>
       </c>
       <c r="G30" s="7" t="n"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[2]/img|alt</t>
         </is>
@@ -14939,12 +15560,13 @@
         </is>
       </c>
       <c r="G31" s="7" t="n"/>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H31" s="8" t="n"/>
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>묶음 19 — 같은 문구 18 곳</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[3]/span|text</t>
         </is>
@@ -14978,12 +15600,13 @@
         </is>
       </c>
       <c r="G32" s="7" t="n"/>
-      <c r="H32" s="5" t="inlineStr">
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="5" t="inlineStr">
         <is>
           <t>묶음 19 — 같은 문구 18 곳</t>
         </is>
       </c>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[4]/span|text</t>
         </is>
@@ -15015,8 +15638,9 @@
         </is>
       </c>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[5]/img|alt</t>
         </is>
@@ -15050,12 +15674,13 @@
         </is>
       </c>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="5" t="inlineStr">
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="5" t="inlineStr">
         <is>
           <t>묶음 19 — 같은 문구 18 곳</t>
         </is>
       </c>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[6]/span|text</t>
         </is>
@@ -15087,8 +15712,9 @@
         </is>
       </c>
       <c r="G35" s="7" t="n"/>
-      <c r="H35" s="5" t="inlineStr"/>
-      <c r="I35" s="8" t="inlineStr">
+      <c r="H35" s="8" t="n"/>
+      <c r="I35" s="5" t="inlineStr"/>
+      <c r="J35" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[7]/img|alt</t>
         </is>
@@ -15122,12 +15748,13 @@
         </is>
       </c>
       <c r="G36" s="7" t="n"/>
-      <c r="H36" s="5" t="inlineStr">
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="5" t="inlineStr">
         <is>
           <t>묶음 19 — 같은 문구 18 곳</t>
         </is>
       </c>
-      <c r="I36" s="8" t="inlineStr">
+      <c r="J36" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[8]/span|text</t>
         </is>
@@ -15161,12 +15788,13 @@
         </is>
       </c>
       <c r="G37" s="7" t="n"/>
-      <c r="H37" s="5" t="inlineStr">
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="5" t="inlineStr">
         <is>
           <t>묶음 19 — 같은 문구 18 곳</t>
         </is>
       </c>
-      <c r="I37" s="8" t="inlineStr">
+      <c r="J37" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[9]/span|text</t>
         </is>
@@ -15200,12 +15828,13 @@
         </is>
       </c>
       <c r="G38" s="7" t="n"/>
-      <c r="H38" s="5" t="inlineStr">
+      <c r="H38" s="8" t="n"/>
+      <c r="I38" s="5" t="inlineStr">
         <is>
           <t>묶음 55 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I38" s="8" t="inlineStr">
+      <c r="J38" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/h2|text</t>
         </is>
@@ -15237,8 +15866,9 @@
         </is>
       </c>
       <c r="G39" s="7" t="n"/>
-      <c r="H39" s="5" t="inlineStr"/>
-      <c r="I39" s="8" t="inlineStr">
+      <c r="H39" s="8" t="n"/>
+      <c r="I39" s="5" t="inlineStr"/>
+      <c r="J39" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[1]|text</t>
         </is>
@@ -15270,8 +15900,9 @@
         </is>
       </c>
       <c r="G40" s="7" t="n"/>
-      <c r="H40" s="5" t="inlineStr"/>
-      <c r="I40" s="8" t="inlineStr">
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="5" t="inlineStr"/>
+      <c r="J40" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[2]|text</t>
         </is>
@@ -15303,8 +15934,9 @@
         </is>
       </c>
       <c r="G41" s="7" t="n"/>
-      <c r="H41" s="5" t="inlineStr"/>
-      <c r="I41" s="8" t="inlineStr">
+      <c r="H41" s="8" t="n"/>
+      <c r="I41" s="5" t="inlineStr"/>
+      <c r="J41" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[3]|text</t>
         </is>
@@ -15338,12 +15970,13 @@
         </is>
       </c>
       <c r="G42" s="7" t="n"/>
-      <c r="H42" s="5" t="inlineStr">
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="5" t="inlineStr">
         <is>
           <t>묶음 56 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I42" s="8" t="inlineStr">
+      <c r="J42" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/h2|text</t>
         </is>
@@ -15375,8 +16008,9 @@
         </is>
       </c>
       <c r="G43" s="7" t="n"/>
-      <c r="H43" s="5" t="inlineStr"/>
-      <c r="I43" s="8" t="inlineStr">
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="5" t="inlineStr"/>
+      <c r="J43" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[1]|text</t>
         </is>
@@ -15408,8 +16042,9 @@
         </is>
       </c>
       <c r="G44" s="7" t="n"/>
-      <c r="H44" s="5" t="inlineStr"/>
-      <c r="I44" s="8" t="inlineStr">
+      <c r="H44" s="8" t="n"/>
+      <c r="I44" s="5" t="inlineStr"/>
+      <c r="J44" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[2]|text</t>
         </is>
@@ -15443,12 +16078,13 @@
         </is>
       </c>
       <c r="G45" s="7" t="n"/>
-      <c r="H45" s="5" t="inlineStr">
+      <c r="H45" s="8" t="n"/>
+      <c r="I45" s="5" t="inlineStr">
         <is>
           <t>묶음 57 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I45" s="8" t="inlineStr">
+      <c r="J45" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/h2|text</t>
         </is>
@@ -15480,8 +16116,9 @@
         </is>
       </c>
       <c r="G46" s="7" t="n"/>
-      <c r="H46" s="5" t="inlineStr"/>
-      <c r="I46" s="8" t="inlineStr">
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="5" t="inlineStr"/>
+      <c r="J46" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[1]|text</t>
         </is>
@@ -15513,8 +16150,9 @@
         </is>
       </c>
       <c r="G47" s="7" t="n"/>
-      <c r="H47" s="5" t="inlineStr"/>
-      <c r="I47" s="8" t="inlineStr">
+      <c r="H47" s="8" t="n"/>
+      <c r="I47" s="5" t="inlineStr"/>
+      <c r="J47" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[2]|text</t>
         </is>
@@ -15548,12 +16186,13 @@
         </is>
       </c>
       <c r="G48" s="7" t="n"/>
-      <c r="H48" s="5" t="inlineStr">
+      <c r="H48" s="8" t="n"/>
+      <c r="I48" s="5" t="inlineStr">
         <is>
           <t>묶음 58 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I48" s="8" t="inlineStr">
+      <c r="J48" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/h2|text</t>
         </is>
@@ -15585,8 +16224,9 @@
         </is>
       </c>
       <c r="G49" s="7" t="n"/>
-      <c r="H49" s="5" t="inlineStr"/>
-      <c r="I49" s="8" t="inlineStr">
+      <c r="H49" s="8" t="n"/>
+      <c r="I49" s="5" t="inlineStr"/>
+      <c r="J49" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[1]|text</t>
         </is>
@@ -15618,8 +16258,9 @@
         </is>
       </c>
       <c r="G50" s="7" t="n"/>
-      <c r="H50" s="5" t="inlineStr"/>
-      <c r="I50" s="8" t="inlineStr">
+      <c r="H50" s="8" t="n"/>
+      <c r="I50" s="5" t="inlineStr"/>
+      <c r="J50" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[2]|text</t>
         </is>
@@ -15653,12 +16294,13 @@
         </is>
       </c>
       <c r="G51" s="7" t="n"/>
-      <c r="H51" s="5" t="inlineStr">
+      <c r="H51" s="8" t="n"/>
+      <c r="I51" s="5" t="inlineStr">
         <is>
           <t>묶음 59 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I51" s="8" t="inlineStr">
+      <c r="J51" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[1]/h2|text</t>
         </is>
@@ -15690,8 +16332,13 @@
         </is>
       </c>
       <c r="G52" s="7" t="n"/>
-      <c r="H52" s="5" t="inlineStr"/>
-      <c r="I52" s="8" t="inlineStr">
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>PICKLE Station</t>
+        </is>
+      </c>
+      <c r="I52" s="5" t="inlineStr"/>
+      <c r="J52" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[1]/p|text</t>
         </is>
@@ -15723,8 +16370,9 @@
         </is>
       </c>
       <c r="G53" s="7" t="n"/>
-      <c r="H53" s="5" t="inlineStr"/>
-      <c r="I53" s="8" t="inlineStr">
+      <c r="H53" s="8" t="n"/>
+      <c r="I53" s="5" t="inlineStr"/>
+      <c r="J53" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[2]/p[1]|text</t>
         </is>
@@ -15756,8 +16404,9 @@
         </is>
       </c>
       <c r="G54" s="7" t="n"/>
-      <c r="H54" s="5" t="inlineStr"/>
-      <c r="I54" s="8" t="inlineStr">
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="5" t="inlineStr"/>
+      <c r="J54" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[2]/p[2]|text</t>
         </is>
@@ -15789,8 +16438,9 @@
         </is>
       </c>
       <c r="G55" s="7" t="n"/>
-      <c r="H55" s="5" t="inlineStr"/>
-      <c r="I55" s="8" t="inlineStr">
+      <c r="H55" s="8" t="n"/>
+      <c r="I55" s="5" t="inlineStr"/>
+      <c r="J55" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[2]/p[3]|text</t>
         </is>
@@ -15824,12 +16474,13 @@
         </is>
       </c>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="5" t="inlineStr">
+      <c r="H56" s="8" t="n"/>
+      <c r="I56" s="5" t="inlineStr">
         <is>
           <t>묶음 60 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I56" s="8" t="inlineStr">
+      <c r="J56" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/h2|text</t>
         </is>
@@ -15863,12 +16514,13 @@
         </is>
       </c>
       <c r="G57" s="7" t="n"/>
-      <c r="H57" s="5" t="inlineStr">
+      <c r="H57" s="8" t="n"/>
+      <c r="I57" s="5" t="inlineStr">
         <is>
           <t>묶음 64 — 같은 문구 3 곳</t>
         </is>
       </c>
-      <c r="I57" s="8" t="inlineStr">
+      <c r="J57" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p|text</t>
         </is>
@@ -15902,12 +16554,13 @@
         </is>
       </c>
       <c r="G58" s="7" t="n"/>
-      <c r="H58" s="5" t="inlineStr">
+      <c r="H58" s="8" t="n"/>
+      <c r="I58" s="5" t="inlineStr">
         <is>
           <t>묶음 61 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I58" s="8" t="inlineStr">
+      <c r="J58" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/h2|text</t>
         </is>
@@ -15939,8 +16592,9 @@
         </is>
       </c>
       <c r="G59" s="7" t="n"/>
-      <c r="H59" s="5" t="inlineStr"/>
-      <c r="I59" s="8" t="inlineStr">
+      <c r="H59" s="8" t="n"/>
+      <c r="I59" s="5" t="inlineStr"/>
+      <c r="J59" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[1]|text</t>
         </is>
@@ -15972,8 +16626,9 @@
         </is>
       </c>
       <c r="G60" s="7" t="n"/>
-      <c r="H60" s="5" t="inlineStr"/>
-      <c r="I60" s="8" t="inlineStr">
+      <c r="H60" s="8" t="n"/>
+      <c r="I60" s="5" t="inlineStr"/>
+      <c r="J60" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[2]|text</t>
         </is>
@@ -16005,8 +16660,9 @@
         </is>
       </c>
       <c r="G61" s="7" t="n"/>
-      <c r="H61" s="5" t="inlineStr"/>
-      <c r="I61" s="8" t="inlineStr">
+      <c r="H61" s="8" t="n"/>
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[3]|text</t>
         </is>
@@ -16040,12 +16696,13 @@
         </is>
       </c>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="5" t="inlineStr">
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="5" t="inlineStr">
         <is>
           <t>묶음 62 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I62" s="8" t="inlineStr">
+      <c r="J62" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/h2|text</t>
         </is>
@@ -16079,12 +16736,13 @@
         </is>
       </c>
       <c r="G63" s="7" t="n"/>
-      <c r="H63" s="5" t="inlineStr">
+      <c r="H63" s="8" t="n"/>
+      <c r="I63" s="5" t="inlineStr">
         <is>
           <t>묶음 64 — 같은 문구 3 곳</t>
         </is>
       </c>
-      <c r="I63" s="8" t="inlineStr">
+      <c r="J63" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p|text</t>
         </is>
@@ -16118,12 +16776,13 @@
         </is>
       </c>
       <c r="G64" s="7" t="n"/>
-      <c r="H64" s="5" t="inlineStr">
+      <c r="H64" s="8" t="n"/>
+      <c r="I64" s="5" t="inlineStr">
         <is>
           <t>묶음 63 — 같은 문구 2 곳</t>
         </is>
       </c>
-      <c r="I64" s="8" t="inlineStr">
+      <c r="J64" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/h2|text</t>
         </is>
@@ -16157,19 +16816,20 @@
         </is>
       </c>
       <c r="G65" s="7" t="n"/>
-      <c r="H65" s="5" t="inlineStr">
+      <c r="H65" s="8" t="n"/>
+      <c r="I65" s="5" t="inlineStr">
         <is>
           <t>묶음 64 — 같은 문구 3 곳</t>
         </is>
       </c>
-      <c r="I65" s="8" t="inlineStr">
+      <c r="J65" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p|text</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I65"/>
+  <autoFilter ref="A1:J65"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -16180,18 +16840,19 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I34"/>
+  <dimension ref="A1:J34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
-    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
     <col width="16" customWidth="1" min="3" max="3"/>
     <col width="8" customWidth="1" min="4" max="4"/>
     <col width="6" customWidth="1" min="5" max="5"/>
-    <col width="62" customWidth="1" min="6" max="6"/>
-    <col width="62" customWidth="1" min="7" max="7"/>
-    <col width="22" customWidth="1" min="8" max="8"/>
-    <col width="46" customWidth="1" min="9" max="9"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="54" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
   </cols>
   <sheetData>
     <row r="1" ht="24" customHeight="1">
@@ -16232,10 +16893,15 @@
       </c>
       <c r="H1" s="4" t="inlineStr">
         <is>
+          <t>영문 문구</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
           <t>비고</t>
         </is>
       </c>
-      <c r="I1" s="4" t="inlineStr">
+      <c r="J1" s="4" t="inlineStr">
         <is>
           <t>자리표(건드리지 마세요)</t>
         </is>
@@ -16267,8 +16933,9 @@
         </is>
       </c>
       <c r="G2" s="7" t="n"/>
-      <c r="H2" s="5" t="inlineStr"/>
-      <c r="I2" s="8" t="inlineStr">
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="5" t="inlineStr"/>
+      <c r="J2" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[1]/div/div/h1/span[1]|text</t>
         </is>
@@ -16300,8 +16967,13 @@
         </is>
       </c>
       <c r="G3" s="7" t="n"/>
-      <c r="H3" s="5" t="inlineStr"/>
-      <c r="I3" s="8" t="inlineStr">
+      <c r="H3" s="8" t="inlineStr">
+        <is>
+          <t>GaN Power Semiconductors</t>
+        </is>
+      </c>
+      <c r="I3" s="5" t="inlineStr"/>
+      <c r="J3" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[1]/div/div/h1/span[2]|text</t>
         </is>
@@ -16333,8 +17005,9 @@
         </is>
       </c>
       <c r="G4" s="7" t="n"/>
-      <c r="H4" s="5" t="inlineStr"/>
-      <c r="I4" s="8" t="inlineStr">
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="5" t="inlineStr"/>
+      <c r="J4" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[1]/p/span[1]|text</t>
         </is>
@@ -16366,8 +17039,9 @@
         </is>
       </c>
       <c r="G5" s="7" t="n"/>
-      <c r="H5" s="5" t="inlineStr"/>
-      <c r="I5" s="8" t="inlineStr">
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="5" t="inlineStr"/>
+      <c r="J5" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[1]/p/span[2]|text</t>
         </is>
@@ -16399,8 +17073,9 @@
         </is>
       </c>
       <c r="G6" s="7" t="n"/>
-      <c r="H6" s="5" t="inlineStr"/>
-      <c r="I6" s="8" t="inlineStr">
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[1]/div/img|alt</t>
         </is>
@@ -16434,12 +17109,13 @@
         </is>
       </c>
       <c r="G7" s="7" t="n"/>
-      <c r="H7" s="5" t="inlineStr">
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="5" t="inlineStr">
         <is>
           <t>묶음 65 — 같은 문구 4 곳</t>
         </is>
       </c>
-      <c r="I7" s="8" t="inlineStr">
+      <c r="J7" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[2]/ul/li[1]/p|text</t>
         </is>
@@ -16471,8 +17147,13 @@
         </is>
       </c>
       <c r="G8" s="7" t="n"/>
-      <c r="H8" s="5" t="inlineStr"/>
-      <c r="I8" s="8" t="inlineStr">
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>GaN Power Device</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr"/>
+      <c r="J8" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[2]/ul/li[2]/p|text</t>
         </is>
@@ -16504,8 +17185,9 @@
         </is>
       </c>
       <c r="G9" s="7" t="n"/>
-      <c r="H9" s="5" t="inlineStr"/>
-      <c r="I9" s="8" t="inlineStr">
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/div[2]/ul/li[3]/p|text</t>
         </is>
@@ -16538,13 +17220,14 @@
           <t>01</t>
         </is>
       </c>
-      <c r="G10" s="7" t="n"/>
-      <c r="H10" s="5" t="inlineStr">
+      <c r="G10" s="6" t="n"/>
+      <c r="H10" s="6" t="n"/>
+      <c r="I10" s="5" t="inlineStr">
         <is>
           <t>묶음 5 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I10" s="8" t="inlineStr">
+      <c r="J10" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[1]/p/span[1]|text</t>
         </is>
@@ -16578,12 +17261,13 @@
         </is>
       </c>
       <c r="G11" s="7" t="n"/>
-      <c r="H11" s="5" t="inlineStr">
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="5" t="inlineStr">
         <is>
           <t>묶음 65 — 같은 문구 4 곳</t>
         </is>
       </c>
-      <c r="I11" s="8" t="inlineStr">
+      <c r="J11" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[1]/p/span[2]|text</t>
         </is>
@@ -16617,12 +17301,13 @@
         </is>
       </c>
       <c r="G12" s="7" t="n"/>
-      <c r="H12" s="5" t="inlineStr">
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="5" t="inlineStr">
         <is>
           <t>묶음 65 — 같은 문구 4 곳</t>
         </is>
       </c>
-      <c r="I12" s="8" t="inlineStr">
+      <c r="J12" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[1]/a|text</t>
         </is>
@@ -16655,13 +17340,14 @@
           <t>02</t>
         </is>
       </c>
-      <c r="G13" s="7" t="n"/>
-      <c r="H13" s="5" t="inlineStr">
+      <c r="G13" s="6" t="n"/>
+      <c r="H13" s="6" t="n"/>
+      <c r="I13" s="5" t="inlineStr">
         <is>
           <t>묶음 8 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I13" s="8" t="inlineStr">
+      <c r="J13" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[2]/p/span[1]|text</t>
         </is>
@@ -16695,12 +17381,13 @@
         </is>
       </c>
       <c r="G14" s="7" t="n"/>
-      <c r="H14" s="5" t="inlineStr">
+      <c r="H14" s="8" t="n"/>
+      <c r="I14" s="5" t="inlineStr">
         <is>
           <t>묶음 66 — 같은 문구 3 곳</t>
         </is>
       </c>
-      <c r="I14" s="8" t="inlineStr">
+      <c r="J14" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[2]/p/span[2]|text</t>
         </is>
@@ -16734,12 +17421,13 @@
         </is>
       </c>
       <c r="G15" s="7" t="n"/>
-      <c r="H15" s="5" t="inlineStr">
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="5" t="inlineStr">
         <is>
           <t>묶음 66 — 같은 문구 3 곳</t>
         </is>
       </c>
-      <c r="I15" s="8" t="inlineStr">
+      <c r="J15" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[2]/a|text</t>
         </is>
@@ -16772,13 +17460,14 @@
           <t>03</t>
         </is>
       </c>
-      <c r="G16" s="7" t="n"/>
-      <c r="H16" s="5" t="inlineStr">
+      <c r="G16" s="6" t="n"/>
+      <c r="H16" s="6" t="n"/>
+      <c r="I16" s="5" t="inlineStr">
         <is>
           <t>묶음 10 — 같은 문구 12 곳</t>
         </is>
       </c>
-      <c r="I16" s="8" t="inlineStr">
+      <c r="J16" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[3]/p/span[1]|text</t>
         </is>
@@ -16812,12 +17501,13 @@
         </is>
       </c>
       <c r="G17" s="7" t="n"/>
-      <c r="H17" s="5" t="inlineStr">
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="5" t="inlineStr">
         <is>
           <t>묶음 67 — 같은 문구 3 곳</t>
         </is>
       </c>
-      <c r="I17" s="8" t="inlineStr">
+      <c r="J17" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[3]/p/span[2]|text</t>
         </is>
@@ -16851,12 +17541,13 @@
         </is>
       </c>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="5" t="inlineStr">
+      <c r="H18" s="8" t="n"/>
+      <c r="I18" s="5" t="inlineStr">
         <is>
           <t>묶음 67 — 같은 문구 3 곳</t>
         </is>
       </c>
-      <c r="I18" s="8" t="inlineStr">
+      <c r="J18" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[3]/a|text</t>
         </is>
@@ -16889,13 +17580,14 @@
           <t>01234567890123456789-0123456789</t>
         </is>
       </c>
-      <c r="G19" s="7" t="n"/>
-      <c r="H19" s="5" t="inlineStr">
+      <c r="G19" s="6" t="n"/>
+      <c r="H19" s="6" t="n"/>
+      <c r="I19" s="5" t="inlineStr">
         <is>
           <t>묶음 18 — 같은 문구 4 곳</t>
         </is>
       </c>
-      <c r="I19" s="8" t="inlineStr">
+      <c r="J19" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[1]/span|text</t>
         </is>
@@ -16929,12 +17621,13 @@
         </is>
       </c>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="5" t="inlineStr">
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="5" t="inlineStr">
         <is>
           <t>묶음 19 — 같은 문구 18 곳</t>
         </is>
       </c>
-      <c r="I20" s="8" t="inlineStr">
+      <c r="J20" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[1]/span|text</t>
         </is>
@@ -16968,12 +17661,13 @@
         </is>
       </c>
       <c r="G21" s="7" t="n"/>
-      <c r="H21" s="5" t="inlineStr">
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="5" t="inlineStr">
         <is>
           <t>묶음 19 — 같은 문구 18 곳</t>
         </is>
       </c>
-      <c r="I21" s="8" t="inlineStr">
+      <c r="J21" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[2]/span|text</t>
         </is>
@@ -17007,12 +17701,13 @@
         </is>
       </c>
       <c r="G22" s="7" t="n"/>
-      <c r="H22" s="5" t="inlineStr">
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="5" t="inlineStr">
         <is>
           <t>묶음 19 — 같은 문구 18 곳</t>
         </is>
       </c>
-      <c r="I22" s="8" t="inlineStr">
+      <c r="J22" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[3]/span|text</t>
         </is>
@@ -17046,12 +17741,13 @@
         </is>
       </c>
       <c r="G23" s="7" t="n"/>
-      <c r="H23" s="5" t="inlineStr">
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="5" t="inlineStr">
         <is>
           <t>묶음 65 — 같은 문구 4 곳</t>
         </is>
       </c>
-      <c r="I23" s="8" t="inlineStr">
+      <c r="J23" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/h2|text</t>
         </is>
@@ -17083,8 +17779,9 @@
         </is>
       </c>
       <c r="G24" s="7" t="n"/>
-      <c r="H24" s="5" t="inlineStr"/>
-      <c r="I24" s="8" t="inlineStr">
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="5" t="inlineStr"/>
+      <c r="J24" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[1]|text</t>
         </is>
@@ -17116,8 +17813,9 @@
         </is>
       </c>
       <c r="G25" s="7" t="n"/>
-      <c r="H25" s="5" t="inlineStr"/>
-      <c r="I25" s="8" t="inlineStr">
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="5" t="inlineStr"/>
+      <c r="J25" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[2]|text</t>
         </is>
@@ -17149,8 +17847,9 @@
         </is>
       </c>
       <c r="G26" s="7" t="n"/>
-      <c r="H26" s="5" t="inlineStr"/>
-      <c r="I26" s="8" t="inlineStr">
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[3]|text</t>
         </is>
@@ -17184,12 +17883,13 @@
         </is>
       </c>
       <c r="G27" s="7" t="n"/>
-      <c r="H27" s="5" t="inlineStr">
+      <c r="H27" s="8" t="n"/>
+      <c r="I27" s="5" t="inlineStr">
         <is>
           <t>묶음 66 — 같은 문구 3 곳</t>
         </is>
       </c>
-      <c r="I27" s="8" t="inlineStr">
+      <c r="J27" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/h2|text</t>
         </is>
@@ -17221,8 +17921,9 @@
         </is>
       </c>
       <c r="G28" s="7" t="n"/>
-      <c r="H28" s="5" t="inlineStr"/>
-      <c r="I28" s="8" t="inlineStr">
+      <c r="H28" s="8" t="n"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[1]|text</t>
         </is>
@@ -17254,8 +17955,9 @@
         </is>
       </c>
       <c r="G29" s="7" t="n"/>
-      <c r="H29" s="5" t="inlineStr"/>
-      <c r="I29" s="8" t="inlineStr">
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[2]|text</t>
         </is>
@@ -17287,8 +17989,9 @@
         </is>
       </c>
       <c r="G30" s="7" t="n"/>
-      <c r="H30" s="5" t="inlineStr"/>
-      <c r="I30" s="8" t="inlineStr">
+      <c r="H30" s="8" t="n"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[3]|text</t>
         </is>
@@ -17322,12 +18025,13 @@
         </is>
       </c>
       <c r="G31" s="7" t="n"/>
-      <c r="H31" s="5" t="inlineStr">
+      <c r="H31" s="8" t="n"/>
+      <c r="I31" s="5" t="inlineStr">
         <is>
           <t>묶음 67 — 같은 문구 3 곳</t>
         </is>
       </c>
-      <c r="I31" s="8" t="inlineStr">
+      <c r="J31" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/h2|text</t>
         </is>
@@ -17359,8 +18063,9 @@
         </is>
       </c>
       <c r="G32" s="7" t="n"/>
-      <c r="H32" s="5" t="inlineStr"/>
-      <c r="I32" s="8" t="inlineStr">
+      <c r="H32" s="8" t="n"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[1]|text</t>
         </is>
@@ -17392,8 +18097,9 @@
         </is>
       </c>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="5" t="inlineStr"/>
-      <c r="I33" s="8" t="inlineStr">
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[2]|text</t>
         </is>
@@ -17425,15 +18131,16 @@
         </is>
       </c>
       <c r="G34" s="7" t="n"/>
-      <c r="H34" s="5" t="inlineStr"/>
-      <c r="I34" s="8" t="inlineStr">
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="5" t="inlineStr"/>
+      <c r="J34" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:I34"/>
+  <autoFilter ref="A1:J34"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/content-export/04_사업영역_문구.xlsx
+++ b/content-export/04_사업영역_문구.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화합물 전력 반도체" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$J$128</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$J$130</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'에너지 솔루션'!$A$1:$J$228</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'인공지능 플랫폼'!$A$1:$J$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'화합물 전력 반도체'!$A$1:$J$34</definedName>
@@ -527,7 +527,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 451 줄입니다.</t>
+          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 453 줄입니다.</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J128"/>
+  <dimension ref="A1:J130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1014,7 +1014,11 @@
         </is>
       </c>
       <c r="G8" s="7" t="n"/>
-      <c r="H8" s="8" t="n"/>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>Cycler(Cell&amp;Module)</t>
+        </is>
+      </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
           <t>묶음 2 — 같은 문구 4 곳</t>
@@ -1342,7 +1346,11 @@
         </is>
       </c>
       <c r="G16" s="7" t="n"/>
-      <c r="H16" s="8" t="n"/>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>Cycler(Cell&amp;Module)</t>
+        </is>
+      </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>묶음 2 — 같은 문구 4 곳</t>
@@ -1506,7 +1514,11 @@
         </is>
       </c>
       <c r="G20" s="7" t="n"/>
-      <c r="H20" s="8" t="n"/>
+      <c r="H20" s="8" t="inlineStr">
+        <is>
+          <t>Automation System</t>
+        </is>
+      </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
           <t>묶음 10 — 같은 문구 2 곳</t>
@@ -1660,7 +1672,11 @@
         </is>
       </c>
       <c r="G24" s="7" t="n"/>
-      <c r="H24" s="8" t="n"/>
+      <c r="H24" s="8" t="inlineStr">
+        <is>
+          <t>Carbon Nano Tube</t>
+        </is>
+      </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
           <t>묶음 12 — 같은 문구 2 곳</t>
@@ -1700,7 +1716,11 @@
         </is>
       </c>
       <c r="G25" s="7" t="n"/>
-      <c r="H25" s="8" t="n"/>
+      <c r="H25" s="8" t="inlineStr">
+        <is>
+          <t>Electrolyte</t>
+        </is>
+      </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
           <t>묶음 13 — 같은 문구 2 곳</t>
@@ -1740,7 +1760,11 @@
         </is>
       </c>
       <c r="G26" s="7" t="n"/>
-      <c r="H26" s="8" t="n"/>
+      <c r="H26" s="8" t="inlineStr">
+        <is>
+          <t>HNBR Binder</t>
+        </is>
+      </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
           <t>묶음 14 — 같은 문구 2 곳</t>
@@ -1780,7 +1804,11 @@
         </is>
       </c>
       <c r="G27" s="7" t="n"/>
-      <c r="H27" s="8" t="n"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Pouch Cell Manufacturing</t>
+        </is>
+      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>묶음 15 — 같은 문구 2 곳</t>
@@ -2517,7 +2545,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>작은 제목</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -2528,17 +2556,11 @@
       <c r="E48" s="5" t="inlineStr"/>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>독보적인 기술력으로 완성하는 이차전지 활성화 통합 솔루션
-에이프로는 이차전지 활성화(Formation) 공정 전체 설비의 자체 제작 기술을 보유한 리딩 기업입니다. 공정에 필요한 모든 설비를 직접 생산하여 국내외 유수의 고객사에 안정적으로 공급하고 있습니다.</t>
+          <t>독보적인 기술력으로 완성하는 이차전지 활성화 통합 솔루션</t>
         </is>
       </c>
       <c r="G48" s="7" t="n"/>
-      <c r="H48" s="8" t="inlineStr">
-        <is>
-          <t>An Integrated Formation Solution Built on Proprietary Battery Technology 
-A-PRO is a leading enterprise with proprietary technology for manufacturing the entire spectrum of secondary battery formation process equipment. We directly produce and reliably supply essential equipment required for the formation process to premier domestic and international customers.</t>
-        </is>
-      </c>
+      <c r="H48" s="8" t="n"/>
       <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="9" t="inlineStr">
         <is>
@@ -2568,15 +2590,11 @@
       <c r="E49" s="5" t="inlineStr"/>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>당사는 독보적인 정밀 충·방전 기술과 고도화된 자동화 역량을 기반으로, 배터리 셀 활성화 공정 전반을 아우르는 '통합 자동화 솔루션'을 제공합니다. 더불어 각 공정에서 발생하는 전압, 전류, 온도 등의 핵심 데이터를 정밀하게 측정하고 체계적으로 관리함으로써, 배터리 셀의 완성도 높은 품질과 생산 안정성을 극대화합니다.</t>
+          <t>에이프로는 이차전지 활성화(Formation) 공정 전체 설비의 자체 제작 기술을 보유한 리딩 기업입니다. 공정에 필요한 모든 설비를 직접 생산하여 국내외 유수의 고객사에 안정적으로 공급하고 있습니다.</t>
         </is>
       </c>
       <c r="G49" s="7" t="n"/>
-      <c r="H49" s="8" t="inlineStr">
-        <is>
-          <t>Based on our unrivaled precision charge-discharge technology and advanced automation capabilities, we deliver comprehensive 'integrated automation solutions' that encompass the entire battery cell formation process. Furthermore, we precisely measure and systematically manage critical data—such as voltage, current, and temperature generated during each stage—to maximize the seamless quality and production stability of battery cells.</t>
-        </is>
-      </c>
+      <c r="H49" s="8" t="n"/>
       <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="9" t="inlineStr">
         <is>
@@ -2595,32 +2613,30 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="E50" s="5" t="n">
-        <v>5</v>
-      </c>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E50" s="5" t="inlineStr"/>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="G50" s="6" t="n"/>
-      <c r="H50" s="6" t="n"/>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>묶음 5 — 같은 문구 12 곳</t>
-        </is>
-      </c>
+          <t>당사는 독보적인 정밀 충·방전 기술과 고도화된 자동화 역량을 기반으로, 배터리 셀 활성화 공정 전반을 아우르는 '통합 자동화 솔루션'을 제공합니다. 더불어 각 공정에서 발생하는 전압, 전류, 온도 등의 핵심 데이터를 정밀하게 측정하고 체계적으로 관리함으로써, 배터리 셀의 완성도 높은 품질과 생산 안정성을 극대화합니다.</t>
+        </is>
+      </c>
+      <c r="G50" s="7" t="n"/>
+      <c r="H50" s="8" t="inlineStr">
+        <is>
+          <t>Based on our unrivaled precision charge-discharge technology and advanced automation capabilities, we deliver comprehensive 'integrated automation solutions' that encompass the entire battery cell formation process. Furthermore, we precisely measure and systematically manage critical data—such as voltage, current, and temperature generated during each stage—to maximize the seamless quality and production stability of battery cells.</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[1]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -2635,26 +2651,32 @@
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E51" s="5" t="inlineStr"/>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>1차 충전</t>
-        </is>
-      </c>
-      <c r="G51" s="7" t="n"/>
-      <c r="H51" s="8" t="n"/>
-      <c r="I51" s="5" t="inlineStr"/>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="G51" s="6" t="n"/>
+      <c r="H51" s="6" t="n"/>
+      <c r="I51" s="5" t="inlineStr">
+        <is>
+          <t>묶음 5 — 같은 문구 12 곳</t>
+        </is>
+      </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[1]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[1]/b|text</t>
         </is>
       </c>
     </row>
@@ -2669,32 +2691,26 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>8</v>
-      </c>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="inlineStr"/>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="G52" s="6" t="n"/>
-      <c r="H52" s="6" t="n"/>
-      <c r="I52" s="5" t="inlineStr">
-        <is>
-          <t>묶음 8 — 같은 문구 12 곳</t>
-        </is>
-      </c>
+          <t>1차 충전</t>
+        </is>
+      </c>
+      <c r="G52" s="7" t="n"/>
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[2]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[1]/span|text</t>
         </is>
       </c>
     </row>
@@ -2709,26 +2725,32 @@
       </c>
       <c r="C53" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="inlineStr"/>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>8</v>
+      </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>디개싱 공정</t>
-        </is>
-      </c>
-      <c r="G53" s="7" t="n"/>
-      <c r="H53" s="8" t="n"/>
-      <c r="I53" s="5" t="inlineStr"/>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="G53" s="6" t="n"/>
+      <c r="H53" s="6" t="n"/>
+      <c r="I53" s="5" t="inlineStr">
+        <is>
+          <t>묶음 8 — 같은 문구 12 곳</t>
+        </is>
+      </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[2]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[2]/b|text</t>
         </is>
       </c>
     </row>
@@ -2743,32 +2765,26 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="E54" s="5" t="n">
-        <v>9</v>
-      </c>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E54" s="5" t="inlineStr"/>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="G54" s="6" t="n"/>
-      <c r="H54" s="6" t="n"/>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>묶음 9 — 같은 문구 12 곳</t>
-        </is>
-      </c>
+          <t>디개싱 공정</t>
+        </is>
+      </c>
+      <c r="G54" s="7" t="n"/>
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[3]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[2]/span|text</t>
         </is>
       </c>
     </row>
@@ -2783,26 +2799,32 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E55" s="5" t="inlineStr"/>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E55" s="5" t="n">
+        <v>9</v>
+      </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>에이징 공정</t>
-        </is>
-      </c>
-      <c r="G55" s="7" t="n"/>
-      <c r="H55" s="8" t="n"/>
-      <c r="I55" s="5" t="inlineStr"/>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="G55" s="6" t="n"/>
+      <c r="H55" s="6" t="n"/>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>묶음 9 — 같은 문구 12 곳</t>
+        </is>
+      </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[3]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[3]/b|text</t>
         </is>
       </c>
     </row>
@@ -2817,32 +2839,26 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>11</v>
-      </c>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E56" s="5" t="inlineStr"/>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="G56" s="6" t="n"/>
-      <c r="H56" s="6" t="n"/>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>묶음 11 — 같은 문구 9 곳</t>
-        </is>
-      </c>
+          <t>에이징 공정</t>
+        </is>
+      </c>
+      <c r="G56" s="7" t="n"/>
+      <c r="H56" s="8" t="n"/>
+      <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[4]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[3]/span|text</t>
         </is>
       </c>
     </row>
@@ -2857,26 +2873,32 @@
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="inlineStr"/>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="n">
+        <v>11</v>
+      </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>충·방전</t>
-        </is>
-      </c>
-      <c r="G57" s="7" t="n"/>
-      <c r="H57" s="8" t="n"/>
-      <c r="I57" s="5" t="inlineStr"/>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="G57" s="6" t="n"/>
+      <c r="H57" s="6" t="n"/>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>묶음 11 — 같은 문구 9 곳</t>
+        </is>
+      </c>
       <c r="J57" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[4]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[4]/b|text</t>
         </is>
       </c>
     </row>
@@ -2891,32 +2913,26 @@
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>18</v>
-      </c>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="inlineStr"/>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="G58" s="6" t="n"/>
-      <c r="H58" s="6" t="n"/>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>묶음 18 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+          <t>충·방전</t>
+        </is>
+      </c>
+      <c r="G58" s="7" t="n"/>
+      <c r="H58" s="8" t="n"/>
+      <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[5]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[4]/span|text</t>
         </is>
       </c>
     </row>
@@ -2931,26 +2947,32 @@
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="inlineStr"/>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>18</v>
+      </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>품질 검사</t>
-        </is>
-      </c>
-      <c r="G59" s="7" t="n"/>
-      <c r="H59" s="8" t="n"/>
-      <c r="I59" s="5" t="inlineStr"/>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="G59" s="6" t="n"/>
+      <c r="H59" s="6" t="n"/>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>묶음 18 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J59" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[5]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[5]/b|text</t>
         </is>
       </c>
     </row>
@@ -2965,26 +2987,26 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E60" s="5" t="inlineStr"/>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="G60" s="6" t="n"/>
-      <c r="H60" s="6" t="n"/>
+          <t>품질 검사</t>
+        </is>
+      </c>
+      <c r="G60" s="7" t="n"/>
+      <c r="H60" s="8" t="n"/>
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[6]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[5]/span|text</t>
         </is>
       </c>
     </row>
@@ -2999,26 +3021,26 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E61" s="5" t="inlineStr"/>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>불량 선별</t>
-        </is>
-      </c>
-      <c r="G61" s="7" t="n"/>
-      <c r="H61" s="8" t="n"/>
+          <t>06</t>
+        </is>
+      </c>
+      <c r="G61" s="6" t="n"/>
+      <c r="H61" s="6" t="n"/>
       <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[6]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[6]/b|text</t>
         </is>
       </c>
     </row>
@@ -3028,12 +3050,12 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>01-2 글로벌 에이프로 네트워크</t>
+          <t>01-1 활성화 공정 &amp; 설비</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -3041,28 +3063,18 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E62" s="5" t="n">
-        <v>7</v>
-      </c>
+      <c r="E62" s="5" t="inlineStr"/>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>글로벌 에이프로 네트워크</t>
+          <t>불량 선별</t>
         </is>
       </c>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="8" t="inlineStr">
-        <is>
-          <t>Global A-PRO Network</t>
-        </is>
-      </c>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>묶음 7 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[6]/span|text</t>
         </is>
       </c>
     </row>
@@ -3077,7 +3089,7 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -3085,22 +3097,28 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E63" s="5" t="inlineStr"/>
+      <c r="E63" s="5" t="n">
+        <v>7</v>
+      </c>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>전 세계 배터리 생산의 중심, 에이프로 글로벌 네트워크</t>
+          <t>글로벌 에이프로 네트워크</t>
         </is>
       </c>
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>At the Heart of Global Battery Production: A-PRO’s Global Network</t>
-        </is>
-      </c>
-      <c r="I63" s="5" t="inlineStr"/>
+          <t>Global A-PRO Network</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>묶음 7 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J63" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -3115,7 +3133,7 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>작은 제목</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -3126,19 +3144,19 @@
       <c r="E64" s="5" t="inlineStr"/>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>글로벌 시장을 선도하는 고객사를 위해 미국 미시간, 폴란드, 중국 남경, 인도네시아에 현지 법인을 구축했습니다.</t>
+          <t>전 세계 배터리 생산의 중심, 에이프로 글로벌 네트워크</t>
         </is>
       </c>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>To support our global market-leading customers, we have established local subsidiaries in Michigan (USA), Poland, Nanjing (China), and Indonesia.</t>
+          <t>At the Heart of Global Battery Production: A-PRO’s Global Network</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3164,19 +3182,19 @@
       <c r="E65" s="5" t="inlineStr"/>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>현지에 상주하는 전문 엔지니어들이 셋업부터 유지보수까지 원스톱(One-stop)으로 지원하며, 안정적인 해외 거점을 바탕으로 고객사의 성공을 함께합니다.</t>
+          <t>글로벌 시장을 선도하는 고객사를 위해 미국 미시간, 폴란드, 중국 남경, 인도네시아에 현지 법인을 구축했습니다.</t>
         </is>
       </c>
       <c r="G65" s="7" t="n"/>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>Our on-site expert engineers provide one-stop service from setup to maintenance, ensuring customer success through our robust global network.</t>
+          <t>To support our global market-leading customers, we have established local subsidiaries in Michigan (USA), Poland, Nanjing (China), and Indonesia.</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr"/>
       <c r="J65" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3186,12 +3204,12 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>02-1 Cycler(Cell&amp;Module)</t>
+          <t>01-2 글로벌 에이프로 네트워크</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -3199,28 +3217,22 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E66" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="E66" s="5" t="inlineStr"/>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>Cycler(Cell&amp;Module)</t>
+          <t>현지에 상주하는 전문 엔지니어들이 셋업부터 유지보수까지 원스톱(One-stop)으로 지원하며, 안정적인 해외 거점을 바탕으로 고객사의 성공을 함께합니다.</t>
         </is>
       </c>
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>Cycler(Cell&amp;Module)</t>
-        </is>
-      </c>
-      <c r="I66" s="5" t="inlineStr">
-        <is>
-          <t>묶음 2 — 같은 문구 4 곳</t>
-        </is>
-      </c>
+          <t>Our on-site expert engineers provide one-stop service from setup to maintenance, ensuring customer success through our robust global network.</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -3235,7 +3247,7 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -3243,22 +3255,28 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E67" s="5" t="inlineStr"/>
+      <c r="E67" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>배터리의 미래를 검증하는 고효율 친환경 사이클러</t>
+          <t>Cycler(Cell&amp;Module)</t>
         </is>
       </c>
       <c r="G67" s="7" t="n"/>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>High-Efficiency Eco-Friendly Cyclers Validating the Future of Batteries</t>
-        </is>
-      </c>
-      <c r="I67" s="5" t="inlineStr"/>
+          <t>Cycler(Cell&amp;Module)</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>묶음 2 — 같은 문구 4 곳</t>
+        </is>
+      </c>
       <c r="J67" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -3273,7 +3291,7 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>작은 제목</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -3284,19 +3302,19 @@
       <c r="E68" s="5" t="inlineStr"/>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>에이프로의 이차전지 사이클러(Battery Cycler)는 독보적인 양방향 전력 제어와 에너지 회생 기술을 통해 배터리의 성능 평가를 최적화하고, 완벽한 제조 안정성을 확보합니다.</t>
+          <t>배터리의 미래를 검증하는 고효율 친환경 사이클러</t>
         </is>
       </c>
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>A-PRO’s Battery Cycler optimizes battery performance evaluation and ensures flawless manufacturing stability through unrivaled bidirectional power control and energy regeneration technology.</t>
+          <t>High-Efficiency Eco-Friendly Cyclers Validating the Future of Batteries</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3322,19 +3340,19 @@
       <c r="E69" s="5" t="inlineStr"/>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>에이프로의 이차전지 사이클러는 배터리를 반복적으로 충·방전하여 성능, 효율성, 수명을 정밀하게 평가하는 핵심 테스트 장비입니다. 용량, 수명 주기(Cycle Life), 내부 저항을 정밀 측정하고 실제 사용 환경을 완벽히 시뮬레이션하여, 연구 개발 및 제조 단계에서 발생할 수 있는 열화 현상과 안전 문제를 사전에 빈틈없이 검출합니다.</t>
+          <t>에이프로의 이차전지 사이클러(Battery Cycler)는 독보적인 양방향 전력 제어와 에너지 회생 기술을 통해 배터리의 성능 평가를 최적화하고, 완벽한 제조 안정성을 확보합니다.</t>
         </is>
       </c>
       <c r="G69" s="7" t="n"/>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>A-PRO’s Battery Cycler is an essential testing solution that precisely evaluates battery performance, efficiency, and lifespan through continuous charge and discharge cycles. By accurately measuring capacity, cycle life, and internal resistance, our cyclers replicate real-world operating conditions to flawlessly detect degradation and safety issues during the R&amp;D and manufacturing stages.</t>
+          <t>A-PRO’s Battery Cycler optimizes battery performance evaluation and ensures flawless manufacturing stability through unrivaled bidirectional power control and energy regeneration technology.</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3360,19 +3378,19 @@
       <c r="E70" s="5" t="inlineStr"/>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>특히 에이프로의 Cycler는 전류 공급(충전)과 흡수(방전)가 모두 가능한 양방향 전력 시스템과 혁신적인 에너지 회생(Regenerative) 기능을 탑재하고 있습니다. 방전 시 버려지는 에너지를 회수하여 전력망으로 되돌려주는 이 기술은 공장의 전력 낭비를 획기적으로 줄이고 냉각 부하를 저감하여, 가장 경제적이고 친환경적인 생산 환경을 완성합니다.</t>
+          <t>에이프로의 이차전지 사이클러는 배터리를 반복적으로 충·방전하여 성능, 효율성, 수명을 정밀하게 평가하는 핵심 테스트 장비입니다. 용량, 수명 주기(Cycle Life), 내부 저항을 정밀 측정하고 실제 사용 환경을 완벽히 시뮬레이션하여, 연구 개발 및 제조 단계에서 발생할 수 있는 열화 현상과 안전 문제를 사전에 빈틈없이 검출합니다.</t>
         </is>
       </c>
       <c r="G70" s="7" t="n"/>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>In particular, A-PRO’s Cycler features an advanced bidirectional system capable of both supplying (charging) and absorbing (discharging) current, integrated with innovative energy regeneration technology. By capturing energy released during discharge and feeding it back into the power grid, this technology drastically reduces power waste and cooling loads, enabling an exceptionally economical and eco-friendly production environment.</t>
+          <t>A-PRO’s Battery Cycler is an essential testing solution that precisely evaluates battery performance, efficiency, and lifespan through continuous charge and discharge cycles. By accurately measuring capacity, cycle life, and internal resistance, our cyclers replicate real-world operating conditions to flawlessly detect degradation and safety issues during the R&amp;D and manufacturing stages.</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr"/>
       <c r="J70" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[4]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -3382,12 +3400,12 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>03-1 자동화 설비</t>
+          <t>02-1 Cycler(Cell&amp;Module)</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -3395,28 +3413,22 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E71" s="5" t="n">
-        <v>10</v>
-      </c>
+      <c r="E71" s="5" t="inlineStr"/>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>자동화 설비</t>
+          <t>특히 에이프로의 Cycler는 전류 공급(충전)과 흡수(방전)가 모두 가능한 양방향 전력 시스템과 혁신적인 에너지 회생(Regenerative) 기능을 탑재하고 있습니다. 방전 시 버려지는 에너지를 회수하여 전력망으로 되돌려주는 이 기술은 공장의 전력 낭비를 획기적으로 줄이고 냉각 부하를 저감하여, 가장 경제적이고 친환경적인 생산 환경을 완성합니다.</t>
         </is>
       </c>
       <c r="G71" s="7" t="n"/>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>Automation System</t>
-        </is>
-      </c>
-      <c r="I71" s="5" t="inlineStr">
-        <is>
-          <t>묶음 10 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+          <t>In particular, A-PRO’s Cycler features an advanced bidirectional system capable of both supplying (charging) and absorbing (discharging) current, integrated with innovative energy regeneration technology. By capturing energy released during discharge and feeding it back into the power grid, this technology drastically reduces power waste and cooling loads, enabling an exceptionally economical and eco-friendly production environment.</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr"/>
       <c r="J71" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[4]|text</t>
         </is>
       </c>
     </row>
@@ -3431,7 +3443,7 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>장 영문 제목</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -3439,24 +3451,28 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E72" s="5" t="inlineStr"/>
+      <c r="E72" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>스마트 팩토리를 완성하는 지능형 통합 제어 솔루션
-활성화 공정 전체 설비의 실시간 정밀 제어와 체계적인 데이터 관리를 통해 최고의 생산 가동 효율과 제조 안정성을 보장합니다.</t>
+          <t>자동화 설비</t>
         </is>
       </c>
       <c r="G72" s="7" t="n"/>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>Intelligent Control Solutions Powering the Smart Factory
-We maximize operational efficiency and production stability through real-time precision control and systematic data management across the entire formation process.</t>
-        </is>
-      </c>
-      <c r="I72" s="5" t="inlineStr"/>
+          <t>Automation System</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>묶음 10 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div[1]/h2|text</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3487,7 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>장 영문 제목</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -3482,19 +3498,15 @@
       <c r="E73" s="5" t="inlineStr"/>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>스마트 설비 제어</t>
+          <t>스마트 팩토리를 완성하는 지능형 통합 제어 솔루션</t>
         </is>
       </c>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="8" t="inlineStr">
-        <is>
-          <t>Smart Equipment Control</t>
-        </is>
-      </c>
+      <c r="H73" s="8" t="n"/>
       <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[1]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div[1]/p|text</t>
         </is>
       </c>
     </row>
@@ -3509,7 +3521,7 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -3520,19 +3532,15 @@
       <c r="E74" s="5" t="inlineStr"/>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>충방전기, 디개싱, 에이징 룸 등 공정 내 모든 하드웨어를 실시간 직접 제어합니다.</t>
+          <t>활성화 공정 전체 설비의 실시간 정밀 제어와 체계적인 데이터 관리를 통해 최고의 생산 가동 효율과 제조 안정성을 보장합니다.</t>
         </is>
       </c>
       <c r="G74" s="7" t="n"/>
-      <c r="H74" s="8" t="inlineStr">
-        <is>
-          <t>Direct, real-time hardware control of all production lines, including cyclers, degassing units, and aging rooms.</t>
-        </is>
-      </c>
+      <c r="H74" s="8" t="n"/>
       <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[1]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div[2]/p|text</t>
         </is>
       </c>
     </row>
@@ -3558,19 +3566,19 @@
       <c r="E75" s="5" t="inlineStr"/>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>실시간 데이터 수집</t>
+          <t>스마트 설비 제어</t>
         </is>
       </c>
       <c r="G75" s="7" t="n"/>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>Real-Time Data Acquisition</t>
+          <t>Smart Equipment Control</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
       <c r="J75" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[2]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[1]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3596,19 +3604,19 @@
       <c r="E76" s="5" t="inlineStr"/>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>미세한 온도·압력·전압·전류 데이터를 정밀 측정하여 완벽한 품질 추적성을 확보합니다.</t>
+          <t>충방전기, 디개싱, 에이징 룸 등 공정 내 모든 하드웨어를 실시간 직접 제어합니다.</t>
         </is>
       </c>
       <c r="G76" s="7" t="n"/>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>Precision monitoring of voltage, current, temperature, and pressure for seamless quality traceability.</t>
+          <t>Direct, real-time hardware control of all production lines, including cyclers, degassing units, and aging rooms.</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr"/>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[2]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[1]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3634,19 +3642,19 @@
       <c r="E77" s="5" t="inlineStr"/>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>지능형 안전 인터록</t>
+          <t>실시간 데이터 수집</t>
         </is>
       </c>
       <c r="G77" s="7" t="n"/>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>Intelligent Safety Interlock</t>
+          <t>Real-Time Data Acquisition</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr"/>
       <c r="J77" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[3]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[2]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3672,19 +3680,19 @@
       <c r="E78" s="5" t="inlineStr"/>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>가스 누출, 과전압 등 이상 징후 감지 시 설비를 즉각 정지시켜 사고를 원천 차단합니다.</t>
+          <t>미세한 온도·압력·전압·전류 데이터를 정밀 측정하여 완벽한 품질 추적성을 확보합니다.</t>
         </is>
       </c>
       <c r="G78" s="7" t="n"/>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>Advanced emergency system that instantly halts operations upon detecting hazards like gas leaks or overvoltage.</t>
+          <t>Precision monitoring of voltage, current, temperature, and pressure for seamless quality traceability.</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr"/>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[3]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[2]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3710,19 +3718,19 @@
       <c r="E79" s="5" t="inlineStr"/>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>유연한 상위 연동</t>
+          <t>지능형 안전 인터록</t>
         </is>
       </c>
       <c r="G79" s="7" t="n"/>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>Seamless Integration</t>
+          <t>Intelligent Safety Interlock</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr"/>
       <c r="J79" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[4]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[3]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3748,19 +3756,19 @@
       <c r="E80" s="5" t="inlineStr"/>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>PC 및 MES와의 고속 통신으로 공정 데이터를 실시간 전송하고 레시피 명령을 완벽히 수행합니다.</t>
+          <t>가스 누출, 과전압 등 이상 징후 감지 시 설비를 즉각 정지시켜 사고를 원천 차단합니다.</t>
         </is>
       </c>
       <c r="G80" s="7" t="n"/>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>High-speed communication with upper-level systems (PCs/MES) to transmit process data and execute recipe commands flawlessly.</t>
+          <t>Advanced emergency system that instantly halts operations upon detecting hazards like gas leaks or overvoltage.</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr"/>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[4]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[3]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3770,12 +3778,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>03-2 충방전 공정 관리 시스템</t>
+          <t>03-1 자동화 설비</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3786,15 +3794,19 @@
       <c r="E81" s="5" t="inlineStr"/>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>충방전 공정 관리시스템</t>
+          <t>유연한 상위 연동</t>
         </is>
       </c>
       <c r="G81" s="7" t="n"/>
-      <c r="H81" s="8" t="n"/>
+      <c r="H81" s="8" t="inlineStr">
+        <is>
+          <t>Seamless Integration</t>
+        </is>
+      </c>
       <c r="I81" s="5" t="inlineStr"/>
       <c r="J81" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[4]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3804,12 +3816,12 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>03-2 충방전 공정 관리 시스템</t>
+          <t>03-1 자동화 설비</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -3820,15 +3832,19 @@
       <c r="E82" s="5" t="inlineStr"/>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>생산 추적</t>
+          <t>PC 및 MES와의 고속 통신으로 공정 데이터를 실시간 전송하고 레시피 명령을 완벽히 수행합니다.</t>
         </is>
       </c>
       <c r="G82" s="7" t="n"/>
-      <c r="H82" s="8" t="n"/>
+      <c r="H82" s="8" t="inlineStr">
+        <is>
+          <t>High-speed communication with upper-level systems (PCs/MES) to transmit process data and execute recipe commands flawlessly.</t>
+        </is>
+      </c>
       <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[1]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[4]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3843,7 +3859,7 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -3854,7 +3870,7 @@
       <c r="E83" s="5" t="inlineStr"/>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>배터리 셀의 바코드를 스캔하여 활성화 공정의 시작부터 끝까지 전 제조 이력을 실시간으로 추적 및 관리합니다.</t>
+          <t>충방전 공정 관리시스템</t>
         </is>
       </c>
       <c r="G83" s="7" t="n"/>
@@ -3862,7 +3878,7 @@
       <c r="I83" s="5" t="inlineStr"/>
       <c r="J83" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[1]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -3888,7 +3904,7 @@
       <c r="E84" s="5" t="inlineStr"/>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>레시피 하향</t>
+          <t>생산 추적</t>
         </is>
       </c>
       <c r="G84" s="7" t="n"/>
@@ -3896,7 +3912,7 @@
       <c r="I84" s="5" t="inlineStr"/>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[2]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[1]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3922,7 +3938,7 @@
       <c r="E85" s="5" t="inlineStr"/>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>배터리 모델별로 정해진 충방전 조건, 에이징 시간 등의 세부 공정 레시피를 각 설비(PLC)에 자동으로 전달합니다.</t>
+          <t>배터리 셀의 바코드를 스캔하여 활성화 공정의 시작부터 끝까지 전 제조 이력을 실시간으로 추적 및 관리합니다.</t>
         </is>
       </c>
       <c r="G85" s="7" t="n"/>
@@ -3930,7 +3946,7 @@
       <c r="I85" s="5" t="inlineStr"/>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[2]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[1]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3956,7 +3972,7 @@
       <c r="E86" s="5" t="inlineStr"/>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>품질 판정</t>
+          <t>레시피 하향</t>
         </is>
       </c>
       <c r="G86" s="7" t="n"/>
@@ -3964,7 +3980,7 @@
       <c r="I86" s="5" t="inlineStr"/>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[3]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[2]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3990,7 +4006,7 @@
       <c r="E87" s="5" t="inlineStr"/>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>충방전 결과 데이터(용량, 저항 등)를 분석하여 해당 배터리 셀의 합격/불합격(Pass/Fail) 및 등급(Grading)을 판정합니다.</t>
+          <t>배터리 모델별로 정해진 충방전 조건, 에이징 시간 등의 세부 공정 레시피를 각 설비(PLC)에 자동으로 전달합니다.</t>
         </is>
       </c>
       <c r="G87" s="7" t="n"/>
@@ -3998,7 +4014,7 @@
       <c r="I87" s="5" t="inlineStr"/>
       <c r="J87" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[3]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[2]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4040,7 @@
       <c r="E88" s="5" t="inlineStr"/>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>데이터 통합</t>
+          <t>품질 판정</t>
         </is>
       </c>
       <c r="G88" s="7" t="n"/>
@@ -4032,7 +4048,7 @@
       <c r="I88" s="5" t="inlineStr"/>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[4]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[3]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4074,7 @@
       <c r="E89" s="5" t="inlineStr"/>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>전체 공정의 생산량, 설비 가동률, 불량률 등의 통계 데이터를 시각화하여 공장 전반의 생산 효율성을 최적화합니다.</t>
+          <t>충방전 결과 데이터(용량, 저항 등)를 분석하여 해당 배터리 셀의 합격/불합격(Pass/Fail) 및 등급(Grading)을 판정합니다.</t>
         </is>
       </c>
       <c r="G89" s="7" t="n"/>
@@ -4066,7 +4082,7 @@
       <c r="I89" s="5" t="inlineStr"/>
       <c r="J89" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[4]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[3]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4076,12 +4092,12 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>04-1 탄소 나노 튜브</t>
+          <t>03-2 충방전 공정 관리 시스템</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -4089,28 +4105,18 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E90" s="5" t="n">
-        <v>12</v>
-      </c>
+      <c r="E90" s="5" t="inlineStr"/>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>탄소 나노 튜브</t>
+          <t>데이터 통합</t>
         </is>
       </c>
       <c r="G90" s="7" t="n"/>
-      <c r="H90" s="8" t="inlineStr">
-        <is>
-          <t>Carbon Nano Tube</t>
-        </is>
-      </c>
-      <c r="I90" s="5" t="inlineStr">
-        <is>
-          <t>묶음 12 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="H90" s="8" t="n"/>
+      <c r="I90" s="5" t="inlineStr"/>
       <c r="J90" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div[1]/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[4]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4120,12 +4126,12 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>04-1 탄소 나노 튜브</t>
+          <t>03-2 충방전 공정 관리 시스템</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -4136,19 +4142,15 @@
       <c r="E91" s="5" t="inlineStr"/>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials의 글로벌 소싱 네트워크를 활용하여 고품질의 탄소나노튜브(CNT) 소재를 안정적으로 공급합니다.</t>
+          <t>전체 공정의 생산량, 설비 가동률, 불량률 등의 통계 데이터를 시각화하여 공장 전반의 생산 효율성을 최적화합니다.</t>
         </is>
       </c>
       <c r="G91" s="7" t="n"/>
-      <c r="H91" s="8" t="inlineStr">
-        <is>
-          <t>We provide a stable supply of high-quality carbon nanotube (CNT) materials through A-PRO Materials' global sourcing network.</t>
-        </is>
-      </c>
+      <c r="H91" s="8" t="n"/>
       <c r="I91" s="5" t="inlineStr"/>
       <c r="J91" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div[1]/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[4]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4163,7 +4165,7 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -4171,22 +4173,28 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E92" s="5" t="inlineStr"/>
+      <c r="E92" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>엄격한 품질 검증을 거친 CNT 소재를 통해 고객사의 배터리 에너지 밀도 향상과 고속 충전 성능 구현을 지원합니다.</t>
+          <t>탄소 나노 튜브</t>
         </is>
       </c>
       <c r="G92" s="7" t="n"/>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>Through rigorously quality-verified CNT materials, we support our customers in enhancing battery energy density and enabling high-speed charging performance.</t>
-        </is>
-      </c>
-      <c r="I92" s="5" t="inlineStr"/>
+          <t>Carbon Nano Tube</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>묶음 12 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div[1]/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div[1]/h2|text</t>
         </is>
       </c>
     </row>
@@ -4201,7 +4209,7 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>제품 단추 이름</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -4212,21 +4220,19 @@
       <c r="E93" s="5" t="inlineStr"/>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>SW/FW-
-CNT Powder</t>
+          <t>A-PRO Materials의 글로벌 소싱 네트워크를 활용하여 고품질의 탄소나노튜브(CNT) 소재를 안정적으로 공급합니다.</t>
         </is>
       </c>
       <c r="G93" s="7" t="n"/>
       <c r="H93" s="8" t="inlineStr">
         <is>
-          <t>SW/FW-
-CNT Powder</t>
+          <t>We provide a stable supply of high-quality carbon nanotube (CNT) materials through A-PRO Materials' global sourcing network.</t>
         </is>
       </c>
       <c r="I93" s="5" t="inlineStr"/>
       <c r="J93" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div[2]/button[1]/span[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div[1]/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4241,7 +4247,7 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>제품 단추 이름</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -4252,21 +4258,19 @@
       <c r="E94" s="5" t="inlineStr"/>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>SW/FW-
-CNT Slurry</t>
+          <t>엄격한 품질 검증을 거친 CNT 소재를 통해 고객사의 배터리 에너지 밀도 향상과 고속 충전 성능 구현을 지원합니다.</t>
         </is>
       </c>
       <c r="G94" s="7" t="n"/>
       <c r="H94" s="8" t="inlineStr">
         <is>
-          <t>SW/FW-
-CNT Slurry</t>
+          <t>Through rigorously quality-verified CNT materials, we support our customers in enhancing battery energy density and enabling high-speed charging performance.</t>
         </is>
       </c>
       <c r="I94" s="5" t="inlineStr"/>
       <c r="J94" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div[2]/button[2]/span[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div[1]/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4292,21 +4296,21 @@
       <c r="E95" s="5" t="inlineStr"/>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>Carbon
-Black</t>
+          <t>SW/FW-
+CNT Powder</t>
         </is>
       </c>
       <c r="G95" s="7" t="n"/>
       <c r="H95" s="8" t="inlineStr">
         <is>
-          <t>Carbon
-Black</t>
+          <t>SW/FW-
+CNT Powder</t>
         </is>
       </c>
       <c r="I95" s="5" t="inlineStr"/>
       <c r="J95" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div[2]/button[3]/span[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div[2]/button[1]/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -4316,12 +4320,12 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>04-2 LiFSI 전해염</t>
+          <t>04-1 탄소 나노 튜브</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>제품 단추 이름</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -4329,28 +4333,24 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E96" s="5" t="n">
-        <v>13</v>
-      </c>
+      <c r="E96" s="5" t="inlineStr"/>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>LiFSI 전해염</t>
+          <t>SW/FW-
+CNT Slurry</t>
         </is>
       </c>
       <c r="G96" s="7" t="n"/>
       <c r="H96" s="8" t="inlineStr">
         <is>
-          <t>Electrolyte</t>
-        </is>
-      </c>
-      <c r="I96" s="5" t="inlineStr">
-        <is>
-          <t>묶음 13 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+          <t>SW/FW-
+CNT Slurry</t>
+        </is>
+      </c>
+      <c r="I96" s="5" t="inlineStr"/>
       <c r="J96" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div[2]/button[2]/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -4360,12 +4360,12 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>04-2 LiFSI 전해염</t>
+          <t>04-1 탄소 나노 튜브</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>제품 단추 이름</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -4376,19 +4376,21 @@
       <c r="E97" s="5" t="inlineStr"/>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials는 엄선된 공급망을 통해 고순도 LiFSI 전해염 소재를 안정적으로 공급합니다.</t>
+          <t>Carbon
+Black</t>
         </is>
       </c>
       <c r="G97" s="7" t="n"/>
       <c r="H97" s="8" t="inlineStr">
         <is>
-          <t>A-PRO Materials provides a stable supply of high-purity LiFSI electrolyte salt through a carefully selected global supply network.</t>
+          <t>Carbon
+Black</t>
         </is>
       </c>
       <c r="I97" s="5" t="inlineStr"/>
       <c r="J97" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div[2]/button[3]/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -4403,7 +4405,7 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -4411,22 +4413,28 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E98" s="5" t="inlineStr"/>
+      <c r="E98" s="5" t="n">
+        <v>13</v>
+      </c>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>우수한 화학적 안정성을 바탕으로 고객사 배터리의 수명 연장과 고온 안정성 및 출력 향상을 지원합니다.</t>
+          <t>LiFSI 전해염</t>
         </is>
       </c>
       <c r="G98" s="7" t="n"/>
       <c r="H98" s="8" t="inlineStr">
         <is>
-          <t>Based on superior chemical stability, we support extended battery life, high-temperature stability, and improved output performance for our customers.</t>
-        </is>
-      </c>
-      <c r="I98" s="5" t="inlineStr"/>
+          <t>Electrolyte</t>
+        </is>
+      </c>
+      <c r="I98" s="5" t="inlineStr">
+        <is>
+          <t>묶음 13 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -4436,12 +4444,12 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-2 LiFSI 전해염</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
@@ -4449,28 +4457,22 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E99" s="5" t="n">
-        <v>14</v>
-      </c>
+      <c r="E99" s="5" t="inlineStr"/>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>HNBR 바인더</t>
+          <t>A-PRO Materials는 엄선된 공급망을 통해 고순도 LiFSI 전해염 소재를 안정적으로 공급합니다.</t>
         </is>
       </c>
       <c r="G99" s="7" t="n"/>
       <c r="H99" s="8" t="inlineStr">
         <is>
-          <t>HNBR Binder</t>
-        </is>
-      </c>
-      <c r="I99" s="5" t="inlineStr">
-        <is>
-          <t>묶음 14 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+          <t>A-PRO Materials provides a stable supply of high-purity LiFSI electrolyte salt through a carefully selected global supply network.</t>
+        </is>
+      </c>
+      <c r="I99" s="5" t="inlineStr"/>
       <c r="J99" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4480,7 +4482,7 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-2 LiFSI 전해염</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
@@ -4496,19 +4498,19 @@
       <c r="E100" s="5" t="inlineStr"/>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>PVDF 바인더의 일부 대체 가능성을 검토할 수 있는 HNBR 바인더 소재입니다.</t>
+          <t>우수한 화학적 안정성을 바탕으로 고객사 배터리의 수명 연장과 고온 안정성 및 출력 향상을 지원합니다.</t>
         </is>
       </c>
       <c r="G100" s="7" t="n"/>
       <c r="H100" s="8" t="inlineStr">
         <is>
-          <t>HNBR is a binder material that can be evaluated as a partial alternative to PVDF binders.</t>
+          <t>Based on superior chemical stability, we support extended battery life, high-temperature stability, and improved output performance for our customers.</t>
         </is>
       </c>
       <c r="I100" s="5" t="inlineStr"/>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4523,7 +4525,7 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -4531,22 +4533,28 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E101" s="5" t="inlineStr"/>
+      <c r="E101" s="5" t="n">
+        <v>14</v>
+      </c>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>우수한 결합력과 유연성, 전극 저항 감소 효과를 통해 배터리의 고율 충·방전 성능과 안정성 향상에 기여할 수 있습니다.</t>
+          <t>HNBR 바인더</t>
         </is>
       </c>
       <c r="G101" s="7" t="n"/>
       <c r="H101" s="8" t="inlineStr">
         <is>
-          <t>With excellent bonding strength, flexibility, and reduced electrode resistance, it can contribute to improved high-rate charge/discharge performance and stability.</t>
-        </is>
-      </c>
-      <c r="I101" s="5" t="inlineStr"/>
+          <t>HNBR Binder</t>
+        </is>
+      </c>
+      <c r="I101" s="5" t="inlineStr">
+        <is>
+          <t>묶음 14 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J101" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4569,7 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
@@ -4572,15 +4580,19 @@
       <c r="E102" s="5" t="inlineStr"/>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>PVDF 대체</t>
+          <t>PVDF 바인더의 일부 대체 가능성을 검토할 수 있는 HNBR 바인더 소재입니다.</t>
         </is>
       </c>
       <c r="G102" s="7" t="n"/>
-      <c r="H102" s="8" t="n"/>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t>HNBR is a binder material that can be evaluated as a partial alternative to PVDF binders.</t>
+        </is>
+      </c>
       <c r="I102" s="5" t="inlineStr"/>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[1]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4595,7 +4607,7 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -4606,15 +4618,19 @@
       <c r="E103" s="5" t="inlineStr"/>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>기존 불소계 바인더의 5~15% 이상을 친환경 HNBR로 대체.</t>
+          <t>우수한 결합력과 유연성, 전극 저항 감소 효과를 통해 배터리의 고율 충·방전 성능과 안정성 향상에 기여할 수 있습니다.</t>
         </is>
       </c>
       <c r="G103" s="7" t="n"/>
-      <c r="H103" s="8" t="n"/>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>With excellent bonding strength, flexibility, and reduced electrode resistance, it can contribute to improved high-rate charge/discharge performance and stability.</t>
+        </is>
+      </c>
       <c r="I103" s="5" t="inlineStr"/>
       <c r="J103" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[1]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4640,7 +4656,7 @@
       <c r="E104" s="5" t="inlineStr"/>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>고율 충방전 특성</t>
+          <t>PVDF 대체</t>
         </is>
       </c>
       <c r="G104" s="7" t="n"/>
@@ -4648,7 +4664,7 @@
       <c r="I104" s="5" t="inlineStr"/>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[2]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[1]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4674,7 +4690,7 @@
       <c r="E105" s="5" t="inlineStr"/>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>10C 고속 충전 조건에서도 우수한 용량 유지.</t>
+          <t>기존 불소계 바인더의 5~15% 이상을 친환경 HNBR로 대체.</t>
         </is>
       </c>
       <c r="G105" s="7" t="n"/>
@@ -4682,7 +4698,7 @@
       <c r="I105" s="5" t="inlineStr"/>
       <c r="J105" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[2]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[1]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4708,7 +4724,7 @@
       <c r="E106" s="5" t="inlineStr"/>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>내부 저항 감소</t>
+          <t>고율 충방전 특성</t>
         </is>
       </c>
       <c r="G106" s="7" t="n"/>
@@ -4716,7 +4732,7 @@
       <c r="I106" s="5" t="inlineStr"/>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[3]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[2]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4742,7 +4758,7 @@
       <c r="E107" s="5" t="inlineStr"/>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>젖음성 개선으로 이온 전달 및 계면 저항 최소화.</t>
+          <t>10C 고속 충전 조건에서도 우수한 용량 유지.</t>
         </is>
       </c>
       <c r="G107" s="7" t="n"/>
@@ -4750,7 +4766,7 @@
       <c r="I107" s="5" t="inlineStr"/>
       <c r="J107" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[3]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[2]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4776,7 +4792,7 @@
       <c r="E108" s="5" t="inlineStr"/>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>높은 강도 및 유연성</t>
+          <t>내부 저항 감소</t>
         </is>
       </c>
       <c r="G108" s="7" t="n"/>
@@ -4784,7 +4800,7 @@
       <c r="I108" s="5" t="inlineStr"/>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[4]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[3]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4810,7 +4826,7 @@
       <c r="E109" s="5" t="inlineStr"/>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>전극 활물질 부피 변화 흡수, 탈락 방지.</t>
+          <t>젖음성 개선으로 이온 전달 및 계면 저항 최소화.</t>
         </is>
       </c>
       <c r="G109" s="7" t="n"/>
@@ -4818,7 +4834,7 @@
       <c r="I109" s="5" t="inlineStr"/>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[4]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[3]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4844,7 +4860,7 @@
       <c r="E110" s="5" t="inlineStr"/>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>SWCNT 분산 최적화</t>
+          <t>높은 강도 및 유연성</t>
         </is>
       </c>
       <c r="G110" s="7" t="n"/>
@@ -4852,7 +4868,7 @@
       <c r="I110" s="5" t="inlineStr"/>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[5]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[4]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4878,7 +4894,7 @@
       <c r="E111" s="5" t="inlineStr"/>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>단일벽 탄소나노튜브의 응집 해소, 점도 감소.</t>
+          <t>전극 활물질 부피 변화 흡수, 탈락 방지.</t>
         </is>
       </c>
       <c r="G111" s="7" t="n"/>
@@ -4886,7 +4902,7 @@
       <c r="I111" s="5" t="inlineStr"/>
       <c r="J111" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[5]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[4]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4896,12 +4912,12 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>04-4 파우치셀 제조</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
@@ -4909,28 +4925,18 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E112" s="5" t="n">
-        <v>15</v>
-      </c>
+      <c r="E112" s="5" t="inlineStr"/>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>파우치셀 제조</t>
+          <t>SWCNT 분산 최적화</t>
         </is>
       </c>
       <c r="G112" s="7" t="n"/>
-      <c r="H112" s="8" t="inlineStr">
-        <is>
-          <t>Pouch Cell Manufacturing</t>
-        </is>
-      </c>
-      <c r="I112" s="5" t="inlineStr">
-        <is>
-          <t>묶음 15 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="H112" s="8" t="n"/>
+      <c r="I112" s="5" t="inlineStr"/>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[5]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4940,12 +4946,12 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>04-4 파우치셀 제조</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
@@ -4956,19 +4962,15 @@
       <c r="E113" s="5" t="inlineStr"/>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials는 Lab-scale 파우치셀 제작 및 소재 적용성 검증 서비스를 제공합니다.</t>
+          <t>단일벽 탄소나노튜브의 응집 해소, 점도 감소.</t>
         </is>
       </c>
       <c r="G113" s="7" t="n"/>
-      <c r="H113" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Materials provides lab-scale pouch cell fabrication and material validation services.</t>
-        </is>
-      </c>
+      <c r="H113" s="8" t="n"/>
       <c r="I113" s="5" t="inlineStr"/>
       <c r="J113" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[5]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4983,7 +4985,7 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
@@ -4991,22 +4993,28 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E114" s="5" t="inlineStr"/>
+      <c r="E114" s="5" t="n">
+        <v>15</v>
+      </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>셀 설계부터 조립 공정, 품질 평가까지 통합 프로세스를 통해 고객사의 신소재 적용 가능성을 사전 검증합니다.</t>
+          <t>파우치셀 제조</t>
         </is>
       </c>
       <c r="G114" s="7" t="n"/>
       <c r="H114" s="8" t="inlineStr">
         <is>
-          <t>Through an integrated process encompassing cell design, assembly, and quality evaluation, we help our clients pre-validate the applicability of new materials.</t>
-        </is>
-      </c>
-      <c r="I114" s="5" t="inlineStr"/>
+          <t>Pouch Cell Manufacturing</t>
+        </is>
+      </c>
+      <c r="I114" s="5" t="inlineStr">
+        <is>
+          <t>묶음 15 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J114" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -5021,32 +5029,30 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="E115" s="5" t="n">
-        <v>5</v>
-      </c>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E115" s="5" t="inlineStr"/>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="G115" s="6" t="n"/>
-      <c r="H115" s="6" t="n"/>
-      <c r="I115" s="5" t="inlineStr">
-        <is>
-          <t>묶음 5 — 같은 문구 12 곳</t>
-        </is>
-      </c>
+          <t>A-PRO Materials는 Lab-scale 파우치셀 제작 및 소재 적용성 검증 서비스를 제공합니다.</t>
+        </is>
+      </c>
+      <c r="G115" s="7" t="n"/>
+      <c r="H115" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Materials provides lab-scale pouch cell fabrication and material validation services.</t>
+        </is>
+      </c>
+      <c r="I115" s="5" t="inlineStr"/>
       <c r="J115" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -5061,7 +5067,7 @@
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -5072,15 +5078,19 @@
       <c r="E116" s="5" t="inlineStr"/>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>사양 협의</t>
+          <t>셀 설계부터 조립 공정, 품질 평가까지 통합 프로세스를 통해 고객사의 신소재 적용 가능성을 사전 검증합니다.</t>
         </is>
       </c>
       <c r="G116" s="7" t="n"/>
-      <c r="H116" s="8" t="n"/>
+      <c r="H116" s="8" t="inlineStr">
+        <is>
+          <t>Through an integrated process encompassing cell design, assembly, and quality evaluation, we help our clients pre-validate the applicability of new materials.</t>
+        </is>
+      </c>
       <c r="I116" s="5" t="inlineStr"/>
       <c r="J116" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -5104,23 +5114,23 @@
         </is>
       </c>
       <c r="E117" s="5" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>01</t>
         </is>
       </c>
       <c r="G117" s="6" t="n"/>
       <c r="H117" s="6" t="n"/>
       <c r="I117" s="5" t="inlineStr">
         <is>
-          <t>묶음 8 — 같은 문구 12 곳</t>
+          <t>묶음 5 — 같은 문구 12 곳</t>
         </is>
       </c>
       <c r="J117" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/b|text</t>
         </is>
       </c>
     </row>
@@ -5146,7 +5156,7 @@
       <c r="E118" s="5" t="inlineStr"/>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>소재 입고 및 검수</t>
+          <t>사양 협의</t>
         </is>
       </c>
       <c r="G118" s="7" t="n"/>
@@ -5154,7 +5164,7 @@
       <c r="I118" s="5" t="inlineStr"/>
       <c r="J118" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/span|text</t>
         </is>
       </c>
     </row>
@@ -5178,23 +5188,23 @@
         </is>
       </c>
       <c r="E119" s="5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>02</t>
         </is>
       </c>
       <c r="G119" s="6" t="n"/>
       <c r="H119" s="6" t="n"/>
       <c r="I119" s="5" t="inlineStr">
         <is>
-          <t>묶음 9 — 같은 문구 12 곳</t>
+          <t>묶음 8 — 같은 문구 12 곳</t>
         </is>
       </c>
       <c r="J119" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/b|text</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5230,7 @@
       <c r="E120" s="5" t="inlineStr"/>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>파우치셀 조립</t>
+          <t>소재 입고 및 검수</t>
         </is>
       </c>
       <c r="G120" s="7" t="n"/>
@@ -5228,7 +5238,7 @@
       <c r="I120" s="5" t="inlineStr"/>
       <c r="J120" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/span|text</t>
         </is>
       </c>
     </row>
@@ -5252,23 +5262,23 @@
         </is>
       </c>
       <c r="E121" s="5" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>03</t>
         </is>
       </c>
       <c r="G121" s="6" t="n"/>
       <c r="H121" s="6" t="n"/>
       <c r="I121" s="5" t="inlineStr">
         <is>
-          <t>묶음 11 — 같은 문구 9 곳</t>
+          <t>묶음 9 — 같은 문구 12 곳</t>
         </is>
       </c>
       <c r="J121" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[4]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/b|text</t>
         </is>
       </c>
     </row>
@@ -5294,7 +5304,7 @@
       <c r="E122" s="5" t="inlineStr"/>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>화성 공정</t>
+          <t>파우치셀 조립</t>
         </is>
       </c>
       <c r="G122" s="7" t="n"/>
@@ -5302,7 +5312,7 @@
       <c r="I122" s="5" t="inlineStr"/>
       <c r="J122" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[4]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/span|text</t>
         </is>
       </c>
     </row>
@@ -5326,23 +5336,23 @@
         </is>
       </c>
       <c r="E123" s="5" t="n">
-        <v>18</v>
+        <v>11</v>
       </c>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>04</t>
         </is>
       </c>
       <c r="G123" s="6" t="n"/>
       <c r="H123" s="6" t="n"/>
       <c r="I123" s="5" t="inlineStr">
         <is>
-          <t>묶음 18 — 같은 문구 2 곳</t>
+          <t>묶음 11 — 같은 문구 9 곳</t>
         </is>
       </c>
       <c r="J123" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[5]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[4]/b|text</t>
         </is>
       </c>
     </row>
@@ -5368,7 +5378,7 @@
       <c r="E124" s="5" t="inlineStr"/>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>제품 출하</t>
+          <t>화성 공정</t>
         </is>
       </c>
       <c r="G124" s="7" t="n"/>
@@ -5376,7 +5386,7 @@
       <c r="I124" s="5" t="inlineStr"/>
       <c r="J124" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[5]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[4]/span|text</t>
         </is>
       </c>
     </row>
@@ -5386,31 +5396,37 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>04-5 에이프로머티리얼즈</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="inlineStr"/>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E125" s="5" t="n">
+        <v>18</v>
+      </c>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>차세대 기술 개발</t>
-        </is>
-      </c>
-      <c r="G125" s="7" t="n"/>
-      <c r="H125" s="8" t="n"/>
-      <c r="I125" s="5" t="inlineStr"/>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="G125" s="6" t="n"/>
+      <c r="H125" s="6" t="n"/>
+      <c r="I125" s="5" t="inlineStr">
+        <is>
+          <t>묶음 18 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J125" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[5]/b|text</t>
         </is>
       </c>
     </row>
@@ -5420,12 +5436,12 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>04-5 에이프로머티리얼즈</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
@@ -5436,19 +5452,15 @@
       <c r="E126" s="5" t="inlineStr"/>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials는 차세대 배터리 핵심 기술에 대한 지속적인 연구개발을 통해 미래 이차전지 시장에 대응해 나갑니다.</t>
+          <t>제품 출하</t>
         </is>
       </c>
       <c r="G126" s="7" t="n"/>
-      <c r="H126" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Materials is working to respond to the future secondary battery market through continuous research and development of core next-generation battery technologies.</t>
-        </is>
-      </c>
+      <c r="H126" s="8" t="n"/>
       <c r="I126" s="5" t="inlineStr"/>
       <c r="J126" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[5]/span|text</t>
         </is>
       </c>
     </row>
@@ -5463,7 +5475,7 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
@@ -5474,19 +5486,15 @@
       <c r="E127" s="5" t="inlineStr"/>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>끊임없는 R&amp;D 혁신으로 기존 배터리의 한계를 극복하고, 고성능·고안정성 소재 및 셀 기술을 선제적으로 구현해 나갑니다.</t>
+          <t>차세대 기술 개발</t>
         </is>
       </c>
       <c r="G127" s="7" t="n"/>
-      <c r="H127" s="8" t="inlineStr">
-        <is>
-          <t>Through ongoing R&amp;D innovation, we work to overcome the limitations of existing batteries and proactively develop high-performance, high-stability materials and cell technologies.</t>
-        </is>
-      </c>
+      <c r="H127" s="8" t="n"/>
       <c r="I127" s="5" t="inlineStr"/>
       <c r="J127" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -5512,24 +5520,100 @@
       <c r="E128" s="5" t="inlineStr"/>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials는 국내외 파트너들과의 협력을 통해 최적의 이차전지 소재 솔루션을 모색하고 있습니다.</t>
+          <t>A-PRO Materials는 차세대 배터리 핵심 기술에 대한 지속적인 연구개발을 통해 미래 이차전지 시장에 대응해 나갑니다.</t>
         </is>
       </c>
       <c r="G128" s="7" t="n"/>
       <c r="H128" s="8" t="inlineStr">
         <is>
-          <t>A-PRO Materials is exploring optimal secondary battery material solutions in collaboration with partners at home and abroad.</t>
+          <t>A-PRO Materials is working to respond to the future secondary battery market through continuous research and development of core next-generation battery technologies.</t>
         </is>
       </c>
       <c r="I128" s="5" t="inlineStr"/>
       <c r="J128" s="9" t="inlineStr">
         <is>
+          <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/div/div/p[1]|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="5" t="n">
+        <v>128</v>
+      </c>
+      <c r="B129" s="5" t="inlineStr">
+        <is>
+          <t>04-5 에이프로머티리얼즈</t>
+        </is>
+      </c>
+      <c r="C129" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D129" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E129" s="5" t="inlineStr"/>
+      <c r="F129" s="6" t="inlineStr">
+        <is>
+          <t>끊임없는 R&amp;D 혁신으로 기존 배터리의 한계를 극복하고, 고성능·고안정성 소재 및 셀 기술을 선제적으로 구현해 나갑니다.</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="n"/>
+      <c r="H129" s="8" t="inlineStr">
+        <is>
+          <t>Through ongoing R&amp;D innovation, we work to overcome the limitations of existing batteries and proactively develop high-performance, high-stability materials and cell technologies.</t>
+        </is>
+      </c>
+      <c r="I129" s="5" t="inlineStr"/>
+      <c r="J129" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/div/div/p[2]|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="5" t="n">
+        <v>129</v>
+      </c>
+      <c r="B130" s="5" t="inlineStr">
+        <is>
+          <t>04-5 에이프로머티리얼즈</t>
+        </is>
+      </c>
+      <c r="C130" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D130" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E130" s="5" t="inlineStr"/>
+      <c r="F130" s="6" t="inlineStr">
+        <is>
+          <t>A-PRO Materials는 국내외 파트너들과의 협력을 통해 최적의 이차전지 소재 솔루션을 모색하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="n"/>
+      <c r="H130" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Materials is exploring optimal secondary battery material solutions in collaboration with partners at home and abroad.</t>
+        </is>
+      </c>
+      <c r="I130" s="5" t="inlineStr"/>
+      <c r="J130" s="9" t="inlineStr">
+        <is>
           <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J128"/>
+  <autoFilter ref="A1:J130"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -5861,7 +5945,11 @@
         </is>
       </c>
       <c r="G8" s="7" t="n"/>
-      <c r="H8" s="8" t="n"/>
+      <c r="H8" s="8" t="inlineStr">
+        <is>
+          <t>UPS(Uninterruptible Power Supply)</t>
+        </is>
+      </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
           <t>묶음 20 — 같은 문구 2 곳</t>
@@ -5901,7 +5989,11 @@
         </is>
       </c>
       <c r="G9" s="7" t="n"/>
-      <c r="H9" s="8" t="n"/>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>SOLUTION</t>
+        </is>
+      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>묶음 21 — 같은 문구 2 곳</t>
@@ -6913,7 +7005,11 @@
         </is>
       </c>
       <c r="G33" s="7" t="n"/>
-      <c r="H33" s="8" t="n"/>
+      <c r="H33" s="8" t="inlineStr">
+        <is>
+          <t>GRID ESS</t>
+        </is>
+      </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
           <t>묶음 22 — 같은 문구 2 곳</t>
@@ -7341,7 +7437,11 @@
         </is>
       </c>
       <c r="G44" s="7" t="n"/>
-      <c r="H44" s="8" t="n"/>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>Renewable ESS</t>
+        </is>
+      </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
           <t>묶음 23 — 같은 문구 2 곳</t>
@@ -7695,7 +7795,11 @@
         </is>
       </c>
       <c r="G53" s="7" t="n"/>
-      <c r="H53" s="8" t="n"/>
+      <c r="H53" s="8" t="inlineStr">
+        <is>
+          <t>C&amp;I ESS</t>
+        </is>
+      </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
           <t>묶음 24 — 같은 문구 2 곳</t>
@@ -9463,7 +9567,11 @@
         </is>
       </c>
       <c r="G98" s="7" t="n"/>
-      <c r="H98" s="8" t="n"/>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>Module</t>
+        </is>
+      </c>
       <c r="I98" s="5" t="inlineStr">
         <is>
           <t>묶음 28 — 같은 문구 2 곳</t>
@@ -10577,7 +10685,11 @@
         </is>
       </c>
       <c r="G128" s="7" t="n"/>
-      <c r="H128" s="8" t="n"/>
+      <c r="H128" s="8" t="inlineStr">
+        <is>
+          <t>Rack</t>
+        </is>
+      </c>
       <c r="I128" s="5" t="inlineStr">
         <is>
           <t>묶음 29 — 같은 문구 2 곳</t>
@@ -11663,7 +11775,11 @@
         </is>
       </c>
       <c r="G158" s="7" t="n"/>
-      <c r="H158" s="8" t="n"/>
+      <c r="H158" s="8" t="inlineStr">
+        <is>
+          <t>Container</t>
+        </is>
+      </c>
       <c r="I158" s="5" t="inlineStr">
         <is>
           <t>묶음 30 — 같은 문구 2 곳</t>
@@ -12785,7 +12901,11 @@
         </is>
       </c>
       <c r="G188" s="7" t="n"/>
-      <c r="H188" s="8" t="n"/>
+      <c r="H188" s="8" t="inlineStr">
+        <is>
+          <t>BMS</t>
+        </is>
+      </c>
       <c r="I188" s="5" t="inlineStr">
         <is>
           <t>묶음 31 — 같은 문구 2 곳</t>
@@ -15324,7 +15444,11 @@
         </is>
       </c>
       <c r="G27" s="7" t="n"/>
-      <c r="H27" s="8" t="n"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
           <t>묶음 58 — 같은 문구 2 곳</t>
@@ -17273,7 +17397,11 @@
         </is>
       </c>
       <c r="G11" s="7" t="n"/>
-      <c r="H11" s="8" t="n"/>
+      <c r="H11" s="8" t="inlineStr">
+        <is>
+          <t>GaN Epi-Wafer</t>
+        </is>
+      </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
           <t>묶음 60 — 같은 문구 4 곳</t>
@@ -17313,7 +17441,11 @@
         </is>
       </c>
       <c r="G12" s="7" t="n"/>
-      <c r="H12" s="8" t="n"/>
+      <c r="H12" s="8" t="inlineStr">
+        <is>
+          <t>GaN Epi-Wafer</t>
+        </is>
+      </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
           <t>묶음 60 — 같은 문구 4 곳</t>
@@ -17393,7 +17525,11 @@
         </is>
       </c>
       <c r="G14" s="7" t="n"/>
-      <c r="H14" s="8" t="n"/>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>GaN Power Device</t>
+        </is>
+      </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
           <t>묶음 61 — 같은 문구 4 곳</t>
@@ -17433,7 +17569,11 @@
         </is>
       </c>
       <c r="G15" s="7" t="n"/>
-      <c r="H15" s="8" t="n"/>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>GaN Power Device</t>
+        </is>
+      </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>묶음 61 — 같은 문구 4 곳</t>
@@ -17761,7 +17901,11 @@
         </is>
       </c>
       <c r="G23" s="7" t="n"/>
-      <c r="H23" s="8" t="n"/>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>GaN Epi-Wafer</t>
+        </is>
+      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
           <t>묶음 60 — 같은 문구 4 곳</t>

--- a/content-export/04_사업영역_문구.xlsx
+++ b/content-export/04_사업영역_문구.xlsx
@@ -3472,7 +3472,7 @@
       </c>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div[1]/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>장 영문 제목</t>
+          <t>작은 제목</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -3506,7 +3506,7 @@
       <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div[1]/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3540,7 +3540,7 @@
       <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div[2]/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>

--- a/content-export/04_사업영역_문구.xlsx
+++ b/content-export/04_사업영역_문구.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화합물 전력 반도체" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$J$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$J$119</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'에너지 솔루션'!$A$1:$J$228</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'인공지능 플랫폼'!$A$1:$J$65</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'화합물 전력 반도체'!$A$1:$J$34</definedName>
@@ -527,7 +527,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 453 줄입니다.</t>
+          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 442 줄입니다.</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J130"/>
+  <dimension ref="A1:J119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1526,7 +1526,7 @@
       </c>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[1]/nav/div[3]/a[1]|text</t>
+          <t>/html/body/div[8]/div[1]/nav/div[3]/a|text</t>
         </is>
       </c>
     </row>
@@ -1541,26 +1541,32 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>인덱스 항목</t>
+          <t>인덱스 그룹 번호</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="inlineStr"/>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>11</v>
+      </c>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>충방전 공정 관리 시스템</t>
-        </is>
-      </c>
-      <c r="G21" s="7" t="n"/>
-      <c r="H21" s="8" t="n"/>
-      <c r="I21" s="5" t="inlineStr"/>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="G21" s="6" t="n"/>
+      <c r="H21" s="6" t="n"/>
+      <c r="I21" s="5" t="inlineStr">
+        <is>
+          <t>묶음 11 — 같은 문구 9 곳</t>
+        </is>
+      </c>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[1]/nav/div[3]/a[2]|text</t>
+          <t>/html/body/div[8]/div[1]/nav/div[4]/p/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -1575,32 +1581,32 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>인덱스 그룹 번호</t>
+          <t>인덱스 그룹 이름</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E22" s="5" t="n">
-        <v>11</v>
+        <v>4</v>
       </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="G22" s="6" t="n"/>
-      <c r="H22" s="6" t="n"/>
+          <t>이차전지 소재</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="8" t="n"/>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>묶음 11 — 같은 문구 9 곳</t>
+          <t>묶음 4 — 같은 문구 2 곳</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[1]/nav/div[4]/p/span[1]|text</t>
+          <t>/html/body/div[8]/div[1]/nav/div[4]/p/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -1615,7 +1621,7 @@
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>인덱스 그룹 이름</t>
+          <t>인덱스 항목</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
@@ -1624,23 +1630,27 @@
         </is>
       </c>
       <c r="E23" s="5" t="n">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>이차전지 소재</t>
+          <t>탄소 나노 튜브</t>
         </is>
       </c>
       <c r="G23" s="7" t="n"/>
-      <c r="H23" s="8" t="n"/>
+      <c r="H23" s="8" t="inlineStr">
+        <is>
+          <t>Carbon Nano Tube</t>
+        </is>
+      </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>묶음 4 — 같은 문구 2 곳</t>
+          <t>묶음 12 — 같은 문구 2 곳</t>
         </is>
       </c>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[1]/nav/div[4]/p/span[2]|text</t>
+          <t>/html/body/div[8]/div[1]/nav/div[4]/a[1]|text</t>
         </is>
       </c>
     </row>
@@ -1664,27 +1674,27 @@
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>탄소 나노 튜브</t>
+          <t>LiFSI 전해염</t>
         </is>
       </c>
       <c r="G24" s="7" t="n"/>
       <c r="H24" s="8" t="inlineStr">
         <is>
-          <t>Carbon Nano Tube</t>
+          <t>Electrolyte</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>묶음 12 — 같은 문구 2 곳</t>
+          <t>묶음 13 — 같은 문구 2 곳</t>
         </is>
       </c>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[1]/nav/div[4]/a[1]|text</t>
+          <t>/html/body/div[8]/div[1]/nav/div[4]/a[2]|text</t>
         </is>
       </c>
     </row>
@@ -1708,27 +1718,27 @@
         </is>
       </c>
       <c r="E25" s="5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>LiFSI 전해염</t>
+          <t>HNBR 바인더</t>
         </is>
       </c>
       <c r="G25" s="7" t="n"/>
       <c r="H25" s="8" t="inlineStr">
         <is>
-          <t>Electrolyte</t>
+          <t>HNBR Binder</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>묶음 13 — 같은 문구 2 곳</t>
+          <t>묶음 14 — 같은 문구 2 곳</t>
         </is>
       </c>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[1]/nav/div[4]/a[2]|text</t>
+          <t>/html/body/div[8]/div[1]/nav/div[4]/a[3]|text</t>
         </is>
       </c>
     </row>
@@ -1752,27 +1762,27 @@
         </is>
       </c>
       <c r="E26" s="5" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>HNBR 바인더</t>
+          <t>파우치셀 제조</t>
         </is>
       </c>
       <c r="G26" s="7" t="n"/>
       <c r="H26" s="8" t="inlineStr">
         <is>
-          <t>HNBR Binder</t>
+          <t>Pouch Cell Manufacturing</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>묶음 14 — 같은 문구 2 곳</t>
+          <t>묶음 15 — 같은 문구 2 곳</t>
         </is>
       </c>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[1]/nav/div[4]/a[3]|text</t>
+          <t>/html/body/div[8]/div[1]/nav/div[4]/a[4]|text</t>
         </is>
       </c>
     </row>
@@ -1795,28 +1805,18 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E27" s="5" t="n">
-        <v>15</v>
-      </c>
+      <c r="E27" s="5" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>파우치셀 제조</t>
+          <t>에이프로머티리얼즈</t>
         </is>
       </c>
       <c r="G27" s="7" t="n"/>
-      <c r="H27" s="8" t="inlineStr">
-        <is>
-          <t>Pouch Cell Manufacturing</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>묶음 15 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="H27" s="8" t="n"/>
+      <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[1]/nav/div[4]/a[4]|text</t>
+          <t>/html/body/div[8]/div[1]/nav/div[4]/a[5]|text</t>
         </is>
       </c>
     </row>
@@ -1831,26 +1831,32 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>인덱스 항목</t>
+          <t>장 번호</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="inlineStr"/>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>16</v>
+      </c>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>에이프로머티리얼즈</t>
-        </is>
-      </c>
-      <c r="G28" s="7" t="n"/>
-      <c r="H28" s="8" t="n"/>
-      <c r="I28" s="5" t="inlineStr"/>
+          <t>01234567890123456789-0123456789</t>
+        </is>
+      </c>
+      <c r="G28" s="6" t="n"/>
+      <c r="H28" s="6" t="n"/>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>묶음 16 — 같은 문구 4 곳</t>
+        </is>
+      </c>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[1]/nav/div[4]/a[5]|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[1]/span|text</t>
         </is>
       </c>
     </row>
@@ -1865,32 +1871,32 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>장 번호</t>
+          <t>그림 자리표시 문구</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>자리표시</t>
         </is>
       </c>
       <c r="E29" s="5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>01234567890123456789-0123456789</t>
-        </is>
-      </c>
-      <c r="G29" s="6" t="n"/>
-      <c r="H29" s="6" t="n"/>
+          <t>도표 or 이미지</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="8" t="n"/>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>묶음 16 — 같은 문구 4 곳</t>
+          <t>묶음 17 — 같은 문구 16 곳</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[1]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[1]/span|text</t>
         </is>
       </c>
     </row>
@@ -1905,32 +1911,26 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>그림 자리표시 문구</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>17</v>
-      </c>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>도표 or 이미지</t>
+          <t>신뢰성 검사 장비 외관</t>
         </is>
       </c>
       <c r="G30" s="7" t="n"/>
       <c r="H30" s="8" t="n"/>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>묶음 17 — 같은 문구 17 곳</t>
-        </is>
-      </c>
+      <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[1]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[3]/img|alt</t>
         </is>
       </c>
     </row>
@@ -1956,7 +1956,7 @@
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>신뢰성 검사 장비 외관</t>
+          <t>안전 펜스 안의 다관절 로봇과 제어반으로 이루어진 자동화 설비</t>
         </is>
       </c>
       <c r="G31" s="7" t="n"/>
@@ -1964,7 +1964,7 @@
       <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[3]/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[4]/img|alt</t>
         </is>
       </c>
     </row>
@@ -1990,7 +1990,7 @@
       <c r="E32" s="5" t="inlineStr"/>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>면압 충방전기 PLC 제어 화면</t>
+          <t>유리 접시에 담긴 단일벽·소수벽 CNT 분말</t>
         </is>
       </c>
       <c r="G32" s="7" t="n"/>
@@ -1998,7 +1998,7 @@
       <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[4]/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[5]/div[1]/div/img|alt</t>
         </is>
       </c>
     </row>
@@ -2013,32 +2013,26 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>그림 자리표시 문구</t>
+          <t>사진 설명 제목</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
-        </is>
-      </c>
-      <c r="E33" s="5" t="n">
-        <v>17</v>
-      </c>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="inlineStr"/>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>도표 or 이미지</t>
+          <t>단일벽/소수벽 CNT 분말</t>
         </is>
       </c>
       <c r="G33" s="7" t="n"/>
       <c r="H33" s="8" t="n"/>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>묶음 17 — 같은 문구 17 곳</t>
-        </is>
-      </c>
+      <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[5]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[5]/div[1]/p/b|text</t>
         </is>
       </c>
     </row>
@@ -2053,18 +2047,18 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>그림 대체글</t>
+          <t>사진 설명 본문</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>대체글</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr"/>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>유리 접시에 담긴 단일벽·소수벽 CNT 분말</t>
+          <t>비표면적 ≥ 300~1,000 m²/g</t>
         </is>
       </c>
       <c r="G34" s="7" t="n"/>
@@ -2072,7 +2066,7 @@
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[6]/div[1]/div/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[5]/div[1]/p/span|text</t>
         </is>
       </c>
     </row>
@@ -2087,18 +2081,18 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>사진 설명 제목</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>대체글</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr"/>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>단일벽/소수벽 CNT 분말</t>
+          <t>메스실린더에 담긴 단일벽·소수벽 CNT 분산액</t>
         </is>
       </c>
       <c r="G35" s="7" t="n"/>
@@ -2106,7 +2100,7 @@
       <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[6]/div[1]/p/b|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[5]/div[2]/div/img|alt</t>
         </is>
       </c>
     </row>
@@ -2121,7 +2115,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>사진 설명 본문</t>
+          <t>사진 설명 제목</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -2132,7 +2126,7 @@
       <c r="E36" s="5" t="inlineStr"/>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>비표면적 ≥ 300~1,000 m²/g</t>
+          <t>단일벽/소수벽 CNT 분산액</t>
         </is>
       </c>
       <c r="G36" s="7" t="n"/>
@@ -2140,7 +2134,7 @@
       <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[6]/div[1]/p/span|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[5]/div[2]/p/b|text</t>
         </is>
       </c>
     </row>
@@ -2155,18 +2149,18 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>그림 대체글</t>
+          <t>사진 설명 본문</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>대체글</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr"/>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>메스실린더에 담긴 단일벽·소수벽 CNT 분산액</t>
+          <t>CNT 함량 0.2 ~ 4.0 wt%</t>
         </is>
       </c>
       <c r="G37" s="7" t="n"/>
@@ -2174,7 +2168,7 @@
       <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[6]/div[2]/div/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[5]/div[2]/p/span|text</t>
         </is>
       </c>
     </row>
@@ -2189,18 +2183,18 @@
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>사진 설명 제목</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>대체글</t>
         </is>
       </c>
       <c r="E38" s="5" t="inlineStr"/>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>단일벽/소수벽 CNT 분산액</t>
+          <t>유리 접시에 담긴 전도성 카본블랙</t>
         </is>
       </c>
       <c r="G38" s="7" t="n"/>
@@ -2208,7 +2202,7 @@
       <c r="I38" s="5" t="inlineStr"/>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[6]/div[2]/p/b|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[5]/div[3]/div/img|alt</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2217,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>사진 설명 본문</t>
+          <t>사진 설명 제목</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -2234,7 +2228,7 @@
       <c r="E39" s="5" t="inlineStr"/>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>CNT 함량 0.2 ~ 4.0 wt%</t>
+          <t>전도성 카본블랙</t>
         </is>
       </c>
       <c r="G39" s="7" t="n"/>
@@ -2242,7 +2236,7 @@
       <c r="I39" s="5" t="inlineStr"/>
       <c r="J39" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[6]/div[2]/p/span|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[5]/div[3]/p/b|text</t>
         </is>
       </c>
     </row>
@@ -2257,18 +2251,18 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>그림 대체글</t>
+          <t>사진 설명 본문</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>대체글</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr"/>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>유리 접시에 담긴 전도성 카본블랙</t>
+          <t>비표면적 60 ~ 150 m²/g</t>
         </is>
       </c>
       <c r="G40" s="7" t="n"/>
@@ -2276,7 +2270,7 @@
       <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[6]/div[3]/div/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[5]/div[3]/p/span|text</t>
         </is>
       </c>
     </row>
@@ -2291,18 +2285,18 @@
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>사진 설명 제목</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>대체글</t>
         </is>
       </c>
       <c r="E41" s="5" t="inlineStr"/>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>전도성 카본블랙</t>
+          <t>플라스크에 담긴 LiFSI 전해염 분말</t>
         </is>
       </c>
       <c r="G41" s="7" t="n"/>
@@ -2310,7 +2304,7 @@
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[6]/div[3]/p/b|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[6]/img|alt</t>
         </is>
       </c>
     </row>
@@ -2325,18 +2319,18 @@
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>사진 설명 본문</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>대체글</t>
         </is>
       </c>
       <c r="E42" s="5" t="inlineStr"/>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>비표면적 60 ~ 150 m²/g</t>
+          <t>병에 담긴 HNBR 바인더 용액</t>
         </is>
       </c>
       <c r="G42" s="7" t="n"/>
@@ -2344,7 +2338,7 @@
       <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[6]/div[3]/p/span|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[7]/img|alt</t>
         </is>
       </c>
     </row>
@@ -2370,7 +2364,7 @@
       <c r="E43" s="5" t="inlineStr"/>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>플라스크에 담긴 LiFSI 전해염 분말</t>
+          <t>에이프로 머티리얼즈 파우치셀</t>
         </is>
       </c>
       <c r="G43" s="7" t="n"/>
@@ -2378,7 +2372,7 @@
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[7]/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[8]/img|alt</t>
         </is>
       </c>
     </row>
@@ -2393,26 +2387,32 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>그림 대체글</t>
+          <t>그림 자리표시 문구</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>대체글</t>
-        </is>
-      </c>
-      <c r="E44" s="5" t="inlineStr"/>
+          <t>자리표시</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>17</v>
+      </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>병에 담긴 HNBR 바인더 용액</t>
+          <t>도표 or 이미지</t>
         </is>
       </c>
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="8" t="n"/>
-      <c r="I44" s="5" t="inlineStr"/>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>묶음 17 — 같은 문구 16 곳</t>
+        </is>
+      </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[8]/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[9]/span|text</t>
         </is>
       </c>
     </row>
@@ -2422,31 +2422,41 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>좌측 인덱스</t>
+          <t>01-1 활성화 공정 &amp; 설비</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>그림 대체글</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>대체글</t>
-        </is>
-      </c>
-      <c r="E45" s="5" t="inlineStr"/>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>6</v>
+      </c>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>에이프로 머티리얼즈 파우치셀</t>
+          <t>활성화 공정 &amp; 설비</t>
         </is>
       </c>
       <c r="G45" s="7" t="n"/>
-      <c r="H45" s="8" t="n"/>
-      <c r="I45" s="5" t="inlineStr"/>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>Activation Process &amp; Equipment</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr">
+        <is>
+          <t>묶음 6 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[9]/img|alt</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -2456,37 +2466,31 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>좌측 인덱스</t>
+          <t>01-1 활성화 공정 &amp; 설비</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>그림 자리표시 문구</t>
+          <t>작은 제목</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="n">
-        <v>17</v>
-      </c>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr"/>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>도표 or 이미지</t>
+          <t>독보적인 기술력으로 완성하는 이차전지 활성화 통합 솔루션</t>
         </is>
       </c>
       <c r="G46" s="7" t="n"/>
       <c r="H46" s="8" t="n"/>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>묶음 17 — 같은 문구 17 곳</t>
-        </is>
-      </c>
+      <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[10]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2505,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -2509,28 +2513,18 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E47" s="5" t="n">
-        <v>6</v>
-      </c>
+      <c r="E47" s="5" t="inlineStr"/>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>활성화 공정 &amp; 설비</t>
+          <t>에이프로는 이차전지 활성화(Formation) 공정 전체 설비의 자체 제작 기술을 보유한 리딩 기업입니다. 공정에 필요한 모든 설비를 직접 생산하여 국내외 유수의 고객사에 안정적으로 공급하고 있습니다.</t>
         </is>
       </c>
       <c r="G47" s="7" t="n"/>
-      <c r="H47" s="8" t="inlineStr">
-        <is>
-          <t>Activation Process &amp; Equipment</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>묶음 6 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="H47" s="8" t="n"/>
+      <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -2545,7 +2539,7 @@
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>작은 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -2556,15 +2550,19 @@
       <c r="E48" s="5" t="inlineStr"/>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>독보적인 기술력으로 완성하는 이차전지 활성화 통합 솔루션</t>
+          <t>당사는 독보적인 정밀 충·방전 기술과 고도화된 자동화 역량을 기반으로, 배터리 셀 활성화 공정 전반을 아우르는 '통합 자동화 솔루션'을 제공합니다. 더불어 각 공정에서 발생하는 전압, 전류, 온도 등의 핵심 데이터를 정밀하게 측정하고 체계적으로 관리함으로써, 배터리 셀의 완성도 높은 품질과 생산 안정성을 극대화합니다.</t>
         </is>
       </c>
       <c r="G48" s="7" t="n"/>
-      <c r="H48" s="8" t="n"/>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Based on our unrivaled precision charge-discharge technology and advanced automation capabilities, we deliver comprehensive 'integrated automation solutions' that encompass the entire battery cell formation process. Furthermore, we precisely measure and systematically manage critical data—such as voltage, current, and temperature generated during each stage—to maximize the seamless quality and production stability of battery cells.</t>
+        </is>
+      </c>
       <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -2579,26 +2577,32 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="inlineStr"/>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>에이프로는 이차전지 활성화(Formation) 공정 전체 설비의 자체 제작 기술을 보유한 리딩 기업입니다. 공정에 필요한 모든 설비를 직접 생산하여 국내외 유수의 고객사에 안정적으로 공급하고 있습니다.</t>
-        </is>
-      </c>
-      <c r="G49" s="7" t="n"/>
-      <c r="H49" s="8" t="n"/>
-      <c r="I49" s="5" t="inlineStr"/>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="G49" s="6" t="n"/>
+      <c r="H49" s="6" t="n"/>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>묶음 5 — 같은 문구 12 곳</t>
+        </is>
+      </c>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[1]/b|text</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2617,7 @@
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -2624,19 +2628,15 @@
       <c r="E50" s="5" t="inlineStr"/>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>당사는 독보적인 정밀 충·방전 기술과 고도화된 자동화 역량을 기반으로, 배터리 셀 활성화 공정 전반을 아우르는 '통합 자동화 솔루션'을 제공합니다. 더불어 각 공정에서 발생하는 전압, 전류, 온도 등의 핵심 데이터를 정밀하게 측정하고 체계적으로 관리함으로써, 배터리 셀의 완성도 높은 품질과 생산 안정성을 극대화합니다.</t>
+          <t>1차 충전</t>
         </is>
       </c>
       <c r="G50" s="7" t="n"/>
-      <c r="H50" s="8" t="inlineStr">
-        <is>
-          <t>Based on our unrivaled precision charge-discharge technology and advanced automation capabilities, we deliver comprehensive 'integrated automation solutions' that encompass the entire battery cell formation process. Furthermore, we precisely measure and systematically manage critical data—such as voltage, current, and temperature generated during each stage—to maximize the seamless quality and production stability of battery cells.</t>
-        </is>
-      </c>
+      <c r="H50" s="8" t="n"/>
       <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[1]/span|text</t>
         </is>
       </c>
     </row>
@@ -2660,23 +2660,23 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>02</t>
         </is>
       </c>
       <c r="G51" s="6" t="n"/>
       <c r="H51" s="6" t="n"/>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>묶음 5 — 같은 문구 12 곳</t>
+          <t>묶음 8 — 같은 문구 12 곳</t>
         </is>
       </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[1]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[2]/b|text</t>
         </is>
       </c>
     </row>
@@ -2702,7 +2702,7 @@
       <c r="E52" s="5" t="inlineStr"/>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>1차 충전</t>
+          <t>디개싱 공정</t>
         </is>
       </c>
       <c r="G52" s="7" t="n"/>
@@ -2710,7 +2710,7 @@
       <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[1]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[2]/span|text</t>
         </is>
       </c>
     </row>
@@ -2734,23 +2734,23 @@
         </is>
       </c>
       <c r="E53" s="5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>02</t>
+          <t>03</t>
         </is>
       </c>
       <c r="G53" s="6" t="n"/>
       <c r="H53" s="6" t="n"/>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>묶음 8 — 같은 문구 12 곳</t>
+          <t>묶음 9 — 같은 문구 12 곳</t>
         </is>
       </c>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[2]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[3]/b|text</t>
         </is>
       </c>
     </row>
@@ -2776,7 +2776,7 @@
       <c r="E54" s="5" t="inlineStr"/>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>디개싱 공정</t>
+          <t>에이징 공정</t>
         </is>
       </c>
       <c r="G54" s="7" t="n"/>
@@ -2784,7 +2784,7 @@
       <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[2]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[3]/span|text</t>
         </is>
       </c>
     </row>
@@ -2808,23 +2808,23 @@
         </is>
       </c>
       <c r="E55" s="5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>03</t>
+          <t>04</t>
         </is>
       </c>
       <c r="G55" s="6" t="n"/>
       <c r="H55" s="6" t="n"/>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>묶음 9 — 같은 문구 12 곳</t>
+          <t>묶음 11 — 같은 문구 9 곳</t>
         </is>
       </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[3]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[4]/b|text</t>
         </is>
       </c>
     </row>
@@ -2850,7 +2850,7 @@
       <c r="E56" s="5" t="inlineStr"/>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>에이징 공정</t>
+          <t>충·방전</t>
         </is>
       </c>
       <c r="G56" s="7" t="n"/>
@@ -2858,7 +2858,7 @@
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[3]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[4]/span|text</t>
         </is>
       </c>
     </row>
@@ -2882,23 +2882,23 @@
         </is>
       </c>
       <c r="E57" s="5" t="n">
-        <v>11</v>
+        <v>18</v>
       </c>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>04</t>
+          <t>05</t>
         </is>
       </c>
       <c r="G57" s="6" t="n"/>
       <c r="H57" s="6" t="n"/>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>묶음 11 — 같은 문구 9 곳</t>
+          <t>묶음 18 — 같은 문구 2 곳</t>
         </is>
       </c>
       <c r="J57" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[4]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[5]/b|text</t>
         </is>
       </c>
     </row>
@@ -2924,7 +2924,7 @@
       <c r="E58" s="5" t="inlineStr"/>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>충·방전</t>
+          <t>품질 검사</t>
         </is>
       </c>
       <c r="G58" s="7" t="n"/>
@@ -2932,7 +2932,7 @@
       <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[4]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[5]/span|text</t>
         </is>
       </c>
     </row>
@@ -2955,24 +2955,18 @@
           <t>번호</t>
         </is>
       </c>
-      <c r="E59" s="5" t="n">
-        <v>18</v>
-      </c>
+      <c r="E59" s="5" t="inlineStr"/>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>05</t>
+          <t>06</t>
         </is>
       </c>
       <c r="G59" s="6" t="n"/>
       <c r="H59" s="6" t="n"/>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>묶음 18 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[5]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[6]/b|text</t>
         </is>
       </c>
     </row>
@@ -2998,7 +2992,7 @@
       <c r="E60" s="5" t="inlineStr"/>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>품질 검사</t>
+          <t>불량 선별</t>
         </is>
       </c>
       <c r="G60" s="7" t="n"/>
@@ -3006,7 +3000,7 @@
       <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[5]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[6]/span|text</t>
         </is>
       </c>
     </row>
@@ -3016,31 +3010,41 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>01-1 활성화 공정 &amp; 설비</t>
+          <t>01-2 글로벌 에이프로 네트워크</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="E61" s="5" t="inlineStr"/>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E61" s="5" t="n">
+        <v>7</v>
+      </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>06</t>
-        </is>
-      </c>
-      <c r="G61" s="6" t="n"/>
-      <c r="H61" s="6" t="n"/>
-      <c r="I61" s="5" t="inlineStr"/>
+          <t>글로벌 에이프로 네트워크</t>
+        </is>
+      </c>
+      <c r="G61" s="7" t="n"/>
+      <c r="H61" s="8" t="inlineStr">
+        <is>
+          <t>Global A-PRO Network</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>묶음 7 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J61" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[6]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -3050,12 +3054,12 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>01-1 활성화 공정 &amp; 설비</t>
+          <t>01-2 글로벌 에이프로 네트워크</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>작은 제목</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -3066,15 +3070,19 @@
       <c r="E62" s="5" t="inlineStr"/>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>불량 선별</t>
+          <t>전 세계 배터리 생산의 중심, 에이프로 글로벌 네트워크</t>
         </is>
       </c>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="8" t="n"/>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>At the Heart of Global Battery Production: A-PRO’s Global Network</t>
+        </is>
+      </c>
       <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/ol/li[6]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3089,7 +3097,7 @@
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
@@ -3097,28 +3105,22 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E63" s="5" t="n">
-        <v>7</v>
-      </c>
+      <c r="E63" s="5" t="inlineStr"/>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>글로벌 에이프로 네트워크</t>
+          <t>글로벌 시장을 선도하는 고객사를 위해 미국 미시간, 폴란드, 중국 남경, 인도네시아에 현지 법인을 구축했습니다.</t>
         </is>
       </c>
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>Global A-PRO Network</t>
-        </is>
-      </c>
-      <c r="I63" s="5" t="inlineStr">
-        <is>
-          <t>묶음 7 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+          <t>To support our global market-leading customers, we have established local subsidiaries in Michigan (USA), Poland, Nanjing (China), and Indonesia.</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3133,7 +3135,7 @@
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>작은 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -3144,19 +3146,19 @@
       <c r="E64" s="5" t="inlineStr"/>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>전 세계 배터리 생산의 중심, 에이프로 글로벌 네트워크</t>
+          <t>현지에 상주하는 전문 엔지니어들이 셋업부터 유지보수까지 원스톱(One-stop)으로 지원하며, 안정적인 해외 거점을 바탕으로 고객사의 성공을 함께합니다.</t>
         </is>
       </c>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>At the Heart of Global Battery Production: A-PRO’s Global Network</t>
+          <t>Our on-site expert engineers provide one-stop service from setup to maintenance, ensuring customer success through our robust global network.</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -3166,12 +3168,12 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>01-2 글로벌 에이프로 네트워크</t>
+          <t>02-1 Cycler(Cell&amp;Module)</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -3179,22 +3181,28 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E65" s="5" t="inlineStr"/>
+      <c r="E65" s="5" t="n">
+        <v>2</v>
+      </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>글로벌 시장을 선도하는 고객사를 위해 미국 미시간, 폴란드, 중국 남경, 인도네시아에 현지 법인을 구축했습니다.</t>
+          <t>Cycler(Cell&amp;Module)</t>
         </is>
       </c>
       <c r="G65" s="7" t="n"/>
       <c r="H65" s="8" t="inlineStr">
         <is>
-          <t>To support our global market-leading customers, we have established local subsidiaries in Michigan (USA), Poland, Nanjing (China), and Indonesia.</t>
-        </is>
-      </c>
-      <c r="I65" s="5" t="inlineStr"/>
+          <t>Cycler(Cell&amp;Module)</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>묶음 2 — 같은 문구 4 곳</t>
+        </is>
+      </c>
       <c r="J65" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -3204,12 +3212,12 @@
       </c>
       <c r="B66" s="5" t="inlineStr">
         <is>
-          <t>01-2 글로벌 에이프로 네트워크</t>
+          <t>02-1 Cycler(Cell&amp;Module)</t>
         </is>
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>작은 제목</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
@@ -3220,19 +3228,19 @@
       <c r="E66" s="5" t="inlineStr"/>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>현지에 상주하는 전문 엔지니어들이 셋업부터 유지보수까지 원스톱(One-stop)으로 지원하며, 안정적인 해외 거점을 바탕으로 고객사의 성공을 함께합니다.</t>
+          <t>배터리의 미래를 검증하는 고효율 친환경 사이클러</t>
         </is>
       </c>
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="8" t="inlineStr">
         <is>
-          <t>Our on-site expert engineers provide one-stop service from setup to maintenance, ensuring customer success through our robust global network.</t>
+          <t>High-Efficiency Eco-Friendly Cyclers Validating the Future of Batteries</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3247,7 +3255,7 @@
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
@@ -3255,28 +3263,22 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E67" s="5" t="n">
-        <v>2</v>
-      </c>
+      <c r="E67" s="5" t="inlineStr"/>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>Cycler(Cell&amp;Module)</t>
+          <t>에이프로의 이차전지 사이클러(Battery Cycler)는 독보적인 양방향 전력 제어와 에너지 회생 기술을 통해 배터리의 성능 평가를 최적화하고, 완벽한 제조 안정성을 확보합니다.</t>
         </is>
       </c>
       <c r="G67" s="7" t="n"/>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>Cycler(Cell&amp;Module)</t>
-        </is>
-      </c>
-      <c r="I67" s="5" t="inlineStr">
-        <is>
-          <t>묶음 2 — 같은 문구 4 곳</t>
-        </is>
-      </c>
+          <t>A-PRO’s Battery Cycler optimizes battery performance evaluation and ensures flawless manufacturing stability through unrivaled bidirectional power control and energy regeneration technology.</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3291,7 +3293,7 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
-          <t>작은 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D68" s="5" t="inlineStr">
@@ -3302,19 +3304,19 @@
       <c r="E68" s="5" t="inlineStr"/>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>배터리의 미래를 검증하는 고효율 친환경 사이클러</t>
+          <t>에이프로의 이차전지 사이클러는 배터리를 반복적으로 충·방전하여 성능, 효율성, 수명을 정밀하게 평가하는 핵심 테스트 장비입니다. 용량, 수명 주기(Cycle Life), 내부 저항을 정밀 측정하고 실제 사용 환경을 완벽히 시뮬레이션하여, 연구 개발 및 제조 단계에서 발생할 수 있는 열화 현상과 안전 문제를 사전에 빈틈없이 검출합니다.</t>
         </is>
       </c>
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>High-Efficiency Eco-Friendly Cyclers Validating the Future of Batteries</t>
+          <t>A-PRO’s Battery Cycler is an essential testing solution that precisely evaluates battery performance, efficiency, and lifespan through continuous charge and discharge cycles. By accurately measuring capacity, cycle life, and internal resistance, our cyclers replicate real-world operating conditions to flawlessly detect degradation and safety issues during the R&amp;D and manufacturing stages.</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -3340,19 +3342,19 @@
       <c r="E69" s="5" t="inlineStr"/>
       <c r="F69" s="6" t="inlineStr">
         <is>
-          <t>에이프로의 이차전지 사이클러(Battery Cycler)는 독보적인 양방향 전력 제어와 에너지 회생 기술을 통해 배터리의 성능 평가를 최적화하고, 완벽한 제조 안정성을 확보합니다.</t>
+          <t>특히 에이프로의 Cycler는 전류 공급(충전)과 흡수(방전)가 모두 가능한 양방향 전력 시스템과 혁신적인 에너지 회생(Regenerative) 기능을 탑재하고 있습니다. 방전 시 버려지는 에너지를 회수하여 전력망으로 되돌려주는 이 기술은 공장의 전력 낭비를 획기적으로 줄이고 냉각 부하를 저감하여, 가장 경제적이고 친환경적인 생산 환경을 완성합니다.</t>
         </is>
       </c>
       <c r="G69" s="7" t="n"/>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>A-PRO’s Battery Cycler optimizes battery performance evaluation and ensures flawless manufacturing stability through unrivaled bidirectional power control and energy regeneration technology.</t>
+          <t>In particular, A-PRO’s Cycler features an advanced bidirectional system capable of both supplying (charging) and absorbing (discharging) current, integrated with innovative energy regeneration technology. By capturing energy released during discharge and feeding it back into the power grid, this technology drastically reduces power waste and cooling loads, enabling an exceptionally economical and eco-friendly production environment.</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr"/>
       <c r="J69" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[4]|text</t>
         </is>
       </c>
     </row>
@@ -3362,12 +3364,12 @@
       </c>
       <c r="B70" s="5" t="inlineStr">
         <is>
-          <t>02-1 Cycler(Cell&amp;Module)</t>
+          <t>03-1 자동화 설비</t>
         </is>
       </c>
       <c r="C70" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
@@ -3375,22 +3377,28 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E70" s="5" t="inlineStr"/>
+      <c r="E70" s="5" t="n">
+        <v>10</v>
+      </c>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>에이프로의 이차전지 사이클러는 배터리를 반복적으로 충·방전하여 성능, 효율성, 수명을 정밀하게 평가하는 핵심 테스트 장비입니다. 용량, 수명 주기(Cycle Life), 내부 저항을 정밀 측정하고 실제 사용 환경을 완벽히 시뮬레이션하여, 연구 개발 및 제조 단계에서 발생할 수 있는 열화 현상과 안전 문제를 사전에 빈틈없이 검출합니다.</t>
+          <t>자동화 설비</t>
         </is>
       </c>
       <c r="G70" s="7" t="n"/>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>A-PRO’s Battery Cycler is an essential testing solution that precisely evaluates battery performance, efficiency, and lifespan through continuous charge and discharge cycles. By accurately measuring capacity, cycle life, and internal resistance, our cyclers replicate real-world operating conditions to flawlessly detect degradation and safety issues during the R&amp;D and manufacturing stages.</t>
-        </is>
-      </c>
-      <c r="I70" s="5" t="inlineStr"/>
+          <t>Automation System</t>
+        </is>
+      </c>
+      <c r="I70" s="5" t="inlineStr">
+        <is>
+          <t>묶음 10 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J70" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -3400,12 +3408,12 @@
       </c>
       <c r="B71" s="5" t="inlineStr">
         <is>
-          <t>02-1 Cycler(Cell&amp;Module)</t>
+          <t>03-1 자동화 설비</t>
         </is>
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>작은 제목</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -3416,19 +3424,15 @@
       <c r="E71" s="5" t="inlineStr"/>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>특히 에이프로의 Cycler는 전류 공급(충전)과 흡수(방전)가 모두 가능한 양방향 전력 시스템과 혁신적인 에너지 회생(Regenerative) 기능을 탑재하고 있습니다. 방전 시 버려지는 에너지를 회수하여 전력망으로 되돌려주는 이 기술은 공장의 전력 낭비를 획기적으로 줄이고 냉각 부하를 저감하여, 가장 경제적이고 친환경적인 생산 환경을 완성합니다.</t>
+          <t>스마트 팩토리를 완성하는 지능형 통합 제어 솔루션</t>
         </is>
       </c>
       <c r="G71" s="7" t="n"/>
-      <c r="H71" s="8" t="inlineStr">
-        <is>
-          <t>In particular, A-PRO’s Cycler features an advanced bidirectional system capable of both supplying (charging) and absorbing (discharging) current, integrated with innovative energy regeneration technology. By capturing energy released during discharge and feeding it back into the power grid, this technology drastically reduces power waste and cooling loads, enabling an exceptionally economical and eco-friendly production environment.</t>
-        </is>
-      </c>
+      <c r="H71" s="8" t="n"/>
       <c r="I71" s="5" t="inlineStr"/>
       <c r="J71" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[4]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3443,7 +3447,7 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -3451,28 +3455,18 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E72" s="5" t="n">
-        <v>10</v>
-      </c>
+      <c r="E72" s="5" t="inlineStr"/>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>자동화 설비</t>
+          <t>활성화 공정 전체 설비의 실시간 정밀 제어와 체계적인 데이터 관리를 통해 최고의 생산 가동 효율과 제조 안정성을 보장합니다.</t>
         </is>
       </c>
       <c r="G72" s="7" t="n"/>
-      <c r="H72" s="8" t="inlineStr">
-        <is>
-          <t>Automation System</t>
-        </is>
-      </c>
-      <c r="I72" s="5" t="inlineStr">
-        <is>
-          <t>묶음 10 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="H72" s="8" t="n"/>
+      <c r="I72" s="5" t="inlineStr"/>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3487,7 +3481,7 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>작은 제목</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -3498,15 +3492,19 @@
       <c r="E73" s="5" t="inlineStr"/>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>스마트 팩토리를 완성하는 지능형 통합 제어 솔루션</t>
+          <t>스마트 설비 제어</t>
         </is>
       </c>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="8" t="n"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>Smart Equipment Control</t>
+        </is>
+      </c>
       <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[1]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3521,7 +3519,7 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -3532,15 +3530,19 @@
       <c r="E74" s="5" t="inlineStr"/>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>활성화 공정 전체 설비의 실시간 정밀 제어와 체계적인 데이터 관리를 통해 최고의 생산 가동 효율과 제조 안정성을 보장합니다.</t>
+          <t>충방전기, 디개싱, 에이징 룸 등 공정 내 모든 하드웨어를 실시간 직접 제어합니다.</t>
         </is>
       </c>
       <c r="G74" s="7" t="n"/>
-      <c r="H74" s="8" t="n"/>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Direct, real-time hardware control of all production lines, including cyclers, degassing units, and aging rooms.</t>
+        </is>
+      </c>
       <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[1]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3566,19 +3568,19 @@
       <c r="E75" s="5" t="inlineStr"/>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>스마트 설비 제어</t>
+          <t>실시간 데이터 수집</t>
         </is>
       </c>
       <c r="G75" s="7" t="n"/>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>Smart Equipment Control</t>
+          <t>Real-Time Data Acquisition</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr"/>
       <c r="J75" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[1]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[2]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3604,19 +3606,19 @@
       <c r="E76" s="5" t="inlineStr"/>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>충방전기, 디개싱, 에이징 룸 등 공정 내 모든 하드웨어를 실시간 직접 제어합니다.</t>
+          <t>미세한 온도·압력·전압·전류 데이터를 정밀 측정하여 완벽한 품질 추적성을 확보합니다.</t>
         </is>
       </c>
       <c r="G76" s="7" t="n"/>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>Direct, real-time hardware control of all production lines, including cyclers, degassing units, and aging rooms.</t>
+          <t>Precision monitoring of voltage, current, temperature, and pressure for seamless quality traceability.</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr"/>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[1]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[2]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3642,19 +3644,19 @@
       <c r="E77" s="5" t="inlineStr"/>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>실시간 데이터 수집</t>
+          <t>지능형 안전 인터록</t>
         </is>
       </c>
       <c r="G77" s="7" t="n"/>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>Real-Time Data Acquisition</t>
+          <t>Intelligent Safety Interlock</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr"/>
       <c r="J77" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[2]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[3]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3680,19 +3682,19 @@
       <c r="E78" s="5" t="inlineStr"/>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>미세한 온도·압력·전압·전류 데이터를 정밀 측정하여 완벽한 품질 추적성을 확보합니다.</t>
+          <t>가스 누출, 과전압 등 이상 징후 감지 시 설비를 즉각 정지시켜 사고를 원천 차단합니다.</t>
         </is>
       </c>
       <c r="G78" s="7" t="n"/>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>Precision monitoring of voltage, current, temperature, and pressure for seamless quality traceability.</t>
+          <t>Advanced emergency system that instantly halts operations upon detecting hazards like gas leaks or overvoltage.</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr"/>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[2]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[3]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3718,19 +3720,19 @@
       <c r="E79" s="5" t="inlineStr"/>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>지능형 안전 인터록</t>
+          <t>유연한 상위 연동</t>
         </is>
       </c>
       <c r="G79" s="7" t="n"/>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>Intelligent Safety Interlock</t>
+          <t>Seamless Integration</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr"/>
       <c r="J79" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[3]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[4]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3756,19 +3758,19 @@
       <c r="E80" s="5" t="inlineStr"/>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>가스 누출, 과전압 등 이상 징후 감지 시 설비를 즉각 정지시켜 사고를 원천 차단합니다.</t>
+          <t>PC 및 MES와의 고속 통신으로 공정 데이터를 실시간 전송하고 레시피 명령을 완벽히 수행합니다.</t>
         </is>
       </c>
       <c r="G80" s="7" t="n"/>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>Advanced emergency system that instantly halts operations upon detecting hazards like gas leaks or overvoltage.</t>
+          <t>High-speed communication with upper-level systems (PCs/MES) to transmit process data and execute recipe commands flawlessly.</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr"/>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[3]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[4]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3778,12 +3780,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>03-1 자동화 설비</t>
+          <t>04-1 탄소 나노 튜브</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3791,22 +3793,28 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E81" s="5" t="inlineStr"/>
+      <c r="E81" s="5" t="n">
+        <v>12</v>
+      </c>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>유연한 상위 연동</t>
+          <t>탄소 나노 튜브</t>
         </is>
       </c>
       <c r="G81" s="7" t="n"/>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>Seamless Integration</t>
-        </is>
-      </c>
-      <c r="I81" s="5" t="inlineStr"/>
+          <t>Carbon Nano Tube</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>묶음 12 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J81" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[4]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[1]/h2|text</t>
         </is>
       </c>
     </row>
@@ -3816,12 +3824,12 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>03-1 자동화 설비</t>
+          <t>04-1 탄소 나노 튜브</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -3832,19 +3840,19 @@
       <c r="E82" s="5" t="inlineStr"/>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>PC 및 MES와의 고속 통신으로 공정 데이터를 실시간 전송하고 레시피 명령을 완벽히 수행합니다.</t>
+          <t>A-PRO Materials의 글로벌 소싱 네트워크를 활용하여 고품질의 탄소나노튜브(CNT) 소재를 안정적으로 공급합니다.</t>
         </is>
       </c>
       <c r="G82" s="7" t="n"/>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>High-speed communication with upper-level systems (PCs/MES) to transmit process data and execute recipe commands flawlessly.</t>
+          <t>We provide a stable supply of high-quality carbon nanotube (CNT) materials through A-PRO Materials' global sourcing network.</t>
         </is>
       </c>
       <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[4]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[1]/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3854,12 +3862,12 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>03-2 충방전 공정 관리 시스템</t>
+          <t>04-1 탄소 나노 튜브</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -3870,15 +3878,19 @@
       <c r="E83" s="5" t="inlineStr"/>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>충방전 공정 관리시스템</t>
+          <t>엄격한 품질 검증을 거친 CNT 소재를 통해 고객사의 배터리 에너지 밀도 향상과 고속 충전 성능 구현을 지원합니다.</t>
         </is>
       </c>
       <c r="G83" s="7" t="n"/>
-      <c r="H83" s="8" t="n"/>
+      <c r="H83" s="8" t="inlineStr">
+        <is>
+          <t>Through rigorously quality-verified CNT materials, we support our customers in enhancing battery energy density and enabling high-speed charging performance.</t>
+        </is>
+      </c>
       <c r="I83" s="5" t="inlineStr"/>
       <c r="J83" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[1]/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3888,12 +3900,12 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>03-2 충방전 공정 관리 시스템</t>
+          <t>04-1 탄소 나노 튜브</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>제품 단추 이름</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -3904,15 +3916,21 @@
       <c r="E84" s="5" t="inlineStr"/>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>생산 추적</t>
+          <t>SW/FW-
+CNT Powder</t>
         </is>
       </c>
       <c r="G84" s="7" t="n"/>
-      <c r="H84" s="8" t="n"/>
+      <c r="H84" s="8" t="inlineStr">
+        <is>
+          <t>SW/FW-
+CNT Powder</t>
+        </is>
+      </c>
       <c r="I84" s="5" t="inlineStr"/>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[1]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[1]/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -3922,12 +3940,12 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>03-2 충방전 공정 관리 시스템</t>
+          <t>04-1 탄소 나노 튜브</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>제품 단추 이름</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -3938,15 +3956,21 @@
       <c r="E85" s="5" t="inlineStr"/>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>배터리 셀의 바코드를 스캔하여 활성화 공정의 시작부터 끝까지 전 제조 이력을 실시간으로 추적 및 관리합니다.</t>
+          <t>SW/FW-
+CNT Slurry</t>
         </is>
       </c>
       <c r="G85" s="7" t="n"/>
-      <c r="H85" s="8" t="n"/>
+      <c r="H85" s="8" t="inlineStr">
+        <is>
+          <t>SW/FW-
+CNT Slurry</t>
+        </is>
+      </c>
       <c r="I85" s="5" t="inlineStr"/>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[1]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[2]/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -3956,12 +3980,12 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>03-2 충방전 공정 관리 시스템</t>
+          <t>04-1 탄소 나노 튜브</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>제품 단추 이름</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -3972,15 +3996,21 @@
       <c r="E86" s="5" t="inlineStr"/>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>레시피 하향</t>
+          <t>Carbon
+Black</t>
         </is>
       </c>
       <c r="G86" s="7" t="n"/>
-      <c r="H86" s="8" t="n"/>
+      <c r="H86" s="8" t="inlineStr">
+        <is>
+          <t>Carbon
+Black</t>
+        </is>
+      </c>
       <c r="I86" s="5" t="inlineStr"/>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[2]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[3]/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -3990,12 +4020,12 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>03-2 충방전 공정 관리 시스템</t>
+          <t>04-2 LiFSI 전해염</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -4003,18 +4033,28 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E87" s="5" t="inlineStr"/>
+      <c r="E87" s="5" t="n">
+        <v>13</v>
+      </c>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>배터리 모델별로 정해진 충방전 조건, 에이징 시간 등의 세부 공정 레시피를 각 설비(PLC)에 자동으로 전달합니다.</t>
+          <t>LiFSI 전해염</t>
         </is>
       </c>
       <c r="G87" s="7" t="n"/>
-      <c r="H87" s="8" t="n"/>
-      <c r="I87" s="5" t="inlineStr"/>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>Electrolyte</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="inlineStr">
+        <is>
+          <t>묶음 13 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J87" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[2]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -4024,12 +4064,12 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>03-2 충방전 공정 관리 시스템</t>
+          <t>04-2 LiFSI 전해염</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -4040,15 +4080,19 @@
       <c r="E88" s="5" t="inlineStr"/>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>품질 판정</t>
+          <t>A-PRO Materials는 엄선된 공급망을 통해 고순도 LiFSI 전해염 소재를 안정적으로 공급합니다.</t>
         </is>
       </c>
       <c r="G88" s="7" t="n"/>
-      <c r="H88" s="8" t="n"/>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Materials provides a stable supply of high-purity LiFSI electrolyte salt through a carefully selected global supply network.</t>
+        </is>
+      </c>
       <c r="I88" s="5" t="inlineStr"/>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[3]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4058,12 +4102,12 @@
       </c>
       <c r="B89" s="5" t="inlineStr">
         <is>
-          <t>03-2 충방전 공정 관리 시스템</t>
+          <t>04-2 LiFSI 전해염</t>
         </is>
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -4074,15 +4118,19 @@
       <c r="E89" s="5" t="inlineStr"/>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>충방전 결과 데이터(용량, 저항 등)를 분석하여 해당 배터리 셀의 합격/불합격(Pass/Fail) 및 등급(Grading)을 판정합니다.</t>
+          <t>우수한 화학적 안정성을 바탕으로 고객사 배터리의 수명 연장과 고온 안정성 및 출력 향상을 지원합니다.</t>
         </is>
       </c>
       <c r="G89" s="7" t="n"/>
-      <c r="H89" s="8" t="n"/>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>Based on superior chemical stability, we support extended battery life, high-temperature stability, and improved output performance for our customers.</t>
+        </is>
+      </c>
       <c r="I89" s="5" t="inlineStr"/>
       <c r="J89" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[3]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4092,12 +4140,12 @@
       </c>
       <c r="B90" s="5" t="inlineStr">
         <is>
-          <t>03-2 충방전 공정 관리 시스템</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -4105,18 +4153,28 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E90" s="5" t="inlineStr"/>
+      <c r="E90" s="5" t="n">
+        <v>14</v>
+      </c>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>데이터 통합</t>
+          <t>HNBR 바인더</t>
         </is>
       </c>
       <c r="G90" s="7" t="n"/>
-      <c r="H90" s="8" t="n"/>
-      <c r="I90" s="5" t="inlineStr"/>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>HNBR Binder</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>묶음 14 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J90" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[4]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -4126,12 +4184,12 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>03-2 충방전 공정 관리 시스템</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -4142,15 +4200,19 @@
       <c r="E91" s="5" t="inlineStr"/>
       <c r="F91" s="6" t="inlineStr">
         <is>
-          <t>전체 공정의 생산량, 설비 가동률, 불량률 등의 통계 데이터를 시각화하여 공장 전반의 생산 효율성을 최적화합니다.</t>
+          <t>PVDF 바인더의 일부 대체 가능성을 검토할 수 있는 HNBR 바인더 소재입니다.</t>
         </is>
       </c>
       <c r="G91" s="7" t="n"/>
-      <c r="H91" s="8" t="n"/>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>HNBR is a binder material that can be evaluated as a partial alternative to PVDF binders.</t>
+        </is>
+      </c>
       <c r="I91" s="5" t="inlineStr"/>
       <c r="J91" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/ul/li[4]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4160,12 +4222,12 @@
       </c>
       <c r="B92" s="5" t="inlineStr">
         <is>
-          <t>04-1 탄소 나노 튜브</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -4173,28 +4235,22 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E92" s="5" t="n">
-        <v>12</v>
-      </c>
+      <c r="E92" s="5" t="inlineStr"/>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>탄소 나노 튜브</t>
+          <t>우수한 결합력과 유연성, 전극 저항 감소 효과를 통해 배터리의 고율 충·방전 성능과 안정성 향상에 기여할 수 있습니다.</t>
         </is>
       </c>
       <c r="G92" s="7" t="n"/>
       <c r="H92" s="8" t="inlineStr">
         <is>
-          <t>Carbon Nano Tube</t>
-        </is>
-      </c>
-      <c r="I92" s="5" t="inlineStr">
-        <is>
-          <t>묶음 12 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+          <t>With excellent bonding strength, flexibility, and reduced electrode resistance, it can contribute to improved high-rate charge/discharge performance and stability.</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr"/>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div[1]/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4204,12 +4260,12 @@
       </c>
       <c r="B93" s="5" t="inlineStr">
         <is>
-          <t>04-1 탄소 나노 튜브</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -4220,19 +4276,15 @@
       <c r="E93" s="5" t="inlineStr"/>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials의 글로벌 소싱 네트워크를 활용하여 고품질의 탄소나노튜브(CNT) 소재를 안정적으로 공급합니다.</t>
+          <t>PVDF 대체</t>
         </is>
       </c>
       <c r="G93" s="7" t="n"/>
-      <c r="H93" s="8" t="inlineStr">
-        <is>
-          <t>We provide a stable supply of high-quality carbon nanotube (CNT) materials through A-PRO Materials' global sourcing network.</t>
-        </is>
-      </c>
+      <c r="H93" s="8" t="n"/>
       <c r="I93" s="5" t="inlineStr"/>
       <c r="J93" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div[1]/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul/li[1]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4242,12 +4294,12 @@
       </c>
       <c r="B94" s="5" t="inlineStr">
         <is>
-          <t>04-1 탄소 나노 튜브</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
@@ -4258,19 +4310,15 @@
       <c r="E94" s="5" t="inlineStr"/>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>엄격한 품질 검증을 거친 CNT 소재를 통해 고객사의 배터리 에너지 밀도 향상과 고속 충전 성능 구현을 지원합니다.</t>
+          <t>기존 불소계 바인더의 5~15% 이상을 친환경 HNBR로 대체.</t>
         </is>
       </c>
       <c r="G94" s="7" t="n"/>
-      <c r="H94" s="8" t="inlineStr">
-        <is>
-          <t>Through rigorously quality-verified CNT materials, we support our customers in enhancing battery energy density and enabling high-speed charging performance.</t>
-        </is>
-      </c>
+      <c r="H94" s="8" t="n"/>
       <c r="I94" s="5" t="inlineStr"/>
       <c r="J94" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div[1]/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul/li[1]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4280,12 +4328,12 @@
       </c>
       <c r="B95" s="5" t="inlineStr">
         <is>
-          <t>04-1 탄소 나노 튜브</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>제품 단추 이름</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -4296,21 +4344,15 @@
       <c r="E95" s="5" t="inlineStr"/>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>SW/FW-
-CNT Powder</t>
+          <t>고율 충방전 특성</t>
         </is>
       </c>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="8" t="inlineStr">
-        <is>
-          <t>SW/FW-
-CNT Powder</t>
-        </is>
-      </c>
+      <c r="H95" s="8" t="n"/>
       <c r="I95" s="5" t="inlineStr"/>
       <c r="J95" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div[2]/button[1]/span[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul/li[2]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4320,12 +4362,12 @@
       </c>
       <c r="B96" s="5" t="inlineStr">
         <is>
-          <t>04-1 탄소 나노 튜브</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>제품 단추 이름</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -4336,21 +4378,15 @@
       <c r="E96" s="5" t="inlineStr"/>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>SW/FW-
-CNT Slurry</t>
+          <t>10C 고속 충전 조건에서도 우수한 용량 유지.</t>
         </is>
       </c>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="8" t="inlineStr">
-        <is>
-          <t>SW/FW-
-CNT Slurry</t>
-        </is>
-      </c>
+      <c r="H96" s="8" t="n"/>
       <c r="I96" s="5" t="inlineStr"/>
       <c r="J96" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div[2]/button[2]/span[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul/li[2]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4360,12 +4396,12 @@
       </c>
       <c r="B97" s="5" t="inlineStr">
         <is>
-          <t>04-1 탄소 나노 튜브</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>제품 단추 이름</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -4376,21 +4412,15 @@
       <c r="E97" s="5" t="inlineStr"/>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>Carbon
-Black</t>
+          <t>내부 저항 감소</t>
         </is>
       </c>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="8" t="inlineStr">
-        <is>
-          <t>Carbon
-Black</t>
-        </is>
-      </c>
+      <c r="H97" s="8" t="n"/>
       <c r="I97" s="5" t="inlineStr"/>
       <c r="J97" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div[2]/button[3]/span[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul/li[3]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4400,12 +4430,12 @@
       </c>
       <c r="B98" s="5" t="inlineStr">
         <is>
-          <t>04-2 LiFSI 전해염</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -4413,28 +4443,18 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E98" s="5" t="n">
-        <v>13</v>
-      </c>
+      <c r="E98" s="5" t="inlineStr"/>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>LiFSI 전해염</t>
+          <t>젖음성 개선으로 이온 전달 및 계면 저항 최소화.</t>
         </is>
       </c>
       <c r="G98" s="7" t="n"/>
-      <c r="H98" s="8" t="inlineStr">
-        <is>
-          <t>Electrolyte</t>
-        </is>
-      </c>
-      <c r="I98" s="5" t="inlineStr">
-        <is>
-          <t>묶음 13 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="H98" s="8" t="n"/>
+      <c r="I98" s="5" t="inlineStr"/>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul/li[3]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4444,12 +4464,12 @@
       </c>
       <c r="B99" s="5" t="inlineStr">
         <is>
-          <t>04-2 LiFSI 전해염</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
@@ -4460,19 +4480,15 @@
       <c r="E99" s="5" t="inlineStr"/>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials는 엄선된 공급망을 통해 고순도 LiFSI 전해염 소재를 안정적으로 공급합니다.</t>
+          <t>높은 강도 및 유연성</t>
         </is>
       </c>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Materials provides a stable supply of high-purity LiFSI electrolyte salt through a carefully selected global supply network.</t>
-        </is>
-      </c>
+      <c r="H99" s="8" t="n"/>
       <c r="I99" s="5" t="inlineStr"/>
       <c r="J99" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul/li[4]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4482,12 +4498,12 @@
       </c>
       <c r="B100" s="5" t="inlineStr">
         <is>
-          <t>04-2 LiFSI 전해염</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -4498,19 +4514,15 @@
       <c r="E100" s="5" t="inlineStr"/>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>우수한 화학적 안정성을 바탕으로 고객사 배터리의 수명 연장과 고온 안정성 및 출력 향상을 지원합니다.</t>
+          <t>전극 활물질 부피 변화 흡수, 탈락 방지.</t>
         </is>
       </c>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="8" t="inlineStr">
-        <is>
-          <t>Based on superior chemical stability, we support extended battery life, high-temperature stability, and improved output performance for our customers.</t>
-        </is>
-      </c>
+      <c r="H100" s="8" t="n"/>
       <c r="I100" s="5" t="inlineStr"/>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul/li[4]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4525,7 +4537,7 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -4533,28 +4545,18 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E101" s="5" t="n">
-        <v>14</v>
-      </c>
+      <c r="E101" s="5" t="inlineStr"/>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>HNBR 바인더</t>
+          <t>SWCNT 분산 최적화</t>
         </is>
       </c>
       <c r="G101" s="7" t="n"/>
-      <c r="H101" s="8" t="inlineStr">
-        <is>
-          <t>HNBR Binder</t>
-        </is>
-      </c>
-      <c r="I101" s="5" t="inlineStr">
-        <is>
-          <t>묶음 14 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="H101" s="8" t="n"/>
+      <c r="I101" s="5" t="inlineStr"/>
       <c r="J101" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul/li[5]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4569,7 +4571,7 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
@@ -4580,19 +4582,15 @@
       <c r="E102" s="5" t="inlineStr"/>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>PVDF 바인더의 일부 대체 가능성을 검토할 수 있는 HNBR 바인더 소재입니다.</t>
+          <t>단일벽 탄소나노튜브의 응집 해소, 점도 감소.</t>
         </is>
       </c>
       <c r="G102" s="7" t="n"/>
-      <c r="H102" s="8" t="inlineStr">
-        <is>
-          <t>HNBR is a binder material that can be evaluated as a partial alternative to PVDF binders.</t>
-        </is>
-      </c>
+      <c r="H102" s="8" t="n"/>
       <c r="I102" s="5" t="inlineStr"/>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul/li[5]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4602,12 +4600,12 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -4615,22 +4613,28 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E103" s="5" t="inlineStr"/>
+      <c r="E103" s="5" t="n">
+        <v>15</v>
+      </c>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>우수한 결합력과 유연성, 전극 저항 감소 효과를 통해 배터리의 고율 충·방전 성능과 안정성 향상에 기여할 수 있습니다.</t>
+          <t>파우치셀 제조</t>
         </is>
       </c>
       <c r="G103" s="7" t="n"/>
       <c r="H103" s="8" t="inlineStr">
         <is>
-          <t>With excellent bonding strength, flexibility, and reduced electrode resistance, it can contribute to improved high-rate charge/discharge performance and stability.</t>
-        </is>
-      </c>
-      <c r="I103" s="5" t="inlineStr"/>
+          <t>Pouch Cell Manufacturing</t>
+        </is>
+      </c>
+      <c r="I103" s="5" t="inlineStr">
+        <is>
+          <t>묶음 15 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J103" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -4640,12 +4644,12 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -4656,15 +4660,19 @@
       <c r="E104" s="5" t="inlineStr"/>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>PVDF 대체</t>
+          <t>A-PRO Materials는 Lab-scale 파우치셀 제작 및 소재 적용성 검증 서비스를 제공합니다.</t>
         </is>
       </c>
       <c r="G104" s="7" t="n"/>
-      <c r="H104" s="8" t="n"/>
+      <c r="H104" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Materials provides lab-scale pouch cell fabrication and material validation services.</t>
+        </is>
+      </c>
       <c r="I104" s="5" t="inlineStr"/>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[1]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4674,12 +4682,12 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -4690,15 +4698,19 @@
       <c r="E105" s="5" t="inlineStr"/>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>기존 불소계 바인더의 5~15% 이상을 친환경 HNBR로 대체.</t>
+          <t>셀 설계부터 조립 공정, 품질 평가까지 통합 프로세스를 통해 고객사의 신소재 적용 가능성을 사전 검증합니다.</t>
         </is>
       </c>
       <c r="G105" s="7" t="n"/>
-      <c r="H105" s="8" t="n"/>
+      <c r="H105" s="8" t="inlineStr">
+        <is>
+          <t>Through an integrated process encompassing cell design, assembly, and quality evaluation, we help our clients pre-validate the applicability of new materials.</t>
+        </is>
+      </c>
       <c r="I105" s="5" t="inlineStr"/>
       <c r="J105" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[1]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4708,31 +4720,37 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E106" s="5" t="inlineStr"/>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E106" s="5" t="n">
+        <v>5</v>
+      </c>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>고율 충방전 특성</t>
-        </is>
-      </c>
-      <c r="G106" s="7" t="n"/>
-      <c r="H106" s="8" t="n"/>
-      <c r="I106" s="5" t="inlineStr"/>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="G106" s="6" t="n"/>
+      <c r="H106" s="6" t="n"/>
+      <c r="I106" s="5" t="inlineStr">
+        <is>
+          <t>묶음 5 — 같은 문구 12 곳</t>
+        </is>
+      </c>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[2]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[1]/b|text</t>
         </is>
       </c>
     </row>
@@ -4742,12 +4760,12 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
@@ -4758,7 +4776,7 @@
       <c r="E107" s="5" t="inlineStr"/>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>10C 고속 충전 조건에서도 우수한 용량 유지.</t>
+          <t>사양 협의</t>
         </is>
       </c>
       <c r="G107" s="7" t="n"/>
@@ -4766,7 +4784,7 @@
       <c r="I107" s="5" t="inlineStr"/>
       <c r="J107" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[2]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[1]/span|text</t>
         </is>
       </c>
     </row>
@@ -4776,31 +4794,37 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E108" s="5" t="inlineStr"/>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E108" s="5" t="n">
+        <v>8</v>
+      </c>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>내부 저항 감소</t>
-        </is>
-      </c>
-      <c r="G108" s="7" t="n"/>
-      <c r="H108" s="8" t="n"/>
-      <c r="I108" s="5" t="inlineStr"/>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="G108" s="6" t="n"/>
+      <c r="H108" s="6" t="n"/>
+      <c r="I108" s="5" t="inlineStr">
+        <is>
+          <t>묶음 8 — 같은 문구 12 곳</t>
+        </is>
+      </c>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[3]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[2]/b|text</t>
         </is>
       </c>
     </row>
@@ -4810,12 +4834,12 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
@@ -4826,7 +4850,7 @@
       <c r="E109" s="5" t="inlineStr"/>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>젖음성 개선으로 이온 전달 및 계면 저항 최소화.</t>
+          <t>소재 입고 및 검수</t>
         </is>
       </c>
       <c r="G109" s="7" t="n"/>
@@ -4834,7 +4858,7 @@
       <c r="I109" s="5" t="inlineStr"/>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[3]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[2]/span|text</t>
         </is>
       </c>
     </row>
@@ -4844,31 +4868,37 @@
       </c>
       <c r="B110" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E110" s="5" t="inlineStr"/>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E110" s="5" t="n">
+        <v>9</v>
+      </c>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>높은 강도 및 유연성</t>
-        </is>
-      </c>
-      <c r="G110" s="7" t="n"/>
-      <c r="H110" s="8" t="n"/>
-      <c r="I110" s="5" t="inlineStr"/>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="G110" s="6" t="n"/>
+      <c r="H110" s="6" t="n"/>
+      <c r="I110" s="5" t="inlineStr">
+        <is>
+          <t>묶음 9 — 같은 문구 12 곳</t>
+        </is>
+      </c>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[4]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[3]/b|text</t>
         </is>
       </c>
     </row>
@@ -4878,12 +4908,12 @@
       </c>
       <c r="B111" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
@@ -4894,7 +4924,7 @@
       <c r="E111" s="5" t="inlineStr"/>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>전극 활물질 부피 변화 흡수, 탈락 방지.</t>
+          <t>파우치셀 조립</t>
         </is>
       </c>
       <c r="G111" s="7" t="n"/>
@@ -4902,7 +4932,7 @@
       <c r="I111" s="5" t="inlineStr"/>
       <c r="J111" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[4]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[3]/span|text</t>
         </is>
       </c>
     </row>
@@ -4912,31 +4942,37 @@
       </c>
       <c r="B112" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C112" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D112" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E112" s="5" t="inlineStr"/>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E112" s="5" t="n">
+        <v>11</v>
+      </c>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>SWCNT 분산 최적화</t>
-        </is>
-      </c>
-      <c r="G112" s="7" t="n"/>
-      <c r="H112" s="8" t="n"/>
-      <c r="I112" s="5" t="inlineStr"/>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="G112" s="6" t="n"/>
+      <c r="H112" s="6" t="n"/>
+      <c r="I112" s="5" t="inlineStr">
+        <is>
+          <t>묶음 11 — 같은 문구 9 곳</t>
+        </is>
+      </c>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[5]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[4]/b|text</t>
         </is>
       </c>
     </row>
@@ -4946,12 +4982,12 @@
       </c>
       <c r="B113" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
@@ -4962,7 +4998,7 @@
       <c r="E113" s="5" t="inlineStr"/>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>단일벽 탄소나노튜브의 응집 해소, 점도 감소.</t>
+          <t>화성 공정</t>
         </is>
       </c>
       <c r="G113" s="7" t="n"/>
@@ -4970,7 +5006,7 @@
       <c r="I113" s="5" t="inlineStr"/>
       <c r="J113" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ul/li[5]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[4]/span|text</t>
         </is>
       </c>
     </row>
@@ -4985,36 +5021,32 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E114" s="5" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>파우치셀 제조</t>
-        </is>
-      </c>
-      <c r="G114" s="7" t="n"/>
-      <c r="H114" s="8" t="inlineStr">
-        <is>
-          <t>Pouch Cell Manufacturing</t>
-        </is>
-      </c>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="G114" s="6" t="n"/>
+      <c r="H114" s="6" t="n"/>
       <c r="I114" s="5" t="inlineStr">
         <is>
-          <t>묶음 15 — 같은 문구 2 곳</t>
+          <t>묶음 18 — 같은 문구 2 곳</t>
         </is>
       </c>
       <c r="J114" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[5]/b|text</t>
         </is>
       </c>
     </row>
@@ -5029,7 +5061,7 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
@@ -5040,19 +5072,15 @@
       <c r="E115" s="5" t="inlineStr"/>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials는 Lab-scale 파우치셀 제작 및 소재 적용성 검증 서비스를 제공합니다.</t>
+          <t>제품 출하</t>
         </is>
       </c>
       <c r="G115" s="7" t="n"/>
-      <c r="H115" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Materials provides lab-scale pouch cell fabrication and material validation services.</t>
-        </is>
-      </c>
+      <c r="H115" s="8" t="n"/>
       <c r="I115" s="5" t="inlineStr"/>
       <c r="J115" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[5]/span|text</t>
         </is>
       </c>
     </row>
@@ -5062,12 +5090,12 @@
       </c>
       <c r="B116" s="5" t="inlineStr">
         <is>
-          <t>04-4 파우치셀 제조</t>
+          <t>04-5 에이프로머티리얼즈</t>
         </is>
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -5078,19 +5106,15 @@
       <c r="E116" s="5" t="inlineStr"/>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>셀 설계부터 조립 공정, 품질 평가까지 통합 프로세스를 통해 고객사의 신소재 적용 가능성을 사전 검증합니다.</t>
+          <t>차세대 기술 개발</t>
         </is>
       </c>
       <c r="G116" s="7" t="n"/>
-      <c r="H116" s="8" t="inlineStr">
-        <is>
-          <t>Through an integrated process encompassing cell design, assembly, and quality evaluation, we help our clients pre-validate the applicability of new materials.</t>
-        </is>
-      </c>
+      <c r="H116" s="8" t="n"/>
       <c r="I116" s="5" t="inlineStr"/>
       <c r="J116" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -5100,37 +5124,35 @@
       </c>
       <c r="B117" s="5" t="inlineStr">
         <is>
-          <t>04-4 파우치셀 제조</t>
+          <t>04-5 에이프로머티리얼즈</t>
         </is>
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="E117" s="5" t="n">
-        <v>5</v>
-      </c>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E117" s="5" t="inlineStr"/>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="G117" s="6" t="n"/>
-      <c r="H117" s="6" t="n"/>
-      <c r="I117" s="5" t="inlineStr">
-        <is>
-          <t>묶음 5 — 같은 문구 12 곳</t>
-        </is>
-      </c>
+          <t>A-PRO Materials는 차세대 배터리 핵심 기술에 대한 지속적인 연구개발을 통해 미래 이차전지 시장에 대응해 나갑니다.</t>
+        </is>
+      </c>
+      <c r="G117" s="7" t="n"/>
+      <c r="H117" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Materials is working to respond to the future secondary battery market through continuous research and development of core next-generation battery technologies.</t>
+        </is>
+      </c>
+      <c r="I117" s="5" t="inlineStr"/>
       <c r="J117" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -5140,12 +5162,12 @@
       </c>
       <c r="B118" s="5" t="inlineStr">
         <is>
-          <t>04-4 파우치셀 제조</t>
+          <t>04-5 에이프로머티리얼즈</t>
         </is>
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
@@ -5156,15 +5178,19 @@
       <c r="E118" s="5" t="inlineStr"/>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>사양 협의</t>
+          <t>끊임없는 R&amp;D 혁신으로 기존 배터리의 한계를 극복하고, 고성능·고안정성 소재 및 셀 기술을 선제적으로 구현해 나갑니다.</t>
         </is>
       </c>
       <c r="G118" s="7" t="n"/>
-      <c r="H118" s="8" t="n"/>
+      <c r="H118" s="8" t="inlineStr">
+        <is>
+          <t>Through ongoing R&amp;D innovation, we work to overcome the limitations of existing batteries and proactively develop high-performance, high-stability materials and cell technologies.</t>
+        </is>
+      </c>
       <c r="I118" s="5" t="inlineStr"/>
       <c r="J118" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -5174,446 +5200,40 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>04-4 파우치셀 제조</t>
+          <t>04-5 에이프로머티리얼즈</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="E119" s="5" t="n">
-        <v>8</v>
-      </c>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E119" s="5" t="inlineStr"/>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="G119" s="6" t="n"/>
-      <c r="H119" s="6" t="n"/>
-      <c r="I119" s="5" t="inlineStr">
-        <is>
-          <t>묶음 8 — 같은 문구 12 곳</t>
-        </is>
-      </c>
+          <t>A-PRO Materials는 국내외 파트너들과의 협력을 통해 최적의 이차전지 소재 솔루션을 모색하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="G119" s="7" t="n"/>
+      <c r="H119" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Materials is exploring optimal secondary battery material solutions in collaboration with partners at home and abroad.</t>
+        </is>
+      </c>
+      <c r="I119" s="5" t="inlineStr"/>
       <c r="J119" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/b|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" s="5" t="n">
-        <v>119</v>
-      </c>
-      <c r="B120" s="5" t="inlineStr">
-        <is>
-          <t>04-4 파우치셀 제조</t>
-        </is>
-      </c>
-      <c r="C120" s="5" t="inlineStr">
-        <is>
-          <t>번호 목록 항목</t>
-        </is>
-      </c>
-      <c r="D120" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E120" s="5" t="inlineStr"/>
-      <c r="F120" s="6" t="inlineStr">
-        <is>
-          <t>소재 입고 및 검수</t>
-        </is>
-      </c>
-      <c r="G120" s="7" t="n"/>
-      <c r="H120" s="8" t="n"/>
-      <c r="I120" s="5" t="inlineStr"/>
-      <c r="J120" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/span|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" s="5" t="n">
-        <v>120</v>
-      </c>
-      <c r="B121" s="5" t="inlineStr">
-        <is>
-          <t>04-4 파우치셀 제조</t>
-        </is>
-      </c>
-      <c r="C121" s="5" t="inlineStr">
-        <is>
-          <t>번호 목록 번호</t>
-        </is>
-      </c>
-      <c r="D121" s="5" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="E121" s="5" t="n">
-        <v>9</v>
-      </c>
-      <c r="F121" s="6" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="G121" s="6" t="n"/>
-      <c r="H121" s="6" t="n"/>
-      <c r="I121" s="5" t="inlineStr">
-        <is>
-          <t>묶음 9 — 같은 문구 12 곳</t>
-        </is>
-      </c>
-      <c r="J121" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/b|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" s="5" t="n">
-        <v>121</v>
-      </c>
-      <c r="B122" s="5" t="inlineStr">
-        <is>
-          <t>04-4 파우치셀 제조</t>
-        </is>
-      </c>
-      <c r="C122" s="5" t="inlineStr">
-        <is>
-          <t>번호 목록 항목</t>
-        </is>
-      </c>
-      <c r="D122" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E122" s="5" t="inlineStr"/>
-      <c r="F122" s="6" t="inlineStr">
-        <is>
-          <t>파우치셀 조립</t>
-        </is>
-      </c>
-      <c r="G122" s="7" t="n"/>
-      <c r="H122" s="8" t="n"/>
-      <c r="I122" s="5" t="inlineStr"/>
-      <c r="J122" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/span|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" s="5" t="n">
-        <v>122</v>
-      </c>
-      <c r="B123" s="5" t="inlineStr">
-        <is>
-          <t>04-4 파우치셀 제조</t>
-        </is>
-      </c>
-      <c r="C123" s="5" t="inlineStr">
-        <is>
-          <t>번호 목록 번호</t>
-        </is>
-      </c>
-      <c r="D123" s="5" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="E123" s="5" t="n">
-        <v>11</v>
-      </c>
-      <c r="F123" s="6" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="G123" s="6" t="n"/>
-      <c r="H123" s="6" t="n"/>
-      <c r="I123" s="5" t="inlineStr">
-        <is>
-          <t>묶음 11 — 같은 문구 9 곳</t>
-        </is>
-      </c>
-      <c r="J123" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[4]/b|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" s="5" t="n">
-        <v>123</v>
-      </c>
-      <c r="B124" s="5" t="inlineStr">
-        <is>
-          <t>04-4 파우치셀 제조</t>
-        </is>
-      </c>
-      <c r="C124" s="5" t="inlineStr">
-        <is>
-          <t>번호 목록 항목</t>
-        </is>
-      </c>
-      <c r="D124" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E124" s="5" t="inlineStr"/>
-      <c r="F124" s="6" t="inlineStr">
-        <is>
-          <t>화성 공정</t>
-        </is>
-      </c>
-      <c r="G124" s="7" t="n"/>
-      <c r="H124" s="8" t="n"/>
-      <c r="I124" s="5" t="inlineStr"/>
-      <c r="J124" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[4]/span|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" s="5" t="n">
-        <v>124</v>
-      </c>
-      <c r="B125" s="5" t="inlineStr">
-        <is>
-          <t>04-4 파우치셀 제조</t>
-        </is>
-      </c>
-      <c r="C125" s="5" t="inlineStr">
-        <is>
-          <t>번호 목록 번호</t>
-        </is>
-      </c>
-      <c r="D125" s="5" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="E125" s="5" t="n">
-        <v>18</v>
-      </c>
-      <c r="F125" s="6" t="inlineStr">
-        <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="G125" s="6" t="n"/>
-      <c r="H125" s="6" t="n"/>
-      <c r="I125" s="5" t="inlineStr">
-        <is>
-          <t>묶음 18 — 같은 문구 2 곳</t>
-        </is>
-      </c>
-      <c r="J125" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[5]/b|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" s="5" t="n">
-        <v>125</v>
-      </c>
-      <c r="B126" s="5" t="inlineStr">
-        <is>
-          <t>04-4 파우치셀 제조</t>
-        </is>
-      </c>
-      <c r="C126" s="5" t="inlineStr">
-        <is>
-          <t>번호 목록 항목</t>
-        </is>
-      </c>
-      <c r="D126" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E126" s="5" t="inlineStr"/>
-      <c r="F126" s="6" t="inlineStr">
-        <is>
-          <t>제품 출하</t>
-        </is>
-      </c>
-      <c r="G126" s="7" t="n"/>
-      <c r="H126" s="8" t="n"/>
-      <c r="I126" s="5" t="inlineStr"/>
-      <c r="J126" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[5]/span|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" s="5" t="n">
-        <v>126</v>
-      </c>
-      <c r="B127" s="5" t="inlineStr">
-        <is>
-          <t>04-5 에이프로머티리얼즈</t>
-        </is>
-      </c>
-      <c r="C127" s="5" t="inlineStr">
-        <is>
-          <t>장 제목</t>
-        </is>
-      </c>
-      <c r="D127" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E127" s="5" t="inlineStr"/>
-      <c r="F127" s="6" t="inlineStr">
-        <is>
-          <t>차세대 기술 개발</t>
-        </is>
-      </c>
-      <c r="G127" s="7" t="n"/>
-      <c r="H127" s="8" t="n"/>
-      <c r="I127" s="5" t="inlineStr"/>
-      <c r="J127" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/div/h2|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" s="5" t="n">
-        <v>127</v>
-      </c>
-      <c r="B128" s="5" t="inlineStr">
-        <is>
-          <t>04-5 에이프로머티리얼즈</t>
-        </is>
-      </c>
-      <c r="C128" s="5" t="inlineStr">
-        <is>
-          <t>본문</t>
-        </is>
-      </c>
-      <c r="D128" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E128" s="5" t="inlineStr"/>
-      <c r="F128" s="6" t="inlineStr">
-        <is>
-          <t>A-PRO Materials는 차세대 배터리 핵심 기술에 대한 지속적인 연구개발을 통해 미래 이차전지 시장에 대응해 나갑니다.</t>
-        </is>
-      </c>
-      <c r="G128" s="7" t="n"/>
-      <c r="H128" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Materials is working to respond to the future secondary battery market through continuous research and development of core next-generation battery technologies.</t>
-        </is>
-      </c>
-      <c r="I128" s="5" t="inlineStr"/>
-      <c r="J128" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/div/div/p[1]|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" s="5" t="n">
-        <v>128</v>
-      </c>
-      <c r="B129" s="5" t="inlineStr">
-        <is>
-          <t>04-5 에이프로머티리얼즈</t>
-        </is>
-      </c>
-      <c r="C129" s="5" t="inlineStr">
-        <is>
-          <t>본문</t>
-        </is>
-      </c>
-      <c r="D129" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E129" s="5" t="inlineStr"/>
-      <c r="F129" s="6" t="inlineStr">
-        <is>
-          <t>끊임없는 R&amp;D 혁신으로 기존 배터리의 한계를 극복하고, 고성능·고안정성 소재 및 셀 기술을 선제적으로 구현해 나갑니다.</t>
-        </is>
-      </c>
-      <c r="G129" s="7" t="n"/>
-      <c r="H129" s="8" t="inlineStr">
-        <is>
-          <t>Through ongoing R&amp;D innovation, we work to overcome the limitations of existing batteries and proactively develop high-performance, high-stability materials and cell technologies.</t>
-        </is>
-      </c>
-      <c r="I129" s="5" t="inlineStr"/>
-      <c r="J129" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/div/div/p[2]|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" s="5" t="n">
-        <v>129</v>
-      </c>
-      <c r="B130" s="5" t="inlineStr">
-        <is>
-          <t>04-5 에이프로머티리얼즈</t>
-        </is>
-      </c>
-      <c r="C130" s="5" t="inlineStr">
-        <is>
-          <t>본문</t>
-        </is>
-      </c>
-      <c r="D130" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E130" s="5" t="inlineStr"/>
-      <c r="F130" s="6" t="inlineStr">
-        <is>
-          <t>A-PRO Materials는 국내외 파트너들과의 협력을 통해 최적의 이차전지 소재 솔루션을 모색하고 있습니다.</t>
-        </is>
-      </c>
-      <c r="G130" s="7" t="n"/>
-      <c r="H130" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Materials is exploring optimal secondary battery material solutions in collaboration with partners at home and abroad.</t>
-        </is>
-      </c>
-      <c r="I130" s="5" t="inlineStr"/>
-      <c r="J130" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[10]/div/div[2]/div/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J130"/>
+  <autoFilter ref="A1:J119"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -6768,7 +6388,7 @@
       <c r="H27" s="8" t="n"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 17 곳</t>
+          <t>묶음 17 — 같은 문구 16 곳</t>
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr">
@@ -6808,7 +6428,7 @@
       <c r="H28" s="8" t="n"/>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 17 곳</t>
+          <t>묶음 17 — 같은 문구 16 곳</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
@@ -6848,7 +6468,7 @@
       <c r="H29" s="8" t="n"/>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 17 곳</t>
+          <t>묶음 17 — 같은 문구 16 곳</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
@@ -6888,7 +6508,7 @@
       <c r="H30" s="8" t="n"/>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 17 곳</t>
+          <t>묶음 17 — 같은 문구 16 곳</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
@@ -6928,7 +6548,7 @@
       <c r="H31" s="8" t="n"/>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 17 곳</t>
+          <t>묶음 17 — 같은 문구 16 곳</t>
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">
@@ -6968,7 +6588,7 @@
       <c r="H32" s="8" t="n"/>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 17 곳</t>
+          <t>묶음 17 — 같은 문구 16 곳</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
@@ -15599,7 +15219,7 @@
       <c r="H31" s="8" t="n"/>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 17 곳</t>
+          <t>묶음 17 — 같은 문구 16 곳</t>
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">
@@ -15639,7 +15259,7 @@
       <c r="H32" s="8" t="n"/>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 17 곳</t>
+          <t>묶음 17 — 같은 문구 16 곳</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
@@ -15713,7 +15333,7 @@
       <c r="H34" s="8" t="n"/>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 17 곳</t>
+          <t>묶음 17 — 같은 문구 16 곳</t>
         </is>
       </c>
       <c r="J34" s="9" t="inlineStr">
@@ -15787,7 +15407,7 @@
       <c r="H36" s="8" t="n"/>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 17 곳</t>
+          <t>묶음 17 — 같은 문구 16 곳</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
@@ -15827,7 +15447,7 @@
       <c r="H37" s="8" t="n"/>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 17 곳</t>
+          <t>묶음 17 — 같은 문구 16 곳</t>
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
@@ -17784,7 +17404,7 @@
       <c r="H20" s="8" t="n"/>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 17 곳</t>
+          <t>묶음 17 — 같은 문구 16 곳</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
@@ -17824,7 +17444,7 @@
       <c r="H21" s="8" t="n"/>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 17 곳</t>
+          <t>묶음 17 — 같은 문구 16 곳</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
@@ -17864,7 +17484,7 @@
       <c r="H22" s="8" t="n"/>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 17 곳</t>
+          <t>묶음 17 — 같은 문구 16 곳</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">

--- a/content-export/04_사업영역_문구.xlsx
+++ b/content-export/04_사업영역_문구.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$J$119</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'에너지 솔루션'!$A$1:$J$228</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'인공지능 플랫폼'!$A$1:$J$65</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'인공지능 플랫폼'!$A$1:$J$68</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'화합물 전력 반도체'!$A$1:$J$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -527,7 +527,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 442 줄입니다.</t>
+          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 445 줄입니다.</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       <c r="H29" s="8" t="n"/>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 16 곳</t>
+          <t>묶음 17 — 같은 문구 14 곳</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
@@ -2407,7 +2407,7 @@
       <c r="H44" s="8" t="n"/>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 16 곳</t>
+          <t>묶음 17 — 같은 문구 14 곳</t>
         </is>
       </c>
       <c r="J44" s="9" t="inlineStr">
@@ -3916,15 +3916,13 @@
       <c r="E84" s="5" t="inlineStr"/>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>SW/FW-
-CNT Powder</t>
+          <t>SW/FW-CNT Powder</t>
         </is>
       </c>
       <c r="G84" s="7" t="n"/>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>SW/FW-
-CNT Powder</t>
+          <t>SW/FW-CNT Powder</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr"/>
@@ -3956,15 +3954,13 @@
       <c r="E85" s="5" t="inlineStr"/>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>SW/FW-
-CNT Slurry</t>
+          <t>SW/FW-CNT Slurry</t>
         </is>
       </c>
       <c r="G85" s="7" t="n"/>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>SW/FW-
-CNT Slurry</t>
+          <t>SW/FW-CNT Slurry</t>
         </is>
       </c>
       <c r="I85" s="5" t="inlineStr"/>
@@ -3996,15 +3992,13 @@
       <c r="E86" s="5" t="inlineStr"/>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>Carbon
-Black</t>
+          <t>Carbon Black</t>
         </is>
       </c>
       <c r="G86" s="7" t="n"/>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>Carbon
-Black</t>
+          <t>Carbon Black</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr"/>
@@ -6388,7 +6382,7 @@
       <c r="H27" s="8" t="n"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 16 곳</t>
+          <t>묶음 17 — 같은 문구 14 곳</t>
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr">
@@ -6428,7 +6422,7 @@
       <c r="H28" s="8" t="n"/>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 16 곳</t>
+          <t>묶음 17 — 같은 문구 14 곳</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
@@ -6468,7 +6462,7 @@
       <c r="H29" s="8" t="n"/>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 16 곳</t>
+          <t>묶음 17 — 같은 문구 14 곳</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
@@ -6508,7 +6502,7 @@
       <c r="H30" s="8" t="n"/>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 16 곳</t>
+          <t>묶음 17 — 같은 문구 14 곳</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
@@ -6548,7 +6542,7 @@
       <c r="H31" s="8" t="n"/>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 16 곳</t>
+          <t>묶음 17 — 같은 문구 14 곳</t>
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">
@@ -6588,7 +6582,7 @@
       <c r="H32" s="8" t="n"/>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 16 곳</t>
+          <t>묶음 17 — 같은 문구 14 곳</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
@@ -13979,7 +13973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J65"/>
+  <dimension ref="A1:J68"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -15199,32 +15193,26 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>그림 자리표시 문구</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>17</v>
-      </c>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>도표 or 이미지</t>
+          <t>배터리 셀 안전 분류 결과를 표와 히트맵으로 보여 주는 대시보드 화면</t>
         </is>
       </c>
       <c r="G31" s="7" t="n"/>
       <c r="H31" s="8" t="n"/>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>묶음 17 — 같은 문구 16 곳</t>
-        </is>
-      </c>
+      <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[3]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[3]/div[1]/div/img|alt</t>
         </is>
       </c>
     </row>
@@ -15239,32 +15227,26 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>그림 자리표시 문구</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>17</v>
-      </c>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr"/>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>도표 or 이미지</t>
+          <t>안전 진단 리포트를 등급과 막대로 보여 주는 모바일 화면</t>
         </is>
       </c>
       <c r="G32" s="7" t="n"/>
       <c r="H32" s="8" t="n"/>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>묶음 17 — 같은 문구 16 곳</t>
-        </is>
-      </c>
+      <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[4]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[3]/div[2]/div/img|alt</t>
         </is>
       </c>
     </row>
@@ -15290,7 +15272,7 @@
       <c r="E33" s="5" t="inlineStr"/>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>에이프로 전기자동차 급속 충전기</t>
+          <t>배터리 진단 결과를 항목별 백분율과 레이더 도표로 보여 주는 화면</t>
         </is>
       </c>
       <c r="G33" s="7" t="n"/>
@@ -15298,7 +15280,7 @@
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[5]/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[4]/img|alt</t>
         </is>
       </c>
     </row>
@@ -15313,32 +15295,26 @@
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>그림 자리표시 문구</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>17</v>
-      </c>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="inlineStr"/>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>도표 or 이미지</t>
+          <t>에이프로 전기자동차 급속 충전기</t>
         </is>
       </c>
       <c r="G34" s="7" t="n"/>
       <c r="H34" s="8" t="n"/>
-      <c r="I34" s="5" t="inlineStr">
-        <is>
-          <t>묶음 17 — 같은 문구 16 곳</t>
-        </is>
-      </c>
+      <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[6]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[5]/img|alt</t>
         </is>
       </c>
     </row>
@@ -15353,26 +15329,32 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>그림 대체글</t>
+          <t>그림 자리표시 문구</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>대체글</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="inlineStr"/>
+          <t>자리표시</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n">
+        <v>17</v>
+      </c>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>제어기를 얹은 전기자동차 구동 플랫폼</t>
+          <t>도표 or 이미지</t>
         </is>
       </c>
       <c r="G35" s="7" t="n"/>
       <c r="H35" s="8" t="n"/>
-      <c r="I35" s="5" t="inlineStr"/>
+      <c r="I35" s="5" t="inlineStr">
+        <is>
+          <t>묶음 17 — 같은 문구 14 곳</t>
+        </is>
+      </c>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[7]/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[6]/span|text</t>
         </is>
       </c>
     </row>
@@ -15387,32 +15369,26 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>그림 자리표시 문구</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="n">
-        <v>17</v>
-      </c>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="inlineStr"/>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>도표 or 이미지</t>
+          <t>제어기를 얹은 전기자동차 구동 플랫폼</t>
         </is>
       </c>
       <c r="G36" s="7" t="n"/>
       <c r="H36" s="8" t="n"/>
-      <c r="I36" s="5" t="inlineStr">
-        <is>
-          <t>묶음 17 — 같은 문구 16 곳</t>
-        </is>
-      </c>
+      <c r="I36" s="5" t="inlineStr"/>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[8]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[7]/img|alt</t>
         </is>
       </c>
     </row>
@@ -15447,12 +15423,12 @@
       <c r="H37" s="8" t="n"/>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 16 곳</t>
+          <t>묶음 17 — 같은 문구 14 곳</t>
         </is>
       </c>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[9]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[8]/span|text</t>
         </is>
       </c>
     </row>
@@ -15462,41 +15438,37 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>01-1 산업 안전 진단 솔루션</t>
+          <t>좌측 인덱스</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>그림 자리표시 문구</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>자리표시</t>
         </is>
       </c>
       <c r="E38" s="5" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>산업 안전 진단 솔루션</t>
+          <t>도표 or 이미지</t>
         </is>
       </c>
       <c r="G38" s="7" t="n"/>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>Industrial Safety Diagnosis Solution</t>
-        </is>
-      </c>
+      <c r="H38" s="8" t="n"/>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>묶음 50 — 같은 문구 2 곳</t>
+          <t>묶음 17 — 같은 문구 14 곳</t>
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[9]/span|text</t>
         </is>
       </c>
     </row>
@@ -15511,7 +15483,7 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
@@ -15519,22 +15491,28 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E39" s="5" t="inlineStr"/>
+      <c r="E39" s="5" t="n">
+        <v>50</v>
+      </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>에이프로의 산업 안전 진단 로봇 솔루션은 이동형 로봇과 AI, 원격 관제를 결합해 위험 구역의 안전 점검을 무인·지능화합니다.</t>
+          <t>산업 안전 진단 솔루션</t>
         </is>
       </c>
       <c r="G39" s="7" t="n"/>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>APRO's industrial safety diagnostic robot solution combines mobile robots, AI, and remote control to make safety inspections in hazardous areas unmanned and intelligent.</t>
-        </is>
-      </c>
-      <c r="I39" s="5" t="inlineStr"/>
+          <t>Industrial Safety Diagnosis Solution</t>
+        </is>
+      </c>
+      <c r="I39" s="5" t="inlineStr">
+        <is>
+          <t>묶음 50 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J39" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -15560,19 +15538,19 @@
       <c r="E40" s="5" t="inlineStr"/>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>안전장비 착용 진단, 설비 이상·누출 점검, 열화상·음향 분석 등 6대 핵심 점검을 자율적으로 수행하고 통합 관제로 실시간 모니터링합니다.</t>
+          <t>에이프로의 산업 안전 진단 로봇 솔루션은 이동형 로봇과 AI, 원격 관제를 결합해 위험 구역의 안전 점검을 무인·지능화합니다.</t>
         </is>
       </c>
       <c r="G40" s="7" t="n"/>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>It autonomously performs six key inspections, including safety equipment compliance checks, equipment anomaly and leak detection, and thermal imaging and acoustic analysis, while providing real-time monitoring through integrated control.</t>
+          <t>APRO's industrial safety diagnostic robot solution combines mobile robots, AI, and remote control to make safety inspections in hazardous areas unmanned and intelligent.</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -15598,19 +15576,19 @@
       <c r="E41" s="5" t="inlineStr"/>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>작업자의 위험 노출을 줄이고 점검의 일관성을 높여 선제적이고 스마트한 산업 운영을 지원합니다.</t>
+          <t>안전장비 착용 진단, 설비 이상·누출 점검, 열화상·음향 분석 등 6대 핵심 점검을 자율적으로 수행하고 통합 관제로 실시간 모니터링합니다.</t>
         </is>
       </c>
       <c r="G41" s="7" t="n"/>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>It supports proactive and smart industrial operations by reducing worker risk exposure and enhancing inspection consistency.</t>
+          <t>It autonomously performs six key inspections, including safety equipment compliance checks, equipment anomaly and leak detection, and thermal imaging and acoustic analysis, while providing real-time monitoring through integrated control.</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -15620,12 +15598,12 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>01-2 산업 안전 AI(로봇) 플랫폼</t>
+          <t>01-1 산업 안전 진단 솔루션</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D42" s="5" t="inlineStr">
@@ -15633,28 +15611,22 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E42" s="5" t="n">
-        <v>51</v>
-      </c>
+      <c r="E42" s="5" t="inlineStr"/>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>산업 안전 AI(로봇) 플랫폼</t>
+          <t>작업자의 위험 노출을 줄이고 점검의 일관성을 높여 선제적이고 스마트한 산업 운영을 지원합니다.</t>
         </is>
       </c>
       <c r="G42" s="7" t="n"/>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>Industrial safety robot platform</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>묶음 51 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+          <t>It supports proactive and smart industrial operations by reducing worker risk exposure and enhancing inspection consistency.</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -15669,7 +15641,7 @@
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -15677,22 +15649,28 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E43" s="5" t="inlineStr"/>
+      <c r="E43" s="5" t="n">
+        <v>51</v>
+      </c>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>별도의 조작 없이 자유로운 이동과, 좁은 공간이나 사람이 닿기 위험한 공간에도 접근해 정밀 점검을 수행할 수 있습니다.</t>
+          <t>산업 안전 AI(로봇) 플랫폼</t>
         </is>
       </c>
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>It allows for free movement without separate operation and enables precise inspections by accessing narrow spaces or areas dangerous for humans to reach.</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr"/>
+          <t>Industrial safety robot platform</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>묶음 51 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -15718,19 +15696,19 @@
       <c r="E44" s="5" t="inlineStr"/>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>에이프로 산업안전 AI 플랫폼은 딥러닝 기반 이미지 분석 기술을 통해 이상 징후나 결함을 감지하고 데이터를 실시간으로 관리 시스템에 전송해 즉각적 대응이 가능합니다.</t>
+          <t>별도의 조작 없이 자유로운 이동과, 좁은 공간이나 사람이 닿기 위험한 공간에도 접근해 정밀 점검을 수행할 수 있습니다.</t>
         </is>
       </c>
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>The A-PRO Industrial Safety AI Platform detects abnormal signs or defects through deep learning-based image analysis technology and transmits data to the management system in real time, enabling immediate response.</t>
+          <t>It allows for free movement without separate operation and enables precise inspections by accessing narrow spaces or areas dangerous for humans to reach.</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -15740,12 +15718,12 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>02-1 EV 배터리 안전 진단</t>
+          <t>01-2 산업 안전 AI(로봇) 플랫폼</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D45" s="5" t="inlineStr">
@@ -15753,24 +15731,22 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E45" s="5" t="n">
-        <v>52</v>
-      </c>
+      <c r="E45" s="5" t="inlineStr"/>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>EV 배터리 안전 진단</t>
+          <t>에이프로 산업안전 AI 플랫폼은 딥러닝 기반 이미지 분석 기술을 통해 이상 징후나 결함을 감지하고 데이터를 실시간으로 관리 시스템에 전송해 즉각적 대응이 가능합니다.</t>
         </is>
       </c>
       <c r="G45" s="7" t="n"/>
-      <c r="H45" s="8" t="n"/>
-      <c r="I45" s="5" t="inlineStr">
-        <is>
-          <t>묶음 52 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="H45" s="8" t="inlineStr">
+        <is>
+          <t>The A-PRO Industrial Safety AI Platform detects abnormal signs or defects through deep learning-based image analysis technology and transmits data to the management system in real time, enabling immediate response.</t>
+        </is>
+      </c>
+      <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -15785,7 +15761,7 @@
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -15793,22 +15769,24 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E46" s="5" t="inlineStr"/>
+      <c r="E46" s="5" t="n">
+        <v>52</v>
+      </c>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>전기자동차 충전 중 배터리 데이터를 실시간으로 수집하고, 개별 셀 전압과 모듈 온도 정보를 AI 기반으로 분석하여 배터리의 이상 징후와 안전 상태를 진단하는 솔루션입니다.</t>
+          <t>EV 배터리 안전 진단</t>
         </is>
       </c>
       <c r="G46" s="7" t="n"/>
-      <c r="H46" s="8" t="inlineStr">
-        <is>
-          <t>This is a solution that collects battery data in real time during electric vehicle charging and diagnoses signs of battery abnormalities and safety status by analyzing individual cell voltage and module temperature information using AI.</t>
-        </is>
-      </c>
-      <c r="I46" s="5" t="inlineStr"/>
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="5" t="inlineStr">
+        <is>
+          <t>묶음 52 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[1]/h2|text</t>
         </is>
       </c>
     </row>
@@ -15834,19 +15812,19 @@
       <c r="E47" s="5" t="inlineStr"/>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>이를 통해 배터리 사고 위험을 사전에 감지하고, 안전한 충전 환경 조성과 배터리 유지관리 효율 향상을 지원합니다.</t>
+          <t>전기자동차 충전 중 배터리 데이터를 실시간으로 수집하고, 개별 셀 전압과 모듈 온도 정보를 AI 기반으로 분석하여 배터리의 이상 징후와 안전 상태를 진단하는 솔루션입니다.</t>
         </is>
       </c>
       <c r="G47" s="7" t="n"/>
       <c r="H47" s="8" t="inlineStr">
         <is>
-          <t>Through this, it detects the risk of battery accidents in advance and supports the creation of a safe charging environment and the improvement of battery maintenance efficiency.</t>
+          <t>This is a solution that collects battery data in real time during electric vehicle charging and diagnoses signs of battery abnormalities and safety status by analyzing individual cell voltage and module temperature information using AI.</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[1]/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -15856,12 +15834,12 @@
       </c>
       <c r="B48" s="5" t="inlineStr">
         <is>
-          <t>02-2 EV 배터리 성능 진단</t>
+          <t>02-1 EV 배터리 안전 진단</t>
         </is>
       </c>
       <c r="C48" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D48" s="5" t="inlineStr">
@@ -15869,24 +15847,22 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E48" s="5" t="n">
-        <v>53</v>
-      </c>
+      <c r="E48" s="5" t="inlineStr"/>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>EV 배터리 성능 진단</t>
+          <t>이를 통해 배터리 사고 위험을 사전에 감지하고, 안전한 충전 환경 조성과 배터리 유지관리 효율 향상을 지원합니다.</t>
         </is>
       </c>
       <c r="G48" s="7" t="n"/>
-      <c r="H48" s="8" t="n"/>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>묶음 53 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="H48" s="8" t="inlineStr">
+        <is>
+          <t>Through this, it detects the risk of battery accidents in advance and supports the creation of a safe charging environment and the improvement of battery maintenance efficiency.</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[1]/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -15896,12 +15872,12 @@
       </c>
       <c r="B49" s="5" t="inlineStr">
         <is>
-          <t>02-2 EV 배터리 성능 진단</t>
+          <t>02-1 EV 배터리 안전 진단</t>
         </is>
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>제품 단추 이름</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -15912,19 +15888,15 @@
       <c r="E49" s="5" t="inlineStr"/>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>전기자동차 사용후 배터리의 성능과 잔존가치를 신속하게 평가하는 AI 기반 진단 솔루션입니다.</t>
+          <t>대시보드</t>
         </is>
       </c>
       <c r="G49" s="7" t="n"/>
-      <c r="H49" s="8" t="inlineStr">
-        <is>
-          <t>This is an AI-based diagnostic solution that rapidly evaluates the performance and residual value of used electric vehicle batteries.</t>
-        </is>
-      </c>
+      <c r="H49" s="8" t="n"/>
       <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[2]/button[1]/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -15934,12 +15906,12 @@
       </c>
       <c r="B50" s="5" t="inlineStr">
         <is>
-          <t>02-2 EV 배터리 성능 진단</t>
+          <t>02-1 EV 배터리 안전 진단</t>
         </is>
       </c>
       <c r="C50" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>제품 단추 이름</t>
         </is>
       </c>
       <c r="D50" s="5" t="inlineStr">
@@ -15950,19 +15922,15 @@
       <c r="E50" s="5" t="inlineStr"/>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>배터리의 부분 방전 데이터를 기존 배터리 학습 데이터와 비교·분석하여, 10분 이내에 배터리 셀의 가용 최대 용량과 건강 상태(SOH)를 예측합니다.</t>
+          <t>모바일</t>
         </is>
       </c>
       <c r="G50" s="7" t="n"/>
-      <c r="H50" s="8" t="inlineStr">
-        <is>
-          <t>Battery partial discharge data is compared and analyzed with existing battery training data to predict the maximum available capacity and state of health (SOH) of battery cells within 10 minutes.</t>
-        </is>
-      </c>
+      <c r="H50" s="8" t="n"/>
       <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[2]/button[2]/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -15972,7 +15940,7 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>03-1 급속 충전기</t>
+          <t>02-2 EV 배터리 성능 진단</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
@@ -15986,23 +15954,23 @@
         </is>
       </c>
       <c r="E51" s="5" t="n">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>급속 충전기</t>
+          <t>EV 배터리 성능 진단</t>
         </is>
       </c>
       <c r="G51" s="7" t="n"/>
       <c r="H51" s="8" t="n"/>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>묶음 54 — 같은 문구 2 곳</t>
+          <t>묶음 53 — 같은 문구 2 곳</t>
         </is>
       </c>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[1]/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -16012,12 +15980,12 @@
       </c>
       <c r="B52" s="5" t="inlineStr">
         <is>
-          <t>03-1 급속 충전기</t>
+          <t>02-2 EV 배터리 성능 진단</t>
         </is>
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>장 영문 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -16028,19 +15996,19 @@
       <c r="E52" s="5" t="inlineStr"/>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>PICKLE Station</t>
+          <t>전기자동차 사용후 배터리의 성능과 잔존가치를 신속하게 평가하는 AI 기반 진단 솔루션입니다.</t>
         </is>
       </c>
       <c r="G52" s="7" t="n"/>
       <c r="H52" s="8" t="inlineStr">
         <is>
-          <t>PICKLE Station</t>
+          <t>This is an AI-based diagnostic solution that rapidly evaluates the performance and residual value of used electric vehicle batteries.</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr"/>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[1]/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -16050,7 +16018,7 @@
       </c>
       <c r="B53" s="5" t="inlineStr">
         <is>
-          <t>03-1 급속 충전기</t>
+          <t>02-2 EV 배터리 성능 진단</t>
         </is>
       </c>
       <c r="C53" s="5" t="inlineStr">
@@ -16066,19 +16034,19 @@
       <c r="E53" s="5" t="inlineStr"/>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>에이프로의 전기자동차 충전 솔루션 PICKLE Station은 주거용 충전부터 공공 충전소와 상용 플릿까지 다양한 운영 환경에 대응하는 안정적인 충전 인프라입니다.</t>
+          <t>배터리의 부분 방전 데이터를 기존 배터리 학습 데이터와 비교·분석하여, 10분 이내에 배터리 셀의 가용 최대 용량과 건강 상태(SOH)를 예측합니다.</t>
         </is>
       </c>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>APRO’s electric vehicle charging solution, PICKLE Station, is a stable charging infrastructure designed to support diverse operating environments, ranging from residential charging to public charging stations and commercial fleets.</t>
+          <t>Battery partial discharge data is compared and analyzed with existing battery training data to predict the maximum available capacity and state of health (SOH) of battery cells within 10 minutes.</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[2]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -16093,7 +16061,7 @@
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -16101,22 +16069,24 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E54" s="5" t="inlineStr"/>
+      <c r="E54" s="5" t="n">
+        <v>54</v>
+      </c>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>원격 모니터링과 충전기 운영·유지관리 기능을 지원하며, 충전 운영 플랫폼 및 에너지관리시스템과 연계하여 충전 인프라를 효율적으로 관리하고 유연하게 확장할 수 있습니다.</t>
+          <t>급속 충전기</t>
         </is>
       </c>
       <c r="G54" s="7" t="n"/>
-      <c r="H54" s="8" t="inlineStr">
-        <is>
-          <t>It supports remote monitoring and charger operation and maintenance functions, and integrates with charging operation platforms and energy management systems to enable efficient management and flexible expansion of charging infrastructure.</t>
-        </is>
-      </c>
-      <c r="I54" s="5" t="inlineStr"/>
+      <c r="H54" s="8" t="n"/>
+      <c r="I54" s="5" t="inlineStr">
+        <is>
+          <t>묶음 54 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[2]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[1]/h2|text</t>
         </is>
       </c>
     </row>
@@ -16131,7 +16101,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 영문 제목</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -16142,19 +16112,19 @@
       <c r="E55" s="5" t="inlineStr"/>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>에이프로가 축적해 온 전력전자와 배터리 시스템 기술을 기반으로 안전하고 지속 가능한 전기 모빌리티 충전 생태계를 구축합니다.</t>
+          <t>PICKLE Station</t>
         </is>
       </c>
       <c r="G55" s="7" t="n"/>
       <c r="H55" s="8" t="inlineStr">
         <is>
-          <t>Based on the power electronics and battery system technologies accumulated by APRO, it builds a safe and sustainable electric mobility charging ecosystem.</t>
+          <t>PICKLE Station</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr"/>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[2]/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[1]/p|text</t>
         </is>
       </c>
     </row>
@@ -16164,12 +16134,12 @@
       </c>
       <c r="B56" s="5" t="inlineStr">
         <is>
-          <t>03-2 완속 충전기</t>
+          <t>03-1 급속 충전기</t>
         </is>
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -16177,24 +16147,22 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E56" s="5" t="n">
-        <v>55</v>
-      </c>
+      <c r="E56" s="5" t="inlineStr"/>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>완속 충전기</t>
+          <t>에이프로의 전기자동차 충전 솔루션 PICKLE Station은 주거용 충전부터 공공 충전소와 상용 플릿까지 다양한 운영 환경에 대응하는 안정적인 충전 인프라입니다.</t>
         </is>
       </c>
       <c r="G56" s="7" t="n"/>
-      <c r="H56" s="8" t="n"/>
-      <c r="I56" s="5" t="inlineStr">
-        <is>
-          <t>묶음 55 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="H56" s="8" t="inlineStr">
+        <is>
+          <t>APRO’s electric vehicle charging solution, PICKLE Station, is a stable charging infrastructure designed to support diverse operating environments, ranging from residential charging to public charging stations and commercial fleets.</t>
+        </is>
+      </c>
+      <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[2]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -16204,37 +16172,35 @@
       </c>
       <c r="B57" s="5" t="inlineStr">
         <is>
-          <t>03-2 완속 충전기</t>
+          <t>03-1 급속 충전기</t>
         </is>
       </c>
       <c r="C57" s="5" t="inlineStr">
         <is>
-          <t>본문(예정)</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
-        </is>
-      </c>
-      <c r="E57" s="5" t="n">
-        <v>59</v>
-      </c>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E57" s="5" t="inlineStr"/>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>텍스트 추가 예정</t>
+          <t>원격 모니터링과 충전기 운영·유지관리 기능을 지원하며, 충전 운영 플랫폼 및 에너지관리시스템과 연계하여 충전 인프라를 효율적으로 관리하고 유연하게 확장할 수 있습니다.</t>
         </is>
       </c>
       <c r="G57" s="7" t="n"/>
-      <c r="H57" s="8" t="n"/>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>묶음 59 — 같은 문구 3 곳</t>
-        </is>
-      </c>
+      <c r="H57" s="8" t="inlineStr">
+        <is>
+          <t>It supports remote monitoring and charger operation and maintenance functions, and integrates with charging operation platforms and energy management systems to enable efficient management and flexible expansion of charging infrastructure.</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[2]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -16244,12 +16210,12 @@
       </c>
       <c r="B58" s="5" t="inlineStr">
         <is>
-          <t>04-1 EV 제어기</t>
+          <t>03-1 급속 충전기</t>
         </is>
       </c>
       <c r="C58" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D58" s="5" t="inlineStr">
@@ -16257,24 +16223,22 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E58" s="5" t="n">
-        <v>56</v>
-      </c>
+      <c r="E58" s="5" t="inlineStr"/>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>EV 제어기</t>
+          <t>에이프로가 축적해 온 전력전자와 배터리 시스템 기술을 기반으로 안전하고 지속 가능한 전기 모빌리티 충전 생태계를 구축합니다.</t>
         </is>
       </c>
       <c r="G58" s="7" t="n"/>
-      <c r="H58" s="8" t="n"/>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>묶음 56 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="H58" s="8" t="inlineStr">
+        <is>
+          <t>Based on the power electronics and battery system technologies accumulated by APRO, it builds a safe and sustainable electric mobility charging ecosystem.</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[2]/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -16284,12 +16248,12 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>04-1 EV 제어기</t>
+          <t>03-2 완속 충전기</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -16297,22 +16261,24 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E59" s="5" t="inlineStr"/>
+      <c r="E59" s="5" t="n">
+        <v>55</v>
+      </c>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>에이프로는 ECOTRON 차량·자율주행 제어기의 국내 총판으로서 VCU, ZCU, EVCC, 자율주행 제어기 등 검증된 제어 솔루션을 공급합니다.</t>
+          <t>완속 충전기</t>
         </is>
       </c>
       <c r="G59" s="7" t="n"/>
-      <c r="H59" s="8" t="inlineStr">
-        <is>
-          <t>As the exclusive domestic distributor for ECOTRON vehicle and autonomous driving controllers, APRO supplies proven control solutions, including VCUs, ZCUs, EVCCs, and autonomous driving controllers.</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr"/>
+      <c r="H59" s="8" t="n"/>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>묶음 55 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J59" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -16322,35 +16288,37 @@
       </c>
       <c r="B60" s="5" t="inlineStr">
         <is>
-          <t>04-1 EV 제어기</t>
+          <t>03-2 완속 충전기</t>
         </is>
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>본문(예정)</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E60" s="5" t="inlineStr"/>
+          <t>자리표시</t>
+        </is>
+      </c>
+      <c r="E60" s="5" t="n">
+        <v>59</v>
+      </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>모든 제품은 ASIL-D 등급 반도체와 ISO 26262 기능안전, MATLAB/Simulink 모델 기반 개발을 지원해 높은 안전성과 개발 효율성을 제공합니다.</t>
+          <t>텍스트 추가 예정</t>
         </is>
       </c>
       <c r="G60" s="7" t="n"/>
-      <c r="H60" s="8" t="inlineStr">
-        <is>
-          <t>All products utilize ASIL-D grade semiconductors and support ISO 26262 functional safety and MATLAB/Simulink model-based development, providing high safety and development efficiency.</t>
-        </is>
-      </c>
-      <c r="I60" s="5" t="inlineStr"/>
+      <c r="H60" s="8" t="n"/>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>묶음 59 — 같은 문구 3 곳</t>
+        </is>
+      </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p|text</t>
         </is>
       </c>
     </row>
@@ -16365,7 +16333,7 @@
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
@@ -16373,22 +16341,24 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E61" s="5" t="inlineStr"/>
+      <c r="E61" s="5" t="n">
+        <v>56</v>
+      </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>에이프로는 국내 공급과 기술 지원을 통해 전기차·자율주행·무인 이동체·로봇 분야 고객의 제어기 도입을 지원합니다.</t>
+          <t>EV 제어기</t>
         </is>
       </c>
       <c r="G61" s="7" t="n"/>
-      <c r="H61" s="8" t="inlineStr">
-        <is>
-          <t>Through domestic supply and technical support, APRO facilitates the adoption of controllers by customers in the fields of electric vehicles, autonomous driving, unmanned vehicles, and robotics.</t>
-        </is>
-      </c>
-      <c r="I61" s="5" t="inlineStr"/>
+      <c r="H61" s="8" t="n"/>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>묶음 56 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J61" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -16398,12 +16368,12 @@
       </c>
       <c r="B62" s="5" t="inlineStr">
         <is>
-          <t>04-2 자율주행 제어기</t>
+          <t>04-1 EV 제어기</t>
         </is>
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -16411,24 +16381,22 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E62" s="5" t="n">
-        <v>57</v>
-      </c>
+      <c r="E62" s="5" t="inlineStr"/>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>자율주행 제어기</t>
+          <t>에이프로는 ECOTRON 차량·자율주행 제어기의 국내 총판으로서 VCU, ZCU, EVCC, 자율주행 제어기 등 검증된 제어 솔루션을 공급합니다.</t>
         </is>
       </c>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="8" t="n"/>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>묶음 57 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="H62" s="8" t="inlineStr">
+        <is>
+          <t>As the exclusive domestic distributor for ECOTRON vehicle and autonomous driving controllers, APRO supplies proven control solutions, including VCUs, ZCUs, EVCCs, and autonomous driving controllers.</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr"/>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -16438,37 +16406,35 @@
       </c>
       <c r="B63" s="5" t="inlineStr">
         <is>
-          <t>04-2 자율주행 제어기</t>
+          <t>04-1 EV 제어기</t>
         </is>
       </c>
       <c r="C63" s="5" t="inlineStr">
         <is>
-          <t>본문(예정)</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
-        </is>
-      </c>
-      <c r="E63" s="5" t="n">
-        <v>59</v>
-      </c>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E63" s="5" t="inlineStr"/>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>텍스트 추가 예정</t>
+          <t>모든 제품은 ASIL-D 등급 반도체와 ISO 26262 기능안전, MATLAB/Simulink 모델 기반 개발을 지원해 높은 안전성과 개발 효율성을 제공합니다.</t>
         </is>
       </c>
       <c r="G63" s="7" t="n"/>
-      <c r="H63" s="8" t="n"/>
-      <c r="I63" s="5" t="inlineStr">
-        <is>
-          <t>묶음 59 — 같은 문구 3 곳</t>
-        </is>
-      </c>
+      <c r="H63" s="8" t="inlineStr">
+        <is>
+          <t>All products utilize ASIL-D grade semiconductors and support ISO 26262 functional safety and MATLAB/Simulink model-based development, providing high safety and development efficiency.</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -16478,12 +16444,12 @@
       </c>
       <c r="B64" s="5" t="inlineStr">
         <is>
-          <t>04-3 소프트웨어</t>
+          <t>04-1 EV 제어기</t>
         </is>
       </c>
       <c r="C64" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D64" s="5" t="inlineStr">
@@ -16491,28 +16457,22 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E64" s="5" t="n">
-        <v>58</v>
-      </c>
+      <c r="E64" s="5" t="inlineStr"/>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어</t>
+          <t>에이프로는 국내 공급과 기술 지원을 통해 전기차·자율주행·무인 이동체·로봇 분야 고객의 제어기 도입을 지원합니다.</t>
         </is>
       </c>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>Software</t>
-        </is>
-      </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>묶음 58 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+          <t>Through domestic supply and technical support, APRO facilitates the adoption of controllers by customers in the fields of electric vehicles, autonomous driving, unmanned vehicles, and robotics.</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -16522,42 +16482,166 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>04-3 소프트웨어</t>
+          <t>04-2 자율주행 제어기</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>본문(예정)</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E65" s="5" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>텍스트 추가 예정</t>
+          <t>자율주행 제어기</t>
         </is>
       </c>
       <c r="G65" s="7" t="n"/>
       <c r="H65" s="8" t="n"/>
       <c r="I65" s="5" t="inlineStr">
         <is>
+          <t>묶음 57 — 같은 문구 2 곳</t>
+        </is>
+      </c>
+      <c r="J65" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/h2|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="5" t="n">
+        <v>65</v>
+      </c>
+      <c r="B66" s="5" t="inlineStr">
+        <is>
+          <t>04-2 자율주행 제어기</t>
+        </is>
+      </c>
+      <c r="C66" s="5" t="inlineStr">
+        <is>
+          <t>본문(예정)</t>
+        </is>
+      </c>
+      <c r="D66" s="5" t="inlineStr">
+        <is>
+          <t>자리표시</t>
+        </is>
+      </c>
+      <c r="E66" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="F66" s="6" t="inlineStr">
+        <is>
+          <t>텍스트 추가 예정</t>
+        </is>
+      </c>
+      <c r="G66" s="7" t="n"/>
+      <c r="H66" s="8" t="n"/>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
           <t>묶음 59 — 같은 문구 3 곳</t>
         </is>
       </c>
-      <c r="J65" s="9" t="inlineStr">
+      <c r="J66" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="n">
+        <v>66</v>
+      </c>
+      <c r="B67" s="5" t="inlineStr">
+        <is>
+          <t>04-3 소프트웨어</t>
+        </is>
+      </c>
+      <c r="C67" s="5" t="inlineStr">
+        <is>
+          <t>장 제목</t>
+        </is>
+      </c>
+      <c r="D67" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="F67" s="6" t="inlineStr">
+        <is>
+          <t>소프트웨어</t>
+        </is>
+      </c>
+      <c r="G67" s="7" t="n"/>
+      <c r="H67" s="8" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>묶음 58 — 같은 문구 2 곳</t>
+        </is>
+      </c>
+      <c r="J67" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/h2|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="5" t="n">
+        <v>67</v>
+      </c>
+      <c r="B68" s="5" t="inlineStr">
+        <is>
+          <t>04-3 소프트웨어</t>
+        </is>
+      </c>
+      <c r="C68" s="5" t="inlineStr">
+        <is>
+          <t>본문(예정)</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>자리표시</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>59</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>텍스트 추가 예정</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="n"/>
+      <c r="H68" s="8" t="n"/>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>묶음 59 — 같은 문구 3 곳</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p|text</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J65"/>
+  <autoFilter ref="A1:J68"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
@@ -17404,7 +17488,7 @@
       <c r="H20" s="8" t="n"/>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 16 곳</t>
+          <t>묶음 17 — 같은 문구 14 곳</t>
         </is>
       </c>
       <c r="J20" s="9" t="inlineStr">
@@ -17444,7 +17528,7 @@
       <c r="H21" s="8" t="n"/>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 16 곳</t>
+          <t>묶음 17 — 같은 문구 14 곳</t>
         </is>
       </c>
       <c r="J21" s="9" t="inlineStr">
@@ -17484,7 +17568,7 @@
       <c r="H22" s="8" t="n"/>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 16 곳</t>
+          <t>묶음 17 — 같은 문구 14 곳</t>
         </is>
       </c>
       <c r="J22" s="9" t="inlineStr">

--- a/content-export/04_사업영역_문구.xlsx
+++ b/content-export/04_사업영역_문구.xlsx
@@ -15306,7 +15306,7 @@
       <c r="E34" s="5" t="inlineStr"/>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>에이프로 전기자동차 급속 충전기</t>
+          <t>건물 앞 충전소에 나란히 선 에이프로 전기자동차 급속 충전기 세 대</t>
         </is>
       </c>
       <c r="G34" s="7" t="n"/>

--- a/content-export/04_사업영역_문구.xlsx
+++ b/content-export/04_사업영역_문구.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$J$119</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'에너지 솔루션'!$A$1:$J$228</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'인공지능 플랫폼'!$A$1:$J$68</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'인공지능 플랫폼'!$A$1:$J$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'화합물 전력 반도체'!$A$1:$J$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -527,7 +527,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 445 줄입니다.</t>
+          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 446 줄입니다.</t>
         </is>
       </c>
     </row>
@@ -13973,7 +13973,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J68"/>
+  <dimension ref="A1:J69"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -15280,7 +15280,7 @@
       <c r="I33" s="5" t="inlineStr"/>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[4]/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[4]/div[1]/div/img|alt</t>
         </is>
       </c>
     </row>
@@ -15306,7 +15306,7 @@
       <c r="E34" s="5" t="inlineStr"/>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>건물 앞 충전소에 나란히 선 에이프로 전기자동차 급속 충전기 세 대</t>
+          <t>업체와 차량, 배터리 제원을 입력하는 진단 준비 화면</t>
         </is>
       </c>
       <c r="G34" s="7" t="n"/>
@@ -15314,7 +15314,7 @@
       <c r="I34" s="5" t="inlineStr"/>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[5]/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[4]/div[2]/div/img|alt</t>
         </is>
       </c>
     </row>
@@ -15329,32 +15329,26 @@
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>그림 자리표시 문구</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>17</v>
-      </c>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="inlineStr"/>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>도표 or 이미지</t>
+          <t>건물 앞 충전소에 나란히 선 에이프로 전기자동차 급속 충전기 세 대</t>
         </is>
       </c>
       <c r="G35" s="7" t="n"/>
       <c r="H35" s="8" t="n"/>
-      <c r="I35" s="5" t="inlineStr">
-        <is>
-          <t>묶음 17 — 같은 문구 14 곳</t>
-        </is>
-      </c>
+      <c r="I35" s="5" t="inlineStr"/>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[6]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[5]/img|alt</t>
         </is>
       </c>
     </row>
@@ -15369,26 +15363,32 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>그림 대체글</t>
+          <t>그림 자리표시 문구</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>대체글</t>
-        </is>
-      </c>
-      <c r="E36" s="5" t="inlineStr"/>
+          <t>자리표시</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>17</v>
+      </c>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>제어기를 얹은 전기자동차 구동 플랫폼</t>
+          <t>도표 or 이미지</t>
         </is>
       </c>
       <c r="G36" s="7" t="n"/>
       <c r="H36" s="8" t="n"/>
-      <c r="I36" s="5" t="inlineStr"/>
+      <c r="I36" s="5" t="inlineStr">
+        <is>
+          <t>묶음 17 — 같은 문구 14 곳</t>
+        </is>
+      </c>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[7]/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[6]/span|text</t>
         </is>
       </c>
     </row>
@@ -15403,32 +15403,26 @@
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>그림 자리표시 문구</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
-        </is>
-      </c>
-      <c r="E37" s="5" t="n">
-        <v>17</v>
-      </c>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="inlineStr"/>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>도표 or 이미지</t>
+          <t>제어기를 얹은 전기자동차 구동 플랫폼</t>
         </is>
       </c>
       <c r="G37" s="7" t="n"/>
       <c r="H37" s="8" t="n"/>
-      <c r="I37" s="5" t="inlineStr">
-        <is>
-          <t>묶음 17 — 같은 문구 14 곳</t>
-        </is>
-      </c>
+      <c r="I37" s="5" t="inlineStr"/>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[8]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[7]/img|alt</t>
         </is>
       </c>
     </row>
@@ -15468,7 +15462,7 @@
       </c>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[9]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[8]/span|text</t>
         </is>
       </c>
     </row>
@@ -15478,41 +15472,37 @@
       </c>
       <c r="B39" s="5" t="inlineStr">
         <is>
-          <t>01-1 산업 안전 진단 솔루션</t>
+          <t>좌측 인덱스</t>
         </is>
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>그림 자리표시 문구</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>자리표시</t>
         </is>
       </c>
       <c r="E39" s="5" t="n">
-        <v>50</v>
+        <v>17</v>
       </c>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>산업 안전 진단 솔루션</t>
+          <t>도표 or 이미지</t>
         </is>
       </c>
       <c r="G39" s="7" t="n"/>
-      <c r="H39" s="8" t="inlineStr">
-        <is>
-          <t>Industrial Safety Diagnosis Solution</t>
-        </is>
-      </c>
+      <c r="H39" s="8" t="n"/>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>묶음 50 — 같은 문구 2 곳</t>
+          <t>묶음 17 — 같은 문구 14 곳</t>
         </is>
       </c>
       <c r="J39" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[9]/span|text</t>
         </is>
       </c>
     </row>
@@ -15527,7 +15517,7 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
@@ -15535,22 +15525,28 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E40" s="5" t="inlineStr"/>
+      <c r="E40" s="5" t="n">
+        <v>50</v>
+      </c>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>에이프로의 산업 안전 진단 로봇 솔루션은 이동형 로봇과 AI, 원격 관제를 결합해 위험 구역의 안전 점검을 무인·지능화합니다.</t>
+          <t>산업 안전 진단 솔루션</t>
         </is>
       </c>
       <c r="G40" s="7" t="n"/>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>APRO's industrial safety diagnostic robot solution combines mobile robots, AI, and remote control to make safety inspections in hazardous areas unmanned and intelligent.</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr"/>
+          <t>Industrial Safety Diagnosis Solution</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>묶음 50 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -15576,19 +15572,19 @@
       <c r="E41" s="5" t="inlineStr"/>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>안전장비 착용 진단, 설비 이상·누출 점검, 열화상·음향 분석 등 6대 핵심 점검을 자율적으로 수행하고 통합 관제로 실시간 모니터링합니다.</t>
+          <t>에이프로의 산업 안전 진단 로봇 솔루션은 이동형 로봇과 AI, 원격 관제를 결합해 위험 구역의 안전 점검을 무인·지능화합니다.</t>
         </is>
       </c>
       <c r="G41" s="7" t="n"/>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>It autonomously performs six key inspections, including safety equipment compliance checks, equipment anomaly and leak detection, and thermal imaging and acoustic analysis, while providing real-time monitoring through integrated control.</t>
+          <t>APRO's industrial safety diagnostic robot solution combines mobile robots, AI, and remote control to make safety inspections in hazardous areas unmanned and intelligent.</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -15614,19 +15610,19 @@
       <c r="E42" s="5" t="inlineStr"/>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>작업자의 위험 노출을 줄이고 점검의 일관성을 높여 선제적이고 스마트한 산업 운영을 지원합니다.</t>
+          <t>안전장비 착용 진단, 설비 이상·누출 점검, 열화상·음향 분석 등 6대 핵심 점검을 자율적으로 수행하고 통합 관제로 실시간 모니터링합니다.</t>
         </is>
       </c>
       <c r="G42" s="7" t="n"/>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>It supports proactive and smart industrial operations by reducing worker risk exposure and enhancing inspection consistency.</t>
+          <t>It autonomously performs six key inspections, including safety equipment compliance checks, equipment anomaly and leak detection, and thermal imaging and acoustic analysis, while providing real-time monitoring through integrated control.</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -15636,12 +15632,12 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>01-2 산업 안전 AI(로봇) 플랫폼</t>
+          <t>01-1 산업 안전 진단 솔루션</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D43" s="5" t="inlineStr">
@@ -15649,28 +15645,22 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E43" s="5" t="n">
-        <v>51</v>
-      </c>
+      <c r="E43" s="5" t="inlineStr"/>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>산업 안전 AI(로봇) 플랫폼</t>
+          <t>작업자의 위험 노출을 줄이고 점검의 일관성을 높여 선제적이고 스마트한 산업 운영을 지원합니다.</t>
         </is>
       </c>
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>Industrial safety robot platform</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>묶음 51 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+          <t>It supports proactive and smart industrial operations by reducing worker risk exposure and enhancing inspection consistency.</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -15685,7 +15675,7 @@
       </c>
       <c r="C44" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D44" s="5" t="inlineStr">
@@ -15693,22 +15683,28 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E44" s="5" t="inlineStr"/>
+      <c r="E44" s="5" t="n">
+        <v>51</v>
+      </c>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>별도의 조작 없이 자유로운 이동과, 좁은 공간이나 사람이 닿기 위험한 공간에도 접근해 정밀 점검을 수행할 수 있습니다.</t>
+          <t>산업 안전 AI(로봇) 플랫폼</t>
         </is>
       </c>
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>It allows for free movement without separate operation and enables precise inspections by accessing narrow spaces or areas dangerous for humans to reach.</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr"/>
+          <t>Industrial safety robot platform</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>묶음 51 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -15734,19 +15730,19 @@
       <c r="E45" s="5" t="inlineStr"/>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>에이프로 산업안전 AI 플랫폼은 딥러닝 기반 이미지 분석 기술을 통해 이상 징후나 결함을 감지하고 데이터를 실시간으로 관리 시스템에 전송해 즉각적 대응이 가능합니다.</t>
+          <t>별도의 조작 없이 자유로운 이동과, 좁은 공간이나 사람이 닿기 위험한 공간에도 접근해 정밀 점검을 수행할 수 있습니다.</t>
         </is>
       </c>
       <c r="G45" s="7" t="n"/>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>The A-PRO Industrial Safety AI Platform detects abnormal signs or defects through deep learning-based image analysis technology and transmits data to the management system in real time, enabling immediate response.</t>
+          <t>It allows for free movement without separate operation and enables precise inspections by accessing narrow spaces or areas dangerous for humans to reach.</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr"/>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -15756,12 +15752,12 @@
       </c>
       <c r="B46" s="5" t="inlineStr">
         <is>
-          <t>02-1 EV 배터리 안전 진단</t>
+          <t>01-2 산업 안전 AI(로봇) 플랫폼</t>
         </is>
       </c>
       <c r="C46" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D46" s="5" t="inlineStr">
@@ -15769,24 +15765,22 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E46" s="5" t="n">
-        <v>52</v>
-      </c>
+      <c r="E46" s="5" t="inlineStr"/>
       <c r="F46" s="6" t="inlineStr">
         <is>
-          <t>EV 배터리 안전 진단</t>
+          <t>에이프로 산업안전 AI 플랫폼은 딥러닝 기반 이미지 분석 기술을 통해 이상 징후나 결함을 감지하고 데이터를 실시간으로 관리 시스템에 전송해 즉각적 대응이 가능합니다.</t>
         </is>
       </c>
       <c r="G46" s="7" t="n"/>
-      <c r="H46" s="8" t="n"/>
-      <c r="I46" s="5" t="inlineStr">
-        <is>
-          <t>묶음 52 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>The A-PRO Industrial Safety AI Platform detects abnormal signs or defects through deep learning-based image analysis technology and transmits data to the management system in real time, enabling immediate response.</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="inlineStr"/>
       <c r="J46" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[1]/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -15801,7 +15795,7 @@
       </c>
       <c r="C47" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D47" s="5" t="inlineStr">
@@ -15809,22 +15803,24 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E47" s="5" t="inlineStr"/>
+      <c r="E47" s="5" t="n">
+        <v>52</v>
+      </c>
       <c r="F47" s="6" t="inlineStr">
         <is>
-          <t>전기자동차 충전 중 배터리 데이터를 실시간으로 수집하고, 개별 셀 전압과 모듈 온도 정보를 AI 기반으로 분석하여 배터리의 이상 징후와 안전 상태를 진단하는 솔루션입니다.</t>
+          <t>EV 배터리 안전 진단</t>
         </is>
       </c>
       <c r="G47" s="7" t="n"/>
-      <c r="H47" s="8" t="inlineStr">
-        <is>
-          <t>This is a solution that collects battery data in real time during electric vehicle charging and diagnoses signs of battery abnormalities and safety status by analyzing individual cell voltage and module temperature information using AI.</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr"/>
+      <c r="H47" s="8" t="n"/>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>묶음 52 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J47" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[1]/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[1]/h2|text</t>
         </is>
       </c>
     </row>
@@ -15850,19 +15846,19 @@
       <c r="E48" s="5" t="inlineStr"/>
       <c r="F48" s="6" t="inlineStr">
         <is>
-          <t>이를 통해 배터리 사고 위험을 사전에 감지하고, 안전한 충전 환경 조성과 배터리 유지관리 효율 향상을 지원합니다.</t>
+          <t>전기자동차 충전 중 배터리 데이터를 실시간으로 수집하고, 개별 셀 전압과 모듈 온도 정보를 AI 기반으로 분석하여 배터리의 이상 징후와 안전 상태를 진단하는 솔루션입니다.</t>
         </is>
       </c>
       <c r="G48" s="7" t="n"/>
       <c r="H48" s="8" t="inlineStr">
         <is>
-          <t>Through this, it detects the risk of battery accidents in advance and supports the creation of a safe charging environment and the improvement of battery maintenance efficiency.</t>
+          <t>This is a solution that collects battery data in real time during electric vehicle charging and diagnoses signs of battery abnormalities and safety status by analyzing individual cell voltage and module temperature information using AI.</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[1]/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[1]/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -15877,7 +15873,7 @@
       </c>
       <c r="C49" s="5" t="inlineStr">
         <is>
-          <t>제품 단추 이름</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D49" s="5" t="inlineStr">
@@ -15888,15 +15884,19 @@
       <c r="E49" s="5" t="inlineStr"/>
       <c r="F49" s="6" t="inlineStr">
         <is>
-          <t>대시보드</t>
+          <t>이를 통해 배터리 사고 위험을 사전에 감지하고, 안전한 충전 환경 조성과 배터리 유지관리 효율 향상을 지원합니다.</t>
         </is>
       </c>
       <c r="G49" s="7" t="n"/>
-      <c r="H49" s="8" t="n"/>
+      <c r="H49" s="8" t="inlineStr">
+        <is>
+          <t>Through this, it detects the risk of battery accidents in advance and supports the creation of a safe charging environment and the improvement of battery maintenance efficiency.</t>
+        </is>
+      </c>
       <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[2]/button[1]/span[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[1]/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -15922,7 +15922,7 @@
       <c r="E50" s="5" t="inlineStr"/>
       <c r="F50" s="6" t="inlineStr">
         <is>
-          <t>모바일</t>
+          <t>대시보드</t>
         </is>
       </c>
       <c r="G50" s="7" t="n"/>
@@ -15930,7 +15930,7 @@
       <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[2]/button[2]/span[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[2]/button[1]/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -15940,12 +15940,12 @@
       </c>
       <c r="B51" s="5" t="inlineStr">
         <is>
-          <t>02-2 EV 배터리 성능 진단</t>
+          <t>02-1 EV 배터리 안전 진단</t>
         </is>
       </c>
       <c r="C51" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>제품 단추 이름</t>
         </is>
       </c>
       <c r="D51" s="5" t="inlineStr">
@@ -15953,24 +15953,18 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E51" s="5" t="n">
-        <v>53</v>
-      </c>
+      <c r="E51" s="5" t="inlineStr"/>
       <c r="F51" s="6" t="inlineStr">
         <is>
-          <t>EV 배터리 성능 진단</t>
+          <t>모바일</t>
         </is>
       </c>
       <c r="G51" s="7" t="n"/>
       <c r="H51" s="8" t="n"/>
-      <c r="I51" s="5" t="inlineStr">
-        <is>
-          <t>묶음 53 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="I51" s="5" t="inlineStr"/>
       <c r="J51" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[2]/button[2]/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -15985,7 +15979,7 @@
       </c>
       <c r="C52" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D52" s="5" t="inlineStr">
@@ -15993,22 +15987,24 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E52" s="5" t="inlineStr"/>
+      <c r="E52" s="5" t="n">
+        <v>53</v>
+      </c>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>전기자동차 사용후 배터리의 성능과 잔존가치를 신속하게 평가하는 AI 기반 진단 솔루션입니다.</t>
+          <t>EV 배터리 성능 진단</t>
         </is>
       </c>
       <c r="G52" s="7" t="n"/>
-      <c r="H52" s="8" t="inlineStr">
-        <is>
-          <t>This is an AI-based diagnostic solution that rapidly evaluates the performance and residual value of used electric vehicle batteries.</t>
-        </is>
-      </c>
-      <c r="I52" s="5" t="inlineStr"/>
+      <c r="H52" s="8" t="n"/>
+      <c r="I52" s="5" t="inlineStr">
+        <is>
+          <t>묶음 53 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J52" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -16034,19 +16030,19 @@
       <c r="E53" s="5" t="inlineStr"/>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>배터리의 부분 방전 데이터를 기존 배터리 학습 데이터와 비교·분석하여, 10분 이내에 배터리 셀의 가용 최대 용량과 건강 상태(SOH)를 예측합니다.</t>
+          <t>전기자동차 사용후 배터리의 성능과 잔존가치를 신속하게 평가하는 AI 기반 진단 솔루션입니다.</t>
         </is>
       </c>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>Battery partial discharge data is compared and analyzed with existing battery training data to predict the maximum available capacity and state of health (SOH) of battery cells within 10 minutes.</t>
+          <t>This is an AI-based diagnostic solution that rapidly evaluates the performance and residual value of used electric vehicle batteries.</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr"/>
       <c r="J53" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -16056,12 +16052,12 @@
       </c>
       <c r="B54" s="5" t="inlineStr">
         <is>
-          <t>03-1 급속 충전기</t>
+          <t>02-2 EV 배터리 성능 진단</t>
         </is>
       </c>
       <c r="C54" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D54" s="5" t="inlineStr">
@@ -16069,24 +16065,22 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E54" s="5" t="n">
-        <v>54</v>
-      </c>
+      <c r="E54" s="5" t="inlineStr"/>
       <c r="F54" s="6" t="inlineStr">
         <is>
-          <t>급속 충전기</t>
+          <t>배터리의 부분 방전 데이터를 기존 배터리 학습 데이터와 비교·분석하여, 10분 이내에 배터리 셀의 가용 최대 용량과 건강 상태(SOH)를 예측합니다.</t>
         </is>
       </c>
       <c r="G54" s="7" t="n"/>
-      <c r="H54" s="8" t="n"/>
-      <c r="I54" s="5" t="inlineStr">
-        <is>
-          <t>묶음 54 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="H54" s="8" t="inlineStr">
+        <is>
+          <t>Battery partial discharge data is compared and analyzed with existing battery training data to predict the maximum available capacity and state of health (SOH) of battery cells within 10 minutes.</t>
+        </is>
+      </c>
+      <c r="I54" s="5" t="inlineStr"/>
       <c r="J54" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[1]/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -16101,7 +16095,7 @@
       </c>
       <c r="C55" s="5" t="inlineStr">
         <is>
-          <t>장 영문 제목</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D55" s="5" t="inlineStr">
@@ -16109,22 +16103,24 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E55" s="5" t="inlineStr"/>
+      <c r="E55" s="5" t="n">
+        <v>54</v>
+      </c>
       <c r="F55" s="6" t="inlineStr">
         <is>
-          <t>PICKLE Station</t>
+          <t>급속 충전기</t>
         </is>
       </c>
       <c r="G55" s="7" t="n"/>
-      <c r="H55" s="8" t="inlineStr">
-        <is>
-          <t>PICKLE Station</t>
-        </is>
-      </c>
-      <c r="I55" s="5" t="inlineStr"/>
+      <c r="H55" s="8" t="n"/>
+      <c r="I55" s="5" t="inlineStr">
+        <is>
+          <t>묶음 54 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[1]/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[1]/h2|text</t>
         </is>
       </c>
     </row>
@@ -16139,7 +16135,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 영문 제목</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -16150,19 +16146,19 @@
       <c r="E56" s="5" t="inlineStr"/>
       <c r="F56" s="6" t="inlineStr">
         <is>
-          <t>에이프로의 전기자동차 충전 솔루션 PICKLE Station은 주거용 충전부터 공공 충전소와 상용 플릿까지 다양한 운영 환경에 대응하는 안정적인 충전 인프라입니다.</t>
+          <t>PICKLE Station</t>
         </is>
       </c>
       <c r="G56" s="7" t="n"/>
       <c r="H56" s="8" t="inlineStr">
         <is>
-          <t>APRO’s electric vehicle charging solution, PICKLE Station, is a stable charging infrastructure designed to support diverse operating environments, ranging from residential charging to public charging stations and commercial fleets.</t>
+          <t>PICKLE Station</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[2]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[1]/p|text</t>
         </is>
       </c>
     </row>
@@ -16188,19 +16184,19 @@
       <c r="E57" s="5" t="inlineStr"/>
       <c r="F57" s="6" t="inlineStr">
         <is>
-          <t>원격 모니터링과 충전기 운영·유지관리 기능을 지원하며, 충전 운영 플랫폼 및 에너지관리시스템과 연계하여 충전 인프라를 효율적으로 관리하고 유연하게 확장할 수 있습니다.</t>
+          <t>에이프로의 전기자동차 충전 솔루션 PICKLE Station은 주거용 충전부터 공공 충전소와 상용 플릿까지 다양한 운영 환경에 대응하는 안정적인 충전 인프라입니다.</t>
         </is>
       </c>
       <c r="G57" s="7" t="n"/>
       <c r="H57" s="8" t="inlineStr">
         <is>
-          <t>It supports remote monitoring and charger operation and maintenance functions, and integrates with charging operation platforms and energy management systems to enable efficient management and flexible expansion of charging infrastructure.</t>
+          <t>APRO’s electric vehicle charging solution, PICKLE Station, is a stable charging infrastructure designed to support diverse operating environments, ranging from residential charging to public charging stations and commercial fleets.</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[2]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[2]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -16226,19 +16222,19 @@
       <c r="E58" s="5" t="inlineStr"/>
       <c r="F58" s="6" t="inlineStr">
         <is>
-          <t>에이프로가 축적해 온 전력전자와 배터리 시스템 기술을 기반으로 안전하고 지속 가능한 전기 모빌리티 충전 생태계를 구축합니다.</t>
+          <t>원격 모니터링과 충전기 운영·유지관리 기능을 지원하며, 충전 운영 플랫폼 및 에너지관리시스템과 연계하여 충전 인프라를 효율적으로 관리하고 유연하게 확장할 수 있습니다.</t>
         </is>
       </c>
       <c r="G58" s="7" t="n"/>
       <c r="H58" s="8" t="inlineStr">
         <is>
-          <t>Based on the power electronics and battery system technologies accumulated by APRO, it builds a safe and sustainable electric mobility charging ecosystem.</t>
+          <t>It supports remote monitoring and charger operation and maintenance functions, and integrates with charging operation platforms and energy management systems to enable efficient management and flexible expansion of charging infrastructure.</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[2]/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[2]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -16248,12 +16244,12 @@
       </c>
       <c r="B59" s="5" t="inlineStr">
         <is>
-          <t>03-2 완속 충전기</t>
+          <t>03-1 급속 충전기</t>
         </is>
       </c>
       <c r="C59" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D59" s="5" t="inlineStr">
@@ -16261,24 +16257,22 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E59" s="5" t="n">
-        <v>55</v>
-      </c>
+      <c r="E59" s="5" t="inlineStr"/>
       <c r="F59" s="6" t="inlineStr">
         <is>
-          <t>완속 충전기</t>
+          <t>에이프로가 축적해 온 전력전자와 배터리 시스템 기술을 기반으로 안전하고 지속 가능한 전기 모빌리티 충전 생태계를 구축합니다.</t>
         </is>
       </c>
       <c r="G59" s="7" t="n"/>
-      <c r="H59" s="8" t="n"/>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>묶음 55 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="H59" s="8" t="inlineStr">
+        <is>
+          <t>Based on the power electronics and battery system technologies accumulated by APRO, it builds a safe and sustainable electric mobility charging ecosystem.</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[2]/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -16293,32 +16287,32 @@
       </c>
       <c r="C60" s="5" t="inlineStr">
         <is>
-          <t>본문(예정)</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E60" s="5" t="n">
-        <v>59</v>
+        <v>55</v>
       </c>
       <c r="F60" s="6" t="inlineStr">
         <is>
-          <t>텍스트 추가 예정</t>
+          <t>완속 충전기</t>
         </is>
       </c>
       <c r="G60" s="7" t="n"/>
       <c r="H60" s="8" t="n"/>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>묶음 59 — 같은 문구 3 곳</t>
+          <t>묶음 55 — 같은 문구 2 곳</t>
         </is>
       </c>
       <c r="J60" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -16328,37 +16322,37 @@
       </c>
       <c r="B61" s="5" t="inlineStr">
         <is>
-          <t>04-1 EV 제어기</t>
+          <t>03-2 완속 충전기</t>
         </is>
       </c>
       <c r="C61" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문(예정)</t>
         </is>
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>자리표시</t>
         </is>
       </c>
       <c r="E61" s="5" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="F61" s="6" t="inlineStr">
         <is>
-          <t>EV 제어기</t>
+          <t>텍스트 추가 예정</t>
         </is>
       </c>
       <c r="G61" s="7" t="n"/>
       <c r="H61" s="8" t="n"/>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>묶음 56 — 같은 문구 2 곳</t>
+          <t>묶음 59 — 같은 문구 3 곳</t>
         </is>
       </c>
       <c r="J61" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p|text</t>
         </is>
       </c>
     </row>
@@ -16373,7 +16367,7 @@
       </c>
       <c r="C62" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D62" s="5" t="inlineStr">
@@ -16381,22 +16375,24 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E62" s="5" t="inlineStr"/>
+      <c r="E62" s="5" t="n">
+        <v>56</v>
+      </c>
       <c r="F62" s="6" t="inlineStr">
         <is>
-          <t>에이프로는 ECOTRON 차량·자율주행 제어기의 국내 총판으로서 VCU, ZCU, EVCC, 자율주행 제어기 등 검증된 제어 솔루션을 공급합니다.</t>
+          <t>EV 제어기</t>
         </is>
       </c>
       <c r="G62" s="7" t="n"/>
-      <c r="H62" s="8" t="inlineStr">
-        <is>
-          <t>As the exclusive domestic distributor for ECOTRON vehicle and autonomous driving controllers, APRO supplies proven control solutions, including VCUs, ZCUs, EVCCs, and autonomous driving controllers.</t>
-        </is>
-      </c>
-      <c r="I62" s="5" t="inlineStr"/>
+      <c r="H62" s="8" t="n"/>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>묶음 56 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J62" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -16422,19 +16418,19 @@
       <c r="E63" s="5" t="inlineStr"/>
       <c r="F63" s="6" t="inlineStr">
         <is>
-          <t>모든 제품은 ASIL-D 등급 반도체와 ISO 26262 기능안전, MATLAB/Simulink 모델 기반 개발을 지원해 높은 안전성과 개발 효율성을 제공합니다.</t>
+          <t>에이프로는 ECOTRON 차량·자율주행 제어기의 국내 총판으로서 VCU, ZCU, EVCC, 자율주행 제어기 등 검증된 제어 솔루션을 공급합니다.</t>
         </is>
       </c>
       <c r="G63" s="7" t="n"/>
       <c r="H63" s="8" t="inlineStr">
         <is>
-          <t>All products utilize ASIL-D grade semiconductors and support ISO 26262 functional safety and MATLAB/Simulink model-based development, providing high safety and development efficiency.</t>
+          <t>As the exclusive domestic distributor for ECOTRON vehicle and autonomous driving controllers, APRO supplies proven control solutions, including VCUs, ZCUs, EVCCs, and autonomous driving controllers.</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr"/>
       <c r="J63" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -16460,19 +16456,19 @@
       <c r="E64" s="5" t="inlineStr"/>
       <c r="F64" s="6" t="inlineStr">
         <is>
-          <t>에이프로는 국내 공급과 기술 지원을 통해 전기차·자율주행·무인 이동체·로봇 분야 고객의 제어기 도입을 지원합니다.</t>
+          <t>모든 제품은 ASIL-D 등급 반도체와 ISO 26262 기능안전, MATLAB/Simulink 모델 기반 개발을 지원해 높은 안전성과 개발 효율성을 제공합니다.</t>
         </is>
       </c>
       <c r="G64" s="7" t="n"/>
       <c r="H64" s="8" t="inlineStr">
         <is>
-          <t>Through domestic supply and technical support, APRO facilitates the adoption of controllers by customers in the fields of electric vehicles, autonomous driving, unmanned vehicles, and robotics.</t>
+          <t>All products utilize ASIL-D grade semiconductors and support ISO 26262 functional safety and MATLAB/Simulink model-based development, providing high safety and development efficiency.</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -16482,12 +16478,12 @@
       </c>
       <c r="B65" s="5" t="inlineStr">
         <is>
-          <t>04-2 자율주행 제어기</t>
+          <t>04-1 EV 제어기</t>
         </is>
       </c>
       <c r="C65" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D65" s="5" t="inlineStr">
@@ -16495,24 +16491,22 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E65" s="5" t="n">
-        <v>57</v>
-      </c>
+      <c r="E65" s="5" t="inlineStr"/>
       <c r="F65" s="6" t="inlineStr">
         <is>
-          <t>자율주행 제어기</t>
+          <t>에이프로는 국내 공급과 기술 지원을 통해 전기차·자율주행·무인 이동체·로봇 분야 고객의 제어기 도입을 지원합니다.</t>
         </is>
       </c>
       <c r="G65" s="7" t="n"/>
-      <c r="H65" s="8" t="n"/>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>묶음 57 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="H65" s="8" t="inlineStr">
+        <is>
+          <t>Through domestic supply and technical support, APRO facilitates the adoption of controllers by customers in the fields of electric vehicles, autonomous driving, unmanned vehicles, and robotics.</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr"/>
       <c r="J65" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -16527,32 +16521,32 @@
       </c>
       <c r="C66" s="5" t="inlineStr">
         <is>
-          <t>본문(예정)</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E66" s="5" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="F66" s="6" t="inlineStr">
         <is>
-          <t>텍스트 추가 예정</t>
+          <t>자율주행 제어기</t>
         </is>
       </c>
       <c r="G66" s="7" t="n"/>
       <c r="H66" s="8" t="n"/>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>묶음 59 — 같은 문구 3 곳</t>
+          <t>묶음 57 — 같은 문구 2 곳</t>
         </is>
       </c>
       <c r="J66" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -16562,41 +16556,37 @@
       </c>
       <c r="B67" s="5" t="inlineStr">
         <is>
-          <t>04-3 소프트웨어</t>
+          <t>04-2 자율주행 제어기</t>
         </is>
       </c>
       <c r="C67" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문(예정)</t>
         </is>
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>자리표시</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>소프트웨어</t>
+          <t>텍스트 추가 예정</t>
         </is>
       </c>
       <c r="G67" s="7" t="n"/>
-      <c r="H67" s="8" t="inlineStr">
-        <is>
-          <t>Software</t>
-        </is>
-      </c>
+      <c r="H67" s="8" t="n"/>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>묶음 58 — 같은 문구 2 곳</t>
+          <t>묶음 59 — 같은 문구 3 곳</t>
         </is>
       </c>
       <c r="J67" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p|text</t>
         </is>
       </c>
     </row>
@@ -16611,37 +16601,81 @@
       </c>
       <c r="C68" s="5" t="inlineStr">
         <is>
+          <t>장 제목</t>
+        </is>
+      </c>
+      <c r="D68" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E68" s="5" t="n">
+        <v>58</v>
+      </c>
+      <c r="F68" s="6" t="inlineStr">
+        <is>
+          <t>소프트웨어</t>
+        </is>
+      </c>
+      <c r="G68" s="7" t="n"/>
+      <c r="H68" s="8" t="inlineStr">
+        <is>
+          <t>Software</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>묶음 58 — 같은 문구 2 곳</t>
+        </is>
+      </c>
+      <c r="J68" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/h2|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="5" t="n">
+        <v>68</v>
+      </c>
+      <c r="B69" s="5" t="inlineStr">
+        <is>
+          <t>04-3 소프트웨어</t>
+        </is>
+      </c>
+      <c r="C69" s="5" t="inlineStr">
+        <is>
           <t>본문(예정)</t>
         </is>
       </c>
-      <c r="D68" s="5" t="inlineStr">
+      <c r="D69" s="5" t="inlineStr">
         <is>
           <t>자리표시</t>
         </is>
       </c>
-      <c r="E68" s="5" t="n">
+      <c r="E69" s="5" t="n">
         <v>59</v>
       </c>
-      <c r="F68" s="6" t="inlineStr">
+      <c r="F69" s="6" t="inlineStr">
         <is>
           <t>텍스트 추가 예정</t>
         </is>
       </c>
-      <c r="G68" s="7" t="n"/>
-      <c r="H68" s="8" t="n"/>
-      <c r="I68" s="5" t="inlineStr">
+      <c r="G69" s="7" t="n"/>
+      <c r="H69" s="8" t="n"/>
+      <c r="I69" s="5" t="inlineStr">
         <is>
           <t>묶음 59 — 같은 문구 3 곳</t>
         </is>
       </c>
-      <c r="J68" s="9" t="inlineStr">
+      <c r="J69" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p|text</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J68"/>
+  <autoFilter ref="A1:J69"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/content-export/04_사업영역_문구.xlsx
+++ b/content-export/04_사업영역_문구.xlsx
@@ -16120,7 +16120,7 @@
       </c>
       <c r="J55" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[1]/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -16135,7 +16135,7 @@
       </c>
       <c r="C56" s="5" t="inlineStr">
         <is>
-          <t>장 영문 제목</t>
+          <t>작은 제목</t>
         </is>
       </c>
       <c r="D56" s="5" t="inlineStr">
@@ -16158,7 +16158,7 @@
       <c r="I56" s="5" t="inlineStr"/>
       <c r="J56" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[1]/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -16196,7 +16196,7 @@
       <c r="I57" s="5" t="inlineStr"/>
       <c r="J57" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[2]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -16234,7 +16234,7 @@
       <c r="I58" s="5" t="inlineStr"/>
       <c r="J58" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[2]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -16272,7 +16272,7 @@
       <c r="I59" s="5" t="inlineStr"/>
       <c r="J59" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div[2]/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/p[4]|text</t>
         </is>
       </c>
     </row>

--- a/content-export/04_사업영역_문구.xlsx
+++ b/content-export/04_사업영역_문구.xlsx
@@ -1891,7 +1891,7 @@
       <c r="H29" s="8" t="n"/>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 14 곳</t>
+          <t>묶음 17 — 같은 문구 11 곳</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
@@ -2407,7 +2407,7 @@
       <c r="H44" s="8" t="n"/>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 14 곳</t>
+          <t>묶음 17 — 같은 문구 11 곳</t>
         </is>
       </c>
       <c r="J44" s="9" t="inlineStr">
@@ -6382,7 +6382,7 @@
       <c r="H27" s="8" t="n"/>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 14 곳</t>
+          <t>묶음 17 — 같은 문구 11 곳</t>
         </is>
       </c>
       <c r="J27" s="9" t="inlineStr">
@@ -6422,7 +6422,7 @@
       <c r="H28" s="8" t="n"/>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 14 곳</t>
+          <t>묶음 17 — 같은 문구 11 곳</t>
         </is>
       </c>
       <c r="J28" s="9" t="inlineStr">
@@ -6462,7 +6462,7 @@
       <c r="H29" s="8" t="n"/>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 14 곳</t>
+          <t>묶음 17 — 같은 문구 11 곳</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
@@ -6502,7 +6502,7 @@
       <c r="H30" s="8" t="n"/>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 14 곳</t>
+          <t>묶음 17 — 같은 문구 11 곳</t>
         </is>
       </c>
       <c r="J30" s="9" t="inlineStr">
@@ -6542,7 +6542,7 @@
       <c r="H31" s="8" t="n"/>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 14 곳</t>
+          <t>묶음 17 — 같은 문구 11 곳</t>
         </is>
       </c>
       <c r="J31" s="9" t="inlineStr">
@@ -6582,7 +6582,7 @@
       <c r="H32" s="8" t="n"/>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 14 곳</t>
+          <t>묶음 17 — 같은 문구 11 곳</t>
         </is>
       </c>
       <c r="J32" s="9" t="inlineStr">
@@ -15383,7 +15383,7 @@
       <c r="H36" s="8" t="n"/>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 14 곳</t>
+          <t>묶음 17 — 같은 문구 11 곳</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
@@ -15457,7 +15457,7 @@
       <c r="H38" s="8" t="n"/>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 14 곳</t>
+          <t>묶음 17 — 같은 문구 11 곳</t>
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
@@ -15497,7 +15497,7 @@
       <c r="H39" s="8" t="n"/>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 14 곳</t>
+          <t>묶음 17 — 같은 문구 11 곳</t>
         </is>
       </c>
       <c r="J39" s="9" t="inlineStr">
@@ -17502,32 +17502,26 @@
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>그림 자리표시 문구</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>17</v>
-      </c>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="inlineStr"/>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>도표 or 이미지</t>
+          <t>GaN 에피웨이퍼를 키우는 MOCVD 장비 한 벌</t>
         </is>
       </c>
       <c r="G20" s="7" t="n"/>
       <c r="H20" s="8" t="n"/>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>묶음 17 — 같은 문구 14 곳</t>
-        </is>
-      </c>
+      <c r="I20" s="5" t="inlineStr"/>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[1]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[1]/img|alt</t>
         </is>
       </c>
     </row>
@@ -17542,32 +17536,26 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>그림 자리표시 문구</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
-        </is>
-      </c>
-      <c r="E21" s="5" t="n">
-        <v>17</v>
-      </c>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="inlineStr"/>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>도표 or 이미지</t>
+          <t>에이프로세미콘 GaN 전력반도체 패키지 두 종</t>
         </is>
       </c>
       <c r="G21" s="7" t="n"/>
       <c r="H21" s="8" t="n"/>
-      <c r="I21" s="5" t="inlineStr">
-        <is>
-          <t>묶음 17 — 같은 문구 14 곳</t>
-        </is>
-      </c>
+      <c r="I21" s="5" t="inlineStr"/>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[2]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[2]/img|alt</t>
         </is>
       </c>
     </row>
@@ -17582,32 +17570,26 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>그림 자리표시 문구</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>17</v>
-      </c>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="inlineStr"/>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>도표 or 이미지</t>
+          <t>해 질 무렵 불을 밝힌 에이프로세미콘 공장 외관</t>
         </is>
       </c>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="8" t="n"/>
-      <c r="I22" s="5" t="inlineStr">
-        <is>
-          <t>묶음 17 — 같은 문구 14 곳</t>
-        </is>
-      </c>
+      <c r="I22" s="5" t="inlineStr"/>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[3]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[3]/img|alt</t>
         </is>
       </c>
     </row>

--- a/content-export/04_사업영역_문구.xlsx
+++ b/content-export/04_사업영역_문구.xlsx
@@ -9,13 +9,13 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="스마트 제조" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="에너지 솔루션" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="에너지 인프라" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인공지능 플랫폼" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화합물 전력 반도체" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$J$119</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'에너지 솔루션'!$A$1:$J$228</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'에너지 인프라'!$A$1:$J$228</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'인공지능 플랫폼'!$A$1:$J$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'화합물 전력 반도체'!$A$1:$J$34</definedName>
   </definedNames>
@@ -1891,7 +1891,7 @@
       <c r="H29" s="8" t="n"/>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 11 곳</t>
+          <t>묶음 17 — 같은 문구 5 곳</t>
         </is>
       </c>
       <c r="J29" s="9" t="inlineStr">
@@ -2407,7 +2407,7 @@
       <c r="H44" s="8" t="n"/>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 11 곳</t>
+          <t>묶음 17 — 같은 문구 5 곳</t>
         </is>
       </c>
       <c r="J44" s="9" t="inlineStr">
@@ -5327,7 +5327,7 @@
       <c r="E2" s="5" t="inlineStr"/>
       <c r="F2" s="6" t="inlineStr">
         <is>
-          <t>에너지 솔루션</t>
+          <t>에너지 인프라</t>
         </is>
       </c>
       <c r="G2" s="7" t="n"/>
@@ -5361,13 +5361,13 @@
       <c r="E3" s="5" t="inlineStr"/>
       <c r="F3" s="6" t="inlineStr">
         <is>
-          <t>Energy Solution</t>
+          <t>Energy Infrastructure</t>
         </is>
       </c>
       <c r="G3" s="7" t="n"/>
       <c r="H3" s="8" t="inlineStr">
         <is>
-          <t>Energy Solution</t>
+          <t>Energy Infrastructure</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr"/>
@@ -5475,7 +5475,7 @@
       <c r="E6" s="5" t="inlineStr"/>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>에너지 솔루션 한눈에 보기 — 태양광·풍력 발전과 ESS 컨테이너, 변전 설비, 수요처가 송전선으로 이어진 그림</t>
+          <t>에너지 인프라 한눈에 보기 — 태양광·풍력 발전과 ESS 컨테이너, 변전 설비, 수요처가 송전선으로 이어진 그림</t>
         </is>
       </c>
       <c r="G6" s="7" t="n"/>
@@ -6362,32 +6362,26 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>그림 자리표시 문구</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
-        </is>
-      </c>
-      <c r="E27" s="5" t="n">
-        <v>17</v>
-      </c>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>도표 or 이미지</t>
+          <t>변전소와 송전탑을 배경으로 놓인 에이프로 ESS 컨테이너</t>
         </is>
       </c>
       <c r="G27" s="7" t="n"/>
       <c r="H27" s="8" t="n"/>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>묶음 17 — 같은 문구 11 곳</t>
-        </is>
-      </c>
+      <c r="I27" s="5" t="inlineStr"/>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[1]/div[1]/div/div[2]/figure[1]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div[1]/div[1]/div/div[2]/figure[1]/img|alt</t>
         </is>
       </c>
     </row>
@@ -6402,32 +6396,26 @@
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>그림 자리표시 문구</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
-        </is>
-      </c>
-      <c r="E28" s="5" t="n">
-        <v>17</v>
-      </c>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="inlineStr"/>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>도표 or 이미지</t>
+          <t>태양광 발전소와 풍력 발전기를 배경으로 놓인 에이프로 ESS 컨테이너</t>
         </is>
       </c>
       <c r="G28" s="7" t="n"/>
       <c r="H28" s="8" t="n"/>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>묶음 17 — 같은 문구 11 곳</t>
-        </is>
-      </c>
+      <c r="I28" s="5" t="inlineStr"/>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[1]/div[1]/div/div[2]/figure[2]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div[1]/div[1]/div/div[2]/figure[2]/img|alt</t>
         </is>
       </c>
     </row>
@@ -6442,32 +6430,26 @@
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>그림 자리표시 문구</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
-        </is>
-      </c>
-      <c r="E29" s="5" t="n">
-        <v>17</v>
-      </c>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="inlineStr"/>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>도표 or 이미지</t>
+          <t>산업단지 플랜트 앞에 놓인 에이프로 ESS 컨테이너</t>
         </is>
       </c>
       <c r="G29" s="7" t="n"/>
       <c r="H29" s="8" t="n"/>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>묶음 17 — 같은 문구 11 곳</t>
-        </is>
-      </c>
+      <c r="I29" s="5" t="inlineStr"/>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[1]/div[1]/div/div[2]/figure[3]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div[1]/div[1]/div/div[2]/figure[3]/img|alt</t>
         </is>
       </c>
     </row>
@@ -6482,32 +6464,26 @@
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>그림 자리표시 문구</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
-        </is>
-      </c>
-      <c r="E30" s="5" t="n">
-        <v>17</v>
-      </c>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>도표 or 이미지</t>
+          <t>도시와 통신 철탑을 배경으로 놓인 데이터 센터용 UPS 한 벌</t>
         </is>
       </c>
       <c r="G30" s="7" t="n"/>
       <c r="H30" s="8" t="n"/>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>묶음 17 — 같은 문구 11 곳</t>
-        </is>
-      </c>
+      <c r="I30" s="5" t="inlineStr"/>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[1]/div[1]/div/div[2]/figure[4]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div[1]/div[1]/div/div[2]/figure[4]/img|alt</t>
         </is>
       </c>
     </row>
@@ -6522,32 +6498,26 @@
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>그림 자리표시 문구</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
-        </is>
-      </c>
-      <c r="E31" s="5" t="n">
-        <v>17</v>
-      </c>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>도표 or 이미지</t>
+          <t>생산 설비가 늘어선 공장 바닥에 놓인 산업용 UPS</t>
         </is>
       </c>
       <c r="G31" s="7" t="n"/>
       <c r="H31" s="8" t="n"/>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>묶음 17 — 같은 문구 11 곳</t>
-        </is>
-      </c>
+      <c r="I31" s="5" t="inlineStr"/>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[1]/div[1]/div/div[2]/figure[5]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div[1]/div[1]/div/div[2]/figure[5]/img|alt</t>
         </is>
       </c>
     </row>
@@ -6562,32 +6532,26 @@
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>그림 자리표시 문구</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>자리표시</t>
-        </is>
-      </c>
-      <c r="E32" s="5" t="n">
-        <v>17</v>
-      </c>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="inlineStr"/>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>도표 or 이미지</t>
+          <t>넓은 전력실에 줄지어 선 주요 전력망용 UPS 캐비닛</t>
         </is>
       </c>
       <c r="G32" s="7" t="n"/>
       <c r="H32" s="8" t="n"/>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>묶음 17 — 같은 문구 11 곳</t>
-        </is>
-      </c>
+      <c r="I32" s="5" t="inlineStr"/>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[1]/div[1]/div/div[2]/figure[6]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div[1]/div[1]/div/div[2]/figure[6]/img|alt</t>
         </is>
       </c>
     </row>
@@ -15383,7 +15347,7 @@
       <c r="H36" s="8" t="n"/>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 11 곳</t>
+          <t>묶음 17 — 같은 문구 5 곳</t>
         </is>
       </c>
       <c r="J36" s="9" t="inlineStr">
@@ -15457,7 +15421,7 @@
       <c r="H38" s="8" t="n"/>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 11 곳</t>
+          <t>묶음 17 — 같은 문구 5 곳</t>
         </is>
       </c>
       <c r="J38" s="9" t="inlineStr">
@@ -15497,7 +15461,7 @@
       <c r="H39" s="8" t="n"/>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>묶음 17 — 같은 문구 11 곳</t>
+          <t>묶음 17 — 같은 문구 5 곳</t>
         </is>
       </c>
       <c r="J39" s="9" t="inlineStr">

--- a/content-export/04_사업영역_문구.xlsx
+++ b/content-export/04_사업영역_문구.xlsx
@@ -15,7 +15,7 @@
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$J$119</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'에너지 인프라'!$A$1:$J$228</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'에너지 인프라'!$A$1:$J$227</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'인공지능 플랫폼'!$A$1:$J$69</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'화합물 전력 반도체'!$A$1:$J$34</definedName>
   </definedNames>
@@ -527,7 +527,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 446 줄입니다.</t>
+          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 445 줄입니다.</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J228"/>
+  <dimension ref="A1:J227"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -9270,7 +9270,7 @@
       <c r="H101" s="8" t="n"/>
       <c r="I101" s="5" t="inlineStr">
         <is>
-          <t>묶음 35 — 같은 문구 4 곳</t>
+          <t>묶음 35 — 같은 문구 3 곳</t>
         </is>
       </c>
       <c r="J101" s="9" t="inlineStr">
@@ -10388,7 +10388,7 @@
       <c r="H131" s="8" t="n"/>
       <c r="I131" s="5" t="inlineStr">
         <is>
-          <t>묶음 35 — 같은 문구 4 곳</t>
+          <t>묶음 35 — 같은 문구 3 곳</t>
         </is>
       </c>
       <c r="J131" s="9" t="inlineStr">
@@ -11478,12 +11478,12 @@
       <c r="H161" s="8" t="n"/>
       <c r="I161" s="5" t="inlineStr">
         <is>
-          <t>묶음 35 — 같은 문구 4 곳</t>
+          <t>묶음 35 — 같은 문구 3 곳</t>
         </is>
       </c>
       <c r="J161" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[1]/div/div[2]/ul/li[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[1]/div/div[2]/ul/li|text</t>
         </is>
       </c>
     </row>
@@ -11498,32 +11498,26 @@
       </c>
       <c r="C162" s="5" t="inlineStr">
         <is>
-          <t>인증 항목</t>
+          <t>제품 사진 대체글</t>
         </is>
       </c>
       <c r="D162" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E162" s="5" t="n">
-        <v>35</v>
-      </c>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E162" s="5" t="inlineStr"/>
       <c r="F162" s="6" t="inlineStr">
         <is>
-          <t>KC / IEC / UL</t>
+          <t>공기 흡배기 방향을 표시한 에어 쿨링 타입 ESS 컨테이너</t>
         </is>
       </c>
       <c r="G162" s="7" t="n"/>
       <c r="H162" s="8" t="n"/>
-      <c r="I162" s="5" t="inlineStr">
-        <is>
-          <t>묶음 35 — 같은 문구 4 곳</t>
-        </is>
-      </c>
+      <c r="I162" s="5" t="inlineStr"/>
       <c r="J162" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[1]/div/div[2]/ul/li[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[1]/img|alt</t>
         </is>
       </c>
     </row>
@@ -11538,26 +11532,30 @@
       </c>
       <c r="C163" s="5" t="inlineStr">
         <is>
-          <t>제품 사진 대체글</t>
+          <t>제품 이름</t>
         </is>
       </c>
       <c r="D163" s="5" t="inlineStr">
         <is>
-          <t>대체글</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E163" s="5" t="inlineStr"/>
       <c r="F163" s="6" t="inlineStr">
         <is>
-          <t>공기 흡배기 방향을 표시한 에어 쿨링 타입 ESS 컨테이너</t>
+          <t>Container Air Cooling Type</t>
         </is>
       </c>
       <c r="G163" s="7" t="n"/>
-      <c r="H163" s="8" t="n"/>
+      <c r="H163" s="8" t="inlineStr">
+        <is>
+          <t>Container Air Cooling Type</t>
+        </is>
+      </c>
       <c r="I163" s="5" t="inlineStr"/>
       <c r="J163" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[1]/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/p/b|text</t>
         </is>
       </c>
     </row>
@@ -11572,7 +11570,7 @@
       </c>
       <c r="C164" s="5" t="inlineStr">
         <is>
-          <t>제품 이름</t>
+          <t>제품 특징 항목</t>
         </is>
       </c>
       <c r="D164" s="5" t="inlineStr">
@@ -11583,19 +11581,15 @@
       <c r="E164" s="5" t="inlineStr"/>
       <c r="F164" s="6" t="inlineStr">
         <is>
-          <t>Container Air Cooling Type</t>
+          <t>자연 공기 순환 방식</t>
         </is>
       </c>
       <c r="G164" s="7" t="n"/>
-      <c r="H164" s="8" t="inlineStr">
-        <is>
-          <t>Container Air Cooling Type</t>
-        </is>
-      </c>
+      <c r="H164" s="8" t="n"/>
       <c r="I164" s="5" t="inlineStr"/>
       <c r="J164" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/p/b|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[1]/span/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -11610,7 +11604,7 @@
       </c>
       <c r="C165" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 항목</t>
+          <t>제품 특징 설명</t>
         </is>
       </c>
       <c r="D165" s="5" t="inlineStr">
@@ -11621,7 +11615,7 @@
       <c r="E165" s="5" t="inlineStr"/>
       <c r="F165" s="6" t="inlineStr">
         <is>
-          <t>자연 공기 순환 방식</t>
+          <t>팬을 이용한 공기 순환을 통해 컨테이너 내부의 열을 외부로 배출합니다.</t>
         </is>
       </c>
       <c r="G165" s="7" t="n"/>
@@ -11629,7 +11623,7 @@
       <c r="I165" s="5" t="inlineStr"/>
       <c r="J165" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[1]/span/span[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[1]/span/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -11644,7 +11638,7 @@
       </c>
       <c r="C166" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 설명</t>
+          <t>제품 특징 항목</t>
         </is>
       </c>
       <c r="D166" s="5" t="inlineStr">
@@ -11655,7 +11649,7 @@
       <c r="E166" s="5" t="inlineStr"/>
       <c r="F166" s="6" t="inlineStr">
         <is>
-          <t>팬을 이용한 공기 순환을 통해 컨테이너 내부의 열을 외부로 배출합니다.</t>
+          <t>구조가 단순하고 유지보수가 용이</t>
         </is>
       </c>
       <c r="G166" s="7" t="n"/>
@@ -11663,7 +11657,7 @@
       <c r="I166" s="5" t="inlineStr"/>
       <c r="J166" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[1]/span/span[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[2]/span/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -11678,7 +11672,7 @@
       </c>
       <c r="C167" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 항목</t>
+          <t>제품 특징 설명</t>
         </is>
       </c>
       <c r="D167" s="5" t="inlineStr">
@@ -11689,7 +11683,7 @@
       <c r="E167" s="5" t="inlineStr"/>
       <c r="F167" s="6" t="inlineStr">
         <is>
-          <t>구조가 단순하고 유지보수가 용이</t>
+          <t>냉각 시스템이 단순하여 설치와 유지보수가 용이하고 운영 비용이 낮습니다.</t>
         </is>
       </c>
       <c r="G167" s="7" t="n"/>
@@ -11697,7 +11691,7 @@
       <c r="I167" s="5" t="inlineStr"/>
       <c r="J167" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[2]/span/span[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[2]/span/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -11712,7 +11706,7 @@
       </c>
       <c r="C168" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 설명</t>
+          <t>제품 특징 항목</t>
         </is>
       </c>
       <c r="D168" s="5" t="inlineStr">
@@ -11723,7 +11717,7 @@
       <c r="E168" s="5" t="inlineStr"/>
       <c r="F168" s="6" t="inlineStr">
         <is>
-          <t>냉각 시스템이 단순하여 설치와 유지보수가 용이하고 운영 비용이 낮습니다.</t>
+          <t>다양한 환경에서 안정적 운용</t>
         </is>
       </c>
       <c r="G168" s="7" t="n"/>
@@ -11731,7 +11725,7 @@
       <c r="I168" s="5" t="inlineStr"/>
       <c r="J168" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[2]/span/span[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[3]/span/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -11746,7 +11740,7 @@
       </c>
       <c r="C169" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 항목</t>
+          <t>제품 특징 설명</t>
         </is>
       </c>
       <c r="D169" s="5" t="inlineStr">
@@ -11757,7 +11751,7 @@
       <c r="E169" s="5" t="inlineStr"/>
       <c r="F169" s="6" t="inlineStr">
         <is>
-          <t>다양한 환경에서 안정적 운용</t>
+          <t>넓은 온도 범위에서 안정적으로 운용할 수 있어 다양한 설치 환경에 적합합니다.</t>
         </is>
       </c>
       <c r="G169" s="7" t="n"/>
@@ -11765,7 +11759,7 @@
       <c r="I169" s="5" t="inlineStr"/>
       <c r="J169" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[3]/span/span[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[3]/span/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -11780,7 +11774,7 @@
       </c>
       <c r="C170" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 설명</t>
+          <t>제품 특징 항목</t>
         </is>
       </c>
       <c r="D170" s="5" t="inlineStr">
@@ -11788,18 +11782,24 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E170" s="5" t="inlineStr"/>
+      <c r="E170" s="5" t="n">
+        <v>37</v>
+      </c>
       <c r="F170" s="6" t="inlineStr">
         <is>
-          <t>넓은 온도 범위에서 안정적으로 운용할 수 있어 다양한 설치 환경에 적합합니다.</t>
+          <t>경제성 우수</t>
         </is>
       </c>
       <c r="G170" s="7" t="n"/>
       <c r="H170" s="8" t="n"/>
-      <c r="I170" s="5" t="inlineStr"/>
+      <c r="I170" s="5" t="inlineStr">
+        <is>
+          <t>묶음 37 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J170" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[3]/span/span[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[4]/span/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -11814,7 +11814,7 @@
       </c>
       <c r="C171" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 항목</t>
+          <t>제품 특징 설명</t>
         </is>
       </c>
       <c r="D171" s="5" t="inlineStr">
@@ -11822,24 +11822,18 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E171" s="5" t="n">
-        <v>37</v>
-      </c>
+      <c r="E171" s="5" t="inlineStr"/>
       <c r="F171" s="6" t="inlineStr">
         <is>
-          <t>경제성 우수</t>
+          <t>추가적인 냉각 설비가 필요 없어 초기 투자 비용과 운영 비용이 절감됩니다.</t>
         </is>
       </c>
       <c r="G171" s="7" t="n"/>
       <c r="H171" s="8" t="n"/>
-      <c r="I171" s="5" t="inlineStr">
-        <is>
-          <t>묶음 37 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="I171" s="5" t="inlineStr"/>
       <c r="J171" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[4]/span/span[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[4]/span/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -11854,7 +11848,7 @@
       </c>
       <c r="C172" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 설명</t>
+          <t>제품 용도 제목</t>
         </is>
       </c>
       <c r="D172" s="5" t="inlineStr">
@@ -11862,18 +11856,24 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E172" s="5" t="inlineStr"/>
+      <c r="E172" s="5" t="n">
+        <v>38</v>
+      </c>
       <c r="F172" s="6" t="inlineStr">
         <is>
-          <t>추가적인 냉각 설비가 필요 없어 초기 투자 비용과 운영 비용이 절감됩니다.</t>
+          <t>주요 적용 분야</t>
         </is>
       </c>
       <c r="G172" s="7" t="n"/>
       <c r="H172" s="8" t="n"/>
-      <c r="I172" s="5" t="inlineStr"/>
+      <c r="I172" s="5" t="inlineStr">
+        <is>
+          <t>묶음 38 — 같은 문구 9 곳</t>
+        </is>
+      </c>
       <c r="J172" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/ul/li[4]/span/span[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/p/b|text</t>
         </is>
       </c>
     </row>
@@ -11888,7 +11888,7 @@
       </c>
       <c r="C173" s="5" t="inlineStr">
         <is>
-          <t>제품 용도 제목</t>
+          <t>제품 용도 설명</t>
         </is>
       </c>
       <c r="D173" s="5" t="inlineStr">
@@ -11897,23 +11897,23 @@
         </is>
       </c>
       <c r="E173" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F173" s="6" t="inlineStr">
         <is>
-          <t>주요 적용 분야</t>
+          <t>ESS, Telecom, Military, Electric Vehicle, Industrial, Aerospace, Marine 등</t>
         </is>
       </c>
       <c r="G173" s="7" t="n"/>
       <c r="H173" s="8" t="n"/>
       <c r="I173" s="5" t="inlineStr">
         <is>
-          <t>묶음 38 — 같은 문구 9 곳</t>
+          <t>묶음 39 — 같은 문구 9 곳</t>
         </is>
       </c>
       <c r="J173" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/p/b|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/p/span|text</t>
         </is>
       </c>
     </row>
@@ -11928,32 +11928,26 @@
       </c>
       <c r="C174" s="5" t="inlineStr">
         <is>
-          <t>제품 용도 설명</t>
+          <t>제품 사진 대체글</t>
         </is>
       </c>
       <c r="D174" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E174" s="5" t="n">
-        <v>39</v>
-      </c>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E174" s="5" t="inlineStr"/>
       <c r="F174" s="6" t="inlineStr">
         <is>
-          <t>ESS, Telecom, Military, Electric Vehicle, Industrial, Aerospace, Marine 등</t>
+          <t>냉각 유닛이 보이는 리퀴드 쿨링 타입 ESS 컨테이너</t>
         </is>
       </c>
       <c r="G174" s="7" t="n"/>
       <c r="H174" s="8" t="n"/>
-      <c r="I174" s="5" t="inlineStr">
-        <is>
-          <t>묶음 39 — 같은 문구 9 곳</t>
-        </is>
-      </c>
+      <c r="I174" s="5" t="inlineStr"/>
       <c r="J174" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[1]/div[2]/div/p/span|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[1]/img|alt</t>
         </is>
       </c>
     </row>
@@ -11968,26 +11962,30 @@
       </c>
       <c r="C175" s="5" t="inlineStr">
         <is>
-          <t>제품 사진 대체글</t>
+          <t>제품 이름</t>
         </is>
       </c>
       <c r="D175" s="5" t="inlineStr">
         <is>
-          <t>대체글</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E175" s="5" t="inlineStr"/>
       <c r="F175" s="6" t="inlineStr">
         <is>
-          <t>냉각 유닛이 보이는 리퀴드 쿨링 타입 ESS 컨테이너</t>
+          <t>Container Liquid Cooling Type</t>
         </is>
       </c>
       <c r="G175" s="7" t="n"/>
-      <c r="H175" s="8" t="n"/>
+      <c r="H175" s="8" t="inlineStr">
+        <is>
+          <t>Container Liquid Cooling Type</t>
+        </is>
+      </c>
       <c r="I175" s="5" t="inlineStr"/>
       <c r="J175" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[1]/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/p/b|text</t>
         </is>
       </c>
     </row>
@@ -12002,7 +12000,7 @@
       </c>
       <c r="C176" s="5" t="inlineStr">
         <is>
-          <t>제품 이름</t>
+          <t>제품 특징 항목</t>
         </is>
       </c>
       <c r="D176" s="5" t="inlineStr">
@@ -12010,22 +12008,24 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E176" s="5" t="inlineStr"/>
+      <c r="E176" s="5" t="n">
+        <v>40</v>
+      </c>
       <c r="F176" s="6" t="inlineStr">
         <is>
-          <t>Container Liquid Cooling Type</t>
+          <t>직접 액체 냉각 방식</t>
         </is>
       </c>
       <c r="G176" s="7" t="n"/>
-      <c r="H176" s="8" t="inlineStr">
-        <is>
-          <t>Container Liquid Cooling Type</t>
-        </is>
-      </c>
-      <c r="I176" s="5" t="inlineStr"/>
+      <c r="H176" s="8" t="n"/>
+      <c r="I176" s="5" t="inlineStr">
+        <is>
+          <t>묶음 40 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J176" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/p/b|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[1]/span/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -12040,7 +12040,7 @@
       </c>
       <c r="C177" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 항목</t>
+          <t>제품 특징 설명</t>
         </is>
       </c>
       <c r="D177" s="5" t="inlineStr">
@@ -12048,24 +12048,18 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E177" s="5" t="n">
-        <v>40</v>
-      </c>
+      <c r="E177" s="5" t="inlineStr"/>
       <c r="F177" s="6" t="inlineStr">
         <is>
-          <t>직접 액체 냉각 방식</t>
+          <t>냉각수가 배터리 모듈 및 주요 부품의 냉각판을 따라 순환하며 열을 효과적으로 제거합니다.</t>
         </is>
       </c>
       <c r="G177" s="7" t="n"/>
       <c r="H177" s="8" t="n"/>
-      <c r="I177" s="5" t="inlineStr">
-        <is>
-          <t>묶음 40 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+      <c r="I177" s="5" t="inlineStr"/>
       <c r="J177" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[1]/span/span[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[1]/span/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -12080,7 +12074,7 @@
       </c>
       <c r="C178" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 설명</t>
+          <t>제품 특징 항목</t>
         </is>
       </c>
       <c r="D178" s="5" t="inlineStr">
@@ -12088,18 +12082,24 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E178" s="5" t="inlineStr"/>
+      <c r="E178" s="5" t="n">
+        <v>41</v>
+      </c>
       <c r="F178" s="6" t="inlineStr">
         <is>
-          <t>냉각수가 배터리 모듈 및 주요 부품의 냉각판을 따라 순환하며 열을 효과적으로 제거합니다.</t>
+          <t>우수한 열 관리 성능</t>
         </is>
       </c>
       <c r="G178" s="7" t="n"/>
       <c r="H178" s="8" t="n"/>
-      <c r="I178" s="5" t="inlineStr"/>
+      <c r="I178" s="5" t="inlineStr">
+        <is>
+          <t>묶음 41 — 같은 문구 3 곳</t>
+        </is>
+      </c>
       <c r="J178" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[1]/span/span[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[2]/span/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -12114,7 +12114,7 @@
       </c>
       <c r="C179" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 항목</t>
+          <t>제품 특징 설명</t>
         </is>
       </c>
       <c r="D179" s="5" t="inlineStr">
@@ -12122,24 +12122,18 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E179" s="5" t="n">
-        <v>41</v>
-      </c>
+      <c r="E179" s="5" t="inlineStr"/>
       <c r="F179" s="6" t="inlineStr">
         <is>
-          <t>우수한 열 관리 성능</t>
+          <t>높은 열전도 효율로 컨테이너 내부 온도를 균일하게 유지하고, 고출력 운용이 가능합니다.</t>
         </is>
       </c>
       <c r="G179" s="7" t="n"/>
       <c r="H179" s="8" t="n"/>
-      <c r="I179" s="5" t="inlineStr">
-        <is>
-          <t>묶음 41 — 같은 문구 3 곳</t>
-        </is>
-      </c>
+      <c r="I179" s="5" t="inlineStr"/>
       <c r="J179" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[2]/span/span[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[2]/span/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -12154,7 +12148,7 @@
       </c>
       <c r="C180" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 설명</t>
+          <t>제품 특징 항목</t>
         </is>
       </c>
       <c r="D180" s="5" t="inlineStr">
@@ -12162,18 +12156,24 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E180" s="5" t="inlineStr"/>
+      <c r="E180" s="5" t="n">
+        <v>42</v>
+      </c>
       <c r="F180" s="6" t="inlineStr">
         <is>
-          <t>높은 열전도 효율로 컨테이너 내부 온도를 균일하게 유지하고, 고출력 운용이 가능합니다.</t>
+          <t>고출력·고밀도 시스템에 최적</t>
         </is>
       </c>
       <c r="G180" s="7" t="n"/>
       <c r="H180" s="8" t="n"/>
-      <c r="I180" s="5" t="inlineStr"/>
+      <c r="I180" s="5" t="inlineStr">
+        <is>
+          <t>묶음 42 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J180" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[2]/span/span[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[3]/span/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -12188,7 +12188,7 @@
       </c>
       <c r="C181" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 항목</t>
+          <t>제품 특징 설명</t>
         </is>
       </c>
       <c r="D181" s="5" t="inlineStr">
@@ -12197,23 +12197,23 @@
         </is>
       </c>
       <c r="E181" s="5" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="F181" s="6" t="inlineStr">
         <is>
-          <t>고출력·고밀도 시스템에 최적</t>
+          <t>높은 에너지 밀도와 연속 고출력 환경에서도 안정적인 성능을 제공합니다.</t>
         </is>
       </c>
       <c r="G181" s="7" t="n"/>
       <c r="H181" s="8" t="n"/>
       <c r="I181" s="5" t="inlineStr">
         <is>
-          <t>묶음 42 — 같은 문구 2 곳</t>
+          <t>묶음 43 — 같은 문구 2 곳</t>
         </is>
       </c>
       <c r="J181" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[3]/span/span[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[3]/span/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -12228,7 +12228,7 @@
       </c>
       <c r="C182" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 설명</t>
+          <t>제품 특징 항목</t>
         </is>
       </c>
       <c r="D182" s="5" t="inlineStr">
@@ -12237,23 +12237,23 @@
         </is>
       </c>
       <c r="E182" s="5" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="F182" s="6" t="inlineStr">
         <is>
-          <t>높은 에너지 밀도와 연속 고출력 환경에서도 안정적인 성능을 제공합니다.</t>
+          <t>저소음 설계 가능</t>
         </is>
       </c>
       <c r="G182" s="7" t="n"/>
       <c r="H182" s="8" t="n"/>
       <c r="I182" s="5" t="inlineStr">
         <is>
-          <t>묶음 43 — 같은 문구 2 곳</t>
+          <t>묶음 44 — 같은 문구 2 곳</t>
         </is>
       </c>
       <c r="J182" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[3]/span/span[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[4]/span/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -12268,7 +12268,7 @@
       </c>
       <c r="C183" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 항목</t>
+          <t>제품 특징 설명</t>
         </is>
       </c>
       <c r="D183" s="5" t="inlineStr">
@@ -12277,23 +12277,23 @@
         </is>
       </c>
       <c r="E183" s="5" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="F183" s="6" t="inlineStr">
         <is>
-          <t>저소음 설계 가능</t>
+          <t>팬 사용을 최소화하여 소음을 줄이고, 시스템 효율을 향상시킵니다.</t>
         </is>
       </c>
       <c r="G183" s="7" t="n"/>
       <c r="H183" s="8" t="n"/>
       <c r="I183" s="5" t="inlineStr">
         <is>
-          <t>묶음 44 — 같은 문구 2 곳</t>
+          <t>묶음 45 — 같은 문구 2 곳</t>
         </is>
       </c>
       <c r="J183" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[4]/span/span[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[4]/span/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -12308,7 +12308,7 @@
       </c>
       <c r="C184" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 설명</t>
+          <t>제품 용도 제목</t>
         </is>
       </c>
       <c r="D184" s="5" t="inlineStr">
@@ -12317,23 +12317,23 @@
         </is>
       </c>
       <c r="E184" s="5" t="n">
-        <v>45</v>
+        <v>38</v>
       </c>
       <c r="F184" s="6" t="inlineStr">
         <is>
-          <t>팬 사용을 최소화하여 소음을 줄이고, 시스템 효율을 향상시킵니다.</t>
+          <t>주요 적용 분야</t>
         </is>
       </c>
       <c r="G184" s="7" t="n"/>
       <c r="H184" s="8" t="n"/>
       <c r="I184" s="5" t="inlineStr">
         <is>
-          <t>묶음 45 — 같은 문구 2 곳</t>
+          <t>묶음 38 — 같은 문구 9 곳</t>
         </is>
       </c>
       <c r="J184" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/ul/li[4]/span/span[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/p/b|text</t>
         </is>
       </c>
     </row>
@@ -12348,7 +12348,7 @@
       </c>
       <c r="C185" s="5" t="inlineStr">
         <is>
-          <t>제품 용도 제목</t>
+          <t>제품 용도 설명</t>
         </is>
       </c>
       <c r="D185" s="5" t="inlineStr">
@@ -12357,23 +12357,23 @@
         </is>
       </c>
       <c r="E185" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F185" s="6" t="inlineStr">
         <is>
-          <t>주요 적용 분야</t>
+          <t>ESS, Telecom, Military, Electric Vehicle, Industrial, Aerospace, Marine 등</t>
         </is>
       </c>
       <c r="G185" s="7" t="n"/>
       <c r="H185" s="8" t="n"/>
       <c r="I185" s="5" t="inlineStr">
         <is>
-          <t>묶음 38 — 같은 문구 9 곳</t>
+          <t>묶음 39 — 같은 문구 9 곳</t>
         </is>
       </c>
       <c r="J185" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/p/b|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/p/span|text</t>
         </is>
       </c>
     </row>
@@ -12383,37 +12383,31 @@
       </c>
       <c r="B186" s="5" t="inlineStr">
         <is>
-          <t>03-3 Container</t>
+          <t>03-4 BMS</t>
         </is>
       </c>
       <c r="C186" s="5" t="inlineStr">
         <is>
-          <t>제품 용도 설명</t>
+          <t>머리 번호</t>
         </is>
       </c>
       <c r="D186" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E186" s="5" t="n">
-        <v>39</v>
-      </c>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E186" s="5" t="inlineStr"/>
       <c r="F186" s="6" t="inlineStr">
         <is>
-          <t>ESS, Telecom, Military, Electric Vehicle, Industrial, Aerospace, Marine 등</t>
-        </is>
-      </c>
-      <c r="G186" s="7" t="n"/>
-      <c r="H186" s="8" t="n"/>
-      <c r="I186" s="5" t="inlineStr">
-        <is>
-          <t>묶음 39 — 같은 문구 9 곳</t>
-        </is>
-      </c>
+          <t>03-4</t>
+        </is>
+      </c>
+      <c r="G186" s="6" t="n"/>
+      <c r="H186" s="6" t="n"/>
+      <c r="I186" s="5" t="inlineStr"/>
       <c r="J186" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[3]/div[2]/div[2]/div[2]/div/p/span|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[1]/p/span|text</t>
         </is>
       </c>
     </row>
@@ -12428,26 +12422,36 @@
       </c>
       <c r="C187" s="5" t="inlineStr">
         <is>
-          <t>머리 번호</t>
+          <t>소분류 제목</t>
         </is>
       </c>
       <c r="D187" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="E187" s="5" t="inlineStr"/>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E187" s="5" t="n">
+        <v>31</v>
+      </c>
       <c r="F187" s="6" t="inlineStr">
         <is>
-          <t>03-4</t>
-        </is>
-      </c>
-      <c r="G187" s="6" t="n"/>
-      <c r="H187" s="6" t="n"/>
-      <c r="I187" s="5" t="inlineStr"/>
+          <t>BMS</t>
+        </is>
+      </c>
+      <c r="G187" s="7" t="n"/>
+      <c r="H187" s="8" t="inlineStr">
+        <is>
+          <t>BMS</t>
+        </is>
+      </c>
+      <c r="I187" s="5" t="inlineStr">
+        <is>
+          <t>묶음 31 — 같은 문구 2 곳</t>
+        </is>
+      </c>
       <c r="J187" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[1]/p/span|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[1]/div/div[1]/h2|text</t>
         </is>
       </c>
     </row>
@@ -12462,7 +12466,7 @@
       </c>
       <c r="C188" s="5" t="inlineStr">
         <is>
-          <t>소분류 제목</t>
+          <t>소분류 리드</t>
         </is>
       </c>
       <c r="D188" s="5" t="inlineStr">
@@ -12470,28 +12474,22 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E188" s="5" t="n">
-        <v>31</v>
-      </c>
+      <c r="E188" s="5" t="inlineStr"/>
       <c r="F188" s="6" t="inlineStr">
         <is>
-          <t>BMS</t>
+          <t>Battery의 상태를 지속적으로 Monitoring하고 각 시스템 Level의 정보를 통합하여 안정적인 Battery System을 운영할 수 있는 BMS Solution을 제공합니다.</t>
         </is>
       </c>
       <c r="G188" s="7" t="n"/>
       <c r="H188" s="8" t="inlineStr">
         <is>
-          <t>BMS</t>
-        </is>
-      </c>
-      <c r="I188" s="5" t="inlineStr">
-        <is>
-          <t>묶음 31 — 같은 문구 2 곳</t>
-        </is>
-      </c>
+          <t>We provide a BMS solution that enables stable battery system operation by continuously monitoring the battery status and integrating information from each system level.</t>
+        </is>
+      </c>
+      <c r="I188" s="5" t="inlineStr"/>
       <c r="J188" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[1]/div/div[1]/h2|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[1]/div/div[1]/p|text</t>
         </is>
       </c>
     </row>
@@ -12506,7 +12504,7 @@
       </c>
       <c r="C189" s="5" t="inlineStr">
         <is>
-          <t>소분류 리드</t>
+          <t>인증 제목</t>
         </is>
       </c>
       <c r="D189" s="5" t="inlineStr">
@@ -12514,22 +12512,24 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E189" s="5" t="inlineStr"/>
+      <c r="E189" s="5" t="n">
+        <v>34</v>
+      </c>
       <c r="F189" s="6" t="inlineStr">
         <is>
-          <t>Battery의 상태를 지속적으로 Monitoring하고 각 시스템 Level의 정보를 통합하여 안정적인 Battery System을 운영할 수 있는 BMS Solution을 제공합니다.</t>
+          <t>Certification</t>
         </is>
       </c>
       <c r="G189" s="7" t="n"/>
-      <c r="H189" s="8" t="inlineStr">
-        <is>
-          <t>We provide a BMS solution that enables stable battery system operation by continuously monitoring the battery status and integrating information from each system level.</t>
-        </is>
-      </c>
-      <c r="I189" s="5" t="inlineStr"/>
+      <c r="H189" s="8" t="n"/>
+      <c r="I189" s="5" t="inlineStr">
+        <is>
+          <t>묶음 34 — 같은 문구 4 곳</t>
+        </is>
+      </c>
       <c r="J189" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[1]/div/div[1]/p|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[1]/div/div[2]/p|text</t>
         </is>
       </c>
     </row>
@@ -12544,7 +12544,7 @@
       </c>
       <c r="C190" s="5" t="inlineStr">
         <is>
-          <t>인증 제목</t>
+          <t>인증 항목</t>
         </is>
       </c>
       <c r="D190" s="5" t="inlineStr">
@@ -12552,24 +12552,24 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E190" s="5" t="n">
-        <v>34</v>
-      </c>
+      <c r="E190" s="5" t="inlineStr"/>
       <c r="F190" s="6" t="inlineStr">
         <is>
-          <t>Certification</t>
+          <t>Functional Safety
+(IEC 60730-1)</t>
         </is>
       </c>
       <c r="G190" s="7" t="n"/>
-      <c r="H190" s="8" t="n"/>
-      <c r="I190" s="5" t="inlineStr">
-        <is>
-          <t>묶음 34 — 같은 문구 4 곳</t>
-        </is>
-      </c>
+      <c r="H190" s="8" t="inlineStr">
+        <is>
+          <t>Functional Safety
+(IEC 60730-1)</t>
+        </is>
+      </c>
+      <c r="I190" s="5" t="inlineStr"/>
       <c r="J190" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[1]/div/div[2]/p|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[1]/div/div[2]/ul/li[1]|text</t>
         </is>
       </c>
     </row>
@@ -12595,21 +12595,21 @@
       <c r="E191" s="5" t="inlineStr"/>
       <c r="F191" s="6" t="inlineStr">
         <is>
-          <t>Functional Safety
-(IEC 60730-1)</t>
+          <t>Cybersecurity solutions
+(IEC 62443)</t>
         </is>
       </c>
       <c r="G191" s="7" t="n"/>
       <c r="H191" s="8" t="inlineStr">
         <is>
-          <t>Functional Safety
-(IEC 60730-1)</t>
+          <t>Cybersecurity solutions
+(IEC 62443)</t>
         </is>
       </c>
       <c r="I191" s="5" t="inlineStr"/>
       <c r="J191" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[1]/div/div[2]/ul/li[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[1]/div/div[2]/ul/li[2]|text</t>
         </is>
       </c>
     </row>
@@ -12624,32 +12624,26 @@
       </c>
       <c r="C192" s="5" t="inlineStr">
         <is>
-          <t>인증 항목</t>
+          <t>제품 사진 대체글</t>
         </is>
       </c>
       <c r="D192" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>대체글</t>
         </is>
       </c>
       <c r="E192" s="5" t="inlineStr"/>
       <c r="F192" s="6" t="inlineStr">
         <is>
-          <t>Cybersecurity solutions
-(IEC 62443)</t>
+          <t>모듈 BMS(CMU) 제어 보드</t>
         </is>
       </c>
       <c r="G192" s="7" t="n"/>
-      <c r="H192" s="8" t="inlineStr">
-        <is>
-          <t>Cybersecurity solutions
-(IEC 62443)</t>
-        </is>
-      </c>
+      <c r="H192" s="8" t="n"/>
       <c r="I192" s="5" t="inlineStr"/>
       <c r="J192" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[1]/div/div[2]/ul/li[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[1]/img|alt</t>
         </is>
       </c>
     </row>
@@ -12664,26 +12658,30 @@
       </c>
       <c r="C193" s="5" t="inlineStr">
         <is>
-          <t>제품 사진 대체글</t>
+          <t>제품 이름</t>
         </is>
       </c>
       <c r="D193" s="5" t="inlineStr">
         <is>
-          <t>대체글</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E193" s="5" t="inlineStr"/>
       <c r="F193" s="6" t="inlineStr">
         <is>
-          <t>모듈 BMS(CMU) 제어 보드</t>
+          <t>Module BMS(CMU)</t>
         </is>
       </c>
       <c r="G193" s="7" t="n"/>
-      <c r="H193" s="8" t="n"/>
+      <c r="H193" s="8" t="inlineStr">
+        <is>
+          <t>Module BMS(CMU)</t>
+        </is>
+      </c>
       <c r="I193" s="5" t="inlineStr"/>
       <c r="J193" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[1]/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/p/b|text</t>
         </is>
       </c>
     </row>
@@ -12698,7 +12696,7 @@
       </c>
       <c r="C194" s="5" t="inlineStr">
         <is>
-          <t>제품 이름</t>
+          <t>제품 특징 항목</t>
         </is>
       </c>
       <c r="D194" s="5" t="inlineStr">
@@ -12709,19 +12707,15 @@
       <c r="E194" s="5" t="inlineStr"/>
       <c r="F194" s="6" t="inlineStr">
         <is>
-          <t>Module BMS(CMU)</t>
+          <t>정밀한 셀 모니터링</t>
         </is>
       </c>
       <c r="G194" s="7" t="n"/>
-      <c r="H194" s="8" t="inlineStr">
-        <is>
-          <t>Module BMS(CMU)</t>
-        </is>
-      </c>
+      <c r="H194" s="8" t="n"/>
       <c r="I194" s="5" t="inlineStr"/>
       <c r="J194" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/p/b|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[1]/span/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -12736,7 +12730,7 @@
       </c>
       <c r="C195" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 항목</t>
+          <t>제품 특징 설명</t>
         </is>
       </c>
       <c r="D195" s="5" t="inlineStr">
@@ -12747,7 +12741,7 @@
       <c r="E195" s="5" t="inlineStr"/>
       <c r="F195" s="6" t="inlineStr">
         <is>
-          <t>정밀한 셀 모니터링</t>
+          <t>셀 전압, 온도, 밸런싱 상태 등 다양한 데이터를 고정밀로 실시간 측정 및 전송합니다.</t>
         </is>
       </c>
       <c r="G195" s="7" t="n"/>
@@ -12755,7 +12749,7 @@
       <c r="I195" s="5" t="inlineStr"/>
       <c r="J195" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[1]/span/span[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[1]/span/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -12770,7 +12764,7 @@
       </c>
       <c r="C196" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 설명</t>
+          <t>제품 특징 항목</t>
         </is>
       </c>
       <c r="D196" s="5" t="inlineStr">
@@ -12781,7 +12775,7 @@
       <c r="E196" s="5" t="inlineStr"/>
       <c r="F196" s="6" t="inlineStr">
         <is>
-          <t>셀 전압, 온도, 밸런싱 상태 등 다양한 데이터를 고정밀로 실시간 측정 및 전송합니다.</t>
+          <t>높은 신뢰성과 안정성</t>
         </is>
       </c>
       <c r="G196" s="7" t="n"/>
@@ -12789,7 +12783,7 @@
       <c r="I196" s="5" t="inlineStr"/>
       <c r="J196" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[1]/span/span[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[2]/span/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -12804,7 +12798,7 @@
       </c>
       <c r="C197" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 항목</t>
+          <t>제품 특징 설명</t>
         </is>
       </c>
       <c r="D197" s="5" t="inlineStr">
@@ -12815,7 +12809,7 @@
       <c r="E197" s="5" t="inlineStr"/>
       <c r="F197" s="6" t="inlineStr">
         <is>
-          <t>높은 신뢰성과 안정성</t>
+          <t>산업용 등급의 설계와 검증을 통해 장기간 안정적인 모니터링 성능을 제공합니다.</t>
         </is>
       </c>
       <c r="G197" s="7" t="n"/>
@@ -12823,7 +12817,7 @@
       <c r="I197" s="5" t="inlineStr"/>
       <c r="J197" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[2]/span/span[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[2]/span/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -12838,7 +12832,7 @@
       </c>
       <c r="C198" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 설명</t>
+          <t>제품 특징 항목</t>
         </is>
       </c>
       <c r="D198" s="5" t="inlineStr">
@@ -12849,7 +12843,7 @@
       <c r="E198" s="5" t="inlineStr"/>
       <c r="F198" s="6" t="inlineStr">
         <is>
-          <t>산업용 등급의 설계와 검증을 통해 장기간 안정적인 모니터링 성능을 제공합니다.</t>
+          <t>Rack BMS와 완벽 연동</t>
         </is>
       </c>
       <c r="G198" s="7" t="n"/>
@@ -12857,7 +12851,7 @@
       <c r="I198" s="5" t="inlineStr"/>
       <c r="J198" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[2]/span/span[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[3]/span/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -12872,7 +12866,7 @@
       </c>
       <c r="C199" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 항목</t>
+          <t>제품 특징 설명</t>
         </is>
       </c>
       <c r="D199" s="5" t="inlineStr">
@@ -12883,7 +12877,7 @@
       <c r="E199" s="5" t="inlineStr"/>
       <c r="F199" s="6" t="inlineStr">
         <is>
-          <t>Rack BMS와 완벽 연동</t>
+          <t>CMU는 Rack BMS와 안정적인 통신을 통해 셀 정보를 정확하게 전달하고, 제어 명령을 신속하게 수행합니다.</t>
         </is>
       </c>
       <c r="G199" s="7" t="n"/>
@@ -12891,7 +12885,7 @@
       <c r="I199" s="5" t="inlineStr"/>
       <c r="J199" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[3]/span/span[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[3]/span/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -12906,7 +12900,7 @@
       </c>
       <c r="C200" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 설명</t>
+          <t>제품 특징 항목</t>
         </is>
       </c>
       <c r="D200" s="5" t="inlineStr">
@@ -12917,7 +12911,7 @@
       <c r="E200" s="5" t="inlineStr"/>
       <c r="F200" s="6" t="inlineStr">
         <is>
-          <t>CMU는 Rack BMS와 안정적인 통신을 통해 셀 정보를 정확하게 전달하고, 제어 명령을 신속하게 수행합니다.</t>
+          <t>높은 확장성</t>
         </is>
       </c>
       <c r="G200" s="7" t="n"/>
@@ -12925,7 +12919,7 @@
       <c r="I200" s="5" t="inlineStr"/>
       <c r="J200" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[3]/span/span[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[4]/span/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -12940,7 +12934,7 @@
       </c>
       <c r="C201" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 항목</t>
+          <t>제품 특징 설명</t>
         </is>
       </c>
       <c r="D201" s="5" t="inlineStr">
@@ -12951,7 +12945,7 @@
       <c r="E201" s="5" t="inlineStr"/>
       <c r="F201" s="6" t="inlineStr">
         <is>
-          <t>높은 확장성</t>
+          <t>다양한 셀 구성과 모듈 구조를 지원하여 유연한 시스템 확장과 호환성을 제공합니다.</t>
         </is>
       </c>
       <c r="G201" s="7" t="n"/>
@@ -12959,7 +12953,7 @@
       <c r="I201" s="5" t="inlineStr"/>
       <c r="J201" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[4]/span/span[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[4]/span/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -12974,7 +12968,7 @@
       </c>
       <c r="C202" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 설명</t>
+          <t>제품 용도 제목</t>
         </is>
       </c>
       <c r="D202" s="5" t="inlineStr">
@@ -12982,18 +12976,24 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E202" s="5" t="inlineStr"/>
+      <c r="E202" s="5" t="n">
+        <v>38</v>
+      </c>
       <c r="F202" s="6" t="inlineStr">
         <is>
-          <t>다양한 셀 구성과 모듈 구조를 지원하여 유연한 시스템 확장과 호환성을 제공합니다.</t>
+          <t>주요 적용 분야</t>
         </is>
       </c>
       <c r="G202" s="7" t="n"/>
       <c r="H202" s="8" t="n"/>
-      <c r="I202" s="5" t="inlineStr"/>
+      <c r="I202" s="5" t="inlineStr">
+        <is>
+          <t>묶음 38 — 같은 문구 9 곳</t>
+        </is>
+      </c>
       <c r="J202" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/ul/li[4]/span/span[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/p/b|text</t>
         </is>
       </c>
     </row>
@@ -13008,7 +13008,7 @@
       </c>
       <c r="C203" s="5" t="inlineStr">
         <is>
-          <t>제품 용도 제목</t>
+          <t>제품 용도 설명</t>
         </is>
       </c>
       <c r="D203" s="5" t="inlineStr">
@@ -13017,23 +13017,23 @@
         </is>
       </c>
       <c r="E203" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F203" s="6" t="inlineStr">
         <is>
-          <t>주요 적용 분야</t>
+          <t>ESS, Telecom, Military, Electric Vehicle, Industrial, Aerospace, Marine 등</t>
         </is>
       </c>
       <c r="G203" s="7" t="n"/>
       <c r="H203" s="8" t="n"/>
       <c r="I203" s="5" t="inlineStr">
         <is>
-          <t>묶음 38 — 같은 문구 9 곳</t>
+          <t>묶음 39 — 같은 문구 9 곳</t>
         </is>
       </c>
       <c r="J203" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/p/b|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/p/span|text</t>
         </is>
       </c>
     </row>
@@ -13048,32 +13048,26 @@
       </c>
       <c r="C204" s="5" t="inlineStr">
         <is>
-          <t>제품 용도 설명</t>
+          <t>제품 사진 대체글</t>
         </is>
       </c>
       <c r="D204" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E204" s="5" t="n">
-        <v>39</v>
-      </c>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E204" s="5" t="inlineStr"/>
       <c r="F204" s="6" t="inlineStr">
         <is>
-          <t>ESS, Telecom, Military, Electric Vehicle, Industrial, Aerospace, Marine 등</t>
+          <t>랙 BMS(BPU) 제어 유닛</t>
         </is>
       </c>
       <c r="G204" s="7" t="n"/>
       <c r="H204" s="8" t="n"/>
-      <c r="I204" s="5" t="inlineStr">
-        <is>
-          <t>묶음 39 — 같은 문구 9 곳</t>
-        </is>
-      </c>
+      <c r="I204" s="5" t="inlineStr"/>
       <c r="J204" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[1]/div[2]/div/p/span|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[1]/img|alt</t>
         </is>
       </c>
     </row>
@@ -13088,26 +13082,30 @@
       </c>
       <c r="C205" s="5" t="inlineStr">
         <is>
-          <t>제품 사진 대체글</t>
+          <t>제품 이름</t>
         </is>
       </c>
       <c r="D205" s="5" t="inlineStr">
         <is>
-          <t>대체글</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E205" s="5" t="inlineStr"/>
       <c r="F205" s="6" t="inlineStr">
         <is>
-          <t>랙 BMS(BPU) 제어 유닛</t>
+          <t>Rack BMS(BPU)</t>
         </is>
       </c>
       <c r="G205" s="7" t="n"/>
-      <c r="H205" s="8" t="n"/>
+      <c r="H205" s="8" t="inlineStr">
+        <is>
+          <t>Rack BMS(BPU)</t>
+        </is>
+      </c>
       <c r="I205" s="5" t="inlineStr"/>
       <c r="J205" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[1]/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/p/b|text</t>
         </is>
       </c>
     </row>
@@ -13122,7 +13120,7 @@
       </c>
       <c r="C206" s="5" t="inlineStr">
         <is>
-          <t>제품 이름</t>
+          <t>제품 특징 항목</t>
         </is>
       </c>
       <c r="D206" s="5" t="inlineStr">
@@ -13133,19 +13131,15 @@
       <c r="E206" s="5" t="inlineStr"/>
       <c r="F206" s="6" t="inlineStr">
         <is>
-          <t>Rack BMS(BPU)</t>
+          <t>Rack 상태 통합 모니터링</t>
         </is>
       </c>
       <c r="G206" s="7" t="n"/>
-      <c r="H206" s="8" t="inlineStr">
-        <is>
-          <t>Rack BMS(BPU)</t>
-        </is>
-      </c>
+      <c r="H206" s="8" t="n"/>
       <c r="I206" s="5" t="inlineStr"/>
       <c r="J206" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/p/b|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[1]/span/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -13160,7 +13154,7 @@
       </c>
       <c r="C207" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 항목</t>
+          <t>제품 특징 설명</t>
         </is>
       </c>
       <c r="D207" s="5" t="inlineStr">
@@ -13171,7 +13165,7 @@
       <c r="E207" s="5" t="inlineStr"/>
       <c r="F207" s="6" t="inlineStr">
         <is>
-          <t>Rack 상태 통합 모니터링</t>
+          <t>Rack 내 모듈의 전압, 전류, 온도 및 SOC/SOH 등 주요 상태 정보를 통합 관리합니다.</t>
         </is>
       </c>
       <c r="G207" s="7" t="n"/>
@@ -13179,7 +13173,7 @@
       <c r="I207" s="5" t="inlineStr"/>
       <c r="J207" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[1]/span/span[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[1]/span/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -13194,7 +13188,7 @@
       </c>
       <c r="C208" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 설명</t>
+          <t>제품 특징 항목</t>
         </is>
       </c>
       <c r="D208" s="5" t="inlineStr">
@@ -13205,7 +13199,7 @@
       <c r="E208" s="5" t="inlineStr"/>
       <c r="F208" s="6" t="inlineStr">
         <is>
-          <t>Rack 내 모듈의 전압, 전류, 온도 및 SOC/SOH 등 주요 상태 정보를 통합 관리합니다.</t>
+          <t>보호 및 제어 기능</t>
         </is>
       </c>
       <c r="G208" s="7" t="n"/>
@@ -13213,7 +13207,7 @@
       <c r="I208" s="5" t="inlineStr"/>
       <c r="J208" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[1]/span/span[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[2]/span/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -13228,7 +13222,7 @@
       </c>
       <c r="C209" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 항목</t>
+          <t>제품 특징 설명</t>
         </is>
       </c>
       <c r="D209" s="5" t="inlineStr">
@@ -13239,7 +13233,7 @@
       <c r="E209" s="5" t="inlineStr"/>
       <c r="F209" s="6" t="inlineStr">
         <is>
-          <t>보호 및 제어 기능</t>
+          <t>과전압/과전류/과온도 등 이상 상황을 실시간 감지하고 보호 동작과 제어를 수행합니다.</t>
         </is>
       </c>
       <c r="G209" s="7" t="n"/>
@@ -13247,7 +13241,7 @@
       <c r="I209" s="5" t="inlineStr"/>
       <c r="J209" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[2]/span/span[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[2]/span/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -13262,7 +13256,7 @@
       </c>
       <c r="C210" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 설명</t>
+          <t>제품 특징 항목</t>
         </is>
       </c>
       <c r="D210" s="5" t="inlineStr">
@@ -13273,7 +13267,7 @@
       <c r="E210" s="5" t="inlineStr"/>
       <c r="F210" s="6" t="inlineStr">
         <is>
-          <t>과전압/과전류/과온도 등 이상 상황을 실시간 감지하고 보호 동작과 제어를 수행합니다.</t>
+          <t>BPU 하드웨어 통합 보호</t>
         </is>
       </c>
       <c r="G210" s="7" t="n"/>
@@ -13281,7 +13275,7 @@
       <c r="I210" s="5" t="inlineStr"/>
       <c r="J210" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[2]/span/span[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[3]/span/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -13296,7 +13290,7 @@
       </c>
       <c r="C211" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 항목</t>
+          <t>제품 특징 설명</t>
         </is>
       </c>
       <c r="D211" s="5" t="inlineStr">
@@ -13307,7 +13301,7 @@
       <c r="E211" s="5" t="inlineStr"/>
       <c r="F211" s="6" t="inlineStr">
         <is>
-          <t>BPU 하드웨어 통합 보호</t>
+          <t>차단기, 퓨즈, 접촉기 등 보호 장치와 연계하여 안전한 배터리 시스템을 구성합니다.</t>
         </is>
       </c>
       <c r="G211" s="7" t="n"/>
@@ -13315,7 +13309,7 @@
       <c r="I211" s="5" t="inlineStr"/>
       <c r="J211" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[3]/span/span[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[3]/span/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -13330,7 +13324,7 @@
       </c>
       <c r="C212" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 설명</t>
+          <t>제품 특징 항목</t>
         </is>
       </c>
       <c r="D212" s="5" t="inlineStr">
@@ -13341,7 +13335,7 @@
       <c r="E212" s="5" t="inlineStr"/>
       <c r="F212" s="6" t="inlineStr">
         <is>
-          <t>차단기, 퓨즈, 접촉기 등 보호 장치와 연계하여 안전한 배터리 시스템을 구성합니다.</t>
+          <t>기능안전 인증 취득</t>
         </is>
       </c>
       <c r="G212" s="7" t="n"/>
@@ -13349,7 +13343,7 @@
       <c r="I212" s="5" t="inlineStr"/>
       <c r="J212" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[3]/span/span[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[4]/span/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -13364,7 +13358,7 @@
       </c>
       <c r="C213" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 항목</t>
+          <t>제품 특징 설명</t>
         </is>
       </c>
       <c r="D213" s="5" t="inlineStr">
@@ -13375,7 +13369,7 @@
       <c r="E213" s="5" t="inlineStr"/>
       <c r="F213" s="6" t="inlineStr">
         <is>
-          <t>기능안전 인증 취득</t>
+          <t>IEC 60730 국제 표준에 기반한 기능안전 인증을 취득하여 안정성과 신뢰성을 검증받았습니다.</t>
         </is>
       </c>
       <c r="G213" s="7" t="n"/>
@@ -13383,7 +13377,7 @@
       <c r="I213" s="5" t="inlineStr"/>
       <c r="J213" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[4]/span/span[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[4]/span/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -13398,7 +13392,7 @@
       </c>
       <c r="C214" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 설명</t>
+          <t>제품 용도 제목</t>
         </is>
       </c>
       <c r="D214" s="5" t="inlineStr">
@@ -13406,18 +13400,24 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E214" s="5" t="inlineStr"/>
+      <c r="E214" s="5" t="n">
+        <v>38</v>
+      </c>
       <c r="F214" s="6" t="inlineStr">
         <is>
-          <t>IEC 60730 국제 표준에 기반한 기능안전 인증을 취득하여 안정성과 신뢰성을 검증받았습니다.</t>
+          <t>주요 적용 분야</t>
         </is>
       </c>
       <c r="G214" s="7" t="n"/>
       <c r="H214" s="8" t="n"/>
-      <c r="I214" s="5" t="inlineStr"/>
+      <c r="I214" s="5" t="inlineStr">
+        <is>
+          <t>묶음 38 — 같은 문구 9 곳</t>
+        </is>
+      </c>
       <c r="J214" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/ul/li[4]/span/span[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/p/b|text</t>
         </is>
       </c>
     </row>
@@ -13432,7 +13432,7 @@
       </c>
       <c r="C215" s="5" t="inlineStr">
         <is>
-          <t>제품 용도 제목</t>
+          <t>제품 용도 설명</t>
         </is>
       </c>
       <c r="D215" s="5" t="inlineStr">
@@ -13441,23 +13441,23 @@
         </is>
       </c>
       <c r="E215" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F215" s="6" t="inlineStr">
         <is>
-          <t>주요 적용 분야</t>
+          <t>ESS, Telecom, Military, Electric Vehicle, Industrial, Aerospace, Marine 등</t>
         </is>
       </c>
       <c r="G215" s="7" t="n"/>
       <c r="H215" s="8" t="n"/>
       <c r="I215" s="5" t="inlineStr">
         <is>
-          <t>묶음 38 — 같은 문구 9 곳</t>
+          <t>묶음 39 — 같은 문구 9 곳</t>
         </is>
       </c>
       <c r="J215" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/p/b|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/p/span|text</t>
         </is>
       </c>
     </row>
@@ -13472,32 +13472,26 @@
       </c>
       <c r="C216" s="5" t="inlineStr">
         <is>
-          <t>제품 용도 설명</t>
+          <t>제품 사진 대체글</t>
         </is>
       </c>
       <c r="D216" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E216" s="5" t="n">
-        <v>39</v>
-      </c>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E216" s="5" t="inlineStr"/>
       <c r="F216" s="6" t="inlineStr">
         <is>
-          <t>ESS, Telecom, Military, Electric Vehicle, Industrial, Aerospace, Marine 등</t>
+          <t>시스템 BMS(BCP) 제어반</t>
         </is>
       </c>
       <c r="G216" s="7" t="n"/>
       <c r="H216" s="8" t="n"/>
-      <c r="I216" s="5" t="inlineStr">
-        <is>
-          <t>묶음 39 — 같은 문구 9 곳</t>
-        </is>
-      </c>
+      <c r="I216" s="5" t="inlineStr"/>
       <c r="J216" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[2]/div[2]/div/p/span|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[1]/img|alt</t>
         </is>
       </c>
     </row>
@@ -13512,26 +13506,30 @@
       </c>
       <c r="C217" s="5" t="inlineStr">
         <is>
-          <t>제품 사진 대체글</t>
+          <t>제품 이름</t>
         </is>
       </c>
       <c r="D217" s="5" t="inlineStr">
         <is>
-          <t>대체글</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E217" s="5" t="inlineStr"/>
       <c r="F217" s="6" t="inlineStr">
         <is>
-          <t>시스템 BMS(BCP) 제어반</t>
+          <t>System BMS(BCP)</t>
         </is>
       </c>
       <c r="G217" s="7" t="n"/>
-      <c r="H217" s="8" t="n"/>
+      <c r="H217" s="8" t="inlineStr">
+        <is>
+          <t>System BMS(BCP)</t>
+        </is>
+      </c>
       <c r="I217" s="5" t="inlineStr"/>
       <c r="J217" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[1]/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/p/b|text</t>
         </is>
       </c>
     </row>
@@ -13546,7 +13544,7 @@
       </c>
       <c r="C218" s="5" t="inlineStr">
         <is>
-          <t>제품 이름</t>
+          <t>제품 특징 항목</t>
         </is>
       </c>
       <c r="D218" s="5" t="inlineStr">
@@ -13557,19 +13555,15 @@
       <c r="E218" s="5" t="inlineStr"/>
       <c r="F218" s="6" t="inlineStr">
         <is>
-          <t>System BMS(BCP)</t>
+          <t>전체 시스템 통합 관리</t>
         </is>
       </c>
       <c r="G218" s="7" t="n"/>
-      <c r="H218" s="8" t="inlineStr">
-        <is>
-          <t>System BMS(BCP)</t>
-        </is>
-      </c>
+      <c r="H218" s="8" t="n"/>
       <c r="I218" s="5" t="inlineStr"/>
       <c r="J218" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/p/b|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[1]/span/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -13584,7 +13578,7 @@
       </c>
       <c r="C219" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 항목</t>
+          <t>제품 특징 설명</t>
         </is>
       </c>
       <c r="D219" s="5" t="inlineStr">
@@ -13595,7 +13589,7 @@
       <c r="E219" s="5" t="inlineStr"/>
       <c r="F219" s="6" t="inlineStr">
         <is>
-          <t>전체 시스템 통합 관리</t>
+          <t>다수의 Rack 상태를 통합 모니터링하고, 시스템 레벨의 운영 및 보호 기능을 수행합니다.</t>
         </is>
       </c>
       <c r="G219" s="7" t="n"/>
@@ -13603,7 +13597,7 @@
       <c r="I219" s="5" t="inlineStr"/>
       <c r="J219" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[1]/span/span[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[1]/span/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -13618,7 +13612,7 @@
       </c>
       <c r="C220" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 설명</t>
+          <t>제품 특징 항목</t>
         </is>
       </c>
       <c r="D220" s="5" t="inlineStr">
@@ -13629,7 +13623,7 @@
       <c r="E220" s="5" t="inlineStr"/>
       <c r="F220" s="6" t="inlineStr">
         <is>
-          <t>다수의 Rack 상태를 통합 모니터링하고, 시스템 레벨의 운영 및 보호 기능을 수행합니다.</t>
+          <t>상위 시스템 연계</t>
         </is>
       </c>
       <c r="G220" s="7" t="n"/>
@@ -13637,7 +13631,7 @@
       <c r="I220" s="5" t="inlineStr"/>
       <c r="J220" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[1]/span/span[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[2]/span/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -13652,7 +13646,7 @@
       </c>
       <c r="C221" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 항목</t>
+          <t>제품 특징 설명</t>
         </is>
       </c>
       <c r="D221" s="5" t="inlineStr">
@@ -13663,7 +13657,7 @@
       <c r="E221" s="5" t="inlineStr"/>
       <c r="F221" s="6" t="inlineStr">
         <is>
-          <t>상위 시스템 연계</t>
+          <t>EMS, PCS, SCADA 등 상위 시스템과 연동하여 효율적인 에너지 운영을 지원합니다.</t>
         </is>
       </c>
       <c r="G221" s="7" t="n"/>
@@ -13671,7 +13665,7 @@
       <c r="I221" s="5" t="inlineStr"/>
       <c r="J221" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[2]/span/span[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[2]/span/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -13686,7 +13680,7 @@
       </c>
       <c r="C222" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 설명</t>
+          <t>제품 특징 항목</t>
         </is>
       </c>
       <c r="D222" s="5" t="inlineStr">
@@ -13697,7 +13691,7 @@
       <c r="E222" s="5" t="inlineStr"/>
       <c r="F222" s="6" t="inlineStr">
         <is>
-          <t>EMS, PCS, SCADA 등 상위 시스템과 연동하여 효율적인 에너지 운영을 지원합니다.</t>
+          <t>시스템 보호 및 제어</t>
         </is>
       </c>
       <c r="G222" s="7" t="n"/>
@@ -13705,7 +13699,7 @@
       <c r="I222" s="5" t="inlineStr"/>
       <c r="J222" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[2]/span/span[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[3]/span/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -13720,7 +13714,7 @@
       </c>
       <c r="C223" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 항목</t>
+          <t>제품 특징 설명</t>
         </is>
       </c>
       <c r="D223" s="5" t="inlineStr">
@@ -13731,7 +13725,7 @@
       <c r="E223" s="5" t="inlineStr"/>
       <c r="F223" s="6" t="inlineStr">
         <is>
-          <t>시스템 보호 및 제어</t>
+          <t>시스템 차단, 절연 감시, 고장 진단 등 다양한 보호 및 제어 기능으로 안전성을 극대화합니다.</t>
         </is>
       </c>
       <c r="G223" s="7" t="n"/>
@@ -13739,7 +13733,7 @@
       <c r="I223" s="5" t="inlineStr"/>
       <c r="J223" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[3]/span/span[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[3]/span/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -13754,7 +13748,7 @@
       </c>
       <c r="C224" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 설명</t>
+          <t>제품 특징 항목</t>
         </is>
       </c>
       <c r="D224" s="5" t="inlineStr">
@@ -13765,7 +13759,7 @@
       <c r="E224" s="5" t="inlineStr"/>
       <c r="F224" s="6" t="inlineStr">
         <is>
-          <t>시스템 차단, 절연 감시, 고장 진단 등 다양한 보호 및 제어 기능으로 안전성을 극대화합니다.</t>
+          <t>사이버 보안 솔루션 제공</t>
         </is>
       </c>
       <c r="G224" s="7" t="n"/>
@@ -13773,7 +13767,7 @@
       <c r="I224" s="5" t="inlineStr"/>
       <c r="J224" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[3]/span/span[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[4]/span/span[1]|text</t>
         </is>
       </c>
     </row>
@@ -13788,7 +13782,7 @@
       </c>
       <c r="C225" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 항목</t>
+          <t>제품 특징 설명</t>
         </is>
       </c>
       <c r="D225" s="5" t="inlineStr">
@@ -13799,7 +13793,7 @@
       <c r="E225" s="5" t="inlineStr"/>
       <c r="F225" s="6" t="inlineStr">
         <is>
-          <t>사이버 보안 솔루션 제공</t>
+          <t>IEC 62443 기반의 사이버 보안 솔루션을 제공하여 네트워크 보안, 데이터 암호화, 접근 제어, 침입 탐지 등 다계층 보안 체계를 지원합니다.</t>
         </is>
       </c>
       <c r="G225" s="7" t="n"/>
@@ -13807,7 +13801,7 @@
       <c r="I225" s="5" t="inlineStr"/>
       <c r="J225" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[4]/span/span[1]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[4]/span/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -13822,7 +13816,7 @@
       </c>
       <c r="C226" s="5" t="inlineStr">
         <is>
-          <t>제품 특징 설명</t>
+          <t>제품 용도 제목</t>
         </is>
       </c>
       <c r="D226" s="5" t="inlineStr">
@@ -13830,18 +13824,24 @@
           <t>문구</t>
         </is>
       </c>
-      <c r="E226" s="5" t="inlineStr"/>
+      <c r="E226" s="5" t="n">
+        <v>38</v>
+      </c>
       <c r="F226" s="6" t="inlineStr">
         <is>
-          <t>IEC 62443 기반의 사이버 보안 솔루션을 제공하여 네트워크 보안, 데이터 암호화, 접근 제어, 침입 탐지 등 다계층 보안 체계를 지원합니다.</t>
+          <t>주요 적용 분야</t>
         </is>
       </c>
       <c r="G226" s="7" t="n"/>
       <c r="H226" s="8" t="n"/>
-      <c r="I226" s="5" t="inlineStr"/>
+      <c r="I226" s="5" t="inlineStr">
+        <is>
+          <t>묶음 38 — 같은 문구 9 곳</t>
+        </is>
+      </c>
       <c r="J226" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/ul/li[4]/span/span[2]|text</t>
+          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/p/b|text</t>
         </is>
       </c>
     </row>
@@ -13856,7 +13856,7 @@
       </c>
       <c r="C227" s="5" t="inlineStr">
         <is>
-          <t>제품 용도 제목</t>
+          <t>제품 용도 설명</t>
         </is>
       </c>
       <c r="D227" s="5" t="inlineStr">
@@ -13865,68 +13865,28 @@
         </is>
       </c>
       <c r="E227" s="5" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="F227" s="6" t="inlineStr">
         <is>
-          <t>주요 적용 분야</t>
+          <t>ESS, Telecom, Military, Electric Vehicle, Industrial, Aerospace, Marine 등</t>
         </is>
       </c>
       <c r="G227" s="7" t="n"/>
       <c r="H227" s="8" t="n"/>
       <c r="I227" s="5" t="inlineStr">
         <is>
-          <t>묶음 38 — 같은 문구 9 곳</t>
+          <t>묶음 39 — 같은 문구 9 곳</t>
         </is>
       </c>
       <c r="J227" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/p/b|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" s="5" t="n">
-        <v>227</v>
-      </c>
-      <c r="B228" s="5" t="inlineStr">
-        <is>
-          <t>03-4 BMS</t>
-        </is>
-      </c>
-      <c r="C228" s="5" t="inlineStr">
-        <is>
-          <t>제품 용도 설명</t>
-        </is>
-      </c>
-      <c r="D228" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E228" s="5" t="n">
-        <v>39</v>
-      </c>
-      <c r="F228" s="6" t="inlineStr">
-        <is>
-          <t>ESS, Telecom, Military, Electric Vehicle, Industrial, Aerospace, Marine 등</t>
-        </is>
-      </c>
-      <c r="G228" s="7" t="n"/>
-      <c r="H228" s="8" t="n"/>
-      <c r="I228" s="5" t="inlineStr">
-        <is>
-          <t>묶음 39 — 같은 문구 9 곳</t>
-        </is>
-      </c>
-      <c r="J228" s="9" t="inlineStr">
-        <is>
           <t>/html/body/div[8]/div[2]/div[2]/section[4]/div[2]/div[3]/div[2]/div/p/span|text</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J228"/>
+  <autoFilter ref="A1:J227"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/content-export/04_사업영역_문구.xlsx
+++ b/content-export/04_사업영역_문구.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$J$144</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'에너지 인프라'!$A$1:$J$189</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'인공지능 플랫폼'!$A$1:$J$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'인공지능 플랫폼'!$A$1:$J$45</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'화합물 전력 반도체'!$A$1:$J$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="B1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 401 줄입니다.</t>
+          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 399 줄입니다.</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -13183,7 +13183,11 @@
         </is>
       </c>
       <c r="G9" s="7" t="n"/>
-      <c r="H9" s="8" t="n"/>
+      <c r="H9" s="8" t="inlineStr">
+        <is>
+          <t>EV Charging Platform</t>
+        </is>
+      </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
           <t>같은 문구 2 곳 — 한 줄로 합침</t>
@@ -13202,12 +13206,12 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>개요 · 좌측 인덱스</t>
+          <t>개요 · 좌측 인덱스 · 04-1 전기자동차 제어 플랫폼</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>개요 카드 · 인덱스 그룹 이름</t>
+          <t>개요 카드 · 인덱스 그룹 이름 · 인덱스 항목 · 장 제목</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
@@ -13222,16 +13226,22 @@
         </is>
       </c>
       <c r="G10" s="7" t="n"/>
-      <c r="H10" s="8" t="n"/>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>EV Control Platform</t>
+        </is>
+      </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 2 곳 — 한 줄로 합침</t>
+          <t>같은 문구 4 곳 — 한 줄로 합침</t>
         </is>
       </c>
       <c r="J10" s="9" t="inlineStr">
         <is>
           <t>/html/body/section[2]/ul/li[4]/p|text
-/html/body/div[8]/div[1]/nav/div[4]/p/span[2]|text</t>
+/html/body/div[8]/div[1]/nav/div[4]/p/span[2]|text
+/html/body/div[8]/div[1]/nav/div[4]/a|text
+/html/body/div[8]/div[3]/section[6]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -13338,7 +13348,11 @@
         </is>
       </c>
       <c r="G13" s="7" t="n"/>
-      <c r="H13" s="8" t="n"/>
+      <c r="H13" s="8" t="inlineStr">
+        <is>
+          <t>Robot Fleet Management Platform</t>
+        </is>
+      </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
           <t>같은 문구 2 곳 — 한 줄로 합침</t>
@@ -13411,7 +13425,11 @@
         </is>
       </c>
       <c r="G15" s="7" t="n"/>
-      <c r="H15" s="8" t="n"/>
+      <c r="H15" s="8" t="inlineStr">
+        <is>
+          <t>EV Battery Safety Diagnosis</t>
+        </is>
+      </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
           <t>같은 문구 2 곳 — 한 줄로 합침</t>
@@ -13450,7 +13468,11 @@
         </is>
       </c>
       <c r="G16" s="7" t="n"/>
-      <c r="H16" s="8" t="n"/>
+      <c r="H16" s="8" t="inlineStr">
+        <is>
+          <t>EV Battery Performance Diagnosis</t>
+        </is>
+      </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
           <t>같은 문구 2 곳 — 한 줄로 합침</t>
@@ -13503,12 +13525,12 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>좌측 인덱스 · 03-1 급속 충전기</t>
+          <t>좌측 인덱스 · 03-1 PICKLE Station</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>인덱스 항목 · 장 제목</t>
+          <t>인덱스 항목 · 장 제목 · 작은 제목</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -13519,20 +13541,25 @@
       <c r="E18" s="5" t="inlineStr"/>
       <c r="F18" s="6" t="inlineStr">
         <is>
-          <t>급속 충전기</t>
+          <t>PICKLE Station</t>
         </is>
       </c>
       <c r="G18" s="7" t="n"/>
-      <c r="H18" s="8" t="n"/>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>PICKLE Station</t>
+        </is>
+      </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 2 곳 — 한 줄로 합침</t>
+          <t>같은 문구 3 곳 — 한 줄로 합침</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[3]/a|text
-/html/body/div[8]/div[3]/section[5]/div/div[2]/div/h2|text</t>
+/html/body/div[8]/div[3]/section[5]/div/div[2]/div/h2|text
+/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -13576,36 +13603,31 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>좌측 인덱스 · 04-1 EV 제어기</t>
+          <t>좌측 인덱스</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>인덱스 항목 · 장 제목</t>
+          <t>장 번호</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr"/>
       <c r="F20" s="6" t="inlineStr">
         <is>
-          <t>EV 제어기</t>
-        </is>
-      </c>
-      <c r="G20" s="7" t="n"/>
-      <c r="H20" s="8" t="n"/>
-      <c r="I20" s="5" t="inlineStr">
-        <is>
-          <t>같은 문구 2 곳 — 한 줄로 합침</t>
-        </is>
-      </c>
+          <t>01234567890123456789-0123456789</t>
+        </is>
+      </c>
+      <c r="G20" s="6" t="n"/>
+      <c r="H20" s="6" t="n"/>
+      <c r="I20" s="5" t="n"/>
       <c r="J20" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[1]/nav/div[4]/a|text
-/html/body/div[8]/div[3]/section[6]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[1]/span|text</t>
         </is>
       </c>
     </row>
@@ -13620,26 +13642,26 @@
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>장 번호</t>
+          <t>그림 대체글</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>대체글</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr"/>
       <c r="F21" s="6" t="inlineStr">
         <is>
-          <t>01234567890123456789-0123456789</t>
-        </is>
-      </c>
-      <c r="G21" s="6" t="n"/>
-      <c r="H21" s="6" t="n"/>
+          <t>이차전지 설비 앞을 도는 바퀴형 안전 진단 로봇</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="8" t="n"/>
       <c r="I21" s="5" t="n"/>
       <c r="J21" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[1]/span|text</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[1]/img|alt</t>
         </is>
       </c>
     </row>
@@ -13665,7 +13687,7 @@
       <c r="E22" s="5" t="inlineStr"/>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>이차전지 설비 앞을 도는 바퀴형 안전 진단 로봇</t>
+          <t>펌프 설비를 점검하는 네 발 보행 로봇</t>
         </is>
       </c>
       <c r="G22" s="7" t="n"/>
@@ -13673,7 +13695,7 @@
       <c r="I22" s="5" t="n"/>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[1]/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[2]/img|alt</t>
         </is>
       </c>
     </row>
@@ -13699,7 +13721,7 @@
       <c r="E23" s="5" t="inlineStr"/>
       <c r="F23" s="6" t="inlineStr">
         <is>
-          <t>펌프 설비를 점검하는 네 발 보행 로봇</t>
+          <t>배터리 셀 안전 분류 결과를 표와 히트맵으로 보여 주는 대시보드 화면</t>
         </is>
       </c>
       <c r="G23" s="7" t="n"/>
@@ -13707,7 +13729,7 @@
       <c r="I23" s="5" t="n"/>
       <c r="J23" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[2]/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[3]/div[1]/div/img|alt</t>
         </is>
       </c>
     </row>
@@ -13733,7 +13755,7 @@
       <c r="E24" s="5" t="inlineStr"/>
       <c r="F24" s="6" t="inlineStr">
         <is>
-          <t>배터리 셀 안전 분류 결과를 표와 히트맵으로 보여 주는 대시보드 화면</t>
+          <t>안전 진단 리포트를 등급과 막대로 보여 주는 모바일 화면</t>
         </is>
       </c>
       <c r="G24" s="7" t="n"/>
@@ -13741,7 +13763,7 @@
       <c r="I24" s="5" t="n"/>
       <c r="J24" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[3]/div[1]/div/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[3]/div[2]/div/img|alt</t>
         </is>
       </c>
     </row>
@@ -13767,7 +13789,7 @@
       <c r="E25" s="5" t="inlineStr"/>
       <c r="F25" s="6" t="inlineStr">
         <is>
-          <t>안전 진단 리포트를 등급과 막대로 보여 주는 모바일 화면</t>
+          <t>배터리 진단 결과를 항목별 백분율과 레이더 도표로 보여 주는 화면</t>
         </is>
       </c>
       <c r="G25" s="7" t="n"/>
@@ -13775,7 +13797,7 @@
       <c r="I25" s="5" t="n"/>
       <c r="J25" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[3]/div[2]/div/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[4]/div[1]/div/img|alt</t>
         </is>
       </c>
     </row>
@@ -13801,7 +13823,7 @@
       <c r="E26" s="5" t="inlineStr"/>
       <c r="F26" s="6" t="inlineStr">
         <is>
-          <t>배터리 진단 결과를 항목별 백분율과 레이더 도표로 보여 주는 화면</t>
+          <t>업체와 차량, 배터리 제원을 입력하는 진단 준비 화면</t>
         </is>
       </c>
       <c r="G26" s="7" t="n"/>
@@ -13809,7 +13831,7 @@
       <c r="I26" s="5" t="n"/>
       <c r="J26" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[4]/div[1]/div/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[4]/div[2]/div/img|alt</t>
         </is>
       </c>
     </row>
@@ -13835,7 +13857,7 @@
       <c r="E27" s="5" t="inlineStr"/>
       <c r="F27" s="6" t="inlineStr">
         <is>
-          <t>업체와 차량, 배터리 제원을 입력하는 진단 준비 화면</t>
+          <t>건물 앞 충전소에 나란히 선 에이프로 전기자동차 급속 충전기 세 대</t>
         </is>
       </c>
       <c r="G27" s="7" t="n"/>
@@ -13843,7 +13865,7 @@
       <c r="I27" s="5" t="n"/>
       <c r="J27" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[4]/div[2]/div/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[5]/img|alt</t>
         </is>
       </c>
     </row>
@@ -13869,7 +13891,7 @@
       <c r="E28" s="5" t="inlineStr"/>
       <c r="F28" s="6" t="inlineStr">
         <is>
-          <t>건물 앞 충전소에 나란히 선 에이프로 전기자동차 급속 충전기 세 대</t>
+          <t>제어기를 얹은 전기자동차 구동 플랫폼</t>
         </is>
       </c>
       <c r="G28" s="7" t="n"/>
@@ -13877,7 +13899,7 @@
       <c r="I28" s="5" t="n"/>
       <c r="J28" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[5]/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[6]/img|alt</t>
         </is>
       </c>
     </row>
@@ -13887,31 +13909,35 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>좌측 인덱스</t>
+          <t>01-1 산업 안전 진단 솔루션</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>그림 대체글</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>대체글</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr"/>
       <c r="F29" s="6" t="inlineStr">
         <is>
-          <t>제어기를 얹은 전기자동차 구동 플랫폼</t>
+          <t>에이프로의 산업 안전 진단 로봇 솔루션은 이동형 로봇, AI, 원격 관제 기술을 결합하여 위험 산업 현장의 안전 점검을 자율화·지능화합니다.</t>
         </is>
       </c>
       <c r="G29" s="7" t="n"/>
-      <c r="H29" s="8" t="n"/>
+      <c r="H29" s="8" t="inlineStr">
+        <is>
+          <t>APRO’s Industrial Safety Diagnostic Robot Solution combines mobile robots, AI, and remote monitoring technologies to automate and enhance safety inspections in hazardous industrial environments.</t>
+        </is>
+      </c>
       <c r="I29" s="5" t="n"/>
       <c r="J29" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[6]/img|alt</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -13937,19 +13963,19 @@
       <c r="E30" s="5" t="inlineStr"/>
       <c r="F30" s="6" t="inlineStr">
         <is>
-          <t>에이프로의 산업 안전 진단 로봇 솔루션은 이동형 로봇과 AI, 원격 관제를 결합해 위험 구역의 안전 점검을 무인·지능화합니다.</t>
+          <t>안전장비 착용 여부, 설비 이상 및 누출, 열화상, 음향 등 6대 핵심 점검 항목을 로봇이 자율적으로 수행하며, 수집된 데이터를 통합 관제 시스템에서 실시간으로 모니터링하고 분석합니다.</t>
         </is>
       </c>
       <c r="G30" s="7" t="n"/>
       <c r="H30" s="8" t="inlineStr">
         <is>
-          <t>APRO's industrial safety diagnostic robot solution combines mobile robots, AI, and remote control to make safety inspections in hazardous areas unmanned and intelligent.</t>
+          <t>The system autonomously performs six key inspection functions, including safety equipment compliance, equipment anomaly and leak detection, thermal imaging, and acoustic analysis, while monitoring and analyzing collected data in real time through an integrated control system.</t>
         </is>
       </c>
       <c r="I30" s="5" t="n"/>
       <c r="J30" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -13975,19 +14001,19 @@
       <c r="E31" s="5" t="inlineStr"/>
       <c r="F31" s="6" t="inlineStr">
         <is>
-          <t>안전장비 착용 진단, 설비 이상·누출 점검, 열화상·음향 분석 등 6대 핵심 점검을 자율적으로 수행하고 통합 관제로 실시간 모니터링합니다.</t>
+          <t>이를 통해 작업자의 위험 구역 노출을 최소화하고 점검의 일관성과 신뢰성을 높여, 선제적이고 스마트한 산업 안전 운영을 지원합니다.</t>
         </is>
       </c>
       <c r="G31" s="7" t="n"/>
       <c r="H31" s="8" t="inlineStr">
         <is>
-          <t>It autonomously performs six key inspections, including safety equipment compliance checks, equipment anomaly and leak detection, and thermal imaging and acoustic analysis, while providing real-time monitoring through integrated control.</t>
+          <t>By reducing worker exposure to hazardous areas and improving the consistency and reliability of inspections, the solution supports proactive and intelligent industrial safety operations.</t>
         </is>
       </c>
       <c r="I31" s="5" t="n"/>
       <c r="J31" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -13997,7 +14023,7 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>01-1 산업 안전 진단 솔루션</t>
+          <t>01-2 로봇 통합 운영 플랫폼</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
@@ -14013,19 +14039,19 @@
       <c r="E32" s="5" t="inlineStr"/>
       <c r="F32" s="6" t="inlineStr">
         <is>
-          <t>작업자의 위험 노출을 줄이고 점검의 일관성을 높여 선제적이고 스마트한 산업 운영을 지원합니다.</t>
+          <t>APRISM은 제조사와 기종이 서로 다른 로봇을 하나의 플랫폼에서 통합 관제하는 이기종 로봇 통합 관제 플랫폼입니다.</t>
         </is>
       </c>
       <c r="G32" s="7" t="n"/>
       <c r="H32" s="8" t="inlineStr">
         <is>
-          <t>It supports proactive and smart industrial operations by reducing worker risk exposure and enhancing inspection consistency.</t>
+          <t>APRISM is a heterogeneous robot management platform that enables unified monitoring and control of robots from different manufacturers and platforms through a single integrated system.</t>
         </is>
       </c>
       <c r="I32" s="5" t="n"/>
       <c r="J32" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[1]/div/div[2]/div/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -14051,19 +14077,21 @@
       <c r="E33" s="5" t="inlineStr"/>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>별도의 조작 없이 자유로운 이동과, 좁은 공간이나 사람이 닿기 위험한 공간에도 접근해 정밀 점검을 수행할 수 있습니다.</t>
+          <t>객체 검출, VLM, 시계열 데이터 분석 등 다양한 AI 기술을 기반으로 현장에서 수집되는 영상·센서·설비 데이터를 분석하고, 에이프로의 LLM 기반 지능형 통신 모델 DELTA가 이를 해석·요약하여 로봇, 현장 설비, 관제실을 하나의 정보 체계로 연결합니다.
+APRISM은 지하 발전소, 변전소, 산업 플랜트, 데이터센터 등 사람이 상시 접근하기 어렵거나 위험한 산업 현장에서 무인 순찰, 이상 감지, 상태 진단 및 예지보전을 지원합니다.</t>
         </is>
       </c>
       <c r="G33" s="7" t="n"/>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>It allows for free movement without separate operation and enables precise inspections by accessing narrow spaces or areas dangerous for humans to reach.</t>
+          <t>Using AI technologies such as object detection, Vision-Language Models (VLM), and time-series data analysis, APRISM processes video, sensor, and equipment data collected from the field. APRO’s LLM-based intelligence engine, DELTA, interprets and summarizes this information, connecting robots, industrial sites, and control rooms through a unified information framework.
+APRISM supports unmanned patrol, anomaly detection, condition monitoring, and predictive maintenance in hazardous or hard-to-access industrial environments such as underground power plants, substations, industrial plants, and data centers.</t>
         </is>
       </c>
       <c r="I33" s="5" t="n"/>
       <c r="J33" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -14073,7 +14101,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>01-2 로봇 통합 운영 플랫폼</t>
+          <t>02-1 EV 배터리 안전 진단</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -14089,19 +14117,19 @@
       <c r="E34" s="5" t="inlineStr"/>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>에이프로 산업안전 AI 플랫폼은 딥러닝 기반 이미지 분석 기술을 통해 이상 징후나 결함을 감지하고 데이터를 실시간으로 관리 시스템에 전송해 즉각적 대응이 가능합니다.</t>
+          <t>전기자동차 충전 중 배터리 데이터를 실시간으로 수집하고, 개별 셀 전압과 모듈 온도 정보를 AI 기반으로 분석하여 배터리의 이상 징후와 안전 상태를 진단하는 솔루션입니다.</t>
         </is>
       </c>
       <c r="G34" s="7" t="n"/>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>The A-PRO Industrial Safety AI Platform detects abnormal signs or defects through deep learning-based image analysis technology and transmits data to the management system in real time, enabling immediate response.</t>
+          <t>This solution collects battery data in real time during EV charging and uses AI to analyze individual cell voltages and module temperatures, enabling early detection of battery abnormalities and assessment of battery safety.</t>
         </is>
       </c>
       <c r="I34" s="5" t="n"/>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[1]/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -14127,19 +14155,19 @@
       <c r="E35" s="5" t="inlineStr"/>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>전기자동차 충전 중 배터리 데이터를 실시간으로 수집하고, 개별 셀 전압과 모듈 온도 정보를 AI 기반으로 분석하여 배터리의 이상 징후와 안전 상태를 진단하는 솔루션입니다.</t>
+          <t>배터리 이상을 조기에 감지하여 사고 위험을 예방하고, 보다 안전한 충전 환경 구축과 효율적인 배터리 유지관리를 지원합니다.</t>
         </is>
       </c>
       <c r="G35" s="7" t="n"/>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>This is a solution that collects battery data in real time during electric vehicle charging and diagnoses signs of battery abnormalities and safety status by analyzing individual cell voltage and module temperature information using AI.</t>
+          <t>By identifying potential risks at an early stage, it helps prevent battery-related incidents, enhance charging safety, and improve battery maintenance efficiency.</t>
         </is>
       </c>
       <c r="I35" s="5" t="n"/>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[1]/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[1]/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -14154,7 +14182,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>제품 단추 이름</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -14165,19 +14193,15 @@
       <c r="E36" s="5" t="inlineStr"/>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>이를 통해 배터리 사고 위험을 사전에 감지하고, 안전한 충전 환경 조성과 배터리 유지관리 효율 향상을 지원합니다.</t>
+          <t>대시보드</t>
         </is>
       </c>
       <c r="G36" s="7" t="n"/>
-      <c r="H36" s="8" t="inlineStr">
-        <is>
-          <t>Through this, it detects the risk of battery accidents in advance and supports the creation of a safe charging environment and the improvement of battery maintenance efficiency.</t>
-        </is>
-      </c>
+      <c r="H36" s="8" t="n"/>
       <c r="I36" s="5" t="n"/>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[1]/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[2]/button[1]/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14227,7 @@
       <c r="E37" s="5" t="inlineStr"/>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>대시보드</t>
+          <t>모바일</t>
         </is>
       </c>
       <c r="G37" s="7" t="n"/>
@@ -14211,7 +14235,7 @@
       <c r="I37" s="5" t="n"/>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[2]/button[1]/span[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[2]/button[2]/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -14221,12 +14245,12 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>02-1 EV 배터리 안전 진단</t>
+          <t>02-2 EV 배터리 성능 진단</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>제품 단추 이름</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -14237,15 +14261,21 @@
       <c r="E38" s="5" t="inlineStr"/>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>모바일</t>
+          <t>전기자동차 사용후 배터리의 성능과 잔존가치를 신속하게 평가하는 AI 기반 진단 솔루션입니다.
+배터리의 부분 방전 데이터를 기존 학습 데이터와 비교·분석하여, 10분 이내에 배터리 셀의 가용 최대 용량과 건강 상태(SOH)를 예측합니다.</t>
         </is>
       </c>
       <c r="G38" s="7" t="n"/>
-      <c r="H38" s="8" t="n"/>
+      <c r="H38" s="8" t="inlineStr">
+        <is>
+          <t>This AI-based diagnostic solution rapidly evaluates the performance and residual value of used EV batteries.
+By comparing and analyzing partial discharge data with previously trained battery datasets, the solution predicts the maximum available capacity and State of Health (SOH) of battery cells within 10 minutes.</t>
+        </is>
+      </c>
       <c r="I38" s="5" t="n"/>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[2]/button[2]/span[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -14271,19 +14301,19 @@
       <c r="E39" s="5" t="inlineStr"/>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>전기자동차 사용후 배터리의 성능과 잔존가치를 신속하게 평가하는 AI 기반 진단 솔루션입니다.</t>
+          <t>이를 통해 중고 전기차 및 사용후 배터리의 상태를 빠르고 정량적으로 평가하고, 재사용·재제조·재활용 등 배터리 활용 의사결정을 지원합니다.</t>
         </is>
       </c>
       <c r="G39" s="7" t="n"/>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>This is an AI-based diagnostic solution that rapidly evaluates the performance and residual value of used electric vehicle batteries.</t>
+          <t>It enables fast and quantitative battery condition assessment, supporting informed decisions for battery reuse, remanufacturing, and recycling.</t>
         </is>
       </c>
       <c r="I39" s="5" t="n"/>
       <c r="J39" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -14293,7 +14323,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>02-2 EV 배터리 성능 진단</t>
+          <t>03-1 PICKLE Station</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -14309,19 +14339,19 @@
       <c r="E40" s="5" t="inlineStr"/>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>배터리의 부분 방전 데이터를 기존 배터리 학습 데이터와 비교·분석하여, 10분 이내에 배터리 셀의 가용 최대 용량과 건강 상태(SOH)를 예측합니다.</t>
+          <t>에이프로의 전기자동차 충전 솔루션 PICKLE Station은 주거용 충전부터 공공 충전소, 상용 플릿까지 다양한 운영 환경에 대응하는 통합 충전 인프라 솔루션입니다.</t>
         </is>
       </c>
       <c r="G40" s="7" t="n"/>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>Battery partial discharge data is compared and analyzed with existing battery training data to predict the maximum available capacity and state of health (SOH) of battery cells within 10 minutes.</t>
+          <t>APRO’s electric vehicle charging solution, PICKLE Station, is an integrated charging infrastructure solution designed for a wide range of applications, from residential charging to public charging stations and commercial fleets.</t>
         </is>
       </c>
       <c r="I40" s="5" t="n"/>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -14331,12 +14361,12 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>03-1 급속 충전기</t>
+          <t>03-1 PICKLE Station</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
         <is>
-          <t>작은 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D41" s="5" t="inlineStr">
@@ -14347,19 +14377,19 @@
       <c r="E41" s="5" t="inlineStr"/>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>PICKLE Station</t>
+          <t>원격 모니터링과 충전기 운영·유지관리 기능을 지원하며, 충전 운영 플랫폼 및 에너지관리시스템(EMS)과 연계하여 충전 인프라를 효율적으로 관리하고 유연하게 확장할 수 있습니다.</t>
         </is>
       </c>
       <c r="G41" s="7" t="n"/>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>PICKLE Station</t>
+          <t>It supports remote monitoring, charger operation, and maintenance, while integrating with charging management platforms and Energy Management Systems (EMS) for efficient operation and scalable infrastructure expansion.</t>
         </is>
       </c>
       <c r="I41" s="5" t="n"/>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -14369,7 +14399,7 @@
       </c>
       <c r="B42" s="5" t="inlineStr">
         <is>
-          <t>03-1 급속 충전기</t>
+          <t>03-1 PICKLE Station</t>
         </is>
       </c>
       <c r="C42" s="5" t="inlineStr">
@@ -14385,19 +14415,19 @@
       <c r="E42" s="5" t="inlineStr"/>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>에이프로의 전기자동차 충전 솔루션 PICKLE Station은 주거용 충전부터 공공 충전소와 상용 플릿까지 다양한 운영 환경에 대응하는 안정적인 충전 인프라입니다.</t>
+          <t>에이프로가 축적해 온 전력전자 및 배터리 시스템 기술을 기반으로, 안전하고 안정적인 충전 환경과 지속 가능한 전기 모빌리티 생태계를 제공합니다.</t>
         </is>
       </c>
       <c r="G42" s="7" t="n"/>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>APRO’s electric vehicle charging solution, PICKLE Station, is a stable charging infrastructure designed to support diverse operating environments, ranging from residential charging to public charging stations and commercial fleets.</t>
+          <t>Built on APRO’s expertise in power electronics and battery systems, PICKLE Station delivers safe and reliable charging infrastructure for a sustainable electric mobility ecosystem.</t>
         </is>
       </c>
       <c r="I42" s="5" t="n"/>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/p[4]|text</t>
         </is>
       </c>
     </row>
@@ -14407,7 +14437,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>03-1 급속 충전기</t>
+          <t>04-1 전기자동차 제어 플랫폼</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -14423,19 +14453,19 @@
       <c r="E43" s="5" t="inlineStr"/>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>원격 모니터링과 충전기 운영·유지관리 기능을 지원하며, 충전 운영 플랫폼 및 에너지관리시스템과 연계하여 충전 인프라를 효율적으로 관리하고 유연하게 확장할 수 있습니다.</t>
+          <t>에이프로는 ECOTRON 차량 및 자율주행 제어기의 국내 총판으로서 VCU, ZCU, EVCC, 자율주행 제어기 등 검증된 차량 제어 솔루션을 공급합니다.</t>
         </is>
       </c>
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>It supports remote monitoring and charger operation and maintenance functions, and integrates with charging operation platforms and energy management systems to enable efficient management and flexible expansion of charging infrastructure.</t>
+          <t>As the exclusive distributor of ECOTRON vehicle and autonomous driving controllers in Korea, APRO provides proven control solutions, including VCUs, ZCUs, EVCCs, and autonomous driving controllers.</t>
         </is>
       </c>
       <c r="I43" s="5" t="n"/>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -14445,7 +14475,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>03-1 급속 충전기</t>
+          <t>04-1 전기자동차 제어 플랫폼</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -14461,19 +14491,19 @@
       <c r="E44" s="5" t="inlineStr"/>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>에이프로가 축적해 온 전력전자와 배터리 시스템 기술을 기반으로 안전하고 지속 가능한 전기 모빌리티 충전 생태계를 구축합니다.</t>
+          <t>ECOTRON 제어기는 ISO 26262 기능안전과 MATLAB/Simulink 기반의 모델 기반 개발(MBD)을 지원하며, 차량 제어 시스템 개발에 요구되는 높은 안전성과 개발 효율성을 제공합니다.</t>
         </is>
       </c>
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>Based on the power electronics and battery system technologies accumulated by APRO, it builds a safe and sustainable electric mobility charging ecosystem.</t>
+          <t>ECOTRON controllers support ISO 26262 functional safety and MATLAB/Simulink-based Model-Based Development (MBD), helping customers achieve high levels of safety and development efficiency in vehicle control system development.</t>
         </is>
       </c>
       <c r="I44" s="5" t="n"/>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/p[4]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -14483,7 +14513,7 @@
       </c>
       <c r="B45" s="5" t="inlineStr">
         <is>
-          <t>04-1 EV 제어기</t>
+          <t>04-1 전기자동차 제어 플랫폼</t>
         </is>
       </c>
       <c r="C45" s="5" t="inlineStr">
@@ -14499,100 +14529,24 @@
       <c r="E45" s="5" t="inlineStr"/>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>에이프로는 ECOTRON 차량·자율주행 제어기의 국내 총판으로서 VCU, ZCU, EVCC, 자율주행 제어기 등 검증된 제어 솔루션을 공급합니다.</t>
+          <t>에이프로는 국내 공급과 기술 지원을 통해 전기자동차, 자율주행차, 무인 이동체 및 로봇 분야 고객의 제어기 도입부터 시스템 적용까지 지원합니다.</t>
         </is>
       </c>
       <c r="G45" s="7" t="n"/>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>As the exclusive domestic distributor for ECOTRON vehicle and autonomous driving controllers, APRO supplies proven control solutions, including VCUs, ZCUs, EVCCs, and autonomous driving controllers.</t>
+          <t>Through local supply and technical support, APRO supports customers in electric vehicles, autonomous driving, unmanned mobility, and robotics, from controller adoption to system integration.</t>
         </is>
       </c>
       <c r="I45" s="5" t="n"/>
       <c r="J45" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[1]|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="n">
-        <v>45</v>
-      </c>
-      <c r="B46" s="5" t="inlineStr">
-        <is>
-          <t>04-1 EV 제어기</t>
-        </is>
-      </c>
-      <c r="C46" s="5" t="inlineStr">
-        <is>
-          <t>본문</t>
-        </is>
-      </c>
-      <c r="D46" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E46" s="5" t="inlineStr"/>
-      <c r="F46" s="6" t="inlineStr">
-        <is>
-          <t>모든 제품은 ASIL-D 등급 반도체와 ISO 26262 기능안전, MATLAB/Simulink 모델 기반 개발을 지원해 높은 안전성과 개발 효율성을 제공합니다.</t>
-        </is>
-      </c>
-      <c r="G46" s="7" t="n"/>
-      <c r="H46" s="8" t="inlineStr">
-        <is>
-          <t>All products utilize ASIL-D grade semiconductors and support ISO 26262 functional safety and MATLAB/Simulink model-based development, providing high safety and development efficiency.</t>
-        </is>
-      </c>
-      <c r="I46" s="5" t="n"/>
-      <c r="J46" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[2]|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="n">
-        <v>46</v>
-      </c>
-      <c r="B47" s="5" t="inlineStr">
-        <is>
-          <t>04-1 EV 제어기</t>
-        </is>
-      </c>
-      <c r="C47" s="5" t="inlineStr">
-        <is>
-          <t>본문</t>
-        </is>
-      </c>
-      <c r="D47" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="inlineStr"/>
-      <c r="F47" s="6" t="inlineStr">
-        <is>
-          <t>에이프로는 국내 공급과 기술 지원을 통해 전기차·자율주행·무인 이동체·로봇 분야 고객의 제어기 도입을 지원합니다.</t>
-        </is>
-      </c>
-      <c r="G47" s="7" t="n"/>
-      <c r="H47" s="8" t="inlineStr">
-        <is>
-          <t>Through domestic supply and technical support, APRO facilitates the adoption of controllers by customers in the fields of electric vehicles, autonomous driving, unmanned vehicles, and robotics.</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="n"/>
-      <c r="J47" s="9" t="inlineStr">
-        <is>
           <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J47"/>
+  <autoFilter ref="A1:J45"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/content-export/04_사업영역_문구.xlsx
+++ b/content-export/04_사업영역_문구.xlsx
@@ -16,7 +16,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$J$144</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'에너지 인프라'!$A$1:$J$189</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'인공지능 플랫폼'!$A$1:$J$45</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'인공지능 플랫폼'!$A$1:$J$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'화합물 전력 반도체'!$A$1:$J$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -527,7 +527,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 399 줄입니다.</t>
+          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 401 줄입니다.</t>
         </is>
       </c>
     </row>
@@ -12830,7 +12830,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J45"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -13530,7 +13530,7 @@
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>인덱스 항목 · 장 제목 · 작은 제목</t>
+          <t>인덱스 항목 · 장 제목</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
@@ -13552,14 +13552,13 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>같은 문구 3 곳 — 한 줄로 합침</t>
+          <t>같은 문구 2 곳 — 한 줄로 합침</t>
         </is>
       </c>
       <c r="J18" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[1]/nav/div[3]/a|text
-/html/body/div[8]/div[3]/section[5]/div/div[2]/div/h2|text
-/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/p[1]|text</t>
+/html/body/div[8]/div[3]/section[5]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -14077,15 +14076,13 @@
       <c r="E33" s="5" t="inlineStr"/>
       <c r="F33" s="6" t="inlineStr">
         <is>
-          <t>객체 검출, VLM, 시계열 데이터 분석 등 다양한 AI 기술을 기반으로 현장에서 수집되는 영상·센서·설비 데이터를 분석하고, 에이프로의 LLM 기반 지능형 통신 모델 DELTA가 이를 해석·요약하여 로봇, 현장 설비, 관제실을 하나의 정보 체계로 연결합니다.
-APRISM은 지하 발전소, 변전소, 산업 플랜트, 데이터센터 등 사람이 상시 접근하기 어렵거나 위험한 산업 현장에서 무인 순찰, 이상 감지, 상태 진단 및 예지보전을 지원합니다.</t>
+          <t>객체 검출, VLM, 시계열 데이터 분석 등 다양한 AI 기술을 기반으로 현장에서 수집되는 영상·센서·설비 데이터를 분석하고, 에이프로의 LLM 기반 지능형 통신 모델 DELTA가 이를 해석·요약하여 로봇, 현장 설비, 관제실을 하나의 정보 체계로 연결합니다.</t>
         </is>
       </c>
       <c r="G33" s="7" t="n"/>
       <c r="H33" s="8" t="inlineStr">
         <is>
-          <t>Using AI technologies such as object detection, Vision-Language Models (VLM), and time-series data analysis, APRISM processes video, sensor, and equipment data collected from the field. APRO’s LLM-based intelligence engine, DELTA, interprets and summarizes this information, connecting robots, industrial sites, and control rooms through a unified information framework.
-APRISM supports unmanned patrol, anomaly detection, condition monitoring, and predictive maintenance in hazardous or hard-to-access industrial environments such as underground power plants, substations, industrial plants, and data centers.</t>
+          <t>Using AI technologies such as object detection, Vision-Language Models (VLM), and time-series data analysis, APRISM processes video, sensor, and equipment data collected from the field. APRO’s LLM-based intelligence engine, DELTA, interprets and summarizes this information, connecting robots, industrial sites, and control rooms through a unified information framework.</t>
         </is>
       </c>
       <c r="I33" s="5" t="n"/>
@@ -14101,7 +14098,7 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>02-1 EV 배터리 안전 진단</t>
+          <t>01-2 로봇 통합 운영 플랫폼</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
@@ -14117,19 +14114,19 @@
       <c r="E34" s="5" t="inlineStr"/>
       <c r="F34" s="6" t="inlineStr">
         <is>
-          <t>전기자동차 충전 중 배터리 데이터를 실시간으로 수집하고, 개별 셀 전압과 모듈 온도 정보를 AI 기반으로 분석하여 배터리의 이상 징후와 안전 상태를 진단하는 솔루션입니다.</t>
+          <t>APRISM은 지하 발전소, 변전소, 산업 플랜트, 데이터센터 등 사람이 상시 접근하기 어렵거나 위험한 산업 현장에서 무인 순찰, 이상 감지, 상태 진단 및 예지보전을 지원합니다.</t>
         </is>
       </c>
       <c r="G34" s="7" t="n"/>
       <c r="H34" s="8" t="inlineStr">
         <is>
-          <t>This solution collects battery data in real time during EV charging and uses AI to analyze individual cell voltages and module temperatures, enabling early detection of battery abnormalities and assessment of battery safety.</t>
+          <t>APRISM supports unmanned patrol, anomaly detection, condition monitoring, and predictive maintenance in hazardous or hard-to-access industrial environments such as underground power plants, substations, industrial plants, and data centers.</t>
         </is>
       </c>
       <c r="I34" s="5" t="n"/>
       <c r="J34" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[1]/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[2]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -14155,19 +14152,19 @@
       <c r="E35" s="5" t="inlineStr"/>
       <c r="F35" s="6" t="inlineStr">
         <is>
-          <t>배터리 이상을 조기에 감지하여 사고 위험을 예방하고, 보다 안전한 충전 환경 구축과 효율적인 배터리 유지관리를 지원합니다.</t>
+          <t>전기자동차 충전 중 배터리 데이터를 실시간으로 수집하고, 개별 셀 전압과 모듈 온도 정보를 AI 기반으로 분석하여 배터리의 이상 징후와 안전 상태를 진단하는 솔루션입니다.</t>
         </is>
       </c>
       <c r="G35" s="7" t="n"/>
       <c r="H35" s="8" t="inlineStr">
         <is>
-          <t>By identifying potential risks at an early stage, it helps prevent battery-related incidents, enhance charging safety, and improve battery maintenance efficiency.</t>
+          <t>This solution collects battery data in real time during EV charging and uses AI to analyze individual cell voltages and module temperatures, enabling early detection of battery abnormalities and assessment of battery safety.</t>
         </is>
       </c>
       <c r="I35" s="5" t="n"/>
       <c r="J35" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[1]/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[1]/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -14182,7 +14179,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>제품 단추 이름</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -14193,15 +14190,19 @@
       <c r="E36" s="5" t="inlineStr"/>
       <c r="F36" s="6" t="inlineStr">
         <is>
-          <t>대시보드</t>
+          <t>배터리 이상을 조기에 감지하여 사고 위험을 예방하고, 보다 안전한 충전 환경 구축과 효율적인 배터리 유지관리를 지원합니다.</t>
         </is>
       </c>
       <c r="G36" s="7" t="n"/>
-      <c r="H36" s="8" t="n"/>
+      <c r="H36" s="8" t="inlineStr">
+        <is>
+          <t>By identifying potential risks at an early stage, it helps prevent battery-related incidents, enhance charging safety, and improve battery maintenance efficiency.</t>
+        </is>
+      </c>
       <c r="I36" s="5" t="n"/>
       <c r="J36" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[2]/button[1]/span[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[1]/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -14227,7 +14228,7 @@
       <c r="E37" s="5" t="inlineStr"/>
       <c r="F37" s="6" t="inlineStr">
         <is>
-          <t>모바일</t>
+          <t>대시보드</t>
         </is>
       </c>
       <c r="G37" s="7" t="n"/>
@@ -14235,7 +14236,7 @@
       <c r="I37" s="5" t="n"/>
       <c r="J37" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[2]/button[2]/span[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[2]/button[1]/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -14245,12 +14246,12 @@
       </c>
       <c r="B38" s="5" t="inlineStr">
         <is>
-          <t>02-2 EV 배터리 성능 진단</t>
+          <t>02-1 EV 배터리 안전 진단</t>
         </is>
       </c>
       <c r="C38" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>제품 단추 이름</t>
         </is>
       </c>
       <c r="D38" s="5" t="inlineStr">
@@ -14261,21 +14262,15 @@
       <c r="E38" s="5" t="inlineStr"/>
       <c r="F38" s="6" t="inlineStr">
         <is>
-          <t>전기자동차 사용후 배터리의 성능과 잔존가치를 신속하게 평가하는 AI 기반 진단 솔루션입니다.
-배터리의 부분 방전 데이터를 기존 학습 데이터와 비교·분석하여, 10분 이내에 배터리 셀의 가용 최대 용량과 건강 상태(SOH)를 예측합니다.</t>
+          <t>모바일</t>
         </is>
       </c>
       <c r="G38" s="7" t="n"/>
-      <c r="H38" s="8" t="inlineStr">
-        <is>
-          <t>This AI-based diagnostic solution rapidly evaluates the performance and residual value of used EV batteries.
-By comparing and analyzing partial discharge data with previously trained battery datasets, the solution predicts the maximum available capacity and State of Health (SOH) of battery cells within 10 minutes.</t>
-        </is>
-      </c>
+      <c r="H38" s="8" t="n"/>
       <c r="I38" s="5" t="n"/>
       <c r="J38" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div[2]/button[2]/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -14301,19 +14296,19 @@
       <c r="E39" s="5" t="inlineStr"/>
       <c r="F39" s="6" t="inlineStr">
         <is>
-          <t>이를 통해 중고 전기차 및 사용후 배터리의 상태를 빠르고 정량적으로 평가하고, 재사용·재제조·재활용 등 배터리 활용 의사결정을 지원합니다.</t>
+          <t>전기자동차 사용후 배터리의 성능과 잔존가치를 신속하게 평가하는 AI 기반 진단 솔루션입니다.</t>
         </is>
       </c>
       <c r="G39" s="7" t="n"/>
       <c r="H39" s="8" t="inlineStr">
         <is>
-          <t>It enables fast and quantitative battery condition assessment, supporting informed decisions for battery reuse, remanufacturing, and recycling.</t>
+          <t>This AI-based diagnostic solution rapidly evaluates the performance and residual value of used EV batteries.</t>
         </is>
       </c>
       <c r="I39" s="5" t="n"/>
       <c r="J39" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -14323,7 +14318,7 @@
       </c>
       <c r="B40" s="5" t="inlineStr">
         <is>
-          <t>03-1 PICKLE Station</t>
+          <t>02-2 EV 배터리 성능 진단</t>
         </is>
       </c>
       <c r="C40" s="5" t="inlineStr">
@@ -14339,19 +14334,19 @@
       <c r="E40" s="5" t="inlineStr"/>
       <c r="F40" s="6" t="inlineStr">
         <is>
-          <t>에이프로의 전기자동차 충전 솔루션 PICKLE Station은 주거용 충전부터 공공 충전소, 상용 플릿까지 다양한 운영 환경에 대응하는 통합 충전 인프라 솔루션입니다.</t>
+          <t>배터리의 부분 방전 데이터를 기존 학습 데이터와 비교·분석하여, 10분 이내에 배터리 셀의 가용 최대 용량과 건강 상태(SOH)를 예측합니다.</t>
         </is>
       </c>
       <c r="G40" s="7" t="n"/>
       <c r="H40" s="8" t="inlineStr">
         <is>
-          <t>APRO’s electric vehicle charging solution, PICKLE Station, is an integrated charging infrastructure solution designed for a wide range of applications, from residential charging to public charging stations and commercial fleets.</t>
+          <t>By comparing and analyzing partial discharge data with previously trained battery datasets, the solution predicts the maximum available capacity and State of Health (SOH) of battery cells within 10 minutes.</t>
         </is>
       </c>
       <c r="I40" s="5" t="n"/>
       <c r="J40" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -14361,7 +14356,7 @@
       </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>03-1 PICKLE Station</t>
+          <t>02-2 EV 배터리 성능 진단</t>
         </is>
       </c>
       <c r="C41" s="5" t="inlineStr">
@@ -14377,19 +14372,19 @@
       <c r="E41" s="5" t="inlineStr"/>
       <c r="F41" s="6" t="inlineStr">
         <is>
-          <t>원격 모니터링과 충전기 운영·유지관리 기능을 지원하며, 충전 운영 플랫폼 및 에너지관리시스템(EMS)과 연계하여 충전 인프라를 효율적으로 관리하고 유연하게 확장할 수 있습니다.</t>
+          <t>이를 통해 중고 전기차 및 사용후 배터리의 상태를 빠르고 정량적으로 평가하고, 재사용·재제조·재활용 등 배터리 활용 의사결정을 지원합니다.</t>
         </is>
       </c>
       <c r="G41" s="7" t="n"/>
       <c r="H41" s="8" t="inlineStr">
         <is>
-          <t>It supports remote monitoring, charger operation, and maintenance, while integrating with charging management platforms and Energy Management Systems (EMS) for efficient operation and scalable infrastructure expansion.</t>
+          <t>It enables fast and quantitative battery condition assessment, supporting informed decisions for battery reuse, remanufacturing, and recycling.</t>
         </is>
       </c>
       <c r="I41" s="5" t="n"/>
       <c r="J41" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -14415,19 +14410,19 @@
       <c r="E42" s="5" t="inlineStr"/>
       <c r="F42" s="6" t="inlineStr">
         <is>
-          <t>에이프로가 축적해 온 전력전자 및 배터리 시스템 기술을 기반으로, 안전하고 안정적인 충전 환경과 지속 가능한 전기 모빌리티 생태계를 제공합니다.</t>
+          <t>에이프로의 전기자동차 충전 솔루션 PICKLE Station은 주거용 충전부터 공공 충전소, 상용 플릿까지 다양한 운영 환경에 대응하는 통합 충전 인프라 솔루션입니다.</t>
         </is>
       </c>
       <c r="G42" s="7" t="n"/>
       <c r="H42" s="8" t="inlineStr">
         <is>
-          <t>Built on APRO’s expertise in power electronics and battery systems, PICKLE Station delivers safe and reliable charging infrastructure for a sustainable electric mobility ecosystem.</t>
+          <t>APRO’s electric vehicle charging solution, PICKLE Station, is an integrated charging infrastructure solution designed for a wide range of applications, from residential charging to public charging stations and commercial fleets.</t>
         </is>
       </c>
       <c r="I42" s="5" t="n"/>
       <c r="J42" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/p[4]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -14437,7 +14432,7 @@
       </c>
       <c r="B43" s="5" t="inlineStr">
         <is>
-          <t>04-1 전기자동차 제어 플랫폼</t>
+          <t>03-1 PICKLE Station</t>
         </is>
       </c>
       <c r="C43" s="5" t="inlineStr">
@@ -14453,19 +14448,19 @@
       <c r="E43" s="5" t="inlineStr"/>
       <c r="F43" s="6" t="inlineStr">
         <is>
-          <t>에이프로는 ECOTRON 차량 및 자율주행 제어기의 국내 총판으로서 VCU, ZCU, EVCC, 자율주행 제어기 등 검증된 차량 제어 솔루션을 공급합니다.</t>
+          <t>원격 모니터링과 충전기 운영·유지관리 기능을 지원하며, 충전 운영 플랫폼 및 에너지관리시스템(EMS)과 연계하여 충전 인프라를 효율적으로 관리하고 유연하게 확장할 수 있습니다.</t>
         </is>
       </c>
       <c r="G43" s="7" t="n"/>
       <c r="H43" s="8" t="inlineStr">
         <is>
-          <t>As the exclusive distributor of ECOTRON vehicle and autonomous driving controllers in Korea, APRO provides proven control solutions, including VCUs, ZCUs, EVCCs, and autonomous driving controllers.</t>
+          <t>It supports remote monitoring, charger operation, and maintenance, while integrating with charging management platforms and Energy Management Systems (EMS) for efficient operation and scalable infrastructure expansion.</t>
         </is>
       </c>
       <c r="I43" s="5" t="n"/>
       <c r="J43" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -14475,7 +14470,7 @@
       </c>
       <c r="B44" s="5" t="inlineStr">
         <is>
-          <t>04-1 전기자동차 제어 플랫폼</t>
+          <t>03-1 PICKLE Station</t>
         </is>
       </c>
       <c r="C44" s="5" t="inlineStr">
@@ -14491,19 +14486,19 @@
       <c r="E44" s="5" t="inlineStr"/>
       <c r="F44" s="6" t="inlineStr">
         <is>
-          <t>ECOTRON 제어기는 ISO 26262 기능안전과 MATLAB/Simulink 기반의 모델 기반 개발(MBD)을 지원하며, 차량 제어 시스템 개발에 요구되는 높은 안전성과 개발 효율성을 제공합니다.</t>
+          <t>에이프로가 축적해 온 전력전자 및 배터리 시스템 기술을 기반으로, 안전하고 안정적인 충전 환경과 지속 가능한 전기 모빌리티 생태계를 제공합니다.</t>
         </is>
       </c>
       <c r="G44" s="7" t="n"/>
       <c r="H44" s="8" t="inlineStr">
         <is>
-          <t>ECOTRON controllers support ISO 26262 functional safety and MATLAB/Simulink-based Model-Based Development (MBD), helping customers achieve high levels of safety and development efficiency in vehicle control system development.</t>
+          <t>Built on APRO’s expertise in power electronics and battery systems, PICKLE Station delivers safe and reliable charging infrastructure for a sustainable electric mobility ecosystem.</t>
         </is>
       </c>
       <c r="I44" s="5" t="n"/>
       <c r="J44" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -14529,24 +14524,100 @@
       <c r="E45" s="5" t="inlineStr"/>
       <c r="F45" s="6" t="inlineStr">
         <is>
-          <t>에이프로는 국내 공급과 기술 지원을 통해 전기자동차, 자율주행차, 무인 이동체 및 로봇 분야 고객의 제어기 도입부터 시스템 적용까지 지원합니다.</t>
+          <t>에이프로는 ECOTRON 차량 및 자율주행 제어기의 국내 총판으로서 VCU, ZCU, EVCC, 자율주행 제어기 등 검증된 차량 제어 솔루션을 공급합니다.</t>
         </is>
       </c>
       <c r="G45" s="7" t="n"/>
       <c r="H45" s="8" t="inlineStr">
         <is>
-          <t>Through local supply and technical support, APRO supports customers in electric vehicles, autonomous driving, unmanned mobility, and robotics, from controller adoption to system integration.</t>
+          <t>As the exclusive distributor of ECOTRON vehicle and autonomous driving controllers in Korea, APRO provides proven control solutions, including VCUs, ZCUs, EVCCs, and autonomous driving controllers.</t>
         </is>
       </c>
       <c r="I45" s="5" t="n"/>
       <c r="J45" s="9" t="inlineStr">
         <is>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[1]|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>04-1 전기자동차 제어 플랫폼</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="inlineStr"/>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>ECOTRON 제어기는 ISO 26262 기능안전과 MATLAB/Simulink 기반의 모델 기반 개발(MBD)을 지원하며, 차량 제어 시스템 개발에 요구되는 높은 안전성과 개발 효율성을 제공합니다.</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="n"/>
+      <c r="H46" s="8" t="inlineStr">
+        <is>
+          <t>ECOTRON controllers support ISO 26262 functional safety and MATLAB/Simulink-based Model-Based Development (MBD), helping customers achieve high levels of safety and development efficiency in vehicle control system development.</t>
+        </is>
+      </c>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[2]|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>04-1 전기자동차 제어 플랫폼</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="inlineStr"/>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>에이프로는 국내 공급과 기술 지원을 통해 전기자동차, 자율주행차, 무인 이동체 및 로봇 분야 고객의 제어기 도입부터 시스템 적용까지 지원합니다.</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="n"/>
+      <c r="H47" s="8" t="inlineStr">
+        <is>
+          <t>Through local supply and technical support, APRO supports customers in electric vehicles, autonomous driving, unmanned mobility, and robotics, from controller adoption to system integration.</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="n"/>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
           <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J45"/>
+  <autoFilter ref="A1:J47"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/content-export/04_사업영역_문구.xlsx
+++ b/content-export/04_사업영역_문구.xlsx
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B29"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -2562,7 +2562,9 @@
           <t>자리표시</t>
         </is>
       </c>
-      <c r="E50" s="5" t="inlineStr"/>
+      <c r="E50" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="F50" s="6" t="inlineStr">
         <is>
           <t>도표 or 이미지</t>
@@ -2570,7 +2572,11 @@
       </c>
       <c r="G50" s="7" t="n"/>
       <c r="H50" s="8" t="n"/>
-      <c r="I50" s="5" t="n"/>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>묶음 1 — 다른 사업영역 1 장에도 있음</t>
+        </is>
+      </c>
       <c r="J50" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[2]/div/div[2]/figure[9]/span|text</t>
@@ -13675,26 +13681,32 @@
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>그림 대체글</t>
+          <t>그림 자리표시 문구</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>대체글</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="inlineStr"/>
+          <t>자리표시</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>1</v>
+      </c>
       <c r="F22" s="6" t="inlineStr">
         <is>
-          <t>펌프 설비를 점검하는 네 발 보행 로봇</t>
+          <t>도표 or 이미지</t>
         </is>
       </c>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="8" t="n"/>
-      <c r="I22" s="5" t="n"/>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>묶음 1 — 다른 사업영역 1 장에도 있음</t>
+        </is>
+      </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[2]/div/div[2]/figure[2]/img|alt</t>
+          <t>/html/body/div[8]/div[2]/div/div[2]/figure[2]/span|text</t>
         </is>
       </c>
     </row>

--- a/content-export/04_사업영역_문구.xlsx
+++ b/content-export/04_사업영역_문구.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화합물 전력 반도체" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$J$144</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$J$147</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'에너지 인프라'!$A$1:$J$189</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'인공지능 플랫폼'!$A$1:$J$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'화합물 전력 반도체'!$A$1:$J$25</definedName>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="B1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 401 줄입니다.</t>
+          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 404 줄입니다.</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J144"/>
+  <dimension ref="A1:J147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -858,13 +858,13 @@
       <c r="E4" s="5" t="inlineStr"/>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>이차전지 활성화 중요 공정 설비를 자체 기술로 만듭니다.</t>
+          <t>이차전지 활성화 공정의 주요 설비를 자체 기술로 만듭니다.</t>
         </is>
       </c>
       <c r="G4" s="7" t="n"/>
       <c r="H4" s="8" t="inlineStr">
         <is>
-          <t>We manufacture nine pieces of equipment for the secondary battery activation process using our own technology.</t>
+          <t>We develop and manufacture core equipment for the secondary battery activation process using our proprietary technologies.</t>
         </is>
       </c>
       <c r="I4" s="5" t="n"/>
@@ -896,13 +896,13 @@
       <c r="E5" s="5" t="inlineStr"/>
       <c r="F5" s="6" t="inlineStr">
         <is>
-          <t>셀의 성능과 품질을 결정하는 마지막 공정을 책임집니다.</t>
+          <t>셀의 성능과 품질을 결정짓는 마지막 공정까지, A-PRO가 책임집니다.</t>
         </is>
       </c>
       <c r="G5" s="7" t="n"/>
       <c r="H5" s="8" t="inlineStr">
         <is>
-          <t>We are responsible for the final process that determines the performance and quality of the cells.</t>
+          <t>A-PRO takes full ownership of the final process that determines cell performance and quality.</t>
         </is>
       </c>
       <c r="I5" s="5" t="n"/>
@@ -2639,11 +2639,15 @@
       <c r="E52" s="5" t="inlineStr"/>
       <c r="F52" s="6" t="inlineStr">
         <is>
-          <t>에이프로는 이차전지 활성화(Formation) 공정 전체 설비의 자체 제작 기술을 보유한 리딩 기업입니다. 공정에 필요한 모든 설비를 직접 생산하여 국내외 유수의 고객사에 안정적으로 공급하고 있습니다.</t>
+          <t>에이프로는 이차전지 활성화(Formation) 공정의 전 설비를 자체 기술로 완성하는 리딩 기업입니다. 공정 내 모든 설비를 직접 생산하여 국내외 유수의 기업에 안정적인 공급을 제공하고 있습니다.</t>
         </is>
       </c>
       <c r="G52" s="7" t="n"/>
-      <c r="H52" s="8" t="n"/>
+      <c r="H52" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO is a leading company with proprietary manufacturing capabilities for the entire range of equipment used in the secondary battery activation (Formation) process. We manufacture all essential process equipment in-house and reliably supply it to leading customers in Korea and around the world.</t>
+        </is>
+      </c>
       <c r="I52" s="5" t="n"/>
       <c r="J52" s="9" t="inlineStr">
         <is>
@@ -2673,13 +2677,13 @@
       <c r="E53" s="5" t="inlineStr"/>
       <c r="F53" s="6" t="inlineStr">
         <is>
-          <t>당사는 독보적인 정밀 충·방전 기술과 고도화된 자동화 역량을 기반으로, 배터리 셀 활성화 공정 전반을 아우르는 '통합 자동화 솔루션'을 제공합니다. 더불어 각 공정에서 발생하는 전압, 전류, 온도 등의 핵심 데이터를 정밀하게 측정하고 체계적으로 관리함으로써, 배터리 셀의 완성도 높은 품질과 생산 안정성을 극대화합니다.</t>
+          <t>당사는 독보적인 정밀 충방전 기술과 고도화된 자동화 역량을 기반으로, 배터리 셀 활성화 공정 전반을 아우르는 '통합 자동화 솔루션'을 제공합니다. 더불어 각 공정에서 발생하는 전압, 전류, 온도 등의 핵심 데이터를 정밀 측정 및 제어함으로써 배터리 셀의 품질 완성도와 생산 안정성을 극대화합니다.</t>
         </is>
       </c>
       <c r="G53" s="7" t="n"/>
       <c r="H53" s="8" t="inlineStr">
         <is>
-          <t>Based on our unrivaled precision charge-discharge technology and advanced automation capabilities, we deliver comprehensive 'integrated automation solutions' that encompass the entire battery cell formation process. Furthermore, we precisely measure and systematically manage critical data—such as voltage, current, and temperature generated during each stage—to maximize the seamless quality and production stability of battery cells.</t>
+          <t>Built on our unparalleled precision charge/discharge technology and advanced automation capabilities, A-PRO provides a fully integrated automation solution covering the entire battery cell activation process. In addition, we precisely measure and systematically manage critical process data—including voltage, current, and temperature—generated throughout each stage, maximizing cell quality and production stability.</t>
         </is>
       </c>
       <c r="I53" s="5" t="n"/>
@@ -3157,13 +3161,13 @@
       <c r="E67" s="5" t="inlineStr"/>
       <c r="F67" s="6" t="inlineStr">
         <is>
-          <t>글로벌 시장을 선도하는 고객사를 위해 미국 미시간, 폴란드, 중국 남경, 인도네시아에 현지 법인을 구축했습니다.</t>
+          <t>글로벌 시장을 선도하는 고객사의 성공적인 비즈니스를 지원하기 위해 미국 미시간, 폴란드, 중국 남경, 인도네시아에 현지 법인을 구축하고 있습니다.</t>
         </is>
       </c>
       <c r="G67" s="7" t="n"/>
       <c r="H67" s="8" t="inlineStr">
         <is>
-          <t>To support our global market-leading customers, we have established local subsidiaries in Michigan (USA), Poland, Nanjing (China), and Indonesia.</t>
+          <t>To support the business success of our world-leading clients, we are establishing local subsidiaries across key global hubs, including Michigan (USA), Poland, Nanjing (China), and Indonesia.</t>
         </is>
       </c>
       <c r="I67" s="5" t="n"/>
@@ -3195,13 +3199,13 @@
       <c r="E68" s="5" t="inlineStr"/>
       <c r="F68" s="6" t="inlineStr">
         <is>
-          <t>현지에 상주하는 전문 엔지니어들이 셋업부터 유지보수까지 원스톱(One-stop)으로 지원하며, 안정적인 해외 거점을 바탕으로 고객사의 성공을 함께합니다.</t>
+          <t>현지에 상주하는 전문 엔지니어들이 셋업부터 유지보수까지 원스톱(One-stop)으로 지원하며, 안정적인 해외 거점을 바탕으로 고객과의 성장을 함께 이뤄 나갑니다.</t>
         </is>
       </c>
       <c r="G68" s="7" t="n"/>
       <c r="H68" s="8" t="inlineStr">
         <is>
-          <t>Our on-site expert engineers provide one-stop service from setup to maintenance, ensuring customer success through our robust global network.</t>
+          <t>Our on-site professional engineers provide seamless, one-stop support from initial setup to ongoing maintenance, driving mutual growth with our clients through reliable global hubs.</t>
         </is>
       </c>
       <c r="I68" s="5" t="n"/>
@@ -3239,7 +3243,7 @@
       <c r="G69" s="7" t="n"/>
       <c r="H69" s="8" t="inlineStr">
         <is>
-          <t>High-Efficiency Eco-Friendly Cyclers Validating the Future of Batteries</t>
+          <t>High-Efficiency, Eco-Friendly Cyclers Validating the Future of Batteries</t>
         </is>
       </c>
       <c r="I69" s="5" t="n"/>
@@ -3271,13 +3275,13 @@
       <c r="E70" s="5" t="inlineStr"/>
       <c r="F70" s="6" t="inlineStr">
         <is>
-          <t>에이프로의 이차전지 사이클러(Battery Cycler)는 독보적인 양방향 전력 제어와 에너지 회생 기술을 통해 배터리의 성능 평가를 최적화하고, 완벽한 제조 안정성을 확보합니다.</t>
+          <t>에이프로의 Cycler는 독보적인 양방향 전력 제어와 에너지 회생 기술을 통해 배터리의 성능 평가를 최적화하고, 완벽한 제조 안정성을 확보합니다.</t>
         </is>
       </c>
       <c r="G70" s="7" t="n"/>
       <c r="H70" s="8" t="inlineStr">
         <is>
-          <t>A-PRO’s Battery Cycler optimizes battery performance evaluation and ensures flawless manufacturing stability through unrivaled bidirectional power control and energy regeneration technology.</t>
+          <t>With proprietary bidirectional power control and energy regeneration technology, A-PRO’s Cycler optimizes battery performance evaluation and ensures uncompromising manufacturing reliability.</t>
         </is>
       </c>
       <c r="I70" s="5" t="n"/>
@@ -3309,13 +3313,13 @@
       <c r="E71" s="5" t="inlineStr"/>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>에이프로의 이차전지 사이클러는 배터리를 반복적으로 충·방전하여 성능, 효율성, 수명을 정밀하게 평가하는 핵심 테스트 장비입니다. 용량, 수명 주기(Cycle Life), 내부 저항을 정밀 측정하고 실제 사용 환경을 완벽히 시뮬레이션하여, 연구 개발 및 제조 단계에서 발생할 수 있는 열화 현상과 안전 문제를 사전에 빈틈없이 검출합니다.</t>
+          <t>성능 평가 및 신뢰성 검증 : 배터리를 반복적으로 충·방전하여 용량, 수명 주기, 내부 저항을 정밀 측정하고 실제 사용 환경을 완벽히 시뮬레이션하여 연구 개발 및 제조 단계에서 발생할 수 있는 열화 현상과 안전 문제를 사전에 빈틈없이 검출합니다.</t>
         </is>
       </c>
       <c r="G71" s="7" t="n"/>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>A-PRO’s Battery Cycler is an essential testing solution that precisely evaluates battery performance, efficiency, and lifespan through continuous charge and discharge cycles. By accurately measuring capacity, cycle life, and internal resistance, our cyclers replicate real-world operating conditions to flawlessly detect degradation and safety issues during the R&amp;D and manufacturing stages.</t>
+          <t>Performance Evaluation &amp; Reliability Validation: Precisely measures capacity, cycle life, and internal resistance through repetitive charge-discharge cycles. By seamlessly simulating real-world conditions, it proactively detects degradation and safety risks across both R&amp;D and production stages.</t>
         </is>
       </c>
       <c r="I71" s="5" t="n"/>
@@ -3347,13 +3351,14 @@
       <c r="E72" s="5" t="inlineStr"/>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>특히 에이프로의 Cycler는 전류 공급(충전)과 흡수(방전)가 모두 가능한 양방향 전력 시스템과 혁신적인 에너지 회생(Regenerative) 기능을 탑재하고 있습니다. 방전 시 버려지는 에너지를 회수하여 전력망으로 되돌려주는 이 기술은 공장의 전력 낭비를 획기적으로 줄이고 냉각 부하를 저감하여, 가장 경제적이고 친환경적인 생산 환경을 완성합니다.</t>
+          <t>양방향 전력 시스템 : 전류 공급(충전)과 흡수(방전)가 모두 가능한 양방향 전력 시스템을 기반으로 안정적인 테스트 환경을 제공합니다.</t>
         </is>
       </c>
       <c r="G72" s="7" t="n"/>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t>In particular, A-PRO’s Cycler features an advanced bidirectional system capable of both supplying (charging) and absorbing (discharging) current, integrated with innovative energy regeneration technology. By capturing energy released during discharge and feeding it back into the power grid, this technology drastically reduces power waste and cooling loads, enabling an exceptionally economical and eco-friendly production environment.</t>
+          <t xml:space="preserve">Bidirectional Power System: Provides an exceptionally stable testing environment powered by a bidirectional architecture capable of both supplying (charging) and sinking (discharging) electrical current.
+</t>
         </is>
       </c>
       <c r="I72" s="5" t="n"/>
@@ -3369,12 +3374,12 @@
       </c>
       <c r="B73" s="5" t="inlineStr">
         <is>
-          <t>03-1 자동화 설비</t>
+          <t>02-1 Cycler(Cell&amp;Module)</t>
         </is>
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>작은 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -3385,15 +3390,19 @@
       <c r="E73" s="5" t="inlineStr"/>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>스마트 팩토리를 완성하는 지능형 통합 제어 솔루션</t>
+          <t>친환경 에너지 회생 기술 : 방전 시 버려지는 에너지를 회수하여 전력망으로 되돌려주는 기술을 활용합니다. 이는 전력 낭비를 획기적으로 줄이고 냉각 부하를 저감하여 경제적이고 친환경적인 생산 환경을 완성합니다.</t>
         </is>
       </c>
       <c r="G73" s="7" t="n"/>
-      <c r="H73" s="8" t="n"/>
+      <c r="H73" s="8" t="inlineStr">
+        <is>
+          <t>Eco-Friendly Energy Regeneration: Captures surplus energy released during discharge and feeds it back into the power grid. This drastically cuts power consumption and minimizes cooling loads, delivering an economical and sustainable manufacturing environment.</t>
+        </is>
+      </c>
       <c r="I73" s="5" t="n"/>
       <c r="J73" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[5]|text</t>
         </is>
       </c>
     </row>
@@ -3408,7 +3417,7 @@
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>작은 제목</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -3419,15 +3428,19 @@
       <c r="E74" s="5" t="inlineStr"/>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>활성화 공정 전체 설비의 실시간 정밀 제어와 체계적인 데이터 관리를 통해 최고의 생산 가동 효율과 제조 안정성을 보장합니다.</t>
+          <t>스마트 자동화 공정 솔루션</t>
         </is>
       </c>
       <c r="G74" s="7" t="n"/>
-      <c r="H74" s="8" t="n"/>
+      <c r="H74" s="8" t="inlineStr">
+        <is>
+          <t>Smart Automated Process Solutions</t>
+        </is>
+      </c>
       <c r="I74" s="5" t="n"/>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3442,7 +3455,7 @@
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -3453,19 +3466,19 @@
       <c r="E75" s="5" t="inlineStr"/>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>스마트 설비 제어</t>
+          <t>에이프로의 2차전지 활성화 설비는 최첨단 자동화 시스템을 통해 Cell 및 Module 공정의 생산 효율성을 극대화합니다.</t>
         </is>
       </c>
       <c r="G75" s="7" t="n"/>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>Smart Equipment Control</t>
+          <t>A-PRO's secondary battery formation equipment maximizes production efficiency across both Cell and Module processes through cutting-edge automation systems.</t>
         </is>
       </c>
       <c r="I75" s="5" t="n"/>
       <c r="J75" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[1]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3480,7 +3493,7 @@
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -3491,19 +3504,19 @@
       <c r="E76" s="5" t="inlineStr"/>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>충방전기, 디개싱, 에이징 룸 등 공정 내 모든 하드웨어를 실시간 직접 제어합니다.</t>
+          <t>다관절 로봇, 물류 컨베이어, 스태커 크레인, AMR(자율주행로봇) 등 고성능 물류 설비를 유기적으로 연계하여, 상위 시스템(MES, FCS)에서 전달받은 실시간 공정 정보에 따라 자율적이고 정확하게 정밀 이송·투입·배출을 수행합니다.</t>
         </is>
       </c>
       <c r="G76" s="7" t="n"/>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>Direct, real-time hardware control of all production lines, including cyclers, degassing units, and aging rooms.</t>
+          <t>By seamlessly integrating high-performance logistics equipment—including articulated robots, conveyors, stacker cranes, and AMRs (Autonomous Mobile Robots)—our systems autonomously execute precise transfer, loading, and unloading based on real-time process data from host systems (MES, FCS).</t>
         </is>
       </c>
       <c r="I76" s="5" t="n"/>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[1]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -3518,7 +3531,7 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -3529,19 +3542,19 @@
       <c r="E77" s="5" t="inlineStr"/>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>실시간 데이터 수집</t>
+          <t>단순 이송을 넘어, 상위 데이터에 기반한 자율적 판단으로 주어진 업무를 완벽하게 자동 처리함으로써 인적 오차를 줄이고, 최상의 공정 안정성과 데이터 기반의 스마트 팩토리를 실현합니다.</t>
         </is>
       </c>
       <c r="G77" s="7" t="n"/>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>Real-Time Data Acquisition</t>
+          <t>Moving beyond simple material handling, our equipment autonomously processes operations through data-driven decisions. This minimizes human error, ensures superior process stability, and realizes a truly data-centric smart factory.</t>
         </is>
       </c>
       <c r="I77" s="5" t="n"/>
       <c r="J77" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[2]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[4]|text</t>
         </is>
       </c>
     </row>
@@ -3556,7 +3569,7 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -3567,19 +3580,19 @@
       <c r="E78" s="5" t="inlineStr"/>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>미세한 온도·압력·전압·전류 데이터를 정밀 측정하여 완벽한 품질 추적성을 확보합니다.</t>
+          <t>스마트 설비 제어</t>
         </is>
       </c>
       <c r="G78" s="7" t="n"/>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>Precision monitoring of voltage, current, temperature, and pressure for seamless quality traceability.</t>
+          <t>Smart Equipment Control</t>
         </is>
       </c>
       <c r="I78" s="5" t="n"/>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[2]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[1]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3594,7 +3607,7 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -3605,19 +3618,19 @@
       <c r="E79" s="5" t="inlineStr"/>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>지능형 안전 인터록</t>
+          <t>충방전기, 디개싱, 에이징 룸 등 공정 내 모든 하드웨어를 실시간 직접 제어합니다.</t>
         </is>
       </c>
       <c r="G79" s="7" t="n"/>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>Intelligent Safety Interlock</t>
+          <t>Direct, real-time hardware control of all production lines, including cyclers, degassing units, and aging rooms.</t>
         </is>
       </c>
       <c r="I79" s="5" t="n"/>
       <c r="J79" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[3]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[1]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3632,7 +3645,7 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -3643,19 +3656,19 @@
       <c r="E80" s="5" t="inlineStr"/>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>가스 누출, 과전압 등 이상 징후 감지 시 설비를 즉각 정지시켜 사고를 원천 차단합니다.</t>
+          <t>실시간 데이터 수집</t>
         </is>
       </c>
       <c r="G80" s="7" t="n"/>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>Advanced emergency system that instantly halts operations upon detecting hazards like gas leaks or overvoltage.</t>
+          <t>Real-Time Data Acquisition</t>
         </is>
       </c>
       <c r="I80" s="5" t="n"/>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[3]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[2]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3670,7 +3683,7 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3681,19 +3694,19 @@
       <c r="E81" s="5" t="inlineStr"/>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>유연한 상위 연동</t>
+          <t>미세한 온도·압력·전압·전류 데이터를 정밀 측정하여 완벽한 품질 추적성을 확보합니다.</t>
         </is>
       </c>
       <c r="G81" s="7" t="n"/>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>Seamless Integration</t>
+          <t>Precision monitoring of voltage, current, temperature, and pressure for seamless quality traceability.</t>
         </is>
       </c>
       <c r="I81" s="5" t="n"/>
       <c r="J81" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[4]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[2]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3708,7 +3721,7 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -3719,19 +3732,19 @@
       <c r="E82" s="5" t="inlineStr"/>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>PC 및 MES와의 고속 통신으로 공정 데이터를 실시간 전송하고 레시피 명령을 완벽히 수행합니다.</t>
+          <t>지능형 안전 인터록</t>
         </is>
       </c>
       <c r="G82" s="7" t="n"/>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>High-speed communication with upper-level systems (PCs/MES) to transmit process data and execute recipe commands flawlessly.</t>
+          <t>Intelligent Safety Interlock</t>
         </is>
       </c>
       <c r="I82" s="5" t="n"/>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[4]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[3]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3741,12 +3754,12 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>04-1 탄소 나노 튜브</t>
+          <t>03-1 자동화 설비</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -3757,19 +3770,19 @@
       <c r="E83" s="5" t="inlineStr"/>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials의 글로벌 소싱 네트워크를 활용하여 고품질의 탄소나노튜브(CNT) 소재를 안정적으로 공급합니다.</t>
+          <t>가스 누출, 과전압 등 이상 징후 감지 시 설비를 즉각 정지시켜 사고를 원천 차단합니다.</t>
         </is>
       </c>
       <c r="G83" s="7" t="n"/>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>We provide a stable supply of high-quality carbon nanotube (CNT) materials through A-PRO Materials' global sourcing network.</t>
+          <t>Advanced emergency system that instantly halts operations upon detecting hazards like gas leaks or overvoltage.</t>
         </is>
       </c>
       <c r="I83" s="5" t="n"/>
       <c r="J83" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[1]/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[3]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3779,12 +3792,12 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>04-1 탄소 나노 튜브</t>
+          <t>03-1 자동화 설비</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -3795,19 +3808,19 @@
       <c r="E84" s="5" t="inlineStr"/>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>엄격한 품질 검증을 거친 CNT 소재를 통해 고객사의 배터리 에너지 밀도 향상과 고속 충전 성능 구현을 지원합니다.</t>
+          <t>유연한 상위 연동</t>
         </is>
       </c>
       <c r="G84" s="7" t="n"/>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>Through rigorously quality-verified CNT materials, we support our customers in enhancing battery energy density and enabling high-speed charging performance.</t>
+          <t>Seamless Integration</t>
         </is>
       </c>
       <c r="I84" s="5" t="n"/>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[1]/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[4]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3817,12 +3830,12 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>04-1 탄소 나노 튜브</t>
+          <t>03-1 자동화 설비</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>제품 단추 이름</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -3833,19 +3846,19 @@
       <c r="E85" s="5" t="inlineStr"/>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>SW/FW-CNT Powder</t>
+          <t>PC 및 MES와의 고속 통신으로 공정 데이터를 실시간 전송하고 레시피 명령을 완벽히 수행합니다.</t>
         </is>
       </c>
       <c r="G85" s="7" t="n"/>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>SW/FW-CNT Powder</t>
+          <t>High-speed communication with upper-level systems (PCs/MES) to transmit process data and execute recipe commands flawlessly.</t>
         </is>
       </c>
       <c r="I85" s="5" t="n"/>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[1]/span[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[4]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3860,7 +3873,7 @@
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>제품 단추 이름</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -3871,19 +3884,19 @@
       <c r="E86" s="5" t="inlineStr"/>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>SW/FW-CNT Slurry</t>
+          <t>A-PRO Materials의 글로벌 소싱 네트워크를 활용하여 고품질의 탄소나노튜브(CNT) 소재를 안정적으로 공급합니다.</t>
         </is>
       </c>
       <c r="G86" s="7" t="n"/>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>SW/FW-CNT Slurry</t>
+          <t>We provide a stable supply of high-quality carbon nanotube (CNT) materials through A-PRO Materials' global sourcing network.</t>
         </is>
       </c>
       <c r="I86" s="5" t="n"/>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[2]/span[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[1]/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3898,7 +3911,7 @@
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>제품 단추 이름</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -3909,19 +3922,19 @@
       <c r="E87" s="5" t="inlineStr"/>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>Carbon Black</t>
+          <t>엄격한 품질 검증을 거친 CNT 소재를 통해 고객사의 배터리 에너지 밀도 향상과 고속 충전 성능 구현을 지원합니다.</t>
         </is>
       </c>
       <c r="G87" s="7" t="n"/>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>Carbon Black</t>
+          <t>Through rigorously quality-verified CNT materials, we support our customers in enhancing battery energy density and enabling high-speed charging performance.</t>
         </is>
       </c>
       <c r="I87" s="5" t="n"/>
       <c r="J87" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[3]/span[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[1]/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3931,12 +3944,12 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>04-1 탄소 나노 튜브 · 04-2 LiFSI 전해염 · 04-3 HNBR 바인더 · 04-4 파우치셀 제조</t>
+          <t>04-1 탄소 나노 튜브</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>문의 단추</t>
+          <t>제품 단추 이름</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -3947,17 +3960,131 @@
       <c r="E88" s="5" t="inlineStr"/>
       <c r="F88" s="6" t="inlineStr">
         <is>
+          <t>SW/FW-CNT Powder</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="n"/>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>SW/FW-CNT Powder</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="n"/>
+      <c r="J88" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[1]/span[2]|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>04-1 탄소 나노 튜브</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>제품 단추 이름</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr"/>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>SW/FW-CNT Slurry</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="n"/>
+      <c r="H89" s="8" t="inlineStr">
+        <is>
+          <t>SW/FW-CNT Slurry</t>
+        </is>
+      </c>
+      <c r="I89" s="5" t="n"/>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[2]/span[2]|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>04-1 탄소 나노 튜브</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>제품 단추 이름</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr"/>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>Carbon Black</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="n"/>
+      <c r="H90" s="8" t="inlineStr">
+        <is>
+          <t>Carbon Black</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="n"/>
+      <c r="J90" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[3]/span[2]|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>04-1 탄소 나노 튜브 · 04-2 LiFSI 전해염 · 04-3 HNBR 바인더 · 04-4 파우치셀 제조</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>문의 단추</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr"/>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
           <t>문의하기</t>
         </is>
       </c>
-      <c r="G88" s="7" t="n"/>
-      <c r="H88" s="8" t="n"/>
-      <c r="I88" s="5" t="inlineStr">
+      <c r="G91" s="7" t="n"/>
+      <c r="H91" s="8" t="n"/>
+      <c r="I91" s="5" t="inlineStr">
         <is>
           <t>같은 문구 4 곳 — 한 줄로 합침</t>
         </is>
       </c>
-      <c r="J88" s="9" t="inlineStr">
+      <c r="J91" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/a|text
 /html/body/div[8]/div[3]/section[6]/div/div[2]/a|text
@@ -3966,116 +4093,6 @@
         </is>
       </c>
     </row>
-    <row r="89">
-      <c r="A89" s="5" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>04-2 LiFSI 전해염</t>
-        </is>
-      </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>본문</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr"/>
-      <c r="F89" s="6" t="inlineStr">
-        <is>
-          <t>A-PRO Materials는 엄선된 공급망을 통해 고순도 LiFSI 전해염 소재를 안정적으로 공급합니다.</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="n"/>
-      <c r="H89" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Materials provides a stable supply of high-purity LiFSI electrolyte salt through a carefully selected global supply network.</t>
-        </is>
-      </c>
-      <c r="I89" s="5" t="n"/>
-      <c r="J89" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[1]|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>04-2 LiFSI 전해염</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>본문</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr"/>
-      <c r="F90" s="6" t="inlineStr">
-        <is>
-          <t>우수한 화학적 안정성을 바탕으로 고객사 배터리의 수명 연장과 고온 안정성 및 출력 향상을 지원합니다.</t>
-        </is>
-      </c>
-      <c r="G90" s="7" t="n"/>
-      <c r="H90" s="8" t="inlineStr">
-        <is>
-          <t>Based on superior chemical stability, we support extended battery life, high-temperature stability, and improved output performance for our customers.</t>
-        </is>
-      </c>
-      <c r="I90" s="5" t="n"/>
-      <c r="J90" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[2]|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>04-2 LiFSI 전해염</t>
-        </is>
-      </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>제품 이름</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="inlineStr"/>
-      <c r="F91" s="6" t="inlineStr">
-        <is>
-          <t>LiFSI 전해질</t>
-        </is>
-      </c>
-      <c r="G91" s="7" t="n"/>
-      <c r="H91" s="8" t="n"/>
-      <c r="I91" s="5" t="n"/>
-      <c r="J91" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/div/p[1]|text</t>
-        </is>
-      </c>
-    </row>
     <row r="92">
       <c r="A92" s="5" t="n">
         <v>91</v>
@@ -4087,7 +4104,7 @@
       </c>
       <c r="C92" s="5" t="inlineStr">
         <is>
-          <t>제품 설명</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
@@ -4098,15 +4115,19 @@
       <c r="E92" s="5" t="inlineStr"/>
       <c r="F92" s="6" t="inlineStr">
         <is>
-          <t>고출력 · 수명연장용 차세대 전해염</t>
+          <t>A-PRO Materials는 엄선된 공급망을 통해 고순도 LiFSI 전해염 소재를 안정적으로 공급합니다.</t>
         </is>
       </c>
       <c r="G92" s="7" t="n"/>
-      <c r="H92" s="8" t="n"/>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Materials provides a stable supply of high-purity LiFSI electrolyte salt through a carefully selected global supply network.</t>
+        </is>
+      </c>
       <c r="I92" s="5" t="n"/>
       <c r="J92" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4121,7 +4142,7 @@
       </c>
       <c r="C93" s="5" t="inlineStr">
         <is>
-          <t>제품 수치</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
@@ -4132,15 +4153,19 @@
       <c r="E93" s="5" t="inlineStr"/>
       <c r="F93" s="6" t="inlineStr">
         <is>
-          <t>비표면적 ≥300~1,000 m²/g</t>
+          <t>우수한 화학적 안정성을 바탕으로 고객사 배터리의 수명 연장과 고온 안정성 및 출력 향상을 지원합니다.</t>
         </is>
       </c>
       <c r="G93" s="7" t="n"/>
-      <c r="H93" s="8" t="n"/>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>Based on superior chemical stability, we support extended battery life, high-temperature stability, and improved output performance for our customers.</t>
+        </is>
+      </c>
       <c r="I93" s="5" t="n"/>
       <c r="J93" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4155,18 +4180,18 @@
       </c>
       <c r="C94" s="5" t="inlineStr">
         <is>
-          <t>제품 사진 대체글</t>
+          <t>제품 이름</t>
         </is>
       </c>
       <c r="D94" s="5" t="inlineStr">
         <is>
-          <t>대체글</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E94" s="5" t="inlineStr"/>
       <c r="F94" s="6" t="inlineStr">
         <is>
-          <t>LiFSI 전해염 입자 표면의 주사전자현미경 사진 — 크고 작은 구멍이 촘촘한 다공성 구조</t>
+          <t>LiFSI 전해질</t>
         </is>
       </c>
       <c r="G94" s="7" t="n"/>
@@ -4174,7 +4199,7 @@
       <c r="I94" s="5" t="n"/>
       <c r="J94" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/span/img|alt</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4189,7 +4214,7 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>제품 이름</t>
+          <t>제품 설명</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -4200,7 +4225,7 @@
       <c r="E95" s="5" t="inlineStr"/>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>산화물계 전해질</t>
+          <t>고출력 · 수명연장용 차세대 전해염</t>
         </is>
       </c>
       <c r="G95" s="7" t="n"/>
@@ -4208,7 +4233,7 @@
       <c r="I95" s="5" t="n"/>
       <c r="J95" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4223,7 +4248,7 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>제품 설명</t>
+          <t>제품 수치</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -4234,7 +4259,7 @@
       <c r="E96" s="5" t="inlineStr"/>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>산화물계 LLZMO · LATP</t>
+          <t>비표면적 ≥300~1,000 m²/g</t>
         </is>
       </c>
       <c r="G96" s="7" t="n"/>
@@ -4242,7 +4267,7 @@
       <c r="I96" s="5" t="n"/>
       <c r="J96" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -4257,18 +4282,18 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>제품 수치</t>
+          <t>제품 사진 대체글</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>대체글</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr"/>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>이온 전도도 0.2~1.0 mS/cm</t>
+          <t>LiFSI 전해염 입자 표면의 주사전자현미경 사진 — 크고 작은 구멍이 촘촘한 다공성 구조</t>
         </is>
       </c>
       <c r="G97" s="7" t="n"/>
@@ -4276,7 +4301,7 @@
       <c r="I97" s="5" t="n"/>
       <c r="J97" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/span/img|alt</t>
         </is>
       </c>
     </row>
@@ -4291,18 +4316,18 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>제품 사진 대체글</t>
+          <t>제품 이름</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
         <is>
-          <t>대체글</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E98" s="5" t="inlineStr"/>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>산화물계 전해질 모식도 — 왼쪽은 결정 격자, 오른쪽은 고체 전해질 막을 가로지르는 이온 이동</t>
+          <t>산화물계 전해질</t>
         </is>
       </c>
       <c r="G98" s="7" t="n"/>
@@ -4310,7 +4335,7 @@
       <c r="I98" s="5" t="n"/>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/span/img|alt</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4325,7 +4350,7 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>제품 설명</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
@@ -4336,19 +4361,15 @@
       <c r="E99" s="5" t="inlineStr"/>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>High Purity</t>
+          <t>산화물계 LLZMO · LATP</t>
         </is>
       </c>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="8" t="inlineStr">
-        <is>
-          <t>High Purity</t>
-        </is>
-      </c>
+      <c r="H99" s="8" t="n"/>
       <c r="I99" s="5" t="n"/>
       <c r="J99" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[1]/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4363,7 +4384,7 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>제품 수치</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
@@ -4374,19 +4395,15 @@
       <c r="E100" s="5" t="inlineStr"/>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>Thermal Stability</t>
+          <t>이온 전도도 0.2~1.0 mS/cm</t>
         </is>
       </c>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="8" t="inlineStr">
-        <is>
-          <t>Thermal Stability</t>
-        </is>
-      </c>
+      <c r="H100" s="8" t="n"/>
       <c r="I100" s="5" t="n"/>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[2]/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -4401,30 +4418,26 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>제품 사진 대체글</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>대체글</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr"/>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>Long Cycle Life</t>
+          <t>산화물계 전해질 모식도 — 왼쪽은 결정 격자, 오른쪽은 고체 전해질 막을 가로지르는 이온 이동</t>
         </is>
       </c>
       <c r="G101" s="7" t="n"/>
-      <c r="H101" s="8" t="inlineStr">
-        <is>
-          <t>Long Cycle Life</t>
-        </is>
-      </c>
+      <c r="H101" s="8" t="n"/>
       <c r="I101" s="5" t="n"/>
       <c r="J101" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[3]/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/span/img|alt</t>
         </is>
       </c>
     </row>
@@ -4450,19 +4463,19 @@
       <c r="E102" s="5" t="inlineStr"/>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>Fast Charging</t>
+          <t>High Purity</t>
         </is>
       </c>
       <c r="G102" s="7" t="n"/>
       <c r="H102" s="8" t="inlineStr">
         <is>
-          <t>Fast Charging</t>
+          <t>High Purity</t>
         </is>
       </c>
       <c r="I102" s="5" t="n"/>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[4]/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[1]/p|text</t>
         </is>
       </c>
     </row>
@@ -4488,19 +4501,19 @@
       <c r="E103" s="5" t="inlineStr"/>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>Low Resistance &amp; Low Viscosity</t>
+          <t>Thermal Stability</t>
         </is>
       </c>
       <c r="G103" s="7" t="n"/>
       <c r="H103" s="8" t="inlineStr">
         <is>
-          <t>Low Resistance &amp; Low Viscosity</t>
+          <t>Thermal Stability</t>
         </is>
       </c>
       <c r="I103" s="5" t="n"/>
       <c r="J103" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[5]/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[2]/p|text</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4523,12 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-2 LiFSI 전해염</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
@@ -4526,19 +4539,19 @@
       <c r="E104" s="5" t="inlineStr"/>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>PVDF 바인더의 일부 대체 가능성을 검토할 수 있는 HNBR 바인더 소재입니다.</t>
+          <t>Long Cycle Life</t>
         </is>
       </c>
       <c r="G104" s="7" t="n"/>
       <c r="H104" s="8" t="inlineStr">
         <is>
-          <t>HNBR is a binder material that can be evaluated as a partial alternative to PVDF binders.</t>
+          <t>Long Cycle Life</t>
         </is>
       </c>
       <c r="I104" s="5" t="n"/>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[3]/p|text</t>
         </is>
       </c>
     </row>
@@ -4548,12 +4561,12 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-2 LiFSI 전해염</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -4564,19 +4577,19 @@
       <c r="E105" s="5" t="inlineStr"/>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>우수한 결합력과 유연성, 전극 저항 감소 효과를 통해 배터리의 고율 충·방전 성능과 안정성 향상에 기여할 수 있습니다.</t>
+          <t>Fast Charging</t>
         </is>
       </c>
       <c r="G105" s="7" t="n"/>
       <c r="H105" s="8" t="inlineStr">
         <is>
-          <t>With excellent bonding strength, flexibility, and reduced electrode resistance, it can contribute to improved high-rate charge/discharge performance and stability.</t>
+          <t>Fast Charging</t>
         </is>
       </c>
       <c r="I105" s="5" t="n"/>
       <c r="J105" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[4]/p|text</t>
         </is>
       </c>
     </row>
@@ -4586,12 +4599,12 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-2 LiFSI 전해염</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D106" s="5" t="inlineStr">
@@ -4602,15 +4615,19 @@
       <c r="E106" s="5" t="inlineStr"/>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>CNT 분산용 고성능 고무 바인더</t>
+          <t>Low Resistance &amp; Low Viscosity</t>
         </is>
       </c>
       <c r="G106" s="7" t="n"/>
-      <c r="H106" s="8" t="n"/>
+      <c r="H106" s="8" t="inlineStr">
+        <is>
+          <t>Low Resistance &amp; Low Viscosity</t>
+        </is>
+      </c>
       <c r="I106" s="5" t="n"/>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[1]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[5]/p|text</t>
         </is>
       </c>
     </row>
@@ -4625,7 +4642,7 @@
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>표 값</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
@@ -4636,15 +4653,19 @@
       <c r="E107" s="5" t="inlineStr"/>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>포화도 99.6%</t>
+          <t>PVDF 바인더의 일부 대체 가능성을 검토할 수 있는 HNBR 바인더 소재입니다.</t>
         </is>
       </c>
       <c r="G107" s="7" t="n"/>
-      <c r="H107" s="8" t="n"/>
+      <c r="H107" s="8" t="inlineStr">
+        <is>
+          <t>HNBR is a binder material that can be evaluated as a partial alternative to PVDF binders.</t>
+        </is>
+      </c>
       <c r="I107" s="5" t="n"/>
       <c r="J107" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[1]/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4659,7 +4680,7 @@
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
@@ -4670,15 +4691,19 @@
       <c r="E108" s="5" t="inlineStr"/>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>HNBR 라텍스</t>
+          <t>우수한 결합력과 유연성, 전극 저항 감소 효과를 통해 배터리의 고율 충·방전 성능과 안정성 향상에 기여할 수 있습니다.</t>
         </is>
       </c>
       <c r="G108" s="7" t="n"/>
-      <c r="H108" s="8" t="n"/>
+      <c r="H108" s="8" t="inlineStr">
+        <is>
+          <t>With excellent bonding strength, flexibility, and reduced electrode resistance, it can contribute to improved high-rate charge/discharge performance and stability.</t>
+        </is>
+      </c>
       <c r="I108" s="5" t="n"/>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[2]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4704,7 +4729,7 @@
       <c r="E109" s="5" t="inlineStr"/>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>NMP계 고분산 액상 바인더</t>
+          <t>CNT 분산용 고성능 고무 바인더</t>
         </is>
       </c>
       <c r="G109" s="7" t="n"/>
@@ -4712,7 +4737,7 @@
       <c r="I109" s="5" t="n"/>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[2]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[1]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4738,7 +4763,7 @@
       <c r="E110" s="5" t="inlineStr"/>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>고형분 8~10%</t>
+          <t>포화도 99.6%</t>
         </is>
       </c>
       <c r="G110" s="7" t="n"/>
@@ -4746,7 +4771,7 @@
       <c r="I110" s="5" t="n"/>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[2]/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[1]/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4797,7 @@
       <c r="E111" s="5" t="inlineStr"/>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>PVDF 대체</t>
+          <t>HNBR 라텍스</t>
         </is>
       </c>
       <c r="G111" s="7" t="n"/>
@@ -4780,7 +4805,7 @@
       <c r="I111" s="5" t="n"/>
       <c r="J111" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[1]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[2]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4806,7 +4831,7 @@
       <c r="E112" s="5" t="inlineStr"/>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>기존 불소계 바인더의 5~15% 이상을 친환경 HNBR로 대체.</t>
+          <t>NMP계 고분산 액상 바인더</t>
         </is>
       </c>
       <c r="G112" s="7" t="n"/>
@@ -4814,7 +4839,7 @@
       <c r="I112" s="5" t="n"/>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[1]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[2]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4829,7 +4854,7 @@
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>표 값</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
@@ -4840,7 +4865,7 @@
       <c r="E113" s="5" t="inlineStr"/>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>고율 충방전 특성</t>
+          <t>고형분 8~10%</t>
         </is>
       </c>
       <c r="G113" s="7" t="n"/>
@@ -4848,7 +4873,7 @@
       <c r="I113" s="5" t="n"/>
       <c r="J113" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[2]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[2]/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -4863,7 +4888,7 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
@@ -4874,7 +4899,7 @@
       <c r="E114" s="5" t="inlineStr"/>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>10C 고속 충전 조건에서도 우수한 용량 유지.</t>
+          <t>PVDF 대체</t>
         </is>
       </c>
       <c r="G114" s="7" t="n"/>
@@ -4882,7 +4907,7 @@
       <c r="I114" s="5" t="n"/>
       <c r="J114" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[2]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[1]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4897,7 +4922,7 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
@@ -4908,7 +4933,7 @@
       <c r="E115" s="5" t="inlineStr"/>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>내부 저항 감소</t>
+          <t>기존 불소계 바인더의 5~15% 이상을 친환경 HNBR로 대체.</t>
         </is>
       </c>
       <c r="G115" s="7" t="n"/>
@@ -4916,7 +4941,7 @@
       <c r="I115" s="5" t="n"/>
       <c r="J115" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[3]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[1]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4931,7 +4956,7 @@
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -4942,7 +4967,7 @@
       <c r="E116" s="5" t="inlineStr"/>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>젖음성 개선으로 이온 전달 및 계면 저항 최소화.</t>
+          <t>고율 충방전 특성</t>
         </is>
       </c>
       <c r="G116" s="7" t="n"/>
@@ -4950,7 +4975,7 @@
       <c r="I116" s="5" t="n"/>
       <c r="J116" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[3]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[2]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4965,7 +4990,7 @@
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
@@ -4976,7 +5001,7 @@
       <c r="E117" s="5" t="inlineStr"/>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>높은 강도 및 유연성</t>
+          <t>10C 고속 충전 조건에서도 우수한 용량 유지.</t>
         </is>
       </c>
       <c r="G117" s="7" t="n"/>
@@ -4984,7 +5009,7 @@
       <c r="I117" s="5" t="n"/>
       <c r="J117" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[4]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[2]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4999,7 +5024,7 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
@@ -5010,7 +5035,7 @@
       <c r="E118" s="5" t="inlineStr"/>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>전극 활물질 부피 변화 흡수, 탈락 방지.</t>
+          <t>내부 저항 감소</t>
         </is>
       </c>
       <c r="G118" s="7" t="n"/>
@@ -5018,7 +5043,7 @@
       <c r="I118" s="5" t="n"/>
       <c r="J118" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[4]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[3]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -5033,7 +5058,7 @@
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
@@ -5044,7 +5069,7 @@
       <c r="E119" s="5" t="inlineStr"/>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>SWCNT 분산 최적화</t>
+          <t>젖음성 개선으로 이온 전달 및 계면 저항 최소화.</t>
         </is>
       </c>
       <c r="G119" s="7" t="n"/>
@@ -5052,7 +5077,7 @@
       <c r="I119" s="5" t="n"/>
       <c r="J119" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[5]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[3]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -5067,7 +5092,7 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
@@ -5078,7 +5103,7 @@
       <c r="E120" s="5" t="inlineStr"/>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>단일벽 탄소나노튜브의 응집 해소, 점도 감소.</t>
+          <t>높은 강도 및 유연성</t>
         </is>
       </c>
       <c r="G120" s="7" t="n"/>
@@ -5086,7 +5111,7 @@
       <c r="I120" s="5" t="n"/>
       <c r="J120" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[5]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[4]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -5096,12 +5121,12 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>04-4 파우치셀 제조</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
@@ -5112,19 +5137,15 @@
       <c r="E121" s="5" t="inlineStr"/>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials는 Lab-scale 파우치셀 제작 및 소재 적용성 검증 서비스를 제공합니다.</t>
+          <t>전극 활물질 부피 변화 흡수, 탈락 방지.</t>
         </is>
       </c>
       <c r="G121" s="7" t="n"/>
-      <c r="H121" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Materials provides lab-scale pouch cell fabrication and material validation services.</t>
-        </is>
-      </c>
+      <c r="H121" s="8" t="n"/>
       <c r="I121" s="5" t="n"/>
       <c r="J121" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[4]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -5134,12 +5155,12 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>04-4 파우치셀 제조</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
@@ -5150,19 +5171,15 @@
       <c r="E122" s="5" t="inlineStr"/>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>셀 설계부터 조립 공정, 품질 평가까지 통합 프로세스를 통해 고객사의 신소재 적용 가능성을 사전 검증합니다.</t>
+          <t>SWCNT 분산 최적화</t>
         </is>
       </c>
       <c r="G122" s="7" t="n"/>
-      <c r="H122" s="8" t="inlineStr">
-        <is>
-          <t>Through an integrated process encompassing cell design, assembly, and quality evaluation, we help our clients pre-validate the applicability of new materials.</t>
-        </is>
-      </c>
+      <c r="H122" s="8" t="n"/>
       <c r="I122" s="5" t="n"/>
       <c r="J122" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[5]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -5172,31 +5189,31 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>04-4 파우치셀 제조</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr"/>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="G123" s="6" t="n"/>
-      <c r="H123" s="6" t="n"/>
+          <t>단일벽 탄소나노튜브의 응집 해소, 점도 감소.</t>
+        </is>
+      </c>
+      <c r="G123" s="7" t="n"/>
+      <c r="H123" s="8" t="n"/>
       <c r="I123" s="5" t="n"/>
       <c r="J123" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[1]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[5]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -5211,7 +5228,7 @@
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
@@ -5222,15 +5239,19 @@
       <c r="E124" s="5" t="inlineStr"/>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>사양 협의</t>
+          <t>A-PRO Materials는 Lab-scale 파우치셀 제작 및 소재 적용성 검증 서비스를 제공합니다.</t>
         </is>
       </c>
       <c r="G124" s="7" t="n"/>
-      <c r="H124" s="8" t="n"/>
+      <c r="H124" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Materials provides lab-scale pouch cell fabrication and material validation services.</t>
+        </is>
+      </c>
       <c r="I124" s="5" t="n"/>
       <c r="J124" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[1]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -5245,26 +5266,30 @@
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr"/>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="G125" s="6" t="n"/>
-      <c r="H125" s="6" t="n"/>
+          <t>셀 설계부터 조립 공정, 품질 평가까지 통합 프로세스를 통해 고객사의 신소재 적용 가능성을 사전 검증합니다.</t>
+        </is>
+      </c>
+      <c r="G125" s="7" t="n"/>
+      <c r="H125" s="8" t="inlineStr">
+        <is>
+          <t>Through an integrated process encompassing cell design, assembly, and quality evaluation, we help our clients pre-validate the applicability of new materials.</t>
+        </is>
+      </c>
       <c r="I125" s="5" t="n"/>
       <c r="J125" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[2]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -5279,26 +5304,26 @@
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr"/>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>소재 입고 및 검수</t>
-        </is>
-      </c>
-      <c r="G126" s="7" t="n"/>
-      <c r="H126" s="8" t="n"/>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="G126" s="6" t="n"/>
+      <c r="H126" s="6" t="n"/>
       <c r="I126" s="5" t="n"/>
       <c r="J126" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[2]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[1]/b|text</t>
         </is>
       </c>
     </row>
@@ -5313,26 +5338,26 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr"/>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="G127" s="6" t="n"/>
-      <c r="H127" s="6" t="n"/>
+          <t>사양 협의</t>
+        </is>
+      </c>
+      <c r="G127" s="7" t="n"/>
+      <c r="H127" s="8" t="n"/>
       <c r="I127" s="5" t="n"/>
       <c r="J127" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[3]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[1]/span|text</t>
         </is>
       </c>
     </row>
@@ -5347,26 +5372,26 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr"/>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>파우치셀 조립</t>
-        </is>
-      </c>
-      <c r="G128" s="7" t="n"/>
-      <c r="H128" s="8" t="n"/>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="G128" s="6" t="n"/>
+      <c r="H128" s="6" t="n"/>
       <c r="I128" s="5" t="n"/>
       <c r="J128" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[3]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[2]/b|text</t>
         </is>
       </c>
     </row>
@@ -5381,26 +5406,26 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr"/>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="G129" s="6" t="n"/>
-      <c r="H129" s="6" t="n"/>
+          <t>소재 입고 및 검수</t>
+        </is>
+      </c>
+      <c r="G129" s="7" t="n"/>
+      <c r="H129" s="8" t="n"/>
       <c r="I129" s="5" t="n"/>
       <c r="J129" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[4]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[2]/span|text</t>
         </is>
       </c>
     </row>
@@ -5415,26 +5440,26 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr"/>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>화성 공정</t>
-        </is>
-      </c>
-      <c r="G130" s="7" t="n"/>
-      <c r="H130" s="8" t="n"/>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="G130" s="6" t="n"/>
+      <c r="H130" s="6" t="n"/>
       <c r="I130" s="5" t="n"/>
       <c r="J130" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[4]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[3]/b|text</t>
         </is>
       </c>
     </row>
@@ -5449,26 +5474,26 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr"/>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="G131" s="6" t="n"/>
-      <c r="H131" s="6" t="n"/>
+          <t>파우치셀 조립</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="n"/>
+      <c r="H131" s="8" t="n"/>
       <c r="I131" s="5" t="n"/>
       <c r="J131" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[5]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[3]/span|text</t>
         </is>
       </c>
     </row>
@@ -5483,26 +5508,26 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr"/>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>제품 출하</t>
-        </is>
-      </c>
-      <c r="G132" s="7" t="n"/>
-      <c r="H132" s="8" t="n"/>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="G132" s="6" t="n"/>
+      <c r="H132" s="6" t="n"/>
       <c r="I132" s="5" t="n"/>
       <c r="J132" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[5]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[4]/b|text</t>
         </is>
       </c>
     </row>
@@ -5512,12 +5537,12 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>04-5 에이프로머티리얼즈</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
@@ -5528,7 +5553,7 @@
       <c r="E133" s="5" t="inlineStr"/>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>차세대 기술 개발</t>
+          <t>화성 공정</t>
         </is>
       </c>
       <c r="G133" s="7" t="n"/>
@@ -5536,7 +5561,7 @@
       <c r="I133" s="5" t="n"/>
       <c r="J133" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[4]/span|text</t>
         </is>
       </c>
     </row>
@@ -5546,35 +5571,31 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>04-5 에이프로머티리얼즈</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr"/>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials는 차세대 배터리 핵심 기술에 대한 지속적인 연구개발을 통해 미래 이차전지 시장에 대응해 나갑니다.</t>
-        </is>
-      </c>
-      <c r="G134" s="7" t="n"/>
-      <c r="H134" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Materials is working to respond to the future secondary battery market through continuous research and development of core next-generation battery technologies.</t>
-        </is>
-      </c>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="n"/>
+      <c r="H134" s="6" t="n"/>
       <c r="I134" s="5" t="n"/>
       <c r="J134" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[5]/b|text</t>
         </is>
       </c>
     </row>
@@ -5584,12 +5605,12 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>04-5 에이프로머티리얼즈</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
@@ -5600,19 +5621,15 @@
       <c r="E135" s="5" t="inlineStr"/>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>끊임없는 R&amp;D 혁신으로 기존 배터리의 한계를 극복하고, 고성능·고안정성 소재 및 셀 기술을 선제적으로 구현해 나갑니다.</t>
+          <t>제품 출하</t>
         </is>
       </c>
       <c r="G135" s="7" t="n"/>
-      <c r="H135" s="8" t="inlineStr">
-        <is>
-          <t>Through ongoing R&amp;D innovation, we work to overcome the limitations of existing batteries and proactively develop high-performance, high-stability materials and cell technologies.</t>
-        </is>
-      </c>
+      <c r="H135" s="8" t="n"/>
       <c r="I135" s="5" t="n"/>
       <c r="J135" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[5]/span|text</t>
         </is>
       </c>
     </row>
@@ -5627,7 +5644,7 @@
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
@@ -5638,19 +5655,15 @@
       <c r="E136" s="5" t="inlineStr"/>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials는 국내외 파트너들과의 협력을 통해 최적의 이차전지 소재 솔루션을 모색하고 있습니다.</t>
+          <t>차세대 기술 개발</t>
         </is>
       </c>
       <c r="G136" s="7" t="n"/>
-      <c r="H136" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Materials is exploring optimal secondary battery material solutions in collaboration with partners at home and abroad.</t>
-        </is>
-      </c>
+      <c r="H136" s="8" t="n"/>
       <c r="I136" s="5" t="n"/>
       <c r="J136" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -5665,26 +5678,30 @@
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr"/>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="G137" s="6" t="n"/>
-      <c r="H137" s="6" t="n"/>
+          <t>A-PRO Materials는 차세대 배터리 핵심 기술에 대한 지속적인 연구개발을 통해 미래 이차전지 시장에 대응해 나갑니다.</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="n"/>
+      <c r="H137" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Materials is working to respond to the future secondary battery market through continuous research and development of core next-generation battery technologies.</t>
+        </is>
+      </c>
       <c r="I137" s="5" t="n"/>
       <c r="J137" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -5699,7 +5716,7 @@
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
@@ -5710,15 +5727,19 @@
       <c r="E138" s="5" t="inlineStr"/>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>소듐 이온 배터리</t>
+          <t>끊임없는 R&amp;D 혁신으로 기존 배터리의 한계를 극복하고, 고성능·고안정성 소재 및 셀 기술을 선제적으로 구현해 나갑니다.</t>
         </is>
       </c>
       <c r="G138" s="7" t="n"/>
-      <c r="H138" s="8" t="n"/>
+      <c r="H138" s="8" t="inlineStr">
+        <is>
+          <t>Through ongoing R&amp;D innovation, we work to overcome the limitations of existing batteries and proactively develop high-performance, high-stability materials and cell technologies.</t>
+        </is>
+      </c>
       <c r="I138" s="5" t="n"/>
       <c r="J138" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -5733,26 +5754,30 @@
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E139" s="5" t="inlineStr"/>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="G139" s="6" t="n"/>
-      <c r="H139" s="6" t="n"/>
+          <t>A-PRO Materials는 국내외 파트너들과의 협력을 통해 최적의 이차전지 소재 솔루션을 모색하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="G139" s="7" t="n"/>
+      <c r="H139" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Materials is exploring optimal secondary battery material solutions in collaboration with partners at home and abroad.</t>
+        </is>
+      </c>
       <c r="I139" s="5" t="n"/>
       <c r="J139" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -5767,26 +5792,26 @@
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr"/>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>반도체 전지</t>
-        </is>
-      </c>
-      <c r="G140" s="7" t="n"/>
-      <c r="H140" s="8" t="n"/>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="n"/>
+      <c r="H140" s="6" t="n"/>
       <c r="I140" s="5" t="n"/>
       <c r="J140" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/b|text</t>
         </is>
       </c>
     </row>
@@ -5801,26 +5826,26 @@
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E141" s="5" t="inlineStr"/>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="G141" s="6" t="n"/>
-      <c r="H141" s="6" t="n"/>
+          <t>소듐 이온 배터리</t>
+        </is>
+      </c>
+      <c r="G141" s="7" t="n"/>
+      <c r="H141" s="8" t="n"/>
       <c r="I141" s="5" t="n"/>
       <c r="J141" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/span|text</t>
         </is>
       </c>
     </row>
@@ -5835,26 +5860,26 @@
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr"/>
       <c r="F142" s="6" t="inlineStr">
         <is>
-          <t>전고체 전지</t>
-        </is>
-      </c>
-      <c r="G142" s="7" t="n"/>
-      <c r="H142" s="8" t="n"/>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="n"/>
+      <c r="H142" s="6" t="n"/>
       <c r="I142" s="5" t="n"/>
       <c r="J142" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/b|text</t>
         </is>
       </c>
     </row>
@@ -5869,26 +5894,26 @@
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr"/>
       <c r="F143" s="6" t="inlineStr">
         <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="G143" s="6" t="n"/>
-      <c r="H143" s="6" t="n"/>
+          <t>반도체 전지</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="n"/>
+      <c r="H143" s="8" t="n"/>
       <c r="I143" s="5" t="n"/>
       <c r="J143" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[4]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/span|text</t>
         </is>
       </c>
     </row>
@@ -5903,31 +5928,133 @@
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr"/>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>무음극 전지</t>
-        </is>
-      </c>
-      <c r="G144" s="7" t="n"/>
-      <c r="H144" s="8" t="n"/>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="n"/>
+      <c r="H144" s="6" t="n"/>
       <c r="I144" s="5" t="n"/>
       <c r="J144" s="9" t="inlineStr">
         <is>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/b|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" s="5" t="n">
+        <v>144</v>
+      </c>
+      <c r="B145" s="5" t="inlineStr">
+        <is>
+          <t>04-5 에이프로머티리얼즈</t>
+        </is>
+      </c>
+      <c r="C145" s="5" t="inlineStr">
+        <is>
+          <t>번호 목록 항목</t>
+        </is>
+      </c>
+      <c r="D145" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E145" s="5" t="inlineStr"/>
+      <c r="F145" s="6" t="inlineStr">
+        <is>
+          <t>전고체 전지</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="n"/>
+      <c r="H145" s="8" t="n"/>
+      <c r="I145" s="5" t="n"/>
+      <c r="J145" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/span|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="5" t="n">
+        <v>145</v>
+      </c>
+      <c r="B146" s="5" t="inlineStr">
+        <is>
+          <t>04-5 에이프로머티리얼즈</t>
+        </is>
+      </c>
+      <c r="C146" s="5" t="inlineStr">
+        <is>
+          <t>번호 목록 번호</t>
+        </is>
+      </c>
+      <c r="D146" s="5" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E146" s="5" t="inlineStr"/>
+      <c r="F146" s="6" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="G146" s="6" t="n"/>
+      <c r="H146" s="6" t="n"/>
+      <c r="I146" s="5" t="n"/>
+      <c r="J146" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[4]/b|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="5" t="n">
+        <v>146</v>
+      </c>
+      <c r="B147" s="5" t="inlineStr">
+        <is>
+          <t>04-5 에이프로머티리얼즈</t>
+        </is>
+      </c>
+      <c r="C147" s="5" t="inlineStr">
+        <is>
+          <t>번호 목록 항목</t>
+        </is>
+      </c>
+      <c r="D147" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E147" s="5" t="inlineStr"/>
+      <c r="F147" s="6" t="inlineStr">
+        <is>
+          <t>무음극 전지</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="n"/>
+      <c r="H147" s="8" t="n"/>
+      <c r="I147" s="5" t="n"/>
+      <c r="J147" s="9" t="inlineStr">
+        <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[4]/span|text</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J144"/>
+  <autoFilter ref="A1:J147"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/content-export/04_사업영역_문구.xlsx
+++ b/content-export/04_사업영역_문구.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화합물 전력 반도체" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$J$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$J$150</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'에너지 인프라'!$A$1:$J$189</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'인공지능 플랫폼'!$A$1:$J$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'화합물 전력 반도체'!$A$1:$J$25</definedName>
@@ -527,7 +527,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 404 줄입니다.</t>
+          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 407 줄입니다.</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J147"/>
+  <dimension ref="A1:J150"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3302,7 +3302,7 @@
       </c>
       <c r="C71" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
@@ -3313,19 +3313,19 @@
       <c r="E71" s="5" t="inlineStr"/>
       <c r="F71" s="6" t="inlineStr">
         <is>
-          <t>성능 평가 및 신뢰성 검증 : 배터리를 반복적으로 충·방전하여 용량, 수명 주기, 내부 저항을 정밀 측정하고 실제 사용 환경을 완벽히 시뮬레이션하여 연구 개발 및 제조 단계에서 발생할 수 있는 열화 현상과 안전 문제를 사전에 빈틈없이 검출합니다.</t>
+          <t>성능 평가 및 신뢰성 검증</t>
         </is>
       </c>
       <c r="G71" s="7" t="n"/>
       <c r="H71" s="8" t="inlineStr">
         <is>
-          <t>Performance Evaluation &amp; Reliability Validation: Precisely measures capacity, cycle life, and internal resistance through repetitive charge-discharge cycles. By seamlessly simulating real-world conditions, it proactively detects degradation and safety risks across both R&amp;D and production stages.</t>
+          <t>Performance Evaluation &amp; Reliability Validation</t>
         </is>
       </c>
       <c r="I71" s="5" t="n"/>
       <c r="J71" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/ul/li[1]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3340,7 +3340,7 @@
       </c>
       <c r="C72" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D72" s="5" t="inlineStr">
@@ -3351,20 +3351,19 @@
       <c r="E72" s="5" t="inlineStr"/>
       <c r="F72" s="6" t="inlineStr">
         <is>
-          <t>양방향 전력 시스템 : 전류 공급(충전)과 흡수(방전)가 모두 가능한 양방향 전력 시스템을 기반으로 안정적인 테스트 환경을 제공합니다.</t>
+          <t>배터리를 반복적으로 충·방전하여 용량, 수명 주기, 내부 저항을 정밀 측정하고 실제 사용 환경을 완벽히 시뮬레이션하여 연구 개발 및 제조 단계에서 발생할 수 있는 열화 현상과 안전 문제를 사전에 빈틈없이 검출합니다.</t>
         </is>
       </c>
       <c r="G72" s="7" t="n"/>
       <c r="H72" s="8" t="inlineStr">
         <is>
-          <t xml:space="preserve">Bidirectional Power System: Provides an exceptionally stable testing environment powered by a bidirectional architecture capable of both supplying (charging) and sinking (discharging) electrical current.
-</t>
+          <t>Precisely measures capacity, cycle life, and internal resistance through repetitive charge-discharge cycles. By seamlessly simulating real-world conditions, it proactively detects degradation and safety risks across both R&amp;D and production stages.</t>
         </is>
       </c>
       <c r="I72" s="5" t="n"/>
       <c r="J72" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[4]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/ul/li[1]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3379,7 +3378,7 @@
       </c>
       <c r="C73" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D73" s="5" t="inlineStr">
@@ -3390,19 +3389,19 @@
       <c r="E73" s="5" t="inlineStr"/>
       <c r="F73" s="6" t="inlineStr">
         <is>
-          <t>친환경 에너지 회생 기술 : 방전 시 버려지는 에너지를 회수하여 전력망으로 되돌려주는 기술을 활용합니다. 이는 전력 낭비를 획기적으로 줄이고 냉각 부하를 저감하여 경제적이고 친환경적인 생산 환경을 완성합니다.</t>
+          <t>양방향 전력 시스템</t>
         </is>
       </c>
       <c r="G73" s="7" t="n"/>
       <c r="H73" s="8" t="inlineStr">
         <is>
-          <t>Eco-Friendly Energy Regeneration: Captures surplus energy released during discharge and feeds it back into the power grid. This drastically cuts power consumption and minimizes cooling loads, delivering an economical and sustainable manufacturing environment.</t>
+          <t>Bidirectional Power System</t>
         </is>
       </c>
       <c r="I73" s="5" t="n"/>
       <c r="J73" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/div/div/p[5]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/ul/li[2]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3412,12 +3411,12 @@
       </c>
       <c r="B74" s="5" t="inlineStr">
         <is>
-          <t>03-1 자동화 설비</t>
+          <t>02-1 Cycler(Cell&amp;Module)</t>
         </is>
       </c>
       <c r="C74" s="5" t="inlineStr">
         <is>
-          <t>작은 제목</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D74" s="5" t="inlineStr">
@@ -3428,19 +3427,19 @@
       <c r="E74" s="5" t="inlineStr"/>
       <c r="F74" s="6" t="inlineStr">
         <is>
-          <t>스마트 자동화 공정 솔루션</t>
+          <t>전류 공급(충전)과 흡수(방전)가 모두 가능한 양방향 전력 시스템을 기반으로 안정적인 테스트 환경을 제공합니다.</t>
         </is>
       </c>
       <c r="G74" s="7" t="n"/>
       <c r="H74" s="8" t="inlineStr">
         <is>
-          <t>Smart Automated Process Solutions</t>
+          <t>Provides an exceptionally stable testing environment powered by a bidirectional architecture capable of both supplying (charging) and sinking (discharging) electrical current.</t>
         </is>
       </c>
       <c r="I74" s="5" t="n"/>
       <c r="J74" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/ul/li[2]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3450,12 +3449,12 @@
       </c>
       <c r="B75" s="5" t="inlineStr">
         <is>
-          <t>03-1 자동화 설비</t>
+          <t>02-1 Cycler(Cell&amp;Module)</t>
         </is>
       </c>
       <c r="C75" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D75" s="5" t="inlineStr">
@@ -3466,19 +3465,19 @@
       <c r="E75" s="5" t="inlineStr"/>
       <c r="F75" s="6" t="inlineStr">
         <is>
-          <t>에이프로의 2차전지 활성화 설비는 최첨단 자동화 시스템을 통해 Cell 및 Module 공정의 생산 효율성을 극대화합니다.</t>
+          <t>친환경 에너지 회생 기술</t>
         </is>
       </c>
       <c r="G75" s="7" t="n"/>
       <c r="H75" s="8" t="inlineStr">
         <is>
-          <t>A-PRO's secondary battery formation equipment maximizes production efficiency across both Cell and Module processes through cutting-edge automation systems.</t>
+          <t>Eco-Friendly Energy Regeneration</t>
         </is>
       </c>
       <c r="I75" s="5" t="n"/>
       <c r="J75" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/ul/li[3]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3488,12 +3487,12 @@
       </c>
       <c r="B76" s="5" t="inlineStr">
         <is>
-          <t>03-1 자동화 설비</t>
+          <t>02-1 Cycler(Cell&amp;Module)</t>
         </is>
       </c>
       <c r="C76" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D76" s="5" t="inlineStr">
@@ -3504,19 +3503,19 @@
       <c r="E76" s="5" t="inlineStr"/>
       <c r="F76" s="6" t="inlineStr">
         <is>
-          <t>다관절 로봇, 물류 컨베이어, 스태커 크레인, AMR(자율주행로봇) 등 고성능 물류 설비를 유기적으로 연계하여, 상위 시스템(MES, FCS)에서 전달받은 실시간 공정 정보에 따라 자율적이고 정확하게 정밀 이송·투입·배출을 수행합니다.</t>
+          <t>방전 시 버려지는 에너지를 회수하여 전력망으로 되돌려주는 기술을 활용합니다. 이는 전력 낭비를 획기적으로 줄이고 냉각 부하를 저감하여 경제적이고 친환경적인 생산 환경을 완성합니다.</t>
         </is>
       </c>
       <c r="G76" s="7" t="n"/>
       <c r="H76" s="8" t="inlineStr">
         <is>
-          <t>By seamlessly integrating high-performance logistics equipment—including articulated robots, conveyors, stacker cranes, and AMRs (Autonomous Mobile Robots)—our systems autonomously execute precise transfer, loading, and unloading based on real-time process data from host systems (MES, FCS).</t>
+          <t>Captures surplus energy released during discharge and feeds it back into the power grid. This drastically cuts power consumption and minimizes cooling loads, delivering an economical and sustainable manufacturing environment.</t>
         </is>
       </c>
       <c r="I76" s="5" t="n"/>
       <c r="J76" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[3]/div/div[2]/ul/li[3]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3531,7 +3530,7 @@
       </c>
       <c r="C77" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>작은 제목</t>
         </is>
       </c>
       <c r="D77" s="5" t="inlineStr">
@@ -3542,19 +3541,19 @@
       <c r="E77" s="5" t="inlineStr"/>
       <c r="F77" s="6" t="inlineStr">
         <is>
-          <t>단순 이송을 넘어, 상위 데이터에 기반한 자율적 판단으로 주어진 업무를 완벽하게 자동 처리함으로써 인적 오차를 줄이고, 최상의 공정 안정성과 데이터 기반의 스마트 팩토리를 실현합니다.</t>
+          <t>스마트 자동화 공정 솔루션</t>
         </is>
       </c>
       <c r="G77" s="7" t="n"/>
       <c r="H77" s="8" t="inlineStr">
         <is>
-          <t>Moving beyond simple material handling, our equipment autonomously processes operations through data-driven decisions. This minimizes human error, ensures superior process stability, and realizes a truly data-centric smart factory.</t>
+          <t>Smart Automated Process Solutions</t>
         </is>
       </c>
       <c r="I77" s="5" t="n"/>
       <c r="J77" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[4]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3569,7 +3568,7 @@
       </c>
       <c r="C78" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D78" s="5" t="inlineStr">
@@ -3580,19 +3579,19 @@
       <c r="E78" s="5" t="inlineStr"/>
       <c r="F78" s="6" t="inlineStr">
         <is>
-          <t>스마트 설비 제어</t>
+          <t>에이프로의 2차전지 활성화 설비는 최첨단 자동화 시스템을 통해 Cell 및 Module 공정의 생산 효율성을 극대화합니다.</t>
         </is>
       </c>
       <c r="G78" s="7" t="n"/>
       <c r="H78" s="8" t="inlineStr">
         <is>
-          <t>Smart Equipment Control</t>
+          <t>A-PRO's secondary battery formation equipment maximizes production efficiency across both Cell and Module processes through cutting-edge automation systems.</t>
         </is>
       </c>
       <c r="I78" s="5" t="n"/>
       <c r="J78" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[1]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3607,7 +3606,7 @@
       </c>
       <c r="C79" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D79" s="5" t="inlineStr">
@@ -3618,19 +3617,19 @@
       <c r="E79" s="5" t="inlineStr"/>
       <c r="F79" s="6" t="inlineStr">
         <is>
-          <t>충방전기, 디개싱, 에이징 룸 등 공정 내 모든 하드웨어를 실시간 직접 제어합니다.</t>
+          <t>다관절 로봇, 물류 컨베이어, 스태커 크레인, AMR(자율주행로봇) 등 고성능 물류 설비를 유기적으로 연계하여, 상위 시스템(MES, FCS)에서 전달받은 실시간 공정 정보에 따라 자율적이고 정확하게 정밀 이송·투입·배출을 수행합니다.</t>
         </is>
       </c>
       <c r="G79" s="7" t="n"/>
       <c r="H79" s="8" t="inlineStr">
         <is>
-          <t>Direct, real-time hardware control of all production lines, including cyclers, degassing units, and aging rooms.</t>
+          <t>By seamlessly integrating high-performance logistics equipment—including articulated robots, conveyors, stacker cranes, and AMRs (Autonomous Mobile Robots)—our systems autonomously execute precise transfer, loading, and unloading based on real-time process data from host systems (MES, FCS).</t>
         </is>
       </c>
       <c r="I79" s="5" t="n"/>
       <c r="J79" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[1]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -3645,7 +3644,7 @@
       </c>
       <c r="C80" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D80" s="5" t="inlineStr">
@@ -3656,19 +3655,19 @@
       <c r="E80" s="5" t="inlineStr"/>
       <c r="F80" s="6" t="inlineStr">
         <is>
-          <t>실시간 데이터 수집</t>
+          <t>단순 이송을 넘어, 상위 데이터에 기반한 자율적 판단으로 주어진 업무를 완벽하게 자동 처리함으로써 인적 오차를 줄이고, 최상의 공정 안정성과 데이터 기반의 스마트 팩토리를 실현합니다.</t>
         </is>
       </c>
       <c r="G80" s="7" t="n"/>
       <c r="H80" s="8" t="inlineStr">
         <is>
-          <t>Real-Time Data Acquisition</t>
+          <t>Moving beyond simple material handling, our equipment autonomously processes operations through data-driven decisions. This minimizes human error, ensures superior process stability, and realizes a truly data-centric smart factory.</t>
         </is>
       </c>
       <c r="I80" s="5" t="n"/>
       <c r="J80" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[2]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/div/div/p[4]|text</t>
         </is>
       </c>
     </row>
@@ -3683,7 +3682,7 @@
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3694,19 +3693,19 @@
       <c r="E81" s="5" t="inlineStr"/>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>미세한 온도·압력·전압·전류 데이터를 정밀 측정하여 완벽한 품질 추적성을 확보합니다.</t>
+          <t>스마트 설비 제어</t>
         </is>
       </c>
       <c r="G81" s="7" t="n"/>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>Precision monitoring of voltage, current, temperature, and pressure for seamless quality traceability.</t>
+          <t>Smart Equipment Control</t>
         </is>
       </c>
       <c r="I81" s="5" t="n"/>
       <c r="J81" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[2]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[1]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3721,7 +3720,7 @@
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -3732,19 +3731,19 @@
       <c r="E82" s="5" t="inlineStr"/>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>지능형 안전 인터록</t>
+          <t>충방전기, 디개싱, 에이징 룸 등 공정 내 모든 하드웨어를 실시간 직접 제어합니다.</t>
         </is>
       </c>
       <c r="G82" s="7" t="n"/>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>Intelligent Safety Interlock</t>
+          <t>Direct, real-time hardware control of all production lines, including cyclers, degassing units, and aging rooms.</t>
         </is>
       </c>
       <c r="I82" s="5" t="n"/>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[3]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[1]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3759,7 +3758,7 @@
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -3770,19 +3769,19 @@
       <c r="E83" s="5" t="inlineStr"/>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>가스 누출, 과전압 등 이상 징후 감지 시 설비를 즉각 정지시켜 사고를 원천 차단합니다.</t>
+          <t>실시간 데이터 수집</t>
         </is>
       </c>
       <c r="G83" s="7" t="n"/>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>Advanced emergency system that instantly halts operations upon detecting hazards like gas leaks or overvoltage.</t>
+          <t>Real-Time Data Acquisition</t>
         </is>
       </c>
       <c r="I83" s="5" t="n"/>
       <c r="J83" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[3]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[2]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3797,7 +3796,7 @@
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -3808,19 +3807,19 @@
       <c r="E84" s="5" t="inlineStr"/>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>유연한 상위 연동</t>
+          <t>미세한 온도·압력·전압·전류 데이터를 정밀 측정하여 완벽한 품질 추적성을 확보합니다.</t>
         </is>
       </c>
       <c r="G84" s="7" t="n"/>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>Seamless Integration</t>
+          <t>Precision monitoring of voltage, current, temperature, and pressure for seamless quality traceability.</t>
         </is>
       </c>
       <c r="I84" s="5" t="n"/>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[4]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[2]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3835,7 +3834,7 @@
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -3846,19 +3845,19 @@
       <c r="E85" s="5" t="inlineStr"/>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>PC 및 MES와의 고속 통신으로 공정 데이터를 실시간 전송하고 레시피 명령을 완벽히 수행합니다.</t>
+          <t>지능형 안전 인터록</t>
         </is>
       </c>
       <c r="G85" s="7" t="n"/>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>High-speed communication with upper-level systems (PCs/MES) to transmit process data and execute recipe commands flawlessly.</t>
+          <t>Intelligent Safety Interlock</t>
         </is>
       </c>
       <c r="I85" s="5" t="n"/>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[4]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[3]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3868,12 +3867,12 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>04-1 탄소 나노 튜브</t>
+          <t>03-1 자동화 설비</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -3884,19 +3883,19 @@
       <c r="E86" s="5" t="inlineStr"/>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials의 글로벌 소싱 네트워크를 활용하여 고품질의 탄소나노튜브(CNT) 소재를 안정적으로 공급합니다.</t>
+          <t>가스 누출, 과전압 등 이상 징후 감지 시 설비를 즉각 정지시켜 사고를 원천 차단합니다.</t>
         </is>
       </c>
       <c r="G86" s="7" t="n"/>
       <c r="H86" s="8" t="inlineStr">
         <is>
-          <t>We provide a stable supply of high-quality carbon nanotube (CNT) materials through A-PRO Materials' global sourcing network.</t>
+          <t>Advanced emergency system that instantly halts operations upon detecting hazards like gas leaks or overvoltage.</t>
         </is>
       </c>
       <c r="I86" s="5" t="n"/>
       <c r="J86" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[1]/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[3]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3906,12 +3905,12 @@
       </c>
       <c r="B87" s="5" t="inlineStr">
         <is>
-          <t>04-1 탄소 나노 튜브</t>
+          <t>03-1 자동화 설비</t>
         </is>
       </c>
       <c r="C87" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
@@ -3922,19 +3921,19 @@
       <c r="E87" s="5" t="inlineStr"/>
       <c r="F87" s="6" t="inlineStr">
         <is>
-          <t>엄격한 품질 검증을 거친 CNT 소재를 통해 고객사의 배터리 에너지 밀도 향상과 고속 충전 성능 구현을 지원합니다.</t>
+          <t>유연한 상위 연동</t>
         </is>
       </c>
       <c r="G87" s="7" t="n"/>
       <c r="H87" s="8" t="inlineStr">
         <is>
-          <t>Through rigorously quality-verified CNT materials, we support our customers in enhancing battery energy density and enabling high-speed charging performance.</t>
+          <t>Seamless Integration</t>
         </is>
       </c>
       <c r="I87" s="5" t="n"/>
       <c r="J87" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[1]/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[4]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3944,12 +3943,12 @@
       </c>
       <c r="B88" s="5" t="inlineStr">
         <is>
-          <t>04-1 탄소 나노 튜브</t>
+          <t>03-1 자동화 설비</t>
         </is>
       </c>
       <c r="C88" s="5" t="inlineStr">
         <is>
-          <t>제품 단추 이름</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
@@ -3960,19 +3959,19 @@
       <c r="E88" s="5" t="inlineStr"/>
       <c r="F88" s="6" t="inlineStr">
         <is>
-          <t>SW/FW-CNT Powder</t>
+          <t>PC 및 MES와의 고속 통신으로 공정 데이터를 실시간 전송하고 레시피 명령을 완벽히 수행합니다.</t>
         </is>
       </c>
       <c r="G88" s="7" t="n"/>
       <c r="H88" s="8" t="inlineStr">
         <is>
-          <t>SW/FW-CNT Powder</t>
+          <t>High-speed communication with upper-level systems (PCs/MES) to transmit process data and execute recipe commands flawlessly.</t>
         </is>
       </c>
       <c r="I88" s="5" t="n"/>
       <c r="J88" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[1]/span[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[4]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3987,7 +3986,7 @@
       </c>
       <c r="C89" s="5" t="inlineStr">
         <is>
-          <t>제품 단추 이름</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
@@ -3998,19 +3997,19 @@
       <c r="E89" s="5" t="inlineStr"/>
       <c r="F89" s="6" t="inlineStr">
         <is>
-          <t>SW/FW-CNT Slurry</t>
+          <t>A-PRO Materials의 글로벌 소싱 네트워크를 활용하여 고품질의 탄소나노튜브(CNT) 소재를 안정적으로 공급합니다.</t>
         </is>
       </c>
       <c r="G89" s="7" t="n"/>
       <c r="H89" s="8" t="inlineStr">
         <is>
-          <t>SW/FW-CNT Slurry</t>
+          <t>We provide a stable supply of high-quality carbon nanotube (CNT) materials through A-PRO Materials' global sourcing network.</t>
         </is>
       </c>
       <c r="I89" s="5" t="n"/>
       <c r="J89" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[2]/span[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[1]/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4025,7 +4024,7 @@
       </c>
       <c r="C90" s="5" t="inlineStr">
         <is>
-          <t>제품 단추 이름</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
@@ -4036,19 +4035,19 @@
       <c r="E90" s="5" t="inlineStr"/>
       <c r="F90" s="6" t="inlineStr">
         <is>
-          <t>Carbon Black</t>
+          <t>엄격한 품질 검증을 거친 CNT 소재를 통해 고객사의 배터리 에너지 밀도 향상과 고속 충전 성능 구현을 지원합니다.</t>
         </is>
       </c>
       <c r="G90" s="7" t="n"/>
       <c r="H90" s="8" t="inlineStr">
         <is>
-          <t>Carbon Black</t>
+          <t>Through rigorously quality-verified CNT materials, we support our customers in enhancing battery energy density and enabling high-speed charging performance.</t>
         </is>
       </c>
       <c r="I90" s="5" t="n"/>
       <c r="J90" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[3]/span[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[1]/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4058,12 +4057,12 @@
       </c>
       <c r="B91" s="5" t="inlineStr">
         <is>
-          <t>04-1 탄소 나노 튜브 · 04-2 LiFSI 전해염 · 04-3 HNBR 바인더 · 04-4 파우치셀 제조</t>
+          <t>04-1 탄소 나노 튜브</t>
         </is>
       </c>
       <c r="C91" s="5" t="inlineStr">
         <is>
-          <t>문의 단추</t>
+          <t>제품 단추 이름</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
@@ -4074,17 +4073,131 @@
       <c r="E91" s="5" t="inlineStr"/>
       <c r="F91" s="6" t="inlineStr">
         <is>
+          <t>SW/FW-CNT Powder</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="n"/>
+      <c r="H91" s="8" t="inlineStr">
+        <is>
+          <t>SW/FW-CNT Powder</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="n"/>
+      <c r="J91" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[1]/span[2]|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>04-1 탄소 나노 튜브</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>제품 단추 이름</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr"/>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>SW/FW-CNT Slurry</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="n"/>
+      <c r="H92" s="8" t="inlineStr">
+        <is>
+          <t>SW/FW-CNT Slurry</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="n"/>
+      <c r="J92" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[2]/span[2]|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>04-1 탄소 나노 튜브</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>제품 단추 이름</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr"/>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>Carbon Black</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="n"/>
+      <c r="H93" s="8" t="inlineStr">
+        <is>
+          <t>Carbon Black</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="n"/>
+      <c r="J93" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[3]/span[2]|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>04-1 탄소 나노 튜브 · 04-2 LiFSI 전해염 · 04-3 HNBR 바인더 · 04-4 파우치셀 제조</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>문의 단추</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr"/>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
           <t>문의하기</t>
         </is>
       </c>
-      <c r="G91" s="7" t="n"/>
-      <c r="H91" s="8" t="n"/>
-      <c r="I91" s="5" t="inlineStr">
+      <c r="G94" s="7" t="n"/>
+      <c r="H94" s="8" t="n"/>
+      <c r="I94" s="5" t="inlineStr">
         <is>
           <t>같은 문구 4 곳 — 한 줄로 합침</t>
         </is>
       </c>
-      <c r="J91" s="9" t="inlineStr">
+      <c r="J94" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/a|text
 /html/body/div[8]/div[3]/section[6]/div/div[2]/a|text
@@ -4093,116 +4206,6 @@
         </is>
       </c>
     </row>
-    <row r="92">
-      <c r="A92" s="5" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>04-2 LiFSI 전해염</t>
-        </is>
-      </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>본문</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="inlineStr"/>
-      <c r="F92" s="6" t="inlineStr">
-        <is>
-          <t>A-PRO Materials는 엄선된 공급망을 통해 고순도 LiFSI 전해염 소재를 안정적으로 공급합니다.</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="n"/>
-      <c r="H92" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Materials provides a stable supply of high-purity LiFSI electrolyte salt through a carefully selected global supply network.</t>
-        </is>
-      </c>
-      <c r="I92" s="5" t="n"/>
-      <c r="J92" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[1]|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>04-2 LiFSI 전해염</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>본문</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr"/>
-      <c r="F93" s="6" t="inlineStr">
-        <is>
-          <t>우수한 화학적 안정성을 바탕으로 고객사 배터리의 수명 연장과 고온 안정성 및 출력 향상을 지원합니다.</t>
-        </is>
-      </c>
-      <c r="G93" s="7" t="n"/>
-      <c r="H93" s="8" t="inlineStr">
-        <is>
-          <t>Based on superior chemical stability, we support extended battery life, high-temperature stability, and improved output performance for our customers.</t>
-        </is>
-      </c>
-      <c r="I93" s="5" t="n"/>
-      <c r="J93" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[2]|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>04-2 LiFSI 전해염</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>제품 이름</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="inlineStr"/>
-      <c r="F94" s="6" t="inlineStr">
-        <is>
-          <t>LiFSI 전해질</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="n"/>
-      <c r="H94" s="8" t="n"/>
-      <c r="I94" s="5" t="n"/>
-      <c r="J94" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/div/p[1]|text</t>
-        </is>
-      </c>
-    </row>
     <row r="95">
       <c r="A95" s="5" t="n">
         <v>94</v>
@@ -4214,7 +4217,7 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>제품 설명</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -4225,15 +4228,19 @@
       <c r="E95" s="5" t="inlineStr"/>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>고출력 · 수명연장용 차세대 전해염</t>
+          <t>A-PRO Materials는 엄선된 공급망을 통해 고순도 LiFSI 전해염 소재를 안정적으로 공급합니다.</t>
         </is>
       </c>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="8" t="n"/>
+      <c r="H95" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Materials provides a stable supply of high-purity LiFSI electrolyte salt through a carefully selected global supply network.</t>
+        </is>
+      </c>
       <c r="I95" s="5" t="n"/>
       <c r="J95" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4248,7 +4255,7 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>제품 수치</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
@@ -4259,15 +4266,19 @@
       <c r="E96" s="5" t="inlineStr"/>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>비표면적 ≥300~1,000 m²/g</t>
+          <t>우수한 화학적 안정성을 바탕으로 고객사 배터리의 수명 연장과 고온 안정성 및 출력 향상을 지원합니다.</t>
         </is>
       </c>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="8" t="n"/>
+      <c r="H96" s="8" t="inlineStr">
+        <is>
+          <t>Based on superior chemical stability, we support extended battery life, high-temperature stability, and improved output performance for our customers.</t>
+        </is>
+      </c>
       <c r="I96" s="5" t="n"/>
       <c r="J96" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4282,18 +4293,18 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>제품 사진 대체글</t>
+          <t>제품 이름</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
         <is>
-          <t>대체글</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E97" s="5" t="inlineStr"/>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>LiFSI 전해염 입자 표면의 주사전자현미경 사진 — 크고 작은 구멍이 촘촘한 다공성 구조</t>
+          <t>LiFSI 전해질</t>
         </is>
       </c>
       <c r="G97" s="7" t="n"/>
@@ -4301,7 +4312,7 @@
       <c r="I97" s="5" t="n"/>
       <c r="J97" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/span/img|alt</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4316,7 +4327,7 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>제품 이름</t>
+          <t>제품 설명</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -4327,7 +4338,7 @@
       <c r="E98" s="5" t="inlineStr"/>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>산화물계 전해질</t>
+          <t>고출력 · 수명연장용 차세대 전해염</t>
         </is>
       </c>
       <c r="G98" s="7" t="n"/>
@@ -4335,7 +4346,7 @@
       <c r="I98" s="5" t="n"/>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4350,7 +4361,7 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>제품 설명</t>
+          <t>제품 수치</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
@@ -4361,7 +4372,7 @@
       <c r="E99" s="5" t="inlineStr"/>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>산화물계 LLZMO · LATP</t>
+          <t>비표면적 ≥300~1,000 m²/g</t>
         </is>
       </c>
       <c r="G99" s="7" t="n"/>
@@ -4369,7 +4380,7 @@
       <c r="I99" s="5" t="n"/>
       <c r="J99" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -4384,18 +4395,18 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>제품 수치</t>
+          <t>제품 사진 대체글</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>대체글</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr"/>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>이온 전도도 0.2~1.0 mS/cm</t>
+          <t>LiFSI 전해염 입자 표면의 주사전자현미경 사진 — 크고 작은 구멍이 촘촘한 다공성 구조</t>
         </is>
       </c>
       <c r="G100" s="7" t="n"/>
@@ -4403,7 +4414,7 @@
       <c r="I100" s="5" t="n"/>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/span/img|alt</t>
         </is>
       </c>
     </row>
@@ -4418,18 +4429,18 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>제품 사진 대체글</t>
+          <t>제품 이름</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
         <is>
-          <t>대체글</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E101" s="5" t="inlineStr"/>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>산화물계 전해질 모식도 — 왼쪽은 결정 격자, 오른쪽은 고체 전해질 막을 가로지르는 이온 이동</t>
+          <t>산화물계 전해질</t>
         </is>
       </c>
       <c r="G101" s="7" t="n"/>
@@ -4437,7 +4448,7 @@
       <c r="I101" s="5" t="n"/>
       <c r="J101" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/span/img|alt</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4452,7 +4463,7 @@
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>제품 설명</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
@@ -4463,19 +4474,15 @@
       <c r="E102" s="5" t="inlineStr"/>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>High Purity</t>
+          <t>산화물계 LLZMO · LATP</t>
         </is>
       </c>
       <c r="G102" s="7" t="n"/>
-      <c r="H102" s="8" t="inlineStr">
-        <is>
-          <t>High Purity</t>
-        </is>
-      </c>
+      <c r="H102" s="8" t="n"/>
       <c r="I102" s="5" t="n"/>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[1]/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4490,7 +4497,7 @@
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>제품 수치</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -4501,19 +4508,15 @@
       <c r="E103" s="5" t="inlineStr"/>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>Thermal Stability</t>
+          <t>이온 전도도 0.2~1.0 mS/cm</t>
         </is>
       </c>
       <c r="G103" s="7" t="n"/>
-      <c r="H103" s="8" t="inlineStr">
-        <is>
-          <t>Thermal Stability</t>
-        </is>
-      </c>
+      <c r="H103" s="8" t="n"/>
       <c r="I103" s="5" t="n"/>
       <c r="J103" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[2]/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -4528,30 +4531,26 @@
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>제품 사진 대체글</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>대체글</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr"/>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>Long Cycle Life</t>
+          <t>산화물계 전해질 모식도 — 왼쪽은 결정 격자, 오른쪽은 고체 전해질 막을 가로지르는 이온 이동</t>
         </is>
       </c>
       <c r="G104" s="7" t="n"/>
-      <c r="H104" s="8" t="inlineStr">
-        <is>
-          <t>Long Cycle Life</t>
-        </is>
-      </c>
+      <c r="H104" s="8" t="n"/>
       <c r="I104" s="5" t="n"/>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[3]/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/span/img|alt</t>
         </is>
       </c>
     </row>
@@ -4577,19 +4576,19 @@
       <c r="E105" s="5" t="inlineStr"/>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>Fast Charging</t>
+          <t>High Purity</t>
         </is>
       </c>
       <c r="G105" s="7" t="n"/>
       <c r="H105" s="8" t="inlineStr">
         <is>
-          <t>Fast Charging</t>
+          <t>High Purity</t>
         </is>
       </c>
       <c r="I105" s="5" t="n"/>
       <c r="J105" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[4]/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[1]/p|text</t>
         </is>
       </c>
     </row>
@@ -4615,19 +4614,19 @@
       <c r="E106" s="5" t="inlineStr"/>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>Low Resistance &amp; Low Viscosity</t>
+          <t>Thermal Stability</t>
         </is>
       </c>
       <c r="G106" s="7" t="n"/>
       <c r="H106" s="8" t="inlineStr">
         <is>
-          <t>Low Resistance &amp; Low Viscosity</t>
+          <t>Thermal Stability</t>
         </is>
       </c>
       <c r="I106" s="5" t="n"/>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[5]/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[2]/p|text</t>
         </is>
       </c>
     </row>
@@ -4637,12 +4636,12 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-2 LiFSI 전해염</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
@@ -4653,19 +4652,19 @@
       <c r="E107" s="5" t="inlineStr"/>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>PVDF 바인더의 일부 대체 가능성을 검토할 수 있는 HNBR 바인더 소재입니다.</t>
+          <t>Long Cycle Life</t>
         </is>
       </c>
       <c r="G107" s="7" t="n"/>
       <c r="H107" s="8" t="inlineStr">
         <is>
-          <t>HNBR is a binder material that can be evaluated as a partial alternative to PVDF binders.</t>
+          <t>Long Cycle Life</t>
         </is>
       </c>
       <c r="I107" s="5" t="n"/>
       <c r="J107" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[3]/p|text</t>
         </is>
       </c>
     </row>
@@ -4675,12 +4674,12 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-2 LiFSI 전해염</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
@@ -4691,19 +4690,19 @@
       <c r="E108" s="5" t="inlineStr"/>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>우수한 결합력과 유연성, 전극 저항 감소 효과를 통해 배터리의 고율 충·방전 성능과 안정성 향상에 기여할 수 있습니다.</t>
+          <t>Fast Charging</t>
         </is>
       </c>
       <c r="G108" s="7" t="n"/>
       <c r="H108" s="8" t="inlineStr">
         <is>
-          <t>With excellent bonding strength, flexibility, and reduced electrode resistance, it can contribute to improved high-rate charge/discharge performance and stability.</t>
+          <t>Fast Charging</t>
         </is>
       </c>
       <c r="I108" s="5" t="n"/>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[4]/p|text</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4712,12 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-2 LiFSI 전해염</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D109" s="5" t="inlineStr">
@@ -4729,15 +4728,19 @@
       <c r="E109" s="5" t="inlineStr"/>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>CNT 분산용 고성능 고무 바인더</t>
+          <t>Low Resistance &amp; Low Viscosity</t>
         </is>
       </c>
       <c r="G109" s="7" t="n"/>
-      <c r="H109" s="8" t="n"/>
+      <c r="H109" s="8" t="inlineStr">
+        <is>
+          <t>Low Resistance &amp; Low Viscosity</t>
+        </is>
+      </c>
       <c r="I109" s="5" t="n"/>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[1]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[5]/p|text</t>
         </is>
       </c>
     </row>
@@ -4752,7 +4755,7 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>표 값</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
@@ -4763,15 +4766,19 @@
       <c r="E110" s="5" t="inlineStr"/>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>포화도 99.6%</t>
+          <t>PVDF 바인더의 일부 대체 가능성을 검토할 수 있는 HNBR 바인더 소재입니다.</t>
         </is>
       </c>
       <c r="G110" s="7" t="n"/>
-      <c r="H110" s="8" t="n"/>
+      <c r="H110" s="8" t="inlineStr">
+        <is>
+          <t>HNBR is a binder material that can be evaluated as a partial alternative to PVDF binders.</t>
+        </is>
+      </c>
       <c r="I110" s="5" t="n"/>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[1]/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4786,7 +4793,7 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
@@ -4797,15 +4804,19 @@
       <c r="E111" s="5" t="inlineStr"/>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>HNBR 라텍스</t>
+          <t>우수한 결합력과 유연성, 전극 저항 감소 효과를 통해 배터리의 고율 충·방전 성능과 안정성 향상에 기여할 수 있습니다.</t>
         </is>
       </c>
       <c r="G111" s="7" t="n"/>
-      <c r="H111" s="8" t="n"/>
+      <c r="H111" s="8" t="inlineStr">
+        <is>
+          <t>With excellent bonding strength, flexibility, and reduced electrode resistance, it can contribute to improved high-rate charge/discharge performance and stability.</t>
+        </is>
+      </c>
       <c r="I111" s="5" t="n"/>
       <c r="J111" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[2]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4831,7 +4842,7 @@
       <c r="E112" s="5" t="inlineStr"/>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>NMP계 고분산 액상 바인더</t>
+          <t>CNT 분산용 고성능 고무 바인더</t>
         </is>
       </c>
       <c r="G112" s="7" t="n"/>
@@ -4839,7 +4850,7 @@
       <c r="I112" s="5" t="n"/>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[2]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[1]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4865,7 +4876,7 @@
       <c r="E113" s="5" t="inlineStr"/>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>고형분 8~10%</t>
+          <t>포화도 99.6%</t>
         </is>
       </c>
       <c r="G113" s="7" t="n"/>
@@ -4873,7 +4884,7 @@
       <c r="I113" s="5" t="n"/>
       <c r="J113" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[2]/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[1]/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -4899,7 +4910,7 @@
       <c r="E114" s="5" t="inlineStr"/>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>PVDF 대체</t>
+          <t>HNBR 라텍스</t>
         </is>
       </c>
       <c r="G114" s="7" t="n"/>
@@ -4907,7 +4918,7 @@
       <c r="I114" s="5" t="n"/>
       <c r="J114" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[1]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[2]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4933,7 +4944,7 @@
       <c r="E115" s="5" t="inlineStr"/>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>기존 불소계 바인더의 5~15% 이상을 친환경 HNBR로 대체.</t>
+          <t>NMP계 고분산 액상 바인더</t>
         </is>
       </c>
       <c r="G115" s="7" t="n"/>
@@ -4941,7 +4952,7 @@
       <c r="I115" s="5" t="n"/>
       <c r="J115" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[1]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[2]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4956,7 +4967,7 @@
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>표 값</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -4967,7 +4978,7 @@
       <c r="E116" s="5" t="inlineStr"/>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>고율 충방전 특성</t>
+          <t>고형분 8~10%</t>
         </is>
       </c>
       <c r="G116" s="7" t="n"/>
@@ -4975,7 +4986,7 @@
       <c r="I116" s="5" t="n"/>
       <c r="J116" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[2]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[2]/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -4990,7 +5001,7 @@
       </c>
       <c r="C117" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D117" s="5" t="inlineStr">
@@ -5001,7 +5012,7 @@
       <c r="E117" s="5" t="inlineStr"/>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>10C 고속 충전 조건에서도 우수한 용량 유지.</t>
+          <t>PVDF 대체</t>
         </is>
       </c>
       <c r="G117" s="7" t="n"/>
@@ -5009,7 +5020,7 @@
       <c r="I117" s="5" t="n"/>
       <c r="J117" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[2]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[1]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -5024,7 +5035,7 @@
       </c>
       <c r="C118" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D118" s="5" t="inlineStr">
@@ -5035,7 +5046,7 @@
       <c r="E118" s="5" t="inlineStr"/>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>내부 저항 감소</t>
+          <t>기존 불소계 바인더의 5~15% 이상을 친환경 HNBR로 대체.</t>
         </is>
       </c>
       <c r="G118" s="7" t="n"/>
@@ -5043,7 +5054,7 @@
       <c r="I118" s="5" t="n"/>
       <c r="J118" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[3]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[1]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -5058,7 +5069,7 @@
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
@@ -5069,7 +5080,7 @@
       <c r="E119" s="5" t="inlineStr"/>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>젖음성 개선으로 이온 전달 및 계면 저항 최소화.</t>
+          <t>고율 충방전 특성</t>
         </is>
       </c>
       <c r="G119" s="7" t="n"/>
@@ -5077,7 +5088,7 @@
       <c r="I119" s="5" t="n"/>
       <c r="J119" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[3]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[2]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -5092,7 +5103,7 @@
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
@@ -5103,7 +5114,7 @@
       <c r="E120" s="5" t="inlineStr"/>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>높은 강도 및 유연성</t>
+          <t>10C 고속 충전 조건에서도 우수한 용량 유지.</t>
         </is>
       </c>
       <c r="G120" s="7" t="n"/>
@@ -5111,7 +5122,7 @@
       <c r="I120" s="5" t="n"/>
       <c r="J120" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[4]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[2]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -5126,7 +5137,7 @@
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
@@ -5137,7 +5148,7 @@
       <c r="E121" s="5" t="inlineStr"/>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>전극 활물질 부피 변화 흡수, 탈락 방지.</t>
+          <t>내부 저항 감소</t>
         </is>
       </c>
       <c r="G121" s="7" t="n"/>
@@ -5145,7 +5156,7 @@
       <c r="I121" s="5" t="n"/>
       <c r="J121" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[4]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[3]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -5160,7 +5171,7 @@
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
@@ -5171,7 +5182,7 @@
       <c r="E122" s="5" t="inlineStr"/>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>SWCNT 분산 최적화</t>
+          <t>젖음성 개선으로 이온 전달 및 계면 저항 최소화.</t>
         </is>
       </c>
       <c r="G122" s="7" t="n"/>
@@ -5179,7 +5190,7 @@
       <c r="I122" s="5" t="n"/>
       <c r="J122" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[5]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[3]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -5194,7 +5205,7 @@
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
@@ -5205,7 +5216,7 @@
       <c r="E123" s="5" t="inlineStr"/>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>단일벽 탄소나노튜브의 응집 해소, 점도 감소.</t>
+          <t>높은 강도 및 유연성</t>
         </is>
       </c>
       <c r="G123" s="7" t="n"/>
@@ -5213,7 +5224,7 @@
       <c r="I123" s="5" t="n"/>
       <c r="J123" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[5]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[4]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -5223,12 +5234,12 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>04-4 파우치셀 제조</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
@@ -5239,19 +5250,15 @@
       <c r="E124" s="5" t="inlineStr"/>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials는 Lab-scale 파우치셀 제작 및 소재 적용성 검증 서비스를 제공합니다.</t>
+          <t>전극 활물질 부피 변화 흡수, 탈락 방지.</t>
         </is>
       </c>
       <c r="G124" s="7" t="n"/>
-      <c r="H124" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Materials provides lab-scale pouch cell fabrication and material validation services.</t>
-        </is>
-      </c>
+      <c r="H124" s="8" t="n"/>
       <c r="I124" s="5" t="n"/>
       <c r="J124" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[4]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -5261,12 +5268,12 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>04-4 파우치셀 제조</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
@@ -5277,19 +5284,15 @@
       <c r="E125" s="5" t="inlineStr"/>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>셀 설계부터 조립 공정, 품질 평가까지 통합 프로세스를 통해 고객사의 신소재 적용 가능성을 사전 검증합니다.</t>
+          <t>SWCNT 분산 최적화</t>
         </is>
       </c>
       <c r="G125" s="7" t="n"/>
-      <c r="H125" s="8" t="inlineStr">
-        <is>
-          <t>Through an integrated process encompassing cell design, assembly, and quality evaluation, we help our clients pre-validate the applicability of new materials.</t>
-        </is>
-      </c>
+      <c r="H125" s="8" t="n"/>
       <c r="I125" s="5" t="n"/>
       <c r="J125" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[5]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -5299,31 +5302,31 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>04-4 파우치셀 제조</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E126" s="5" t="inlineStr"/>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="G126" s="6" t="n"/>
-      <c r="H126" s="6" t="n"/>
+          <t>단일벽 탄소나노튜브의 응집 해소, 점도 감소.</t>
+        </is>
+      </c>
+      <c r="G126" s="7" t="n"/>
+      <c r="H126" s="8" t="n"/>
       <c r="I126" s="5" t="n"/>
       <c r="J126" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[1]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[5]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -5338,7 +5341,7 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
@@ -5349,15 +5352,19 @@
       <c r="E127" s="5" t="inlineStr"/>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>사양 협의</t>
+          <t>A-PRO Materials는 Lab-scale 파우치셀 제작 및 소재 적용성 검증 서비스를 제공합니다.</t>
         </is>
       </c>
       <c r="G127" s="7" t="n"/>
-      <c r="H127" s="8" t="n"/>
+      <c r="H127" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Materials provides lab-scale pouch cell fabrication and material validation services.</t>
+        </is>
+      </c>
       <c r="I127" s="5" t="n"/>
       <c r="J127" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[1]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -5372,26 +5379,30 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E128" s="5" t="inlineStr"/>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="G128" s="6" t="n"/>
-      <c r="H128" s="6" t="n"/>
+          <t>셀 설계부터 조립 공정, 품질 평가까지 통합 프로세스를 통해 고객사의 신소재 적용 가능성을 사전 검증합니다.</t>
+        </is>
+      </c>
+      <c r="G128" s="7" t="n"/>
+      <c r="H128" s="8" t="inlineStr">
+        <is>
+          <t>Through an integrated process encompassing cell design, assembly, and quality evaluation, we help our clients pre-validate the applicability of new materials.</t>
+        </is>
+      </c>
       <c r="I128" s="5" t="n"/>
       <c r="J128" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[2]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -5406,26 +5417,26 @@
       </c>
       <c r="C129" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D129" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E129" s="5" t="inlineStr"/>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>소재 입고 및 검수</t>
-        </is>
-      </c>
-      <c r="G129" s="7" t="n"/>
-      <c r="H129" s="8" t="n"/>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="G129" s="6" t="n"/>
+      <c r="H129" s="6" t="n"/>
       <c r="I129" s="5" t="n"/>
       <c r="J129" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[2]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[1]/b|text</t>
         </is>
       </c>
     </row>
@@ -5440,26 +5451,26 @@
       </c>
       <c r="C130" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D130" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E130" s="5" t="inlineStr"/>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="G130" s="6" t="n"/>
-      <c r="H130" s="6" t="n"/>
+          <t>사양 협의</t>
+        </is>
+      </c>
+      <c r="G130" s="7" t="n"/>
+      <c r="H130" s="8" t="n"/>
       <c r="I130" s="5" t="n"/>
       <c r="J130" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[3]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[1]/span|text</t>
         </is>
       </c>
     </row>
@@ -5474,26 +5485,26 @@
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr"/>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>파우치셀 조립</t>
-        </is>
-      </c>
-      <c r="G131" s="7" t="n"/>
-      <c r="H131" s="8" t="n"/>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="G131" s="6" t="n"/>
+      <c r="H131" s="6" t="n"/>
       <c r="I131" s="5" t="n"/>
       <c r="J131" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[3]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[2]/b|text</t>
         </is>
       </c>
     </row>
@@ -5508,26 +5519,26 @@
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E132" s="5" t="inlineStr"/>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="G132" s="6" t="n"/>
-      <c r="H132" s="6" t="n"/>
+          <t>소재 입고 및 검수</t>
+        </is>
+      </c>
+      <c r="G132" s="7" t="n"/>
+      <c r="H132" s="8" t="n"/>
       <c r="I132" s="5" t="n"/>
       <c r="J132" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[4]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[2]/span|text</t>
         </is>
       </c>
     </row>
@@ -5542,26 +5553,26 @@
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr"/>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>화성 공정</t>
-        </is>
-      </c>
-      <c r="G133" s="7" t="n"/>
-      <c r="H133" s="8" t="n"/>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="G133" s="6" t="n"/>
+      <c r="H133" s="6" t="n"/>
       <c r="I133" s="5" t="n"/>
       <c r="J133" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[4]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[3]/b|text</t>
         </is>
       </c>
     </row>
@@ -5576,26 +5587,26 @@
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr"/>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="G134" s="6" t="n"/>
-      <c r="H134" s="6" t="n"/>
+          <t>파우치셀 조립</t>
+        </is>
+      </c>
+      <c r="G134" s="7" t="n"/>
+      <c r="H134" s="8" t="n"/>
       <c r="I134" s="5" t="n"/>
       <c r="J134" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[5]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[3]/span|text</t>
         </is>
       </c>
     </row>
@@ -5610,26 +5621,26 @@
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr"/>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>제품 출하</t>
-        </is>
-      </c>
-      <c r="G135" s="7" t="n"/>
-      <c r="H135" s="8" t="n"/>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="G135" s="6" t="n"/>
+      <c r="H135" s="6" t="n"/>
       <c r="I135" s="5" t="n"/>
       <c r="J135" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[5]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[4]/b|text</t>
         </is>
       </c>
     </row>
@@ -5639,12 +5650,12 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>04-5 에이프로머티리얼즈</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
@@ -5655,7 +5666,7 @@
       <c r="E136" s="5" t="inlineStr"/>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>차세대 기술 개발</t>
+          <t>화성 공정</t>
         </is>
       </c>
       <c r="G136" s="7" t="n"/>
@@ -5663,7 +5674,7 @@
       <c r="I136" s="5" t="n"/>
       <c r="J136" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[4]/span|text</t>
         </is>
       </c>
     </row>
@@ -5673,35 +5684,31 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>04-5 에이프로머티리얼즈</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr"/>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials는 차세대 배터리 핵심 기술에 대한 지속적인 연구개발을 통해 미래 이차전지 시장에 대응해 나갑니다.</t>
-        </is>
-      </c>
-      <c r="G137" s="7" t="n"/>
-      <c r="H137" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Materials is working to respond to the future secondary battery market through continuous research and development of core next-generation battery technologies.</t>
-        </is>
-      </c>
+          <t>05</t>
+        </is>
+      </c>
+      <c r="G137" s="6" t="n"/>
+      <c r="H137" s="6" t="n"/>
       <c r="I137" s="5" t="n"/>
       <c r="J137" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[5]/b|text</t>
         </is>
       </c>
     </row>
@@ -5711,12 +5718,12 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>04-5 에이프로머티리얼즈</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
@@ -5727,19 +5734,15 @@
       <c r="E138" s="5" t="inlineStr"/>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>끊임없는 R&amp;D 혁신으로 기존 배터리의 한계를 극복하고, 고성능·고안정성 소재 및 셀 기술을 선제적으로 구현해 나갑니다.</t>
+          <t>제품 출하</t>
         </is>
       </c>
       <c r="G138" s="7" t="n"/>
-      <c r="H138" s="8" t="inlineStr">
-        <is>
-          <t>Through ongoing R&amp;D innovation, we work to overcome the limitations of existing batteries and proactively develop high-performance, high-stability materials and cell technologies.</t>
-        </is>
-      </c>
+      <c r="H138" s="8" t="n"/>
       <c r="I138" s="5" t="n"/>
       <c r="J138" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[5]/span|text</t>
         </is>
       </c>
     </row>
@@ -5754,7 +5757,7 @@
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>장 제목</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
@@ -5765,19 +5768,15 @@
       <c r="E139" s="5" t="inlineStr"/>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials는 국내외 파트너들과의 협력을 통해 최적의 이차전지 소재 솔루션을 모색하고 있습니다.</t>
+          <t>차세대 기술 개발</t>
         </is>
       </c>
       <c r="G139" s="7" t="n"/>
-      <c r="H139" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Materials is exploring optimal secondary battery material solutions in collaboration with partners at home and abroad.</t>
-        </is>
-      </c>
+      <c r="H139" s="8" t="n"/>
       <c r="I139" s="5" t="n"/>
       <c r="J139" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -5792,26 +5791,30 @@
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr"/>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="G140" s="6" t="n"/>
-      <c r="H140" s="6" t="n"/>
+          <t>A-PRO Materials는 차세대 배터리 핵심 기술에 대한 지속적인 연구개발을 통해 미래 이차전지 시장에 대응해 나갑니다.</t>
+        </is>
+      </c>
+      <c r="G140" s="7" t="n"/>
+      <c r="H140" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Materials is working to respond to the future secondary battery market through continuous research and development of core next-generation battery technologies.</t>
+        </is>
+      </c>
       <c r="I140" s="5" t="n"/>
       <c r="J140" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5829,7 @@
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
@@ -5837,15 +5840,19 @@
       <c r="E141" s="5" t="inlineStr"/>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>소듐 이온 배터리</t>
+          <t>끊임없는 R&amp;D 혁신으로 기존 배터리의 한계를 극복하고, 고성능·고안정성 소재 및 셀 기술을 선제적으로 구현해 나갑니다.</t>
         </is>
       </c>
       <c r="G141" s="7" t="n"/>
-      <c r="H141" s="8" t="n"/>
+      <c r="H141" s="8" t="inlineStr">
+        <is>
+          <t>Through ongoing R&amp;D innovation, we work to overcome the limitations of existing batteries and proactively develop high-performance, high-stability materials and cell technologies.</t>
+        </is>
+      </c>
       <c r="I141" s="5" t="n"/>
       <c r="J141" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -5860,26 +5867,30 @@
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr"/>
       <c r="F142" s="6" t="inlineStr">
         <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="G142" s="6" t="n"/>
-      <c r="H142" s="6" t="n"/>
+          <t>A-PRO Materials는 국내외 파트너들과의 협력을 통해 최적의 이차전지 소재 솔루션을 모색하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="G142" s="7" t="n"/>
+      <c r="H142" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Materials is exploring optimal secondary battery material solutions in collaboration with partners at home and abroad.</t>
+        </is>
+      </c>
       <c r="I142" s="5" t="n"/>
       <c r="J142" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -5894,26 +5905,26 @@
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr"/>
       <c r="F143" s="6" t="inlineStr">
         <is>
-          <t>반도체 전지</t>
-        </is>
-      </c>
-      <c r="G143" s="7" t="n"/>
-      <c r="H143" s="8" t="n"/>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="G143" s="6" t="n"/>
+      <c r="H143" s="6" t="n"/>
       <c r="I143" s="5" t="n"/>
       <c r="J143" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/b|text</t>
         </is>
       </c>
     </row>
@@ -5928,26 +5939,26 @@
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr"/>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="G144" s="6" t="n"/>
-      <c r="H144" s="6" t="n"/>
+          <t>소듐 이온 배터리</t>
+        </is>
+      </c>
+      <c r="G144" s="7" t="n"/>
+      <c r="H144" s="8" t="n"/>
       <c r="I144" s="5" t="n"/>
       <c r="J144" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/span|text</t>
         </is>
       </c>
     </row>
@@ -5962,26 +5973,26 @@
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr"/>
       <c r="F145" s="6" t="inlineStr">
         <is>
-          <t>전고체 전지</t>
-        </is>
-      </c>
-      <c r="G145" s="7" t="n"/>
-      <c r="H145" s="8" t="n"/>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="G145" s="6" t="n"/>
+      <c r="H145" s="6" t="n"/>
       <c r="I145" s="5" t="n"/>
       <c r="J145" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/b|text</t>
         </is>
       </c>
     </row>
@@ -5996,26 +6007,26 @@
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr"/>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="G146" s="6" t="n"/>
-      <c r="H146" s="6" t="n"/>
+          <t>반도체 전지</t>
+        </is>
+      </c>
+      <c r="G146" s="7" t="n"/>
+      <c r="H146" s="8" t="n"/>
       <c r="I146" s="5" t="n"/>
       <c r="J146" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[4]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/span|text</t>
         </is>
       </c>
     </row>
@@ -6030,31 +6041,133 @@
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr"/>
       <c r="F147" s="6" t="inlineStr">
         <is>
-          <t>무음극 전지</t>
-        </is>
-      </c>
-      <c r="G147" s="7" t="n"/>
-      <c r="H147" s="8" t="n"/>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="G147" s="6" t="n"/>
+      <c r="H147" s="6" t="n"/>
       <c r="I147" s="5" t="n"/>
       <c r="J147" s="9" t="inlineStr">
         <is>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/b|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="5" t="n">
+        <v>147</v>
+      </c>
+      <c r="B148" s="5" t="inlineStr">
+        <is>
+          <t>04-5 에이프로머티리얼즈</t>
+        </is>
+      </c>
+      <c r="C148" s="5" t="inlineStr">
+        <is>
+          <t>번호 목록 항목</t>
+        </is>
+      </c>
+      <c r="D148" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E148" s="5" t="inlineStr"/>
+      <c r="F148" s="6" t="inlineStr">
+        <is>
+          <t>전고체 전지</t>
+        </is>
+      </c>
+      <c r="G148" s="7" t="n"/>
+      <c r="H148" s="8" t="n"/>
+      <c r="I148" s="5" t="n"/>
+      <c r="J148" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/span|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="5" t="n">
+        <v>148</v>
+      </c>
+      <c r="B149" s="5" t="inlineStr">
+        <is>
+          <t>04-5 에이프로머티리얼즈</t>
+        </is>
+      </c>
+      <c r="C149" s="5" t="inlineStr">
+        <is>
+          <t>번호 목록 번호</t>
+        </is>
+      </c>
+      <c r="D149" s="5" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E149" s="5" t="inlineStr"/>
+      <c r="F149" s="6" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="G149" s="6" t="n"/>
+      <c r="H149" s="6" t="n"/>
+      <c r="I149" s="5" t="n"/>
+      <c r="J149" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[4]/b|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="5" t="n">
+        <v>149</v>
+      </c>
+      <c r="B150" s="5" t="inlineStr">
+        <is>
+          <t>04-5 에이프로머티리얼즈</t>
+        </is>
+      </c>
+      <c r="C150" s="5" t="inlineStr">
+        <is>
+          <t>번호 목록 항목</t>
+        </is>
+      </c>
+      <c r="D150" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E150" s="5" t="inlineStr"/>
+      <c r="F150" s="6" t="inlineStr">
+        <is>
+          <t>무음극 전지</t>
+        </is>
+      </c>
+      <c r="G150" s="7" t="n"/>
+      <c r="H150" s="8" t="n"/>
+      <c r="I150" s="5" t="n"/>
+      <c r="J150" s="9" t="inlineStr">
+        <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[4]/span|text</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J147"/>
+  <autoFilter ref="A1:J150"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/content-export/04_사업영역_문구.xlsx
+++ b/content-export/04_사업영역_문구.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화합물 전력 반도체" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$J$150</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$J$149</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'에너지 인프라'!$A$1:$J$189</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'인공지능 플랫폼'!$A$1:$J$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'화합물 전력 반도체'!$A$1:$J$25</definedName>
@@ -500,7 +500,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B1:B29"/>
+  <dimension ref="A1:B29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -527,7 +527,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 407 줄입니다.</t>
+          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 406 줄입니다.</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J150"/>
+  <dimension ref="A1:J149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1552,12 +1552,12 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>좌측 인덱스</t>
+          <t>좌측 인덱스 · 04-5 에이프로머티리얼즈</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>인덱스 항목</t>
+          <t>인덱스 항목 · 장 제목</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
@@ -1573,10 +1573,15 @@
       </c>
       <c r="G22" s="7" t="n"/>
       <c r="H22" s="8" t="n"/>
-      <c r="I22" s="5" t="n"/>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>같은 문구 2 곳 — 한 줄로 합침</t>
+        </is>
+      </c>
       <c r="J22" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[1]/nav/div[4]/a[5]|text</t>
+          <t>/html/body/div[8]/div[1]/nav/div[4]/a[5]|text
+/html/body/div[8]/div[3]/section[9]/div/div[2]/div/h2|text</t>
         </is>
       </c>
     </row>
@@ -5757,7 +5762,7 @@
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>장 제목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
@@ -5768,15 +5773,19 @@
       <c r="E139" s="5" t="inlineStr"/>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>차세대 기술 개발</t>
+          <t>A-PRO Materials는 차세대 배터리 핵심 기술에 대한 지속적인 연구개발을 통해 미래 이차전지 시장에 대응해 나갑니다.</t>
         </is>
       </c>
       <c r="G139" s="7" t="n"/>
-      <c r="H139" s="8" t="n"/>
+      <c r="H139" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Materials is working to respond to the future secondary battery market through continuous research and development of core next-generation battery technologies.</t>
+        </is>
+      </c>
       <c r="I139" s="5" t="n"/>
       <c r="J139" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/h2|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -5802,19 +5811,19 @@
       <c r="E140" s="5" t="inlineStr"/>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials는 차세대 배터리 핵심 기술에 대한 지속적인 연구개발을 통해 미래 이차전지 시장에 대응해 나갑니다.</t>
+          <t>끊임없는 R&amp;D 혁신으로 기존 배터리의 한계를 극복하고, 고성능·고안정성 소재 및 셀 기술을 선제적으로 구현해 나갑니다.</t>
         </is>
       </c>
       <c r="G140" s="7" t="n"/>
       <c r="H140" s="8" t="inlineStr">
         <is>
-          <t>A-PRO Materials is working to respond to the future secondary battery market through continuous research and development of core next-generation battery technologies.</t>
+          <t>Through ongoing R&amp;D innovation, we work to overcome the limitations of existing batteries and proactively develop high-performance, high-stability materials and cell technologies.</t>
         </is>
       </c>
       <c r="I140" s="5" t="n"/>
       <c r="J140" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -5840,19 +5849,19 @@
       <c r="E141" s="5" t="inlineStr"/>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>끊임없는 R&amp;D 혁신으로 기존 배터리의 한계를 극복하고, 고성능·고안정성 소재 및 셀 기술을 선제적으로 구현해 나갑니다.</t>
+          <t>A-PRO Materials는 국내외 파트너들과의 협력을 통해 최적의 이차전지 소재 솔루션을 모색하고 있습니다.</t>
         </is>
       </c>
       <c r="G141" s="7" t="n"/>
       <c r="H141" s="8" t="inlineStr">
         <is>
-          <t>Through ongoing R&amp;D innovation, we work to overcome the limitations of existing batteries and proactively develop high-performance, high-stability materials and cell technologies.</t>
+          <t>A-PRO Materials is exploring optimal secondary battery material solutions in collaboration with partners at home and abroad.</t>
         </is>
       </c>
       <c r="I141" s="5" t="n"/>
       <c r="J141" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -5867,30 +5876,26 @@
       </c>
       <c r="C142" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D142" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E142" s="5" t="inlineStr"/>
       <c r="F142" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials는 국내외 파트너들과의 협력을 통해 최적의 이차전지 소재 솔루션을 모색하고 있습니다.</t>
-        </is>
-      </c>
-      <c r="G142" s="7" t="n"/>
-      <c r="H142" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Materials is exploring optimal secondary battery material solutions in collaboration with partners at home and abroad.</t>
-        </is>
-      </c>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="G142" s="6" t="n"/>
+      <c r="H142" s="6" t="n"/>
       <c r="I142" s="5" t="n"/>
       <c r="J142" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/b|text</t>
         </is>
       </c>
     </row>
@@ -5905,26 +5910,26 @@
       </c>
       <c r="C143" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D143" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E143" s="5" t="inlineStr"/>
       <c r="F143" s="6" t="inlineStr">
         <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="G143" s="6" t="n"/>
-      <c r="H143" s="6" t="n"/>
+          <t>소듐 이온 배터리</t>
+        </is>
+      </c>
+      <c r="G143" s="7" t="n"/>
+      <c r="H143" s="8" t="n"/>
       <c r="I143" s="5" t="n"/>
       <c r="J143" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/span|text</t>
         </is>
       </c>
     </row>
@@ -5939,26 +5944,26 @@
       </c>
       <c r="C144" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D144" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E144" s="5" t="inlineStr"/>
       <c r="F144" s="6" t="inlineStr">
         <is>
-          <t>소듐 이온 배터리</t>
-        </is>
-      </c>
-      <c r="G144" s="7" t="n"/>
-      <c r="H144" s="8" t="n"/>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="G144" s="6" t="n"/>
+      <c r="H144" s="6" t="n"/>
       <c r="I144" s="5" t="n"/>
       <c r="J144" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/b|text</t>
         </is>
       </c>
     </row>
@@ -5973,26 +5978,26 @@
       </c>
       <c r="C145" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D145" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E145" s="5" t="inlineStr"/>
       <c r="F145" s="6" t="inlineStr">
         <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="G145" s="6" t="n"/>
-      <c r="H145" s="6" t="n"/>
+          <t>반도체 전지</t>
+        </is>
+      </c>
+      <c r="G145" s="7" t="n"/>
+      <c r="H145" s="8" t="n"/>
       <c r="I145" s="5" t="n"/>
       <c r="J145" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/span|text</t>
         </is>
       </c>
     </row>
@@ -6007,26 +6012,26 @@
       </c>
       <c r="C146" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D146" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E146" s="5" t="inlineStr"/>
       <c r="F146" s="6" t="inlineStr">
         <is>
-          <t>반도체 전지</t>
-        </is>
-      </c>
-      <c r="G146" s="7" t="n"/>
-      <c r="H146" s="8" t="n"/>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="G146" s="6" t="n"/>
+      <c r="H146" s="6" t="n"/>
       <c r="I146" s="5" t="n"/>
       <c r="J146" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/b|text</t>
         </is>
       </c>
     </row>
@@ -6041,26 +6046,26 @@
       </c>
       <c r="C147" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D147" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E147" s="5" t="inlineStr"/>
       <c r="F147" s="6" t="inlineStr">
         <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="G147" s="6" t="n"/>
-      <c r="H147" s="6" t="n"/>
+          <t>전고체 전지</t>
+        </is>
+      </c>
+      <c r="G147" s="7" t="n"/>
+      <c r="H147" s="8" t="n"/>
       <c r="I147" s="5" t="n"/>
       <c r="J147" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/span|text</t>
         </is>
       </c>
     </row>
@@ -6075,26 +6080,26 @@
       </c>
       <c r="C148" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D148" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E148" s="5" t="inlineStr"/>
       <c r="F148" s="6" t="inlineStr">
         <is>
-          <t>전고체 전지</t>
-        </is>
-      </c>
-      <c r="G148" s="7" t="n"/>
-      <c r="H148" s="8" t="n"/>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="G148" s="6" t="n"/>
+      <c r="H148" s="6" t="n"/>
       <c r="I148" s="5" t="n"/>
       <c r="J148" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[4]/b|text</t>
         </is>
       </c>
     </row>
@@ -6109,65 +6114,31 @@
       </c>
       <c r="C149" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D149" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E149" s="5" t="inlineStr"/>
       <c r="F149" s="6" t="inlineStr">
         <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="G149" s="6" t="n"/>
-      <c r="H149" s="6" t="n"/>
+          <t>무음극 전지</t>
+        </is>
+      </c>
+      <c r="G149" s="7" t="n"/>
+      <c r="H149" s="8" t="n"/>
       <c r="I149" s="5" t="n"/>
       <c r="J149" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[4]/b|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" s="5" t="n">
-        <v>149</v>
-      </c>
-      <c r="B150" s="5" t="inlineStr">
-        <is>
-          <t>04-5 에이프로머티리얼즈</t>
-        </is>
-      </c>
-      <c r="C150" s="5" t="inlineStr">
-        <is>
-          <t>번호 목록 항목</t>
-        </is>
-      </c>
-      <c r="D150" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E150" s="5" t="inlineStr"/>
-      <c r="F150" s="6" t="inlineStr">
-        <is>
-          <t>무음극 전지</t>
-        </is>
-      </c>
-      <c r="G150" s="7" t="n"/>
-      <c r="H150" s="8" t="n"/>
-      <c r="I150" s="5" t="n"/>
-      <c r="J150" s="9" t="inlineStr">
-        <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[4]/span|text</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J150"/>
+  <autoFilter ref="A1:J149"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/content-export/04_사업영역_문구.xlsx
+++ b/content-export/04_사업영역_문구.xlsx
@@ -14,7 +14,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화합물 전력 반도체" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$J$149</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$J$141</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'에너지 인프라'!$A$1:$J$189</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'인공지능 플랫폼'!$A$1:$J$47</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'화합물 전력 반도체'!$A$1:$J$25</definedName>
@@ -527,7 +527,7 @@
     <row r="4" ht="30" customHeight="1">
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 406 줄입니다.</t>
+          <t>지금 사업영역 세부 네 장(business-*-a1.html)에 들어가 있는 문구 전부입니다. 시트가 사업영역이고, 시트 안에서 섹션 순서대로, 화면에 보이는 순서대로 늘어놓았습니다. 모두 398 줄입니다.</t>
         </is>
       </c>
     </row>
@@ -697,7 +697,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J149"/>
+  <dimension ref="A1:J141"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -3682,12 +3682,12 @@
       </c>
       <c r="B81" s="5" t="inlineStr">
         <is>
-          <t>03-1 자동화 설비</t>
+          <t>04-1 탄소 나노 튜브</t>
         </is>
       </c>
       <c r="C81" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D81" s="5" t="inlineStr">
@@ -3698,19 +3698,19 @@
       <c r="E81" s="5" t="inlineStr"/>
       <c r="F81" s="6" t="inlineStr">
         <is>
-          <t>스마트 설비 제어</t>
+          <t>A-PRO Materials의 글로벌 소싱 네트워크를 활용하여 고품질의 탄소나노튜브(CNT) 소재를 안정적으로 공급합니다.</t>
         </is>
       </c>
       <c r="G81" s="7" t="n"/>
       <c r="H81" s="8" t="inlineStr">
         <is>
-          <t>Smart Equipment Control</t>
+          <t>We provide a stable supply of high-quality carbon nanotube (CNT) materials through A-PRO Materials' global sourcing network.</t>
         </is>
       </c>
       <c r="I81" s="5" t="n"/>
       <c r="J81" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[1]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[1]/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -3720,12 +3720,12 @@
       </c>
       <c r="B82" s="5" t="inlineStr">
         <is>
-          <t>03-1 자동화 설비</t>
+          <t>04-1 탄소 나노 튜브</t>
         </is>
       </c>
       <c r="C82" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D82" s="5" t="inlineStr">
@@ -3736,19 +3736,19 @@
       <c r="E82" s="5" t="inlineStr"/>
       <c r="F82" s="6" t="inlineStr">
         <is>
-          <t>충방전기, 디개싱, 에이징 룸 등 공정 내 모든 하드웨어를 실시간 직접 제어합니다.</t>
+          <t>엄격한 품질 검증을 거친 CNT 소재를 통해 고객사의 배터리 에너지 밀도 향상과 고속 충전 성능 구현을 지원합니다.</t>
         </is>
       </c>
       <c r="G82" s="7" t="n"/>
       <c r="H82" s="8" t="inlineStr">
         <is>
-          <t>Direct, real-time hardware control of all production lines, including cyclers, degassing units, and aging rooms.</t>
+          <t>Through rigorously quality-verified CNT materials, we support our customers in enhancing battery energy density and enabling high-speed charging performance.</t>
         </is>
       </c>
       <c r="I82" s="5" t="n"/>
       <c r="J82" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[1]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[1]/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -3758,12 +3758,12 @@
       </c>
       <c r="B83" s="5" t="inlineStr">
         <is>
-          <t>03-1 자동화 설비</t>
+          <t>04-1 탄소 나노 튜브</t>
         </is>
       </c>
       <c r="C83" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>제품 단추 이름</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
@@ -3774,19 +3774,19 @@
       <c r="E83" s="5" t="inlineStr"/>
       <c r="F83" s="6" t="inlineStr">
         <is>
-          <t>실시간 데이터 수집</t>
+          <t>SW/FW-CNT Powder</t>
         </is>
       </c>
       <c r="G83" s="7" t="n"/>
       <c r="H83" s="8" t="inlineStr">
         <is>
-          <t>Real-Time Data Acquisition</t>
+          <t>SW/FW-CNT Powder</t>
         </is>
       </c>
       <c r="I83" s="5" t="n"/>
       <c r="J83" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[2]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[1]/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -3796,12 +3796,12 @@
       </c>
       <c r="B84" s="5" t="inlineStr">
         <is>
-          <t>03-1 자동화 설비</t>
+          <t>04-1 탄소 나노 튜브</t>
         </is>
       </c>
       <c r="C84" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>제품 단추 이름</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
@@ -3812,19 +3812,19 @@
       <c r="E84" s="5" t="inlineStr"/>
       <c r="F84" s="6" t="inlineStr">
         <is>
-          <t>미세한 온도·압력·전압·전류 데이터를 정밀 측정하여 완벽한 품질 추적성을 확보합니다.</t>
+          <t>SW/FW-CNT Slurry</t>
         </is>
       </c>
       <c r="G84" s="7" t="n"/>
       <c r="H84" s="8" t="inlineStr">
         <is>
-          <t>Precision monitoring of voltage, current, temperature, and pressure for seamless quality traceability.</t>
+          <t>SW/FW-CNT Slurry</t>
         </is>
       </c>
       <c r="I84" s="5" t="n"/>
       <c r="J84" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[2]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[2]/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -3834,12 +3834,12 @@
       </c>
       <c r="B85" s="5" t="inlineStr">
         <is>
-          <t>03-1 자동화 설비</t>
+          <t>04-1 탄소 나노 튜브</t>
         </is>
       </c>
       <c r="C85" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>제품 단추 이름</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
@@ -3850,19 +3850,19 @@
       <c r="E85" s="5" t="inlineStr"/>
       <c r="F85" s="6" t="inlineStr">
         <is>
-          <t>지능형 안전 인터록</t>
+          <t>Carbon Black</t>
         </is>
       </c>
       <c r="G85" s="7" t="n"/>
       <c r="H85" s="8" t="inlineStr">
         <is>
-          <t>Intelligent Safety Interlock</t>
+          <t>Carbon Black</t>
         </is>
       </c>
       <c r="I85" s="5" t="n"/>
       <c r="J85" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[3]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[3]/span[2]|text</t>
         </is>
       </c>
     </row>
@@ -3872,12 +3872,12 @@
       </c>
       <c r="B86" s="5" t="inlineStr">
         <is>
-          <t>03-1 자동화 설비</t>
+          <t>04-1 탄소 나노 튜브 · 04-2 LiFSI 전해염 · 04-3 HNBR 바인더 · 04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C86" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>문의 단추</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
@@ -3888,321 +3888,17 @@
       <c r="E86" s="5" t="inlineStr"/>
       <c r="F86" s="6" t="inlineStr">
         <is>
-          <t>가스 누출, 과전압 등 이상 징후 감지 시 설비를 즉각 정지시켜 사고를 원천 차단합니다.</t>
+          <t>문의하기</t>
         </is>
       </c>
       <c r="G86" s="7" t="n"/>
-      <c r="H86" s="8" t="inlineStr">
-        <is>
-          <t>Advanced emergency system that instantly halts operations upon detecting hazards like gas leaks or overvoltage.</t>
-        </is>
-      </c>
-      <c r="I86" s="5" t="n"/>
+      <c r="H86" s="8" t="n"/>
+      <c r="I86" s="5" t="inlineStr">
+        <is>
+          <t>같은 문구 4 곳 — 한 줄로 합침</t>
+        </is>
+      </c>
       <c r="J86" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[3]/p[2]|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" s="5" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" s="5" t="inlineStr">
-        <is>
-          <t>03-1 자동화 설비</t>
-        </is>
-      </c>
-      <c r="C87" s="5" t="inlineStr">
-        <is>
-          <t>표 왼쪽</t>
-        </is>
-      </c>
-      <c r="D87" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E87" s="5" t="inlineStr"/>
-      <c r="F87" s="6" t="inlineStr">
-        <is>
-          <t>유연한 상위 연동</t>
-        </is>
-      </c>
-      <c r="G87" s="7" t="n"/>
-      <c r="H87" s="8" t="inlineStr">
-        <is>
-          <t>Seamless Integration</t>
-        </is>
-      </c>
-      <c r="I87" s="5" t="n"/>
-      <c r="J87" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[4]/p[1]|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" s="5" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" s="5" t="inlineStr">
-        <is>
-          <t>03-1 자동화 설비</t>
-        </is>
-      </c>
-      <c r="C88" s="5" t="inlineStr">
-        <is>
-          <t>표 오른쪽</t>
-        </is>
-      </c>
-      <c r="D88" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E88" s="5" t="inlineStr"/>
-      <c r="F88" s="6" t="inlineStr">
-        <is>
-          <t>PC 및 MES와의 고속 통신으로 공정 데이터를 실시간 전송하고 레시피 명령을 완벽히 수행합니다.</t>
-        </is>
-      </c>
-      <c r="G88" s="7" t="n"/>
-      <c r="H88" s="8" t="inlineStr">
-        <is>
-          <t>High-speed communication with upper-level systems (PCs/MES) to transmit process data and execute recipe commands flawlessly.</t>
-        </is>
-      </c>
-      <c r="I88" s="5" t="n"/>
-      <c r="J88" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[4]/div/div[2]/ul/li[4]/p[2]|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" s="5" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" s="5" t="inlineStr">
-        <is>
-          <t>04-1 탄소 나노 튜브</t>
-        </is>
-      </c>
-      <c r="C89" s="5" t="inlineStr">
-        <is>
-          <t>본문</t>
-        </is>
-      </c>
-      <c r="D89" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E89" s="5" t="inlineStr"/>
-      <c r="F89" s="6" t="inlineStr">
-        <is>
-          <t>A-PRO Materials의 글로벌 소싱 네트워크를 활용하여 고품질의 탄소나노튜브(CNT) 소재를 안정적으로 공급합니다.</t>
-        </is>
-      </c>
-      <c r="G89" s="7" t="n"/>
-      <c r="H89" s="8" t="inlineStr">
-        <is>
-          <t>We provide a stable supply of high-quality carbon nanotube (CNT) materials through A-PRO Materials' global sourcing network.</t>
-        </is>
-      </c>
-      <c r="I89" s="5" t="n"/>
-      <c r="J89" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[1]/div/p[1]|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" s="5" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" s="5" t="inlineStr">
-        <is>
-          <t>04-1 탄소 나노 튜브</t>
-        </is>
-      </c>
-      <c r="C90" s="5" t="inlineStr">
-        <is>
-          <t>본문</t>
-        </is>
-      </c>
-      <c r="D90" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E90" s="5" t="inlineStr"/>
-      <c r="F90" s="6" t="inlineStr">
-        <is>
-          <t>엄격한 품질 검증을 거친 CNT 소재를 통해 고객사의 배터리 에너지 밀도 향상과 고속 충전 성능 구현을 지원합니다.</t>
-        </is>
-      </c>
-      <c r="G90" s="7" t="n"/>
-      <c r="H90" s="8" t="inlineStr">
-        <is>
-          <t>Through rigorously quality-verified CNT materials, we support our customers in enhancing battery energy density and enabling high-speed charging performance.</t>
-        </is>
-      </c>
-      <c r="I90" s="5" t="n"/>
-      <c r="J90" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[1]/div/p[2]|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" s="5" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" s="5" t="inlineStr">
-        <is>
-          <t>04-1 탄소 나노 튜브</t>
-        </is>
-      </c>
-      <c r="C91" s="5" t="inlineStr">
-        <is>
-          <t>제품 단추 이름</t>
-        </is>
-      </c>
-      <c r="D91" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E91" s="5" t="inlineStr"/>
-      <c r="F91" s="6" t="inlineStr">
-        <is>
-          <t>SW/FW-CNT Powder</t>
-        </is>
-      </c>
-      <c r="G91" s="7" t="n"/>
-      <c r="H91" s="8" t="inlineStr">
-        <is>
-          <t>SW/FW-CNT Powder</t>
-        </is>
-      </c>
-      <c r="I91" s="5" t="n"/>
-      <c r="J91" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[1]/span[2]|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="5" t="n">
-        <v>91</v>
-      </c>
-      <c r="B92" s="5" t="inlineStr">
-        <is>
-          <t>04-1 탄소 나노 튜브</t>
-        </is>
-      </c>
-      <c r="C92" s="5" t="inlineStr">
-        <is>
-          <t>제품 단추 이름</t>
-        </is>
-      </c>
-      <c r="D92" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E92" s="5" t="inlineStr"/>
-      <c r="F92" s="6" t="inlineStr">
-        <is>
-          <t>SW/FW-CNT Slurry</t>
-        </is>
-      </c>
-      <c r="G92" s="7" t="n"/>
-      <c r="H92" s="8" t="inlineStr">
-        <is>
-          <t>SW/FW-CNT Slurry</t>
-        </is>
-      </c>
-      <c r="I92" s="5" t="n"/>
-      <c r="J92" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[2]/span[2]|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="5" t="n">
-        <v>92</v>
-      </c>
-      <c r="B93" s="5" t="inlineStr">
-        <is>
-          <t>04-1 탄소 나노 튜브</t>
-        </is>
-      </c>
-      <c r="C93" s="5" t="inlineStr">
-        <is>
-          <t>제품 단추 이름</t>
-        </is>
-      </c>
-      <c r="D93" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E93" s="5" t="inlineStr"/>
-      <c r="F93" s="6" t="inlineStr">
-        <is>
-          <t>Carbon Black</t>
-        </is>
-      </c>
-      <c r="G93" s="7" t="n"/>
-      <c r="H93" s="8" t="inlineStr">
-        <is>
-          <t>Carbon Black</t>
-        </is>
-      </c>
-      <c r="I93" s="5" t="n"/>
-      <c r="J93" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/div[2]/button[3]/span[2]|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" s="5" t="n">
-        <v>93</v>
-      </c>
-      <c r="B94" s="5" t="inlineStr">
-        <is>
-          <t>04-1 탄소 나노 튜브 · 04-2 LiFSI 전해염 · 04-3 HNBR 바인더 · 04-4 파우치셀 제조</t>
-        </is>
-      </c>
-      <c r="C94" s="5" t="inlineStr">
-        <is>
-          <t>문의 단추</t>
-        </is>
-      </c>
-      <c r="D94" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E94" s="5" t="inlineStr"/>
-      <c r="F94" s="6" t="inlineStr">
-        <is>
-          <t>문의하기</t>
-        </is>
-      </c>
-      <c r="G94" s="7" t="n"/>
-      <c r="H94" s="8" t="n"/>
-      <c r="I94" s="5" t="inlineStr">
-        <is>
-          <t>같은 문구 4 곳 — 한 줄로 합침</t>
-        </is>
-      </c>
-      <c r="J94" s="9" t="inlineStr">
         <is>
           <t>/html/body/div[8]/div[3]/section[5]/div/div[2]/a|text
 /html/body/div[8]/div[3]/section[6]/div/div[2]/a|text
@@ -4211,6 +3907,286 @@
         </is>
       </c>
     </row>
+    <row r="87">
+      <c r="A87" s="5" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" s="5" t="inlineStr">
+        <is>
+          <t>04-2 LiFSI 전해염</t>
+        </is>
+      </c>
+      <c r="C87" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D87" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E87" s="5" t="inlineStr"/>
+      <c r="F87" s="6" t="inlineStr">
+        <is>
+          <t>A-PRO Materials는 엄선된 공급망을 통해 고순도 LiFSI 전해염 소재를 안정적으로 공급합니다.</t>
+        </is>
+      </c>
+      <c r="G87" s="7" t="n"/>
+      <c r="H87" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Materials provides a stable supply of high-purity LiFSI electrolyte salt through a carefully selected global supply network.</t>
+        </is>
+      </c>
+      <c r="I87" s="5" t="n"/>
+      <c r="J87" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[1]|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="5" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" s="5" t="inlineStr">
+        <is>
+          <t>04-2 LiFSI 전해염</t>
+        </is>
+      </c>
+      <c r="C88" s="5" t="inlineStr">
+        <is>
+          <t>본문</t>
+        </is>
+      </c>
+      <c r="D88" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E88" s="5" t="inlineStr"/>
+      <c r="F88" s="6" t="inlineStr">
+        <is>
+          <t>우수한 화학적 안정성을 바탕으로 고객사 배터리의 수명 연장과 고온 안정성 및 출력 향상을 지원합니다.</t>
+        </is>
+      </c>
+      <c r="G88" s="7" t="n"/>
+      <c r="H88" s="8" t="inlineStr">
+        <is>
+          <t>Based on superior chemical stability, we support extended battery life, high-temperature stability, and improved output performance for our customers.</t>
+        </is>
+      </c>
+      <c r="I88" s="5" t="n"/>
+      <c r="J88" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[2]|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="5" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" s="5" t="inlineStr">
+        <is>
+          <t>04-2 LiFSI 전해염</t>
+        </is>
+      </c>
+      <c r="C89" s="5" t="inlineStr">
+        <is>
+          <t>제품 이름</t>
+        </is>
+      </c>
+      <c r="D89" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E89" s="5" t="inlineStr"/>
+      <c r="F89" s="6" t="inlineStr">
+        <is>
+          <t>LiFSI 전해질</t>
+        </is>
+      </c>
+      <c r="G89" s="7" t="n"/>
+      <c r="H89" s="8" t="n"/>
+      <c r="I89" s="5" t="n"/>
+      <c r="J89" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/div/p[1]|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="5" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="5" t="inlineStr">
+        <is>
+          <t>04-2 LiFSI 전해염</t>
+        </is>
+      </c>
+      <c r="C90" s="5" t="inlineStr">
+        <is>
+          <t>제품 설명</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E90" s="5" t="inlineStr"/>
+      <c r="F90" s="6" t="inlineStr">
+        <is>
+          <t>고출력 · 수명연장용 차세대 전해염</t>
+        </is>
+      </c>
+      <c r="G90" s="7" t="n"/>
+      <c r="H90" s="8" t="n"/>
+      <c r="I90" s="5" t="n"/>
+      <c r="J90" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/div/p[2]|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="5" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="5" t="inlineStr">
+        <is>
+          <t>04-2 LiFSI 전해염</t>
+        </is>
+      </c>
+      <c r="C91" s="5" t="inlineStr">
+        <is>
+          <t>제품 수치</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E91" s="5" t="inlineStr"/>
+      <c r="F91" s="6" t="inlineStr">
+        <is>
+          <t>비표면적 ≥300~1,000 m²/g</t>
+        </is>
+      </c>
+      <c r="G91" s="7" t="n"/>
+      <c r="H91" s="8" t="n"/>
+      <c r="I91" s="5" t="n"/>
+      <c r="J91" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/div/p[3]|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="5" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="5" t="inlineStr">
+        <is>
+          <t>04-2 LiFSI 전해염</t>
+        </is>
+      </c>
+      <c r="C92" s="5" t="inlineStr">
+        <is>
+          <t>제품 사진 대체글</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>대체글</t>
+        </is>
+      </c>
+      <c r="E92" s="5" t="inlineStr"/>
+      <c r="F92" s="6" t="inlineStr">
+        <is>
+          <t>LiFSI 전해염 입자 표면의 주사전자현미경 사진 — 크고 작은 구멍이 촘촘한 다공성 구조</t>
+        </is>
+      </c>
+      <c r="G92" s="7" t="n"/>
+      <c r="H92" s="8" t="n"/>
+      <c r="I92" s="5" t="n"/>
+      <c r="J92" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/span/img|alt</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" s="5" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="5" t="inlineStr">
+        <is>
+          <t>04-2 LiFSI 전해염</t>
+        </is>
+      </c>
+      <c r="C93" s="5" t="inlineStr">
+        <is>
+          <t>제품 이름</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E93" s="5" t="inlineStr"/>
+      <c r="F93" s="6" t="inlineStr">
+        <is>
+          <t>산화물계 전해질</t>
+        </is>
+      </c>
+      <c r="G93" s="7" t="n"/>
+      <c r="H93" s="8" t="n"/>
+      <c r="I93" s="5" t="n"/>
+      <c r="J93" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/div/p[1]|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" s="5" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="5" t="inlineStr">
+        <is>
+          <t>04-2 LiFSI 전해염</t>
+        </is>
+      </c>
+      <c r="C94" s="5" t="inlineStr">
+        <is>
+          <t>제품 설명</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E94" s="5" t="inlineStr"/>
+      <c r="F94" s="6" t="inlineStr">
+        <is>
+          <t>산화물계 LLZMO · LATP</t>
+        </is>
+      </c>
+      <c r="G94" s="7" t="n"/>
+      <c r="H94" s="8" t="n"/>
+      <c r="I94" s="5" t="n"/>
+      <c r="J94" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/div/p[2]|text</t>
+        </is>
+      </c>
+    </row>
     <row r="95">
       <c r="A95" s="5" t="n">
         <v>94</v>
@@ -4222,7 +4198,7 @@
       </c>
       <c r="C95" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>제품 수치</t>
         </is>
       </c>
       <c r="D95" s="5" t="inlineStr">
@@ -4233,19 +4209,15 @@
       <c r="E95" s="5" t="inlineStr"/>
       <c r="F95" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials는 엄선된 공급망을 통해 고순도 LiFSI 전해염 소재를 안정적으로 공급합니다.</t>
+          <t>이온 전도도 0.2~1.0 mS/cm</t>
         </is>
       </c>
       <c r="G95" s="7" t="n"/>
-      <c r="H95" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Materials provides a stable supply of high-purity LiFSI electrolyte salt through a carefully selected global supply network.</t>
-        </is>
-      </c>
+      <c r="H95" s="8" t="n"/>
       <c r="I95" s="5" t="n"/>
       <c r="J95" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -4260,30 +4232,26 @@
       </c>
       <c r="C96" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>제품 사진 대체글</t>
         </is>
       </c>
       <c r="D96" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>대체글</t>
         </is>
       </c>
       <c r="E96" s="5" t="inlineStr"/>
       <c r="F96" s="6" t="inlineStr">
         <is>
-          <t>우수한 화학적 안정성을 바탕으로 고객사 배터리의 수명 연장과 고온 안정성 및 출력 향상을 지원합니다.</t>
+          <t>산화물계 전해질 모식도 — 왼쪽은 결정 격자, 오른쪽은 고체 전해질 막을 가로지르는 이온 이동</t>
         </is>
       </c>
       <c r="G96" s="7" t="n"/>
-      <c r="H96" s="8" t="inlineStr">
-        <is>
-          <t>Based on superior chemical stability, we support extended battery life, high-temperature stability, and improved output performance for our customers.</t>
-        </is>
-      </c>
+      <c r="H96" s="8" t="n"/>
       <c r="I96" s="5" t="n"/>
       <c r="J96" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/span/img|alt</t>
         </is>
       </c>
     </row>
@@ -4298,7 +4266,7 @@
       </c>
       <c r="C97" s="5" t="inlineStr">
         <is>
-          <t>제품 이름</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D97" s="5" t="inlineStr">
@@ -4309,15 +4277,19 @@
       <c r="E97" s="5" t="inlineStr"/>
       <c r="F97" s="6" t="inlineStr">
         <is>
-          <t>LiFSI 전해질</t>
+          <t>High Purity</t>
         </is>
       </c>
       <c r="G97" s="7" t="n"/>
-      <c r="H97" s="8" t="n"/>
+      <c r="H97" s="8" t="inlineStr">
+        <is>
+          <t>High Purity</t>
+        </is>
+      </c>
       <c r="I97" s="5" t="n"/>
       <c r="J97" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[1]/p|text</t>
         </is>
       </c>
     </row>
@@ -4332,7 +4304,7 @@
       </c>
       <c r="C98" s="5" t="inlineStr">
         <is>
-          <t>제품 설명</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D98" s="5" t="inlineStr">
@@ -4343,15 +4315,19 @@
       <c r="E98" s="5" t="inlineStr"/>
       <c r="F98" s="6" t="inlineStr">
         <is>
-          <t>고출력 · 수명연장용 차세대 전해염</t>
+          <t>Thermal Stability</t>
         </is>
       </c>
       <c r="G98" s="7" t="n"/>
-      <c r="H98" s="8" t="n"/>
+      <c r="H98" s="8" t="inlineStr">
+        <is>
+          <t>Thermal Stability</t>
+        </is>
+      </c>
       <c r="I98" s="5" t="n"/>
       <c r="J98" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[2]/p|text</t>
         </is>
       </c>
     </row>
@@ -4366,7 +4342,7 @@
       </c>
       <c r="C99" s="5" t="inlineStr">
         <is>
-          <t>제품 수치</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D99" s="5" t="inlineStr">
@@ -4377,15 +4353,19 @@
       <c r="E99" s="5" t="inlineStr"/>
       <c r="F99" s="6" t="inlineStr">
         <is>
-          <t>비표면적 ≥300~1,000 m²/g</t>
+          <t>Long Cycle Life</t>
         </is>
       </c>
       <c r="G99" s="7" t="n"/>
-      <c r="H99" s="8" t="n"/>
+      <c r="H99" s="8" t="inlineStr">
+        <is>
+          <t>Long Cycle Life</t>
+        </is>
+      </c>
       <c r="I99" s="5" t="n"/>
       <c r="J99" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[3]/p|text</t>
         </is>
       </c>
     </row>
@@ -4400,26 +4380,30 @@
       </c>
       <c r="C100" s="5" t="inlineStr">
         <is>
-          <t>제품 사진 대체글</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D100" s="5" t="inlineStr">
         <is>
-          <t>대체글</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E100" s="5" t="inlineStr"/>
       <c r="F100" s="6" t="inlineStr">
         <is>
-          <t>LiFSI 전해염 입자 표면의 주사전자현미경 사진 — 크고 작은 구멍이 촘촘한 다공성 구조</t>
+          <t>Fast Charging</t>
         </is>
       </c>
       <c r="G100" s="7" t="n"/>
-      <c r="H100" s="8" t="n"/>
+      <c r="H100" s="8" t="inlineStr">
+        <is>
+          <t>Fast Charging</t>
+        </is>
+      </c>
       <c r="I100" s="5" t="n"/>
       <c r="J100" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[1]/span/img|alt</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[4]/p|text</t>
         </is>
       </c>
     </row>
@@ -4434,7 +4418,7 @@
       </c>
       <c r="C101" s="5" t="inlineStr">
         <is>
-          <t>제품 이름</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D101" s="5" t="inlineStr">
@@ -4445,15 +4429,19 @@
       <c r="E101" s="5" t="inlineStr"/>
       <c r="F101" s="6" t="inlineStr">
         <is>
-          <t>산화물계 전해질</t>
+          <t>Low Resistance &amp; Low Viscosity</t>
         </is>
       </c>
       <c r="G101" s="7" t="n"/>
-      <c r="H101" s="8" t="n"/>
+      <c r="H101" s="8" t="inlineStr">
+        <is>
+          <t>Low Resistance &amp; Low Viscosity</t>
+        </is>
+      </c>
       <c r="I101" s="5" t="n"/>
       <c r="J101" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[5]/p|text</t>
         </is>
       </c>
     </row>
@@ -4463,12 +4451,12 @@
       </c>
       <c r="B102" s="5" t="inlineStr">
         <is>
-          <t>04-2 LiFSI 전해염</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C102" s="5" t="inlineStr">
         <is>
-          <t>제품 설명</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D102" s="5" t="inlineStr">
@@ -4479,15 +4467,19 @@
       <c r="E102" s="5" t="inlineStr"/>
       <c r="F102" s="6" t="inlineStr">
         <is>
-          <t>산화물계 LLZMO · LATP</t>
+          <t>PVDF 바인더의 일부 대체 가능성을 검토할 수 있는 HNBR 바인더 소재입니다.</t>
         </is>
       </c>
       <c r="G102" s="7" t="n"/>
-      <c r="H102" s="8" t="n"/>
+      <c r="H102" s="8" t="inlineStr">
+        <is>
+          <t>HNBR is a binder material that can be evaluated as a partial alternative to PVDF binders.</t>
+        </is>
+      </c>
       <c r="I102" s="5" t="n"/>
       <c r="J102" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4497,12 +4489,12 @@
       </c>
       <c r="B103" s="5" t="inlineStr">
         <is>
-          <t>04-2 LiFSI 전해염</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C103" s="5" t="inlineStr">
         <is>
-          <t>제품 수치</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D103" s="5" t="inlineStr">
@@ -4513,15 +4505,19 @@
       <c r="E103" s="5" t="inlineStr"/>
       <c r="F103" s="6" t="inlineStr">
         <is>
-          <t>이온 전도도 0.2~1.0 mS/cm</t>
+          <t>우수한 결합력과 유연성, 전극 저항 감소 효과를 통해 배터리의 고율 충·방전 성능과 안정성 향상에 기여할 수 있습니다.</t>
         </is>
       </c>
       <c r="G103" s="7" t="n"/>
-      <c r="H103" s="8" t="n"/>
+      <c r="H103" s="8" t="inlineStr">
+        <is>
+          <t>With excellent bonding strength, flexibility, and reduced electrode resistance, it can contribute to improved high-rate charge/discharge performance and stability.</t>
+        </is>
+      </c>
       <c r="I103" s="5" t="n"/>
       <c r="J103" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/div/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4531,23 +4527,23 @@
       </c>
       <c r="B104" s="5" t="inlineStr">
         <is>
-          <t>04-2 LiFSI 전해염</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C104" s="5" t="inlineStr">
         <is>
-          <t>제품 사진 대체글</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D104" s="5" t="inlineStr">
         <is>
-          <t>대체글</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E104" s="5" t="inlineStr"/>
       <c r="F104" s="6" t="inlineStr">
         <is>
-          <t>산화물계 전해질 모식도 — 왼쪽은 결정 격자, 오른쪽은 고체 전해질 막을 가로지르는 이온 이동</t>
+          <t>CNT 분산용 고성능 고무 바인더</t>
         </is>
       </c>
       <c r="G104" s="7" t="n"/>
@@ -4555,7 +4551,7 @@
       <c r="I104" s="5" t="n"/>
       <c r="J104" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[1]/li[2]/span/img|alt</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[1]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4565,12 +4561,12 @@
       </c>
       <c r="B105" s="5" t="inlineStr">
         <is>
-          <t>04-2 LiFSI 전해염</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C105" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>표 값</t>
         </is>
       </c>
       <c r="D105" s="5" t="inlineStr">
@@ -4581,19 +4577,15 @@
       <c r="E105" s="5" t="inlineStr"/>
       <c r="F105" s="6" t="inlineStr">
         <is>
-          <t>High Purity</t>
+          <t>포화도 99.6%</t>
         </is>
       </c>
       <c r="G105" s="7" t="n"/>
-      <c r="H105" s="8" t="inlineStr">
-        <is>
-          <t>High Purity</t>
-        </is>
-      </c>
+      <c r="H105" s="8" t="n"/>
       <c r="I105" s="5" t="n"/>
       <c r="J105" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[1]/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[1]/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -4603,7 +4595,7 @@
       </c>
       <c r="B106" s="5" t="inlineStr">
         <is>
-          <t>04-2 LiFSI 전해염</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C106" s="5" t="inlineStr">
@@ -4619,19 +4611,15 @@
       <c r="E106" s="5" t="inlineStr"/>
       <c r="F106" s="6" t="inlineStr">
         <is>
-          <t>Thermal Stability</t>
+          <t>HNBR 라텍스</t>
         </is>
       </c>
       <c r="G106" s="7" t="n"/>
-      <c r="H106" s="8" t="inlineStr">
-        <is>
-          <t>Thermal Stability</t>
-        </is>
-      </c>
+      <c r="H106" s="8" t="n"/>
       <c r="I106" s="5" t="n"/>
       <c r="J106" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[2]/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[2]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4641,12 +4629,12 @@
       </c>
       <c r="B107" s="5" t="inlineStr">
         <is>
-          <t>04-2 LiFSI 전해염</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C107" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D107" s="5" t="inlineStr">
@@ -4657,19 +4645,15 @@
       <c r="E107" s="5" t="inlineStr"/>
       <c r="F107" s="6" t="inlineStr">
         <is>
-          <t>Long Cycle Life</t>
+          <t>NMP계 고분산 액상 바인더</t>
         </is>
       </c>
       <c r="G107" s="7" t="n"/>
-      <c r="H107" s="8" t="inlineStr">
-        <is>
-          <t>Long Cycle Life</t>
-        </is>
-      </c>
+      <c r="H107" s="8" t="n"/>
       <c r="I107" s="5" t="n"/>
       <c r="J107" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[3]/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[2]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4679,12 +4663,12 @@
       </c>
       <c r="B108" s="5" t="inlineStr">
         <is>
-          <t>04-2 LiFSI 전해염</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C108" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>표 값</t>
         </is>
       </c>
       <c r="D108" s="5" t="inlineStr">
@@ -4695,19 +4679,15 @@
       <c r="E108" s="5" t="inlineStr"/>
       <c r="F108" s="6" t="inlineStr">
         <is>
-          <t>Fast Charging</t>
+          <t>고형분 8~10%</t>
         </is>
       </c>
       <c r="G108" s="7" t="n"/>
-      <c r="H108" s="8" t="inlineStr">
-        <is>
-          <t>Fast Charging</t>
-        </is>
-      </c>
+      <c r="H108" s="8" t="n"/>
       <c r="I108" s="5" t="n"/>
       <c r="J108" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[4]/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[2]/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4697,7 @@
       </c>
       <c r="B109" s="5" t="inlineStr">
         <is>
-          <t>04-2 LiFSI 전해염</t>
+          <t>04-3 HNBR 바인더</t>
         </is>
       </c>
       <c r="C109" s="5" t="inlineStr">
@@ -4733,19 +4713,15 @@
       <c r="E109" s="5" t="inlineStr"/>
       <c r="F109" s="6" t="inlineStr">
         <is>
-          <t>Low Resistance &amp; Low Viscosity</t>
+          <t>PVDF 대체</t>
         </is>
       </c>
       <c r="G109" s="7" t="n"/>
-      <c r="H109" s="8" t="inlineStr">
-        <is>
-          <t>Low Resistance &amp; Low Viscosity</t>
-        </is>
-      </c>
+      <c r="H109" s="8" t="n"/>
       <c r="I109" s="5" t="n"/>
       <c r="J109" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[6]/div/div[2]/ul[2]/li[5]/p|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[1]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4760,7 +4736,7 @@
       </c>
       <c r="C110" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D110" s="5" t="inlineStr">
@@ -4771,19 +4747,15 @@
       <c r="E110" s="5" t="inlineStr"/>
       <c r="F110" s="6" t="inlineStr">
         <is>
-          <t>PVDF 바인더의 일부 대체 가능성을 검토할 수 있는 HNBR 바인더 소재입니다.</t>
+          <t>기존 불소계 바인더의 5~15% 이상을 친환경 HNBR로 대체.</t>
         </is>
       </c>
       <c r="G110" s="7" t="n"/>
-      <c r="H110" s="8" t="inlineStr">
-        <is>
-          <t>HNBR is a binder material that can be evaluated as a partial alternative to PVDF binders.</t>
-        </is>
-      </c>
+      <c r="H110" s="8" t="n"/>
       <c r="I110" s="5" t="n"/>
       <c r="J110" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[1]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4798,7 +4770,7 @@
       </c>
       <c r="C111" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D111" s="5" t="inlineStr">
@@ -4809,19 +4781,15 @@
       <c r="E111" s="5" t="inlineStr"/>
       <c r="F111" s="6" t="inlineStr">
         <is>
-          <t>우수한 결합력과 유연성, 전극 저항 감소 효과를 통해 배터리의 고율 충·방전 성능과 안정성 향상에 기여할 수 있습니다.</t>
+          <t>고율 충방전 특성</t>
         </is>
       </c>
       <c r="G111" s="7" t="n"/>
-      <c r="H111" s="8" t="inlineStr">
-        <is>
-          <t>With excellent bonding strength, flexibility, and reduced electrode resistance, it can contribute to improved high-rate charge/discharge performance and stability.</t>
-        </is>
-      </c>
+      <c r="H111" s="8" t="n"/>
       <c r="I111" s="5" t="n"/>
       <c r="J111" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[2]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4847,7 +4815,7 @@
       <c r="E112" s="5" t="inlineStr"/>
       <c r="F112" s="6" t="inlineStr">
         <is>
-          <t>CNT 분산용 고성능 고무 바인더</t>
+          <t>10C 고속 충전 조건에서도 우수한 용량 유지.</t>
         </is>
       </c>
       <c r="G112" s="7" t="n"/>
@@ -4855,7 +4823,7 @@
       <c r="I112" s="5" t="n"/>
       <c r="J112" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[1]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[2]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4870,7 +4838,7 @@
       </c>
       <c r="C113" s="5" t="inlineStr">
         <is>
-          <t>표 값</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D113" s="5" t="inlineStr">
@@ -4881,7 +4849,7 @@
       <c r="E113" s="5" t="inlineStr"/>
       <c r="F113" s="6" t="inlineStr">
         <is>
-          <t>포화도 99.6%</t>
+          <t>내부 저항 감소</t>
         </is>
       </c>
       <c r="G113" s="7" t="n"/>
@@ -4889,7 +4857,7 @@
       <c r="I113" s="5" t="n"/>
       <c r="J113" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[1]/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[3]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4904,7 +4872,7 @@
       </c>
       <c r="C114" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D114" s="5" t="inlineStr">
@@ -4915,7 +4883,7 @@
       <c r="E114" s="5" t="inlineStr"/>
       <c r="F114" s="6" t="inlineStr">
         <is>
-          <t>HNBR 라텍스</t>
+          <t>젖음성 개선으로 이온 전달 및 계면 저항 최소화.</t>
         </is>
       </c>
       <c r="G114" s="7" t="n"/>
@@ -4923,7 +4891,7 @@
       <c r="I114" s="5" t="n"/>
       <c r="J114" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[2]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[3]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -4938,7 +4906,7 @@
       </c>
       <c r="C115" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>표 왼쪽</t>
         </is>
       </c>
       <c r="D115" s="5" t="inlineStr">
@@ -4949,7 +4917,7 @@
       <c r="E115" s="5" t="inlineStr"/>
       <c r="F115" s="6" t="inlineStr">
         <is>
-          <t>NMP계 고분산 액상 바인더</t>
+          <t>높은 강도 및 유연성</t>
         </is>
       </c>
       <c r="G115" s="7" t="n"/>
@@ -4957,7 +4925,7 @@
       <c r="I115" s="5" t="n"/>
       <c r="J115" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[2]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[4]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -4972,7 +4940,7 @@
       </c>
       <c r="C116" s="5" t="inlineStr">
         <is>
-          <t>표 값</t>
+          <t>표 오른쪽</t>
         </is>
       </c>
       <c r="D116" s="5" t="inlineStr">
@@ -4983,7 +4951,7 @@
       <c r="E116" s="5" t="inlineStr"/>
       <c r="F116" s="6" t="inlineStr">
         <is>
-          <t>고형분 8~10%</t>
+          <t>전극 활물질 부피 변화 흡수, 탈락 방지.</t>
         </is>
       </c>
       <c r="G116" s="7" t="n"/>
@@ -4991,7 +4959,7 @@
       <c r="I116" s="5" t="n"/>
       <c r="J116" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[1]/li[2]/p[3]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[4]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -5017,7 +4985,7 @@
       <c r="E117" s="5" t="inlineStr"/>
       <c r="F117" s="6" t="inlineStr">
         <is>
-          <t>PVDF 대체</t>
+          <t>SWCNT 분산 최적화</t>
         </is>
       </c>
       <c r="G117" s="7" t="n"/>
@@ -5025,7 +4993,7 @@
       <c r="I117" s="5" t="n"/>
       <c r="J117" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[1]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[5]/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -5051,7 +5019,7 @@
       <c r="E118" s="5" t="inlineStr"/>
       <c r="F118" s="6" t="inlineStr">
         <is>
-          <t>기존 불소계 바인더의 5~15% 이상을 친환경 HNBR로 대체.</t>
+          <t>단일벽 탄소나노튜브의 응집 해소, 점도 감소.</t>
         </is>
       </c>
       <c r="G118" s="7" t="n"/>
@@ -5059,7 +5027,7 @@
       <c r="I118" s="5" t="n"/>
       <c r="J118" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[1]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[5]/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5037,12 @@
       </c>
       <c r="B119" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C119" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D119" s="5" t="inlineStr">
@@ -5085,15 +5053,19 @@
       <c r="E119" s="5" t="inlineStr"/>
       <c r="F119" s="6" t="inlineStr">
         <is>
-          <t>고율 충방전 특성</t>
+          <t>A-PRO Materials는 Lab-scale 파우치셀 제작 및 소재 적용성 검증 서비스를 제공합니다.</t>
         </is>
       </c>
       <c r="G119" s="7" t="n"/>
-      <c r="H119" s="8" t="n"/>
+      <c r="H119" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Materials provides lab-scale pouch cell fabrication and material validation services.</t>
+        </is>
+      </c>
       <c r="I119" s="5" t="n"/>
       <c r="J119" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[2]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -5103,12 +5075,12 @@
       </c>
       <c r="B120" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C120" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D120" s="5" t="inlineStr">
@@ -5119,15 +5091,19 @@
       <c r="E120" s="5" t="inlineStr"/>
       <c r="F120" s="6" t="inlineStr">
         <is>
-          <t>10C 고속 충전 조건에서도 우수한 용량 유지.</t>
+          <t>셀 설계부터 조립 공정, 품질 평가까지 통합 프로세스를 통해 고객사의 신소재 적용 가능성을 사전 검증합니다.</t>
         </is>
       </c>
       <c r="G120" s="7" t="n"/>
-      <c r="H120" s="8" t="n"/>
+      <c r="H120" s="8" t="inlineStr">
+        <is>
+          <t>Through an integrated process encompassing cell design, assembly, and quality evaluation, we help our clients pre-validate the applicability of new materials.</t>
+        </is>
+      </c>
       <c r="I120" s="5" t="n"/>
       <c r="J120" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[2]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -5137,31 +5113,31 @@
       </c>
       <c r="B121" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C121" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D121" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E121" s="5" t="inlineStr"/>
       <c r="F121" s="6" t="inlineStr">
         <is>
-          <t>내부 저항 감소</t>
-        </is>
-      </c>
-      <c r="G121" s="7" t="n"/>
-      <c r="H121" s="8" t="n"/>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="G121" s="6" t="n"/>
+      <c r="H121" s="6" t="n"/>
       <c r="I121" s="5" t="n"/>
       <c r="J121" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[3]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[1]/b|text</t>
         </is>
       </c>
     </row>
@@ -5171,12 +5147,12 @@
       </c>
       <c r="B122" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C122" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D122" s="5" t="inlineStr">
@@ -5187,7 +5163,7 @@
       <c r="E122" s="5" t="inlineStr"/>
       <c r="F122" s="6" t="inlineStr">
         <is>
-          <t>젖음성 개선으로 이온 전달 및 계면 저항 최소화.</t>
+          <t>사양 협의</t>
         </is>
       </c>
       <c r="G122" s="7" t="n"/>
@@ -5195,7 +5171,7 @@
       <c r="I122" s="5" t="n"/>
       <c r="J122" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[3]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[1]/span|text</t>
         </is>
       </c>
     </row>
@@ -5205,31 +5181,31 @@
       </c>
       <c r="B123" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C123" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D123" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E123" s="5" t="inlineStr"/>
       <c r="F123" s="6" t="inlineStr">
         <is>
-          <t>높은 강도 및 유연성</t>
-        </is>
-      </c>
-      <c r="G123" s="7" t="n"/>
-      <c r="H123" s="8" t="n"/>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="G123" s="6" t="n"/>
+      <c r="H123" s="6" t="n"/>
       <c r="I123" s="5" t="n"/>
       <c r="J123" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[4]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[2]/b|text</t>
         </is>
       </c>
     </row>
@@ -5239,12 +5215,12 @@
       </c>
       <c r="B124" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C124" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D124" s="5" t="inlineStr">
@@ -5255,7 +5231,7 @@
       <c r="E124" s="5" t="inlineStr"/>
       <c r="F124" s="6" t="inlineStr">
         <is>
-          <t>전극 활물질 부피 변화 흡수, 탈락 방지.</t>
+          <t>소재 입고 및 검수</t>
         </is>
       </c>
       <c r="G124" s="7" t="n"/>
@@ -5263,7 +5239,7 @@
       <c r="I124" s="5" t="n"/>
       <c r="J124" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[4]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[2]/span|text</t>
         </is>
       </c>
     </row>
@@ -5273,31 +5249,31 @@
       </c>
       <c r="B125" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C125" s="5" t="inlineStr">
         <is>
-          <t>표 왼쪽</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D125" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E125" s="5" t="inlineStr"/>
       <c r="F125" s="6" t="inlineStr">
         <is>
-          <t>SWCNT 분산 최적화</t>
-        </is>
-      </c>
-      <c r="G125" s="7" t="n"/>
-      <c r="H125" s="8" t="n"/>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="G125" s="6" t="n"/>
+      <c r="H125" s="6" t="n"/>
       <c r="I125" s="5" t="n"/>
       <c r="J125" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[5]/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[3]/b|text</t>
         </is>
       </c>
     </row>
@@ -5307,12 +5283,12 @@
       </c>
       <c r="B126" s="5" t="inlineStr">
         <is>
-          <t>04-3 HNBR 바인더</t>
+          <t>04-4 파우치셀 제조</t>
         </is>
       </c>
       <c r="C126" s="5" t="inlineStr">
         <is>
-          <t>표 오른쪽</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D126" s="5" t="inlineStr">
@@ -5323,7 +5299,7 @@
       <c r="E126" s="5" t="inlineStr"/>
       <c r="F126" s="6" t="inlineStr">
         <is>
-          <t>단일벽 탄소나노튜브의 응집 해소, 점도 감소.</t>
+          <t>파우치셀 조립</t>
         </is>
       </c>
       <c r="G126" s="7" t="n"/>
@@ -5331,7 +5307,7 @@
       <c r="I126" s="5" t="n"/>
       <c r="J126" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[7]/div/div[2]/ul[2]/li[5]/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[3]/span|text</t>
         </is>
       </c>
     </row>
@@ -5346,30 +5322,26 @@
       </c>
       <c r="C127" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D127" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E127" s="5" t="inlineStr"/>
       <c r="F127" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials는 Lab-scale 파우치셀 제작 및 소재 적용성 검증 서비스를 제공합니다.</t>
-        </is>
-      </c>
-      <c r="G127" s="7" t="n"/>
-      <c r="H127" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Materials provides lab-scale pouch cell fabrication and material validation services.</t>
-        </is>
-      </c>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="G127" s="6" t="n"/>
+      <c r="H127" s="6" t="n"/>
       <c r="I127" s="5" t="n"/>
       <c r="J127" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[4]/b|text</t>
         </is>
       </c>
     </row>
@@ -5384,7 +5356,7 @@
       </c>
       <c r="C128" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D128" s="5" t="inlineStr">
@@ -5395,19 +5367,15 @@
       <c r="E128" s="5" t="inlineStr"/>
       <c r="F128" s="6" t="inlineStr">
         <is>
-          <t>셀 설계부터 조립 공정, 품질 평가까지 통합 프로세스를 통해 고객사의 신소재 적용 가능성을 사전 검증합니다.</t>
+          <t>화성 공정</t>
         </is>
       </c>
       <c r="G128" s="7" t="n"/>
-      <c r="H128" s="8" t="inlineStr">
-        <is>
-          <t>Through an integrated process encompassing cell design, assembly, and quality evaluation, we help our clients pre-validate the applicability of new materials.</t>
-        </is>
-      </c>
+      <c r="H128" s="8" t="n"/>
       <c r="I128" s="5" t="n"/>
       <c r="J128" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[4]/span|text</t>
         </is>
       </c>
     </row>
@@ -5433,7 +5401,7 @@
       <c r="E129" s="5" t="inlineStr"/>
       <c r="F129" s="6" t="inlineStr">
         <is>
-          <t>01</t>
+          <t>05</t>
         </is>
       </c>
       <c r="G129" s="6" t="n"/>
@@ -5441,7 +5409,7 @@
       <c r="I129" s="5" t="n"/>
       <c r="J129" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[1]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[5]/b|text</t>
         </is>
       </c>
     </row>
@@ -5467,7 +5435,7 @@
       <c r="E130" s="5" t="inlineStr"/>
       <c r="F130" s="6" t="inlineStr">
         <is>
-          <t>사양 협의</t>
+          <t>제품 출하</t>
         </is>
       </c>
       <c r="G130" s="7" t="n"/>
@@ -5475,7 +5443,7 @@
       <c r="I130" s="5" t="n"/>
       <c r="J130" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[1]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[5]/span|text</t>
         </is>
       </c>
     </row>
@@ -5485,31 +5453,35 @@
       </c>
       <c r="B131" s="5" t="inlineStr">
         <is>
-          <t>04-4 파우치셀 제조</t>
+          <t>04-5 에이프로머티리얼즈</t>
         </is>
       </c>
       <c r="C131" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D131" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E131" s="5" t="inlineStr"/>
       <c r="F131" s="6" t="inlineStr">
         <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="G131" s="6" t="n"/>
-      <c r="H131" s="6" t="n"/>
+          <t>A-PRO Materials는 차세대 배터리 핵심 기술에 대한 지속적인 연구개발을 통해 미래 이차전지 시장에 대응해 나갑니다.</t>
+        </is>
+      </c>
+      <c r="G131" s="7" t="n"/>
+      <c r="H131" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Materials is working to respond to the future secondary battery market through continuous research and development of core next-generation battery technologies.</t>
+        </is>
+      </c>
       <c r="I131" s="5" t="n"/>
       <c r="J131" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[2]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[1]|text</t>
         </is>
       </c>
     </row>
@@ -5519,12 +5491,12 @@
       </c>
       <c r="B132" s="5" t="inlineStr">
         <is>
-          <t>04-4 파우치셀 제조</t>
+          <t>04-5 에이프로머티리얼즈</t>
         </is>
       </c>
       <c r="C132" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D132" s="5" t="inlineStr">
@@ -5535,15 +5507,19 @@
       <c r="E132" s="5" t="inlineStr"/>
       <c r="F132" s="6" t="inlineStr">
         <is>
-          <t>소재 입고 및 검수</t>
+          <t>끊임없는 R&amp;D 혁신으로 기존 배터리의 한계를 극복하고, 고성능·고안정성 소재 및 셀 기술을 선제적으로 구현해 나갑니다.</t>
         </is>
       </c>
       <c r="G132" s="7" t="n"/>
-      <c r="H132" s="8" t="n"/>
+      <c r="H132" s="8" t="inlineStr">
+        <is>
+          <t>Through ongoing R&amp;D innovation, we work to overcome the limitations of existing batteries and proactively develop high-performance, high-stability materials and cell technologies.</t>
+        </is>
+      </c>
       <c r="I132" s="5" t="n"/>
       <c r="J132" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[2]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[2]|text</t>
         </is>
       </c>
     </row>
@@ -5553,31 +5529,35 @@
       </c>
       <c r="B133" s="5" t="inlineStr">
         <is>
-          <t>04-4 파우치셀 제조</t>
+          <t>04-5 에이프로머티리얼즈</t>
         </is>
       </c>
       <c r="C133" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>본문</t>
         </is>
       </c>
       <c r="D133" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E133" s="5" t="inlineStr"/>
       <c r="F133" s="6" t="inlineStr">
         <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="G133" s="6" t="n"/>
-      <c r="H133" s="6" t="n"/>
+          <t>A-PRO Materials는 국내외 파트너들과의 협력을 통해 최적의 이차전지 소재 솔루션을 모색하고 있습니다.</t>
+        </is>
+      </c>
+      <c r="G133" s="7" t="n"/>
+      <c r="H133" s="8" t="inlineStr">
+        <is>
+          <t>A-PRO Materials is exploring optimal secondary battery material solutions in collaboration with partners at home and abroad.</t>
+        </is>
+      </c>
       <c r="I133" s="5" t="n"/>
       <c r="J133" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[3]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[3]|text</t>
         </is>
       </c>
     </row>
@@ -5587,31 +5567,31 @@
       </c>
       <c r="B134" s="5" t="inlineStr">
         <is>
-          <t>04-4 파우치셀 제조</t>
+          <t>04-5 에이프로머티리얼즈</t>
         </is>
       </c>
       <c r="C134" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D134" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E134" s="5" t="inlineStr"/>
       <c r="F134" s="6" t="inlineStr">
         <is>
-          <t>파우치셀 조립</t>
-        </is>
-      </c>
-      <c r="G134" s="7" t="n"/>
-      <c r="H134" s="8" t="n"/>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="G134" s="6" t="n"/>
+      <c r="H134" s="6" t="n"/>
       <c r="I134" s="5" t="n"/>
       <c r="J134" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[3]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/b|text</t>
         </is>
       </c>
     </row>
@@ -5621,31 +5601,31 @@
       </c>
       <c r="B135" s="5" t="inlineStr">
         <is>
-          <t>04-4 파우치셀 제조</t>
+          <t>04-5 에이프로머티리얼즈</t>
         </is>
       </c>
       <c r="C135" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D135" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E135" s="5" t="inlineStr"/>
       <c r="F135" s="6" t="inlineStr">
         <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="G135" s="6" t="n"/>
-      <c r="H135" s="6" t="n"/>
+          <t>소듐 이온 배터리</t>
+        </is>
+      </c>
+      <c r="G135" s="7" t="n"/>
+      <c r="H135" s="8" t="n"/>
       <c r="I135" s="5" t="n"/>
       <c r="J135" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[4]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/span|text</t>
         </is>
       </c>
     </row>
@@ -5655,31 +5635,31 @@
       </c>
       <c r="B136" s="5" t="inlineStr">
         <is>
-          <t>04-4 파우치셀 제조</t>
+          <t>04-5 에이프로머티리얼즈</t>
         </is>
       </c>
       <c r="C136" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D136" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E136" s="5" t="inlineStr"/>
       <c r="F136" s="6" t="inlineStr">
         <is>
-          <t>화성 공정</t>
-        </is>
-      </c>
-      <c r="G136" s="7" t="n"/>
-      <c r="H136" s="8" t="n"/>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="G136" s="6" t="n"/>
+      <c r="H136" s="6" t="n"/>
       <c r="I136" s="5" t="n"/>
       <c r="J136" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[4]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/b|text</t>
         </is>
       </c>
     </row>
@@ -5689,31 +5669,31 @@
       </c>
       <c r="B137" s="5" t="inlineStr">
         <is>
-          <t>04-4 파우치셀 제조</t>
+          <t>04-5 에이프로머티리얼즈</t>
         </is>
       </c>
       <c r="C137" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 번호</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D137" s="5" t="inlineStr">
         <is>
-          <t>번호</t>
+          <t>문구</t>
         </is>
       </c>
       <c r="E137" s="5" t="inlineStr"/>
       <c r="F137" s="6" t="inlineStr">
         <is>
-          <t>05</t>
-        </is>
-      </c>
-      <c r="G137" s="6" t="n"/>
-      <c r="H137" s="6" t="n"/>
+          <t>반도체 전지</t>
+        </is>
+      </c>
+      <c r="G137" s="7" t="n"/>
+      <c r="H137" s="8" t="n"/>
       <c r="I137" s="5" t="n"/>
       <c r="J137" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[5]/b|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/span|text</t>
         </is>
       </c>
     </row>
@@ -5723,31 +5703,31 @@
       </c>
       <c r="B138" s="5" t="inlineStr">
         <is>
-          <t>04-4 파우치셀 제조</t>
+          <t>04-5 에이프로머티리얼즈</t>
         </is>
       </c>
       <c r="C138" s="5" t="inlineStr">
         <is>
-          <t>번호 목록 항목</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D138" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E138" s="5" t="inlineStr"/>
       <c r="F138" s="6" t="inlineStr">
         <is>
-          <t>제품 출하</t>
-        </is>
-      </c>
-      <c r="G138" s="7" t="n"/>
-      <c r="H138" s="8" t="n"/>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="G138" s="6" t="n"/>
+      <c r="H138" s="6" t="n"/>
       <c r="I138" s="5" t="n"/>
       <c r="J138" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[8]/div/div[2]/ol/li[5]/span|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/b|text</t>
         </is>
       </c>
     </row>
@@ -5762,7 +5742,7 @@
       </c>
       <c r="C139" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D139" s="5" t="inlineStr">
@@ -5773,19 +5753,15 @@
       <c r="E139" s="5" t="inlineStr"/>
       <c r="F139" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials는 차세대 배터리 핵심 기술에 대한 지속적인 연구개발을 통해 미래 이차전지 시장에 대응해 나갑니다.</t>
+          <t>전고체 전지</t>
         </is>
       </c>
       <c r="G139" s="7" t="n"/>
-      <c r="H139" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Materials is working to respond to the future secondary battery market through continuous research and development of core next-generation battery technologies.</t>
-        </is>
-      </c>
+      <c r="H139" s="8" t="n"/>
       <c r="I139" s="5" t="n"/>
       <c r="J139" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[1]|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/span|text</t>
         </is>
       </c>
     </row>
@@ -5800,30 +5776,26 @@
       </c>
       <c r="C140" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>번호 목록 번호</t>
         </is>
       </c>
       <c r="D140" s="5" t="inlineStr">
         <is>
-          <t>문구</t>
+          <t>번호</t>
         </is>
       </c>
       <c r="E140" s="5" t="inlineStr"/>
       <c r="F140" s="6" t="inlineStr">
         <is>
-          <t>끊임없는 R&amp;D 혁신으로 기존 배터리의 한계를 극복하고, 고성능·고안정성 소재 및 셀 기술을 선제적으로 구현해 나갑니다.</t>
-        </is>
-      </c>
-      <c r="G140" s="7" t="n"/>
-      <c r="H140" s="8" t="inlineStr">
-        <is>
-          <t>Through ongoing R&amp;D innovation, we work to overcome the limitations of existing batteries and proactively develop high-performance, high-stability materials and cell technologies.</t>
-        </is>
-      </c>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="G140" s="6" t="n"/>
+      <c r="H140" s="6" t="n"/>
       <c r="I140" s="5" t="n"/>
       <c r="J140" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[2]|text</t>
+          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[4]/b|text</t>
         </is>
       </c>
     </row>
@@ -5838,7 +5810,7 @@
       </c>
       <c r="C141" s="5" t="inlineStr">
         <is>
-          <t>본문</t>
+          <t>번호 목록 항목</t>
         </is>
       </c>
       <c r="D141" s="5" t="inlineStr">
@@ -5849,296 +5821,20 @@
       <c r="E141" s="5" t="inlineStr"/>
       <c r="F141" s="6" t="inlineStr">
         <is>
-          <t>A-PRO Materials는 국내외 파트너들과의 협력을 통해 최적의 이차전지 소재 솔루션을 모색하고 있습니다.</t>
+          <t>무음극 전지</t>
         </is>
       </c>
       <c r="G141" s="7" t="n"/>
-      <c r="H141" s="8" t="inlineStr">
-        <is>
-          <t>A-PRO Materials is exploring optimal secondary battery material solutions in collaboration with partners at home and abroad.</t>
-        </is>
-      </c>
+      <c r="H141" s="8" t="n"/>
       <c r="I141" s="5" t="n"/>
       <c r="J141" s="9" t="inlineStr">
         <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/div/div/p[3]|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" s="5" t="n">
-        <v>141</v>
-      </c>
-      <c r="B142" s="5" t="inlineStr">
-        <is>
-          <t>04-5 에이프로머티리얼즈</t>
-        </is>
-      </c>
-      <c r="C142" s="5" t="inlineStr">
-        <is>
-          <t>번호 목록 번호</t>
-        </is>
-      </c>
-      <c r="D142" s="5" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="E142" s="5" t="inlineStr"/>
-      <c r="F142" s="6" t="inlineStr">
-        <is>
-          <t>01</t>
-        </is>
-      </c>
-      <c r="G142" s="6" t="n"/>
-      <c r="H142" s="6" t="n"/>
-      <c r="I142" s="5" t="n"/>
-      <c r="J142" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/b|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" s="5" t="n">
-        <v>142</v>
-      </c>
-      <c r="B143" s="5" t="inlineStr">
-        <is>
-          <t>04-5 에이프로머티리얼즈</t>
-        </is>
-      </c>
-      <c r="C143" s="5" t="inlineStr">
-        <is>
-          <t>번호 목록 항목</t>
-        </is>
-      </c>
-      <c r="D143" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E143" s="5" t="inlineStr"/>
-      <c r="F143" s="6" t="inlineStr">
-        <is>
-          <t>소듐 이온 배터리</t>
-        </is>
-      </c>
-      <c r="G143" s="7" t="n"/>
-      <c r="H143" s="8" t="n"/>
-      <c r="I143" s="5" t="n"/>
-      <c r="J143" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[1]/span|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" s="5" t="n">
-        <v>143</v>
-      </c>
-      <c r="B144" s="5" t="inlineStr">
-        <is>
-          <t>04-5 에이프로머티리얼즈</t>
-        </is>
-      </c>
-      <c r="C144" s="5" t="inlineStr">
-        <is>
-          <t>번호 목록 번호</t>
-        </is>
-      </c>
-      <c r="D144" s="5" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="E144" s="5" t="inlineStr"/>
-      <c r="F144" s="6" t="inlineStr">
-        <is>
-          <t>02</t>
-        </is>
-      </c>
-      <c r="G144" s="6" t="n"/>
-      <c r="H144" s="6" t="n"/>
-      <c r="I144" s="5" t="n"/>
-      <c r="J144" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/b|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" s="5" t="n">
-        <v>144</v>
-      </c>
-      <c r="B145" s="5" t="inlineStr">
-        <is>
-          <t>04-5 에이프로머티리얼즈</t>
-        </is>
-      </c>
-      <c r="C145" s="5" t="inlineStr">
-        <is>
-          <t>번호 목록 항목</t>
-        </is>
-      </c>
-      <c r="D145" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E145" s="5" t="inlineStr"/>
-      <c r="F145" s="6" t="inlineStr">
-        <is>
-          <t>반도체 전지</t>
-        </is>
-      </c>
-      <c r="G145" s="7" t="n"/>
-      <c r="H145" s="8" t="n"/>
-      <c r="I145" s="5" t="n"/>
-      <c r="J145" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[2]/span|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" s="5" t="n">
-        <v>145</v>
-      </c>
-      <c r="B146" s="5" t="inlineStr">
-        <is>
-          <t>04-5 에이프로머티리얼즈</t>
-        </is>
-      </c>
-      <c r="C146" s="5" t="inlineStr">
-        <is>
-          <t>번호 목록 번호</t>
-        </is>
-      </c>
-      <c r="D146" s="5" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="E146" s="5" t="inlineStr"/>
-      <c r="F146" s="6" t="inlineStr">
-        <is>
-          <t>03</t>
-        </is>
-      </c>
-      <c r="G146" s="6" t="n"/>
-      <c r="H146" s="6" t="n"/>
-      <c r="I146" s="5" t="n"/>
-      <c r="J146" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/b|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" s="5" t="n">
-        <v>146</v>
-      </c>
-      <c r="B147" s="5" t="inlineStr">
-        <is>
-          <t>04-5 에이프로머티리얼즈</t>
-        </is>
-      </c>
-      <c r="C147" s="5" t="inlineStr">
-        <is>
-          <t>번호 목록 항목</t>
-        </is>
-      </c>
-      <c r="D147" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E147" s="5" t="inlineStr"/>
-      <c r="F147" s="6" t="inlineStr">
-        <is>
-          <t>전고체 전지</t>
-        </is>
-      </c>
-      <c r="G147" s="7" t="n"/>
-      <c r="H147" s="8" t="n"/>
-      <c r="I147" s="5" t="n"/>
-      <c r="J147" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[3]/span|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" s="5" t="n">
-        <v>147</v>
-      </c>
-      <c r="B148" s="5" t="inlineStr">
-        <is>
-          <t>04-5 에이프로머티리얼즈</t>
-        </is>
-      </c>
-      <c r="C148" s="5" t="inlineStr">
-        <is>
-          <t>번호 목록 번호</t>
-        </is>
-      </c>
-      <c r="D148" s="5" t="inlineStr">
-        <is>
-          <t>번호</t>
-        </is>
-      </c>
-      <c r="E148" s="5" t="inlineStr"/>
-      <c r="F148" s="6" t="inlineStr">
-        <is>
-          <t>04</t>
-        </is>
-      </c>
-      <c r="G148" s="6" t="n"/>
-      <c r="H148" s="6" t="n"/>
-      <c r="I148" s="5" t="n"/>
-      <c r="J148" s="9" t="inlineStr">
-        <is>
-          <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[4]/b|text</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" s="5" t="n">
-        <v>148</v>
-      </c>
-      <c r="B149" s="5" t="inlineStr">
-        <is>
-          <t>04-5 에이프로머티리얼즈</t>
-        </is>
-      </c>
-      <c r="C149" s="5" t="inlineStr">
-        <is>
-          <t>번호 목록 항목</t>
-        </is>
-      </c>
-      <c r="D149" s="5" t="inlineStr">
-        <is>
-          <t>문구</t>
-        </is>
-      </c>
-      <c r="E149" s="5" t="inlineStr"/>
-      <c r="F149" s="6" t="inlineStr">
-        <is>
-          <t>무음극 전지</t>
-        </is>
-      </c>
-      <c r="G149" s="7" t="n"/>
-      <c r="H149" s="8" t="n"/>
-      <c r="I149" s="5" t="n"/>
-      <c r="J149" s="9" t="inlineStr">
-        <is>
           <t>/html/body/div[8]/div[3]/section[9]/div/div[2]/ol/li[4]/span|text</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J149"/>
+  <autoFilter ref="A1:J141"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>

--- a/content-export/04_사업영역_문구.xlsx
+++ b/content-export/04_사업영역_문구.xlsx
@@ -8,16 +8,18 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="안내" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="스마트 제조" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="에너지 인프라" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인공지능 플랫폼" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화합물 전력 반도체" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="홈" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="스마트 제조" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="에너지 인프라" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="인공지능 플랫폼" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="화합물 전력 반도체" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'스마트 제조'!$A$1:$J$141</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'에너지 인프라'!$A$1:$J$189</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'인공지능 플랫폼'!$A$1:$J$47</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'화합물 전력 반도체'!$A$1:$J$25</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'홈'!$A$1:$J$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'스마트 제조'!$A$1:$J$141</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'에너지 인프라'!$A$1:$J$189</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'인공지능 플랫폼'!$A$1:$J$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'화합물 전력 반도체'!$A$1:$J$25</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -500,7 +502,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="B1:B34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -686,12 +688,1822 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>홈 시트 (2026-10-07 추가)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>홈(시안 C, index-c.html)의 문구입니다. 히어로 · Business · Who we are · News 순서로, 화면에 보이는 순서대로 담았습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>채우는 법은 사업영역 시트와 같습니다 — 노란 칸에 한글, 파란 칸에 영문. 같은 문구가 여러 자리에 있으면(사업영역 이름이 히어로 탭 · 카드에 함께 있는 것 등) 한 줄로 합쳤습니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>보도자료 기사 제목 · 날짜는 게시판 글이라 넣지 않았습니다. 게시판에서 고칩니다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>사업영역 시트는 A-1 장 기준으로 뽑은 그대로입니다(2026-09-17). 홈 시트만 지금 시안 C 기준입니다.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:J47"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="6" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
+    <col width="8" customWidth="1" min="4" max="4"/>
+    <col width="6" customWidth="1" min="5" max="5"/>
+    <col width="54" customWidth="1" min="6" max="6"/>
+    <col width="54" customWidth="1" min="7" max="7"/>
+    <col width="54" customWidth="1" min="8" max="8"/>
+    <col width="20" customWidth="1" min="9" max="9"/>
+    <col width="44" customWidth="1" min="10" max="10"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="24" customHeight="1">
+      <c r="A1" s="4" t="inlineStr">
+        <is>
+          <t>순번</t>
+        </is>
+      </c>
+      <c r="B1" s="4" t="inlineStr">
+        <is>
+          <t>섹션</t>
+        </is>
+      </c>
+      <c r="C1" s="4" t="inlineStr">
+        <is>
+          <t>자리</t>
+        </is>
+      </c>
+      <c r="D1" s="4" t="inlineStr">
+        <is>
+          <t>구분</t>
+        </is>
+      </c>
+      <c r="E1" s="4" t="inlineStr">
+        <is>
+          <t>묶음</t>
+        </is>
+      </c>
+      <c r="F1" s="4" t="inlineStr">
+        <is>
+          <t>현재 문구</t>
+        </is>
+      </c>
+      <c r="G1" s="4" t="inlineStr">
+        <is>
+          <t>변경 문구</t>
+        </is>
+      </c>
+      <c r="H1" s="4" t="inlineStr">
+        <is>
+          <t>영문 문구</t>
+        </is>
+      </c>
+      <c r="I1" s="4" t="inlineStr">
+        <is>
+          <t>비고</t>
+        </is>
+      </c>
+      <c r="J1" s="4" t="inlineStr">
+        <is>
+          <t>자리표(건드리지 마세요)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="5" t="inlineStr">
+        <is>
+          <t>히어로</t>
+        </is>
+      </c>
+      <c r="C2" s="5" t="inlineStr">
+        <is>
+          <t>페이지 제목(화면 낭독기용)</t>
+        </is>
+      </c>
+      <c r="D2" s="5" t="inlineStr">
+        <is>
+          <t>숨김글</t>
+        </is>
+      </c>
+      <c r="E2" s="5" t="n"/>
+      <c r="F2" s="6" t="inlineStr">
+        <is>
+          <t>에이프로 APRO</t>
+        </is>
+      </c>
+      <c r="G2" s="7" t="n"/>
+      <c r="H2" s="8" t="n"/>
+      <c r="I2" s="5" t="n"/>
+      <c r="J2" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/h1|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="5" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" s="5" t="inlineStr">
+        <is>
+          <t>히어로</t>
+        </is>
+      </c>
+      <c r="C3" s="5" t="inlineStr">
+        <is>
+          <t>메인 문구</t>
+        </is>
+      </c>
+      <c r="D3" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E3" s="5" t="n"/>
+      <c r="F3" s="6" t="inlineStr">
+        <is>
+          <t>에이프로는 함께 나아가는 기업입니다</t>
+        </is>
+      </c>
+      <c r="G3" s="7" t="n"/>
+      <c r="H3" s="8" t="n"/>
+      <c r="I3" s="5" t="n"/>
+      <c r="J3" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[1]/div/div/div[1]/p[1]|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" s="5" t="inlineStr">
+        <is>
+          <t>히어로</t>
+        </is>
+      </c>
+      <c r="C4" s="5" t="inlineStr">
+        <is>
+          <t>서브 문구</t>
+        </is>
+      </c>
+      <c r="D4" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E4" s="5" t="n"/>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>당신이 향하는 세상으로 우리도 같이 나아갑니다</t>
+        </is>
+      </c>
+      <c r="G4" s="7" t="n"/>
+      <c r="H4" s="8" t="n"/>
+      <c r="I4" s="5" t="n"/>
+      <c r="J4" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[1]/div/div/div[1]/p[2]|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" s="5" t="inlineStr">
+        <is>
+          <t>히어로</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="inlineStr">
+        <is>
+          <t>하단 탭</t>
+        </is>
+      </c>
+      <c r="D5" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E5" s="5" t="n"/>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>에이프로</t>
+        </is>
+      </c>
+      <c r="G5" s="7" t="n"/>
+      <c r="H5" s="8" t="n"/>
+      <c r="I5" s="5" t="n"/>
+      <c r="J5" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[1]/div/div/div[2]/div/div/span[1]/span|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="5" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" s="5" t="inlineStr">
+        <is>
+          <t>히어로 · Business</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="inlineStr">
+        <is>
+          <t>하단 탭 · 카드 이름</t>
+        </is>
+      </c>
+      <c r="D6" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E6" s="5" t="n"/>
+      <c r="F6" s="6" t="inlineStr">
+        <is>
+          <t>스마트 제조</t>
+        </is>
+      </c>
+      <c r="G6" s="7" t="n"/>
+      <c r="H6" s="8" t="n"/>
+      <c r="I6" s="5" t="inlineStr">
+        <is>
+          <t>같은 문구 3 곳 — 한 줄로 합침
+카드 제목 자리는 두 줄로 나눠 보입니다 — 줄 나눌 곳이 따로 있으면 비고에 적어 주세요
+GNB · 메가 메뉴 · 푸터의 사업영역 이름도 함께 고칩니다</t>
+        </is>
+      </c>
+      <c r="J6" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[1]/div/div/div[2]/div/div/span[2]/span|text
+/html/body/div[3]/section[2]/div[2]/ul/li[1]/span/span|text
+/html/body/div[3]/section[2]/div[2]/ul/li[1]/div/div[1]/div/h3/a|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" s="5" t="inlineStr">
+        <is>
+          <t>히어로 · Business</t>
+        </is>
+      </c>
+      <c r="C7" s="5" t="inlineStr">
+        <is>
+          <t>하단 탭 · 카드 이름</t>
+        </is>
+      </c>
+      <c r="D7" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>에너지 인프라</t>
+        </is>
+      </c>
+      <c r="G7" s="7" t="n"/>
+      <c r="H7" s="8" t="n"/>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>같은 문구 3 곳 — 한 줄로 합침
+카드 제목 자리는 두 줄로 나눠 보입니다 — 줄 나눌 곳이 따로 있으면 비고에 적어 주세요
+GNB · 메가 메뉴 · 푸터의 사업영역 이름도 함께 고칩니다</t>
+        </is>
+      </c>
+      <c r="J7" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[1]/div/div/div[2]/div/div/span[3]/span|text
+/html/body/div[3]/section[2]/div[2]/ul/li[2]/span/span|text
+/html/body/div[3]/section[2]/div[2]/ul/li[2]/div/div[1]/div/h3/a|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" s="5" t="inlineStr">
+        <is>
+          <t>히어로 · Business</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="inlineStr">
+        <is>
+          <t>하단 탭 · 카드 이름</t>
+        </is>
+      </c>
+      <c r="D8" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="6" t="inlineStr">
+        <is>
+          <t>인공지능 플랫폼</t>
+        </is>
+      </c>
+      <c r="G8" s="7" t="n"/>
+      <c r="H8" s="8" t="n"/>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>같은 문구 3 곳 — 한 줄로 합침
+카드 제목 자리는 두 줄로 나눠 보입니다 — 줄 나눌 곳이 따로 있으면 비고에 적어 주세요
+GNB · 메가 메뉴 · 푸터의 사업영역 이름도 함께 고칩니다</t>
+        </is>
+      </c>
+      <c r="J8" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[1]/div/div/div[2]/div/div/span[4]/span|text
+/html/body/div[3]/section[2]/div[2]/ul/li[3]/span/span|text
+/html/body/div[3]/section[2]/div[2]/ul/li[3]/div/div[1]/div/h3/a|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" s="5" t="inlineStr">
+        <is>
+          <t>히어로 · Business</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="inlineStr">
+        <is>
+          <t>하단 탭 · 카드 이름</t>
+        </is>
+      </c>
+      <c r="D9" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E9" s="5" t="n"/>
+      <c r="F9" s="6" t="inlineStr">
+        <is>
+          <t>화합물 전력 반도체</t>
+        </is>
+      </c>
+      <c r="G9" s="7" t="n"/>
+      <c r="H9" s="8" t="n"/>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>같은 문구 3 곳 — 한 줄로 합침
+카드 제목 자리는 두 줄로 나눠 보입니다 — 줄 나눌 곳이 따로 있으면 비고에 적어 주세요
+GNB · 메가 메뉴 · 푸터의 사업영역 이름도 함께 고칩니다</t>
+        </is>
+      </c>
+      <c r="J9" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[1]/div/div/div[2]/div/div/span[5]/span|text
+/html/body/div[3]/section[2]/div[2]/ul/li[4]/span/span|text
+/html/body/div[3]/section[2]/div[2]/ul/li[4]/div/div[1]/div/h3/a|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" s="5" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="C10" s="5" t="inlineStr">
+        <is>
+          <t>섹션 제목</t>
+        </is>
+      </c>
+      <c r="D10" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E10" s="5" t="n"/>
+      <c r="F10" s="6" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="G10" s="7" t="n"/>
+      <c r="H10" s="8" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="n"/>
+      <c r="J10" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[2]/div[1]/h2|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" s="5" t="inlineStr">
+        <is>
+          <t>Business</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="inlineStr">
+        <is>
+          <t>섹션 라벨</t>
+        </is>
+      </c>
+      <c r="D11" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E11" s="5" t="n"/>
+      <c r="F11" s="6" t="inlineStr">
+        <is>
+          <t>사업영역</t>
+        </is>
+      </c>
+      <c r="G11" s="7" t="n"/>
+      <c r="H11" s="8" t="n"/>
+      <c r="I11" s="5" t="n"/>
+      <c r="J11" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[2]/div[1]/h2/span|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" s="5" t="inlineStr">
+        <is>
+          <t>Business · 스마트 제조</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="inlineStr">
+        <is>
+          <t>카드 설명</t>
+        </is>
+      </c>
+      <c r="D12" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E12" s="5" t="n"/>
+      <c r="F12" s="6" t="inlineStr">
+        <is>
+          <t>이차전지 활성화 공정의 주요 설비를 자체 기술로 만듭니다.
+셀의 성능과 품질을 결정짓는 마지막 공정까지, A-PRO가 책임집니다.</t>
+        </is>
+      </c>
+      <c r="G12" s="7" t="n"/>
+      <c r="H12" s="8" t="n"/>
+      <c r="I12" s="5" t="n"/>
+      <c r="J12" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[2]/div[2]/ul/li[1]/div/div[1]/div/p|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" s="5" t="inlineStr">
+        <is>
+          <t>Business · 스마트 제조</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="inlineStr">
+        <is>
+          <t>소분류 링크</t>
+        </is>
+      </c>
+      <c r="D13" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E13" s="5" t="n"/>
+      <c r="F13" s="6" t="inlineStr">
+        <is>
+          <t>이차전지 활성화</t>
+        </is>
+      </c>
+      <c r="G13" s="7" t="n"/>
+      <c r="H13" s="8" t="n"/>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>사업영역 세부 시트의 소분류 이름과 같은 글 — 한쪽을 바꾸면 함께 고칩니다</t>
+        </is>
+      </c>
+      <c r="J13" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[2]/div[2]/ul/li[1]/div/div[2]/ul/li[1]/a|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" s="5" t="inlineStr">
+        <is>
+          <t>Business · 스마트 제조</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="inlineStr">
+        <is>
+          <t>소분류 링크</t>
+        </is>
+      </c>
+      <c r="D14" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E14" s="5" t="n"/>
+      <c r="F14" s="6" t="inlineStr">
+        <is>
+          <t>Cycler(Cell&amp;Module)</t>
+        </is>
+      </c>
+      <c r="G14" s="7" t="n"/>
+      <c r="H14" s="8" t="inlineStr">
+        <is>
+          <t>Cycler(Cell&amp;Module)</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>사업영역 세부 시트의 소분류 이름과 같은 글 — 한쪽을 바꾸면 함께 고칩니다</t>
+        </is>
+      </c>
+      <c r="J14" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[2]/div[2]/ul/li[1]/div/div[2]/ul/li[2]/a|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>Business · 스마트 제조</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="inlineStr">
+        <is>
+          <t>소분류 링크</t>
+        </is>
+      </c>
+      <c r="D15" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E15" s="5" t="n"/>
+      <c r="F15" s="6" t="inlineStr">
+        <is>
+          <t>자동화 시스템</t>
+        </is>
+      </c>
+      <c r="G15" s="7" t="n"/>
+      <c r="H15" s="8" t="n"/>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>사업영역 세부 시트의 소분류 이름과 같은 글 — 한쪽을 바꾸면 함께 고칩니다</t>
+        </is>
+      </c>
+      <c r="J15" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[2]/div[2]/ul/li[1]/div/div[2]/ul/li[3]/a|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" s="5" t="inlineStr">
+        <is>
+          <t>Business · 스마트 제조</t>
+        </is>
+      </c>
+      <c r="C16" s="5" t="inlineStr">
+        <is>
+          <t>소분류 링크</t>
+        </is>
+      </c>
+      <c r="D16" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E16" s="5" t="n"/>
+      <c r="F16" s="6" t="inlineStr">
+        <is>
+          <t>이차전지 소재</t>
+        </is>
+      </c>
+      <c r="G16" s="7" t="n"/>
+      <c r="H16" s="8" t="n"/>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>사업영역 세부 시트의 소분류 이름과 같은 글 — 한쪽을 바꾸면 함께 고칩니다</t>
+        </is>
+      </c>
+      <c r="J16" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[2]/div[2]/ul/li[1]/div/div[2]/ul/li[4]/a|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="5" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>Business · 에너지 인프라</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="inlineStr">
+        <is>
+          <t>카드 설명</t>
+        </is>
+      </c>
+      <c r="D17" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E17" s="5" t="n"/>
+      <c r="F17" s="6" t="inlineStr">
+        <is>
+          <t>배터리로 전력을 저장하고, 끊기지 않게 지켜냅니다.
+그리드 규모 ESS부터 우주 발사체 전원까지 아우릅니다.</t>
+        </is>
+      </c>
+      <c r="G17" s="7" t="n"/>
+      <c r="H17" s="8" t="n"/>
+      <c r="I17" s="5" t="n"/>
+      <c r="J17" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[2]/div[2]/ul/li[2]/div/div[1]/div/p|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>Business · 에너지 인프라</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="inlineStr">
+        <is>
+          <t>소분류 링크</t>
+        </is>
+      </c>
+      <c r="D18" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E18" s="5" t="n"/>
+      <c r="F18" s="6" t="inlineStr">
+        <is>
+          <t>ESS</t>
+        </is>
+      </c>
+      <c r="G18" s="7" t="n"/>
+      <c r="H18" s="8" t="inlineStr">
+        <is>
+          <t>ESS</t>
+        </is>
+      </c>
+      <c r="I18" s="5" t="inlineStr">
+        <is>
+          <t>사업영역 세부 시트의 소분류 이름과 같은 글 — 한쪽을 바꾸면 함께 고칩니다</t>
+        </is>
+      </c>
+      <c r="J18" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[2]/div[2]/ul/li[2]/div/div[2]/ul/li[1]/a|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" s="5" t="inlineStr">
+        <is>
+          <t>Business · 에너지 인프라</t>
+        </is>
+      </c>
+      <c r="C19" s="5" t="inlineStr">
+        <is>
+          <t>소분류 링크</t>
+        </is>
+      </c>
+      <c r="D19" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="G19" s="7" t="n"/>
+      <c r="H19" s="8" t="inlineStr">
+        <is>
+          <t>UPS</t>
+        </is>
+      </c>
+      <c r="I19" s="5" t="inlineStr">
+        <is>
+          <t>사업영역 세부 시트의 소분류 이름과 같은 글 — 한쪽을 바꾸면 함께 고칩니다</t>
+        </is>
+      </c>
+      <c r="J19" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[2]/div[2]/ul/li[2]/div/div[2]/ul/li[2]/a|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>Business · 에너지 인프라</t>
+        </is>
+      </c>
+      <c r="C20" s="5" t="inlineStr">
+        <is>
+          <t>소분류 링크</t>
+        </is>
+      </c>
+      <c r="D20" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>솔루션</t>
+        </is>
+      </c>
+      <c r="G20" s="7" t="n"/>
+      <c r="H20" s="8" t="n"/>
+      <c r="I20" s="5" t="inlineStr">
+        <is>
+          <t>사업영역 세부 시트의 소분류 이름과 같은 글 — 한쪽을 바꾸면 함께 고칩니다</t>
+        </is>
+      </c>
+      <c r="J20" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[2]/div[2]/ul/li[2]/div/div[2]/ul/li[3]/a|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>Business · 인공지능 플랫폼</t>
+        </is>
+      </c>
+      <c r="C21" s="5" t="inlineStr">
+        <is>
+          <t>카드 설명</t>
+        </is>
+      </c>
+      <c r="D21" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>AI로 배터리와 설비의 상태를 읽어냅니다.
+진단부터 충전·제어까지, 전기 모빌리티의 데이터를 잇습니다.</t>
+        </is>
+      </c>
+      <c r="G21" s="7" t="n"/>
+      <c r="H21" s="8" t="n"/>
+      <c r="I21" s="5" t="n"/>
+      <c r="J21" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[2]/div[2]/ul/li[3]/div/div[1]/div/p|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" s="5" t="inlineStr">
+        <is>
+          <t>Business · 인공지능 플랫폼</t>
+        </is>
+      </c>
+      <c r="C22" s="5" t="inlineStr">
+        <is>
+          <t>소분류 링크</t>
+        </is>
+      </c>
+      <c r="D22" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="6" t="inlineStr">
+        <is>
+          <t>로봇 플랫폼</t>
+        </is>
+      </c>
+      <c r="G22" s="7" t="n"/>
+      <c r="H22" s="8" t="n"/>
+      <c r="I22" s="5" t="inlineStr">
+        <is>
+          <t>사업영역 세부 시트의 소분류 이름과 같은 글 — 한쪽을 바꾸면 함께 고칩니다</t>
+        </is>
+      </c>
+      <c r="J22" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[2]/div[2]/ul/li[3]/div/div[2]/ul/li[1]/a|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="5" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>Business · 인공지능 플랫폼</t>
+        </is>
+      </c>
+      <c r="C23" s="5" t="inlineStr">
+        <is>
+          <t>소분류 링크</t>
+        </is>
+      </c>
+      <c r="D23" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E23" s="5" t="n"/>
+      <c r="F23" s="6" t="inlineStr">
+        <is>
+          <t>배터리 진단 플랫폼</t>
+        </is>
+      </c>
+      <c r="G23" s="7" t="n"/>
+      <c r="H23" s="8" t="n"/>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>사업영역 세부 시트의 소분류 이름과 같은 글 — 한쪽을 바꾸면 함께 고칩니다</t>
+        </is>
+      </c>
+      <c r="J23" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[2]/div[2]/ul/li[3]/div/div[2]/ul/li[2]/a|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>Business · 인공지능 플랫폼</t>
+        </is>
+      </c>
+      <c r="C24" s="5" t="inlineStr">
+        <is>
+          <t>소분류 링크</t>
+        </is>
+      </c>
+      <c r="D24" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="6" t="inlineStr">
+        <is>
+          <t>전기자동차 충전 플랫폼</t>
+        </is>
+      </c>
+      <c r="G24" s="7" t="n"/>
+      <c r="H24" s="8" t="n"/>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>사업영역 세부 시트의 소분류 이름과 같은 글 — 한쪽을 바꾸면 함께 고칩니다</t>
+        </is>
+      </c>
+      <c r="J24" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[2]/div[2]/ul/li[3]/div/div[2]/ul/li[3]/a|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" s="5" t="inlineStr">
+        <is>
+          <t>Business · 인공지능 플랫폼</t>
+        </is>
+      </c>
+      <c r="C25" s="5" t="inlineStr">
+        <is>
+          <t>소분류 링크</t>
+        </is>
+      </c>
+      <c r="D25" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="6" t="inlineStr">
+        <is>
+          <t>전기자동차 제어 플랫폼</t>
+        </is>
+      </c>
+      <c r="G25" s="7" t="n"/>
+      <c r="H25" s="8" t="n"/>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>사업영역 세부 시트의 소분류 이름과 같은 글 — 한쪽을 바꾸면 함께 고칩니다</t>
+        </is>
+      </c>
+      <c r="J25" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[2]/div[2]/ul/li[3]/div/div[2]/ul/li[4]/a|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>Business · 화합물 전력 반도체</t>
+        </is>
+      </c>
+      <c r="C26" s="5" t="inlineStr">
+        <is>
+          <t>카드 설명</t>
+        </is>
+      </c>
+      <c r="D26" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="6" t="inlineStr">
+        <is>
+          <t>질화갈륨(GaN)을 기반으로 전력반도체와 RF반도체를 설계, 생산합니다.
+국내 최대 규모의 8인치 EPI 양산 체계와 칩 설계 역량을 갖췄습니다</t>
+        </is>
+      </c>
+      <c r="G26" s="7" t="n"/>
+      <c r="H26" s="8" t="n"/>
+      <c r="I26" s="5" t="n"/>
+      <c r="J26" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[2]/div[2]/ul/li[4]/div/div[1]/div/p|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>Business · 화합물 전력 반도체</t>
+        </is>
+      </c>
+      <c r="C27" s="5" t="inlineStr">
+        <is>
+          <t>소분류 링크</t>
+        </is>
+      </c>
+      <c r="D27" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E27" s="5" t="n"/>
+      <c r="F27" s="6" t="inlineStr">
+        <is>
+          <t>GaN Epi-Wafer</t>
+        </is>
+      </c>
+      <c r="G27" s="7" t="n"/>
+      <c r="H27" s="8" t="inlineStr">
+        <is>
+          <t>GaN Epi-Wafer</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>사업영역 세부 시트의 소분류 이름과 같은 글 — 한쪽을 바꾸면 함께 고칩니다</t>
+        </is>
+      </c>
+      <c r="J27" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[2]/div[2]/ul/li[4]/div/div[2]/ul/li[1]/a|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" s="5" t="inlineStr">
+        <is>
+          <t>Business · 화합물 전력 반도체</t>
+        </is>
+      </c>
+      <c r="C28" s="5" t="inlineStr">
+        <is>
+          <t>소분류 링크</t>
+        </is>
+      </c>
+      <c r="D28" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E28" s="5" t="n"/>
+      <c r="F28" s="6" t="inlineStr">
+        <is>
+          <t>GaN Power Device</t>
+        </is>
+      </c>
+      <c r="G28" s="7" t="n"/>
+      <c r="H28" s="8" t="inlineStr">
+        <is>
+          <t>GaN Power Device</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>사업영역 세부 시트의 소분류 이름과 같은 글 — 한쪽을 바꾸면 함께 고칩니다</t>
+        </is>
+      </c>
+      <c r="J28" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[2]/div[2]/ul/li[4]/div/div[2]/ul/li[2]/a|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>Business · 화합물 전력 반도체</t>
+        </is>
+      </c>
+      <c r="C29" s="5" t="inlineStr">
+        <is>
+          <t>소분류 링크</t>
+        </is>
+      </c>
+      <c r="D29" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E29" s="5" t="n"/>
+      <c r="F29" s="6" t="inlineStr">
+        <is>
+          <t>에이프로 세미콘</t>
+        </is>
+      </c>
+      <c r="G29" s="7" t="n"/>
+      <c r="H29" s="8" t="n"/>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>사업영역 세부 시트의 소분류 이름과 같은 글 — 한쪽을 바꾸면 함께 고칩니다</t>
+        </is>
+      </c>
+      <c r="J29" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[2]/div[2]/ul/li[4]/div/div[2]/ul/li[3]/a|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="5" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>Who we are</t>
+        </is>
+      </c>
+      <c r="C30" s="5" t="inlineStr">
+        <is>
+          <t>섹션 제목</t>
+        </is>
+      </c>
+      <c r="D30" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n"/>
+      <c r="F30" s="6" t="inlineStr">
+        <is>
+          <t>Who we are</t>
+        </is>
+      </c>
+      <c r="G30" s="7" t="n"/>
+      <c r="H30" s="8" t="inlineStr">
+        <is>
+          <t>Who we are</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="n"/>
+      <c r="J30" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[3]/h2|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" s="5" t="inlineStr">
+        <is>
+          <t>Who we are</t>
+        </is>
+      </c>
+      <c r="C31" s="5" t="inlineStr">
+        <is>
+          <t>섹션 라벨</t>
+        </is>
+      </c>
+      <c r="D31" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="6" t="inlineStr">
+        <is>
+          <t>핵심역량</t>
+        </is>
+      </c>
+      <c r="G31" s="7" t="n"/>
+      <c r="H31" s="8" t="n"/>
+      <c r="I31" s="5" t="n"/>
+      <c r="J31" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[3]/h2/span|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>Who we are · 01</t>
+        </is>
+      </c>
+      <c r="C32" s="5" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="D32" s="5" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="6" t="inlineStr">
+        <is>
+          <t>01</t>
+        </is>
+      </c>
+      <c r="G32" s="6" t="n"/>
+      <c r="H32" s="6" t="n"/>
+      <c r="I32" s="5" t="n"/>
+      <c r="J32" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[3]/ol/li[1]/div/div/div/div/span|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>Who we are · 01</t>
+        </is>
+      </c>
+      <c r="C33" s="5" t="inlineStr">
+        <is>
+          <t>제목</t>
+        </is>
+      </c>
+      <c r="D33" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="6" t="inlineStr">
+        <is>
+          <t>전력 변환 기술 기반의 Total Energy Solution</t>
+        </is>
+      </c>
+      <c r="G33" s="7" t="n"/>
+      <c r="H33" s="8" t="n"/>
+      <c r="I33" s="5" t="n"/>
+      <c r="J33" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[3]/ol/li[1]/div/div/div/div/h3|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="5" t="inlineStr">
+        <is>
+          <t>Who we are · 01</t>
+        </is>
+      </c>
+      <c r="C34" s="5" t="inlineStr">
+        <is>
+          <t>문단</t>
+        </is>
+      </c>
+      <c r="D34" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="6" t="inlineStr">
+        <is>
+          <t>에이프로는 2차전지 활성화 공정 장비부터 ESS, 초고속 전기차 충전 인프라, 우주 발사체 전원 시스템까지 폭넓은 포트폴리오를 구축하고 있습니다. 끊임없는 연구개발을 통해 고효율, 고밀도 전력 변환 기술을 고도화하며 지속 가능한 미래 에너지 생태계를 완성해 나갑니다.</t>
+        </is>
+      </c>
+      <c r="G34" s="7" t="n"/>
+      <c r="H34" s="8" t="n"/>
+      <c r="I34" s="5" t="n"/>
+      <c r="J34" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[3]/ol/li[1]/div/div/div/p|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="5" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>Who we are · 02</t>
+        </is>
+      </c>
+      <c r="C35" s="5" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="D35" s="5" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="6" t="inlineStr">
+        <is>
+          <t>02</t>
+        </is>
+      </c>
+      <c r="G35" s="6" t="n"/>
+      <c r="H35" s="6" t="n"/>
+      <c r="I35" s="5" t="n"/>
+      <c r="J35" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[3]/ol/li[2]/div/div/div/div/span|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>Who we are · 02</t>
+        </is>
+      </c>
+      <c r="C36" s="5" t="inlineStr">
+        <is>
+          <t>제목</t>
+        </is>
+      </c>
+      <c r="D36" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E36" s="5" t="n"/>
+      <c r="F36" s="6" t="inlineStr">
+        <is>
+          <t>소재부터 시스템까지 잇는 수직 계열화 역량 (Materials to System)</t>
+        </is>
+      </c>
+      <c r="G36" s="7" t="n"/>
+      <c r="H36" s="8" t="n"/>
+      <c r="I36" s="5" t="n"/>
+      <c r="J36" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[3]/ol/li[2]/div/div/div/div/h3|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="5" t="inlineStr">
+        <is>
+          <t>Who we are · 02</t>
+        </is>
+      </c>
+      <c r="C37" s="5" t="inlineStr">
+        <is>
+          <t>문단</t>
+        </is>
+      </c>
+      <c r="D37" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="6" t="inlineStr">
+        <is>
+          <t>우리의 혁신은 시스템의 가장 깊은 곳, '반도체'에서 시작됩니다. 차세대 고효율 질화갈륨(GaN) 전력반도체 핵심 소재(Epi-Wafer)와 소자를 직접 설계하고 내재화함으로써, 기존의 한계를 뛰어넘는 초소형·초고효율 전력 변환 모듈을 실현합니다.</t>
+        </is>
+      </c>
+      <c r="G37" s="7" t="n"/>
+      <c r="H37" s="8" t="n"/>
+      <c r="I37" s="5" t="n"/>
+      <c r="J37" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[3]/ol/li[2]/div/div/div/p|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="5" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>Who we are · 03</t>
+        </is>
+      </c>
+      <c r="C38" s="5" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="D38" s="5" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="6" t="inlineStr">
+        <is>
+          <t>03</t>
+        </is>
+      </c>
+      <c r="G38" s="6" t="n"/>
+      <c r="H38" s="6" t="n"/>
+      <c r="I38" s="5" t="n"/>
+      <c r="J38" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[3]/ol/li[3]/div/div/div/div/span|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="5" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="5" t="inlineStr">
+        <is>
+          <t>Who we are · 03</t>
+        </is>
+      </c>
+      <c r="C39" s="5" t="inlineStr">
+        <is>
+          <t>제목</t>
+        </is>
+      </c>
+      <c r="D39" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="6" t="inlineStr">
+        <is>
+          <t>In-house 설계를 통한 완벽한 시스템 통합 (SI) 및 지능형 플랫폼</t>
+        </is>
+      </c>
+      <c r="G39" s="7" t="n"/>
+      <c r="H39" s="8" t="n"/>
+      <c r="I39" s="5" t="n"/>
+      <c r="J39" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[3]/ol/li[3]/div/div/div/div/h3|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="5" t="inlineStr">
+        <is>
+          <t>Who we are · 03</t>
+        </is>
+      </c>
+      <c r="C40" s="5" t="inlineStr">
+        <is>
+          <t>문단</t>
+        </is>
+      </c>
+      <c r="D40" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E40" s="5" t="n"/>
+      <c r="F40" s="6" t="inlineStr">
+        <is>
+          <t>기구, 회로, 소프트웨어에 이르는 100% In-house 설계 역량을 통해 고객의 다양한 요구에 최적화된 하드웨어 시스템을 구축합니다. 나아가 AI 기반의 배터리 진단 플랫폼과 산업 안전 로보틱스 등 지능형 소프트웨어를 융합하여, 시스템의 안정성과 운영 효율을 극대화하는 스마트 솔루션을 제공합니다.</t>
+        </is>
+      </c>
+      <c r="G40" s="7" t="n"/>
+      <c r="H40" s="8" t="n"/>
+      <c r="I40" s="5" t="n"/>
+      <c r="J40" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[3]/ol/li[3]/div/div/div/p|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>Who we are · 04</t>
+        </is>
+      </c>
+      <c r="C41" s="5" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>번호</t>
+        </is>
+      </c>
+      <c r="E41" s="5" t="n"/>
+      <c r="F41" s="6" t="inlineStr">
+        <is>
+          <t>04</t>
+        </is>
+      </c>
+      <c r="G41" s="6" t="n"/>
+      <c r="H41" s="6" t="n"/>
+      <c r="I41" s="5" t="n"/>
+      <c r="J41" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[3]/ol/li[4]/div/div/div/div/span|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>Who we are · 04</t>
+        </is>
+      </c>
+      <c r="C42" s="5" t="inlineStr">
+        <is>
+          <t>제목</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E42" s="5" t="n"/>
+      <c r="F42" s="6" t="inlineStr">
+        <is>
+          <t>세계를 무대로 하는 글로벌 파트너</t>
+        </is>
+      </c>
+      <c r="G42" s="7" t="n"/>
+      <c r="H42" s="8" t="n"/>
+      <c r="I42" s="5" t="n"/>
+      <c r="J42" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[3]/ol/li[4]/div/div/div/div/h3|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="5" t="inlineStr">
+        <is>
+          <t>Who we are · 04</t>
+        </is>
+      </c>
+      <c r="C43" s="5" t="inlineStr">
+        <is>
+          <t>문단</t>
+        </is>
+      </c>
+      <c r="D43" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E43" s="5" t="n"/>
+      <c r="F43" s="6" t="inlineStr">
+        <is>
+          <t>미국, 유럽, 중국, 동남아시아 등 전 세계 핵심 거점에 현지 법인과 전문가 네트워크를 구축했습니다. 글로벌 탑티어 배터리 제조사 및 완성차 기업들과 긴밀히 협력하며, 어떤 환경에서도 기민(Agile)하게 대응하고 최고 품질의 고객 지원을 약속합니다.</t>
+        </is>
+      </c>
+      <c r="G43" s="7" t="n"/>
+      <c r="H43" s="8" t="n"/>
+      <c r="I43" s="5" t="n"/>
+      <c r="J43" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[3]/ol/li[4]/div/div/div/p|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="5" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C44" s="5" t="inlineStr">
+        <is>
+          <t>섹션 제목</t>
+        </is>
+      </c>
+      <c r="D44" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E44" s="5" t="n"/>
+      <c r="F44" s="6" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="G44" s="7" t="n"/>
+      <c r="H44" s="8" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="n"/>
+      <c r="J44" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[4]/div[1]/div/h2|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="5" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C45" s="5" t="inlineStr">
+        <is>
+          <t>섹션 라벨</t>
+        </is>
+      </c>
+      <c r="D45" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E45" s="5" t="n"/>
+      <c r="F45" s="6" t="inlineStr">
+        <is>
+          <t>보도자료</t>
+        </is>
+      </c>
+      <c r="G45" s="7" t="n"/>
+      <c r="H45" s="8" t="n"/>
+      <c r="I45" s="5" t="n"/>
+      <c r="J45" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[4]/div[1]/div/h2/span|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="5" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C46" s="5" t="inlineStr">
+        <is>
+          <t>더보기 단추</t>
+        </is>
+      </c>
+      <c r="D46" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E46" s="5" t="n"/>
+      <c r="F46" s="6" t="inlineStr">
+        <is>
+          <t>더보기</t>
+        </is>
+      </c>
+      <c r="G46" s="7" t="n"/>
+      <c r="H46" s="8" t="n"/>
+      <c r="I46" s="5" t="n"/>
+      <c r="J46" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[4]/div[1]/a|text</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="5" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="5" t="inlineStr">
+        <is>
+          <t>News</t>
+        </is>
+      </c>
+      <c r="C47" s="5" t="inlineStr">
+        <is>
+          <t>목록 '자세히 보기'</t>
+        </is>
+      </c>
+      <c r="D47" s="5" t="inlineStr">
+        <is>
+          <t>문구</t>
+        </is>
+      </c>
+      <c r="E47" s="5" t="n"/>
+      <c r="F47" s="6" t="inlineStr">
+        <is>
+          <t>자세히 보기</t>
+        </is>
+      </c>
+      <c r="G47" s="7" t="n"/>
+      <c r="H47" s="8" t="n"/>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>같은 문구 5 곳 — 한 줄로 합침</t>
+        </is>
+      </c>
+      <c r="J47" s="9" t="inlineStr">
+        <is>
+          <t>/html/body/div[3]/section[4]/ul/li[1]/a/span[3]/span|text
+/html/body/div[3]/section[4]/ul/li[2]/a/span[3]/span|text
+/html/body/div[3]/section[4]/ul/li[3]/a/span[3]/span|text
+/html/body/div[3]/section[4]/ul/li[4]/a/span[3]/span|text
+/html/body/div[3]/section[4]/ul/li[5]/a/span[3]/span|text</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:J47"/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -5839,7 +7651,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12737,7 +14549,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -14541,7 +16353,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
